--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5354,13 +5354,13 @@
         <v>76162.91</v>
       </c>
       <c r="E58" t="n">
-        <v>76643.16</v>
+        <v>76983.95</v>
       </c>
       <c r="F58" t="n">
-        <v>-3706.89</v>
+        <v>-3366.09</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0461</v>
+        <v>-0.0419</v>
       </c>
       <c r="H58" t="n">
         <v>4269.4</v>
@@ -5432,19 +5432,19 @@
         <v>71893.52</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>71546.53</v>
+        <v>72057.72</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>74508.46000000001</v>
+        <v>74849.25</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>77470.38</v>
+        <v>77640.78</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>78777.86</v>
+        <v>79118.64999999999</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>80085.33</v>
+        <v>80596.52</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>84701.71000000001</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -641,83 +641,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>119306.81</v>
+        <v>117453.91</v>
       </c>
       <c r="C2" t="n">
-        <v>124457.12</v>
+        <v>117614.17</v>
       </c>
       <c r="D2" t="n">
-        <v>116864.57</v>
+        <v>111060.55</v>
       </c>
       <c r="E2" t="n">
-        <v>117453.06</v>
+        <v>113458.43</v>
       </c>
       <c r="F2" t="n">
-        <v>-1853.7</v>
+        <v>-3994.63</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0155</v>
+        <v>-0.034</v>
       </c>
       <c r="H2" t="n">
-        <v>7592.55</v>
+        <v>6553.62</v>
       </c>
       <c r="I2" t="n">
-        <v>113649.62</v>
+        <v>109272.02</v>
       </c>
       <c r="J2" t="n">
-        <v>117173.12</v>
+        <v>108256.62</v>
       </c>
       <c r="K2" t="n">
-        <v>117888.98</v>
+        <v>113656.79</v>
       </c>
       <c r="L2" t="n">
-        <v>118604.85</v>
+        <v>119056.95</v>
       </c>
       <c r="M2" t="n">
-        <v>120724.53</v>
+        <v>121249.34</v>
       </c>
       <c r="N2" t="n">
-        <v>122844.21</v>
+        <v>123441.72</v>
       </c>
       <c r="O2" t="n">
-        <v>122156.26</v>
+        <v>132049.66</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -726,67 +718,69 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>117453.91</v>
+        <v>113456.9</v>
       </c>
       <c r="C3" t="n">
-        <v>117614.17</v>
+        <v>113637.84</v>
       </c>
       <c r="D3" t="n">
-        <v>111060.55</v>
+        <v>107444.45</v>
       </c>
       <c r="E3" t="n">
-        <v>113458.43</v>
+        <v>108236.71</v>
       </c>
       <c r="F3" t="n">
-        <v>-3994.63</v>
+        <v>-5221.72</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.034</v>
+        <v>-0.046</v>
       </c>
       <c r="H3" t="n">
-        <v>6553.62</v>
+        <v>6193.4</v>
       </c>
       <c r="I3" t="n">
-        <v>109272.02</v>
+        <v>104506.92</v>
       </c>
       <c r="J3" t="n">
-        <v>108256.62</v>
+        <v>106465.34</v>
       </c>
       <c r="K3" t="n">
-        <v>113656.79</v>
+        <v>110181.62</v>
       </c>
       <c r="L3" t="n">
-        <v>119056.95</v>
+        <v>113897.89</v>
       </c>
       <c r="M3" t="n">
-        <v>121249.34</v>
+        <v>116735.24</v>
       </c>
       <c r="N3" t="n">
-        <v>123441.72</v>
+        <v>119572.59</v>
       </c>
       <c r="O3" t="n">
-        <v>132049.66</v>
+        <v>124167.8</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
@@ -817,75 +811,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>113456.9</v>
+        <v>108228.75</v>
       </c>
       <c r="C4" t="n">
-        <v>113637.84</v>
+        <v>113357.49</v>
       </c>
       <c r="D4" t="n">
-        <v>107444.45</v>
+        <v>107271.18</v>
       </c>
       <c r="E4" t="n">
-        <v>108236.71</v>
+        <v>111167.62</v>
       </c>
       <c r="F4" t="n">
-        <v>-5221.72</v>
+        <v>2930.91</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.046</v>
+        <v>0.0271</v>
       </c>
       <c r="H4" t="n">
-        <v>6193.4</v>
+        <v>6086.31</v>
       </c>
       <c r="I4" t="n">
-        <v>104506.92</v>
+        <v>101251.05</v>
       </c>
       <c r="J4" t="n">
-        <v>106465.34</v>
+        <v>100891.1</v>
       </c>
       <c r="K4" t="n">
-        <v>110181.62</v>
+        <v>105140.01</v>
       </c>
       <c r="L4" t="n">
-        <v>113897.89</v>
+        <v>109388.93</v>
       </c>
       <c r="M4" t="n">
-        <v>116735.24</v>
+        <v>111333.41</v>
       </c>
       <c r="N4" t="n">
-        <v>119572.59</v>
+        <v>113277.89</v>
       </c>
       <c r="O4" t="n">
-        <v>124167.8</v>
+        <v>119831.24</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
@@ -896,57 +890,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108228.75</v>
+        <v>111163.02</v>
       </c>
       <c r="C5" t="n">
-        <v>113357.49</v>
+        <v>116769.38</v>
       </c>
       <c r="D5" t="n">
-        <v>107271.18</v>
+        <v>110630.61</v>
       </c>
       <c r="E5" t="n">
-        <v>111167.62</v>
+        <v>115407.66</v>
       </c>
       <c r="F5" t="n">
-        <v>2930.91</v>
+        <v>4240.04</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0271</v>
+        <v>0.0381</v>
       </c>
       <c r="H5" t="n">
-        <v>6086.31</v>
+        <v>6138.77</v>
       </c>
       <c r="I5" t="n">
-        <v>101251.05</v>
+        <v>101184.87</v>
       </c>
       <c r="J5" t="n">
-        <v>100891.1</v>
+        <v>105507.95</v>
       </c>
       <c r="K5" t="n">
-        <v>105140.01</v>
+        <v>108124.46</v>
       </c>
       <c r="L5" t="n">
-        <v>109388.93</v>
+        <v>110740.98</v>
       </c>
       <c r="M5" t="n">
-        <v>111333.41</v>
+        <v>114210.77</v>
       </c>
       <c r="N5" t="n">
-        <v>113277.89</v>
+        <v>117680.57</v>
       </c>
       <c r="O5" t="n">
-        <v>119831.24</v>
+        <v>119443.8</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -967,10 +961,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -980,59 +972,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111163.02</v>
+        <v>115399.63</v>
       </c>
       <c r="C6" t="n">
-        <v>116769.38</v>
+        <v>117911.79</v>
       </c>
       <c r="D6" t="n">
-        <v>110630.61</v>
+        <v>114461.06</v>
       </c>
       <c r="E6" t="n">
-        <v>115407.66</v>
+        <v>115306.09</v>
       </c>
       <c r="F6" t="n">
-        <v>4240.04</v>
+        <v>-101.56</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0381</v>
+        <v>-0.0009</v>
       </c>
       <c r="H6" t="n">
-        <v>6138.77</v>
+        <v>3450.73</v>
       </c>
       <c r="I6" t="n">
-        <v>101184.87</v>
+        <v>104491.84</v>
       </c>
       <c r="J6" t="n">
-        <v>105507.95</v>
+        <v>110122.71</v>
       </c>
       <c r="K6" t="n">
-        <v>108124.46</v>
+        <v>112338.27</v>
       </c>
       <c r="L6" t="n">
-        <v>110740.98</v>
+        <v>114553.83</v>
       </c>
       <c r="M6" t="n">
-        <v>114210.77</v>
+        <v>118477.04</v>
       </c>
       <c r="N6" t="n">
-        <v>117680.57</v>
+        <v>122400.26</v>
       </c>
       <c r="O6" t="n">
-        <v>119443.8</v>
+        <v>122908.16</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1045,13 +1033,11 @@
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1064,68 +1050,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>115399.63</v>
+        <v>115309.22</v>
       </c>
       <c r="C7" t="n">
-        <v>117911.79</v>
+        <v>115431.31</v>
       </c>
       <c r="D7" t="n">
-        <v>114461.06</v>
+        <v>108713.4</v>
       </c>
       <c r="E7" t="n">
-        <v>115306.09</v>
+        <v>112122.64</v>
       </c>
       <c r="F7" t="n">
-        <v>-101.56</v>
+        <v>-3183.45</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0276</v>
       </c>
       <c r="H7" t="n">
-        <v>3450.73</v>
+        <v>6717.91</v>
       </c>
       <c r="I7" t="n">
-        <v>104491.84</v>
+        <v>111010.34</v>
       </c>
       <c r="J7" t="n">
-        <v>110122.71</v>
+        <v>111415.2</v>
       </c>
       <c r="K7" t="n">
-        <v>112338.27</v>
+        <v>113580.73</v>
       </c>
       <c r="L7" t="n">
-        <v>114553.83</v>
+        <v>115746.26</v>
       </c>
       <c r="M7" t="n">
-        <v>118477.04</v>
+        <v>117031.46</v>
       </c>
       <c r="N7" t="n">
-        <v>122400.26</v>
+        <v>118316.65</v>
       </c>
       <c r="O7" t="n">
-        <v>122908.16</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>121362.52</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1144,237 +1140,233 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>115309.22</v>
+        <v>112117.88</v>
       </c>
       <c r="C8" t="n">
-        <v>115431.31</v>
+        <v>125559.21</v>
       </c>
       <c r="D8" t="n">
-        <v>108713.4</v>
+        <v>111589.95</v>
       </c>
       <c r="E8" t="n">
-        <v>112122.64</v>
+        <v>123513.48</v>
       </c>
       <c r="F8" t="n">
-        <v>-3183.45</v>
+        <v>11390.84</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0276</v>
+        <v>0.1016</v>
       </c>
       <c r="H8" t="n">
-        <v>6717.91</v>
+        <v>13969.26</v>
       </c>
       <c r="I8" t="n">
-        <v>111010.34</v>
+        <v>101995.48</v>
       </c>
       <c r="J8" t="n">
-        <v>111415.2</v>
+        <v>105429.87</v>
       </c>
       <c r="K8" t="n">
-        <v>113580.73</v>
+        <v>108763.68</v>
       </c>
       <c r="L8" t="n">
-        <v>115746.26</v>
+        <v>112097.5</v>
       </c>
       <c r="M8" t="n">
-        <v>117031.46</v>
+        <v>115481.6</v>
       </c>
       <c r="N8" t="n">
-        <v>118316.65</v>
+        <v>118865.7</v>
       </c>
       <c r="O8" t="n">
-        <v>121362.52</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
+        <v>122149.23</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
-      </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>112117.88</v>
+        <v>123510.45</v>
       </c>
       <c r="C9" t="n">
-        <v>125559.21</v>
+        <v>126198.07</v>
       </c>
       <c r="D9" t="n">
-        <v>111589.95</v>
+        <v>104582.41</v>
       </c>
       <c r="E9" t="n">
-        <v>123513.48</v>
+        <v>115169.77</v>
       </c>
       <c r="F9" t="n">
-        <v>11390.84</v>
+        <v>-8343.709999999999</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.1016</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>13969.26</v>
+        <v>21615.66</v>
       </c>
       <c r="I9" t="n">
-        <v>101995.48</v>
+        <v>97620.7</v>
       </c>
       <c r="J9" t="n">
-        <v>105429.87</v>
+        <v>112013.67</v>
       </c>
       <c r="K9" t="n">
-        <v>108763.68</v>
+        <v>116528.85</v>
       </c>
       <c r="L9" t="n">
-        <v>112097.5</v>
+        <v>121044.03</v>
       </c>
       <c r="M9" t="n">
-        <v>115481.6</v>
+        <v>130498.11</v>
       </c>
       <c r="N9" t="n">
-        <v>118865.7</v>
+        <v>139952.18</v>
       </c>
       <c r="O9" t="n">
-        <v>122149.23</v>
+        <v>139528.47</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
+      <c r="Q9" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
+      </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>123510.45</v>
+        <v>115161.68</v>
       </c>
       <c r="C10" t="n">
-        <v>126198.07</v>
+        <v>116020.48</v>
       </c>
       <c r="D10" t="n">
-        <v>104582.41</v>
+        <v>103598.43</v>
       </c>
       <c r="E10" t="n">
-        <v>115169.77</v>
+        <v>108666.71</v>
       </c>
       <c r="F10" t="n">
-        <v>-8343.709999999999</v>
+        <v>-6503.05</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0565</v>
       </c>
       <c r="H10" t="n">
-        <v>21615.66</v>
+        <v>12422.05</v>
       </c>
       <c r="I10" t="n">
-        <v>97620.7</v>
+        <v>82966.75999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>112013.67</v>
+        <v>93443.87</v>
       </c>
       <c r="K10" t="n">
-        <v>116528.85</v>
+        <v>104361.94</v>
       </c>
       <c r="L10" t="n">
-        <v>121044.03</v>
+        <v>115280</v>
       </c>
       <c r="M10" t="n">
-        <v>130498.11</v>
+        <v>125977.59</v>
       </c>
       <c r="N10" t="n">
-        <v>139952.18</v>
+        <v>136675.18</v>
       </c>
       <c r="O10" t="n">
-        <v>139528.47</v>
+        <v>147813.73</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q10" s="6" t="n">
+        <v/>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
@@ -1402,57 +1394,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>115161.68</v>
+        <v>108667.45</v>
       </c>
       <c r="C11" t="n">
-        <v>116020.48</v>
+        <v>115260.91</v>
       </c>
       <c r="D11" t="n">
-        <v>103598.43</v>
+        <v>106778</v>
       </c>
       <c r="E11" t="n">
-        <v>108666.71</v>
+        <v>114472.45</v>
       </c>
       <c r="F11" t="n">
-        <v>-6503.05</v>
+        <v>5805.73</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0565</v>
+        <v>0.0534</v>
       </c>
       <c r="H11" t="n">
-        <v>12422.05</v>
+        <v>8482.91</v>
       </c>
       <c r="I11" t="n">
-        <v>82966.75999999999</v>
+        <v>91176.38</v>
       </c>
       <c r="J11" t="n">
-        <v>93443.87</v>
+        <v>95673.28</v>
       </c>
       <c r="K11" t="n">
-        <v>104361.94</v>
+        <v>102455.68</v>
       </c>
       <c r="L11" t="n">
-        <v>115280</v>
+        <v>109238.08</v>
       </c>
       <c r="M11" t="n">
-        <v>125977.59</v>
+        <v>114877.74</v>
       </c>
       <c r="N11" t="n">
-        <v>136675.18</v>
+        <v>120517.39</v>
       </c>
       <c r="O11" t="n">
-        <v>147813.73</v>
+        <v>128442.54</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1460,19 +1452,19 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1486,77 +1478,79 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>108667.45</v>
+        <v>114479.85</v>
       </c>
       <c r="C12" t="n">
-        <v>115260.91</v>
+        <v>116273.31</v>
       </c>
       <c r="D12" t="n">
-        <v>106778</v>
+        <v>106376.69</v>
       </c>
       <c r="E12" t="n">
-        <v>114472.45</v>
+        <v>110639.62</v>
       </c>
       <c r="F12" t="n">
-        <v>5805.73</v>
+        <v>-3832.82</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0534</v>
+        <v>-0.0335</v>
       </c>
       <c r="H12" t="n">
-        <v>8482.91</v>
+        <v>9896.620000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>91176.38</v>
+        <v>98295.09</v>
       </c>
       <c r="J12" t="n">
-        <v>95673.28</v>
+        <v>107716.04</v>
       </c>
       <c r="K12" t="n">
-        <v>102455.68</v>
+        <v>110230.99</v>
       </c>
       <c r="L12" t="n">
-        <v>109238.08</v>
+        <v>112745.95</v>
       </c>
       <c r="M12" t="n">
-        <v>114877.74</v>
+        <v>118713.9</v>
       </c>
       <c r="N12" t="n">
-        <v>120517.39</v>
+        <v>124681.85</v>
       </c>
       <c r="O12" t="n">
-        <v>128442.54</v>
+        <v>123743.81</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1570,57 +1564,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>114479.85</v>
+        <v>110646.91</v>
       </c>
       <c r="C13" t="n">
-        <v>116273.31</v>
+        <v>110764.91</v>
       </c>
       <c r="D13" t="n">
-        <v>106376.69</v>
+        <v>98962.06</v>
       </c>
       <c r="E13" t="n">
-        <v>110639.62</v>
+        <v>104719.64</v>
       </c>
       <c r="F13" t="n">
-        <v>-3832.82</v>
+        <v>-5919.98</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0335</v>
+        <v>-0.0535</v>
       </c>
       <c r="H13" t="n">
-        <v>9896.620000000001</v>
+        <v>11802.85</v>
       </c>
       <c r="I13" t="n">
-        <v>98295.09</v>
+        <v>96480.06</v>
       </c>
       <c r="J13" t="n">
-        <v>107716.04</v>
+        <v>100400.31</v>
       </c>
       <c r="K13" t="n">
-        <v>110230.99</v>
+        <v>105691.31</v>
       </c>
       <c r="L13" t="n">
-        <v>112745.95</v>
+        <v>110982.31</v>
       </c>
       <c r="M13" t="n">
-        <v>118713.9</v>
+        <v>115587.94</v>
       </c>
       <c r="N13" t="n">
-        <v>124681.85</v>
+        <v>120193.56</v>
       </c>
       <c r="O13" t="n">
-        <v>123743.81</v>
+        <v>126169.94</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1656,69 +1650,69 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>110646.91</v>
+        <v>104723.77</v>
       </c>
       <c r="C14" t="n">
-        <v>110764.91</v>
+        <v>107428.26</v>
       </c>
       <c r="D14" t="n">
-        <v>98962.06</v>
+        <v>92971.16</v>
       </c>
       <c r="E14" t="n">
-        <v>104719.64</v>
+        <v>94177.08</v>
       </c>
       <c r="F14" t="n">
-        <v>-5919.98</v>
+        <v>-10542.56</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0535</v>
+        <v>-0.1007</v>
       </c>
       <c r="H14" t="n">
-        <v>11802.85</v>
+        <v>14457.09</v>
       </c>
       <c r="I14" t="n">
-        <v>96480.06</v>
+        <v>87159.21000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>100400.31</v>
+        <v>92844.87</v>
       </c>
       <c r="K14" t="n">
-        <v>105691.31</v>
+        <v>98818.21000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>110982.31</v>
+        <v>104791.56</v>
       </c>
       <c r="M14" t="n">
-        <v>115587.94</v>
+        <v>110621.07</v>
       </c>
       <c r="N14" t="n">
-        <v>120193.56</v>
+        <v>116450.57</v>
       </c>
       <c r="O14" t="n">
-        <v>126169.94</v>
+        <v>122567.77</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
@@ -1749,62 +1743,60 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>104723.77</v>
+        <v>94180.88</v>
       </c>
       <c r="C15" t="n">
-        <v>107428.26</v>
+        <v>95928.37</v>
       </c>
       <c r="D15" t="n">
-        <v>92971.16</v>
+        <v>80659.81</v>
       </c>
       <c r="E15" t="n">
-        <v>94177.08</v>
+        <v>86805.00999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-10542.56</v>
+        <v>-7372.07</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.1007</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>14457.09</v>
+        <v>15268.55</v>
       </c>
       <c r="I15" t="n">
-        <v>87159.21000000001</v>
+        <v>78514.07000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>92844.87</v>
+        <v>76708.67</v>
       </c>
       <c r="K15" t="n">
-        <v>98818.21000000001</v>
+        <v>86948.53</v>
       </c>
       <c r="L15" t="n">
-        <v>104791.56</v>
+        <v>97188.39</v>
       </c>
       <c r="M15" t="n">
-        <v>110621.07</v>
+        <v>101405.62</v>
       </c>
       <c r="N15" t="n">
-        <v>116450.57</v>
+        <v>105622.86</v>
       </c>
       <c r="O15" t="n">
-        <v>122567.77</v>
+        <v>121885.35</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
@@ -1835,50 +1827,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>94180.88</v>
+        <v>86798.77</v>
       </c>
       <c r="C16" t="n">
-        <v>95928.37</v>
+        <v>92969.09</v>
       </c>
       <c r="D16" t="n">
-        <v>80659.81</v>
+        <v>85272.2</v>
       </c>
       <c r="E16" t="n">
-        <v>86805.00999999999</v>
+        <v>90394.31</v>
       </c>
       <c r="F16" t="n">
-        <v>-7372.07</v>
+        <v>3589.3</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.0413</v>
       </c>
       <c r="H16" t="n">
-        <v>15268.55</v>
+        <v>7696.89</v>
       </c>
       <c r="I16" t="n">
-        <v>78514.07000000001</v>
+        <v>65391.26</v>
       </c>
       <c r="J16" t="n">
-        <v>76708.67</v>
+        <v>70791.91</v>
       </c>
       <c r="K16" t="n">
-        <v>86948.53</v>
+        <v>79170.73</v>
       </c>
       <c r="L16" t="n">
-        <v>97188.39</v>
+        <v>87549.55</v>
       </c>
       <c r="M16" t="n">
-        <v>101405.62</v>
+        <v>94439.28999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>105622.86</v>
+        <v>101329.02</v>
       </c>
       <c r="O16" t="n">
-        <v>121885.35</v>
+        <v>111196.92</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1886,14 +1878,12 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1912,57 +1902,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>86798.77</v>
+        <v>90389.11</v>
       </c>
       <c r="C17" t="n">
-        <v>92969.09</v>
+        <v>94060.77</v>
       </c>
       <c r="D17" t="n">
-        <v>85272.2</v>
+        <v>83862.25</v>
       </c>
       <c r="E17" t="n">
-        <v>90394.31</v>
+        <v>90405.64</v>
       </c>
       <c r="F17" t="n">
-        <v>3589.3</v>
+        <v>11.33</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0413</v>
+        <v>0.0001</v>
       </c>
       <c r="H17" t="n">
-        <v>7696.89</v>
+        <v>10198.52</v>
       </c>
       <c r="I17" t="n">
-        <v>65391.26</v>
+        <v>77575.3</v>
       </c>
       <c r="J17" t="n">
-        <v>70791.91</v>
+        <v>83334.25999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>79170.73</v>
+        <v>86545.87</v>
       </c>
       <c r="L17" t="n">
-        <v>87549.55</v>
+        <v>89757.48</v>
       </c>
       <c r="M17" t="n">
-        <v>94439.28999999999</v>
+        <v>94242.75999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>101329.02</v>
+        <v>98728.03999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>111196.92</v>
+        <v>100665.98</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1970,8 +1960,10 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
@@ -2001,50 +1993,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>90389.11</v>
+        <v>90424.59</v>
       </c>
       <c r="C18" t="n">
-        <v>94060.77</v>
+        <v>94601.57000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>83862.25</v>
+        <v>87634.94</v>
       </c>
       <c r="E18" t="n">
-        <v>90405.64</v>
+        <v>88175.17999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>11.33</v>
+        <v>-2230.46</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0247</v>
       </c>
       <c r="H18" t="n">
-        <v>10198.52</v>
+        <v>6966.63</v>
       </c>
       <c r="I18" t="n">
-        <v>77575.3</v>
+        <v>73663.73</v>
       </c>
       <c r="J18" t="n">
-        <v>83334.25999999999</v>
+        <v>80929.17999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>86545.87</v>
+        <v>85306.38</v>
       </c>
       <c r="L18" t="n">
-        <v>89757.48</v>
+        <v>89683.58</v>
       </c>
       <c r="M18" t="n">
-        <v>94242.75999999999</v>
+        <v>95504.89999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>98728.03999999999</v>
+        <v>101326.23</v>
       </c>
       <c r="O18" t="n">
-        <v>100665.98</v>
+        <v>104259.3</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2052,14 +2044,12 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2085,50 +2075,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>90424.59</v>
+        <v>88171.08</v>
       </c>
       <c r="C19" t="n">
-        <v>94601.57000000001</v>
+        <v>90264.57000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>87634.94</v>
+        <v>84436.31</v>
       </c>
       <c r="E19" t="n">
-        <v>88175.17999999999</v>
+        <v>88621.75</v>
       </c>
       <c r="F19" t="n">
-        <v>-2230.46</v>
+        <v>446.57</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0051</v>
       </c>
       <c r="H19" t="n">
-        <v>6966.63</v>
+        <v>5828.26</v>
       </c>
       <c r="I19" t="n">
-        <v>73663.73</v>
+        <v>80668.3</v>
       </c>
       <c r="J19" t="n">
-        <v>80929.17999999999</v>
+        <v>79737.00999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>85306.38</v>
+        <v>84691.86</v>
       </c>
       <c r="L19" t="n">
-        <v>89683.58</v>
+        <v>89646.72</v>
       </c>
       <c r="M19" t="n">
-        <v>95504.89999999999</v>
+        <v>91658.5</v>
       </c>
       <c r="N19" t="n">
-        <v>101326.23</v>
+        <v>93670.28</v>
       </c>
       <c r="O19" t="n">
-        <v>104259.3</v>
+        <v>101568.2</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2136,8 +2126,10 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
@@ -2160,57 +2152,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>88171.08</v>
+        <v>88621.39999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>90264.57000000001</v>
+        <v>90501.92999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>84436.31</v>
+        <v>86411.8</v>
       </c>
       <c r="E20" t="n">
-        <v>88621.75</v>
+        <v>87835.84</v>
       </c>
       <c r="F20" t="n">
-        <v>446.57</v>
+        <v>-785.91</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0051</v>
+        <v>-0.0089</v>
       </c>
       <c r="H20" t="n">
-        <v>5828.26</v>
+        <v>4090.13</v>
       </c>
       <c r="I20" t="n">
-        <v>80668.3</v>
+        <v>78608.05</v>
       </c>
       <c r="J20" t="n">
-        <v>79737.00999999999</v>
+        <v>83429.14999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>84691.86</v>
+        <v>85707.62</v>
       </c>
       <c r="L20" t="n">
-        <v>89646.72</v>
+        <v>87986.10000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>91658.5</v>
+        <v>91535.88</v>
       </c>
       <c r="N20" t="n">
-        <v>93670.28</v>
+        <v>95085.66</v>
       </c>
       <c r="O20" t="n">
-        <v>101568.2</v>
+        <v>96092.83</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2218,10 +2210,8 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R20" s="6" t="n">
+        <v/>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
@@ -2244,57 +2234,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>88621.39999999999</v>
+        <v>87835.78999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>90501.92999999999</v>
+        <v>91712.59</v>
       </c>
       <c r="D21" t="n">
-        <v>86411.8</v>
+        <v>86717.91</v>
       </c>
       <c r="E21" t="n">
-        <v>87835.84</v>
+        <v>91413.49000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-785.91</v>
+        <v>3577.66</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0089</v>
+        <v>0.0407</v>
       </c>
       <c r="H21" t="n">
-        <v>4090.13</v>
+        <v>4994.67</v>
       </c>
       <c r="I21" t="n">
-        <v>78608.05</v>
+        <v>82321.66</v>
       </c>
       <c r="J21" t="n">
-        <v>83429.14999999999</v>
+        <v>83435.19</v>
       </c>
       <c r="K21" t="n">
-        <v>85707.62</v>
+        <v>85790.77</v>
       </c>
       <c r="L21" t="n">
-        <v>87986.10000000001</v>
+        <v>88146.35000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>91535.88</v>
+        <v>89880.89999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>95085.66</v>
+        <v>91615.46000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>96092.83</v>
+        <v>94592.06</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2305,16 +2295,20 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2324,59 +2318,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>87835.78999999999</v>
+        <v>91414.62</v>
       </c>
       <c r="C22" t="n">
-        <v>91712.59</v>
+        <v>94762.07000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>86717.91</v>
+        <v>89233.88</v>
       </c>
       <c r="E22" t="n">
-        <v>91413.49000000001</v>
+        <v>90827.46000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>3577.66</v>
+        <v>-586.03</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0407</v>
+        <v>-0.0064</v>
       </c>
       <c r="H22" t="n">
-        <v>4994.67</v>
+        <v>5528.2</v>
       </c>
       <c r="I22" t="n">
-        <v>82321.66</v>
+        <v>81723.24000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>83435.19</v>
+        <v>87517.94</v>
       </c>
       <c r="K22" t="n">
-        <v>85790.77</v>
+        <v>88916.16</v>
       </c>
       <c r="L22" t="n">
-        <v>88146.35000000001</v>
+        <v>90314.37</v>
       </c>
       <c r="M22" t="n">
-        <v>89880.89999999999</v>
+        <v>93910.83</v>
       </c>
       <c r="N22" t="n">
-        <v>91615.46000000001</v>
+        <v>97507.28999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>94592.06</v>
+        <v>96707.25999999999</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2389,7 +2379,7 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2397,10 +2387,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2410,55 +2398,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>91414.62</v>
+        <v>90825.86</v>
       </c>
       <c r="C23" t="n">
-        <v>94762.07000000001</v>
+        <v>97860.60000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>89233.88</v>
+        <v>90055.02</v>
       </c>
       <c r="E23" t="n">
-        <v>90827.46000000001</v>
+        <v>93634.42999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-586.03</v>
+        <v>2806.97</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0064</v>
+        <v>0.0309</v>
       </c>
       <c r="H23" t="n">
-        <v>5528.2</v>
+        <v>7805.58</v>
       </c>
       <c r="I23" t="n">
-        <v>81723.24000000001</v>
+        <v>83705.67999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>87517.94</v>
+        <v>84714.00999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>88916.16</v>
+        <v>88063.36</v>
       </c>
       <c r="L23" t="n">
-        <v>90314.37</v>
+        <v>91412.72</v>
       </c>
       <c r="M23" t="n">
-        <v>93910.83</v>
+        <v>93591.56</v>
       </c>
       <c r="N23" t="n">
-        <v>97507.28999999999</v>
+        <v>95770.39999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>96707.25999999999</v>
+        <v>100290.27</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2471,17 +2463,19 @@
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
@@ -2490,84 +2484,80 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>90825.86</v>
+        <v>93655.67</v>
       </c>
       <c r="C24" t="n">
-        <v>97860.60000000001</v>
+        <v>93660.83</v>
       </c>
       <c r="D24" t="n">
-        <v>90055.02</v>
+        <v>86003.71000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>93634.42999999999</v>
+        <v>86572.22</v>
       </c>
       <c r="F24" t="n">
-        <v>2806.97</v>
+        <v>-7062.21</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0309</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>7805.58</v>
+        <v>7657.12</v>
       </c>
       <c r="I24" t="n">
-        <v>83705.67999999999</v>
+        <v>82249.45</v>
       </c>
       <c r="J24" t="n">
-        <v>84714.00999999999</v>
+        <v>85667.16</v>
       </c>
       <c r="K24" t="n">
-        <v>88063.36</v>
+        <v>89731.64</v>
       </c>
       <c r="L24" t="n">
-        <v>91412.72</v>
+        <v>93796.12</v>
       </c>
       <c r="M24" t="n">
-        <v>93591.56</v>
+        <v>97537.22</v>
       </c>
       <c r="N24" t="n">
-        <v>95770.39999999999</v>
+        <v>101278.32</v>
       </c>
       <c r="O24" t="n">
-        <v>100290.27</v>
+        <v>105666.18</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
+      <c r="Q24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
@@ -2576,58 +2566,64 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>93655.67</v>
+        <v>86566.52</v>
       </c>
       <c r="C25" t="n">
-        <v>93660.83</v>
+        <v>90439.28999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>86003.71000000001</v>
+        <v>75698.89999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>86572.22</v>
+        <v>76974.45</v>
       </c>
       <c r="F25" t="n">
-        <v>-7062.21</v>
+        <v>-9597.77</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.1109</v>
       </c>
       <c r="H25" t="n">
-        <v>7657.12</v>
+        <v>14740.39</v>
       </c>
       <c r="I25" t="n">
-        <v>82249.45</v>
+        <v>78346.59</v>
       </c>
       <c r="J25" t="n">
-        <v>85667.16</v>
+        <v>77285.08</v>
       </c>
       <c r="K25" t="n">
-        <v>89731.64</v>
+        <v>82743.66</v>
       </c>
       <c r="L25" t="n">
-        <v>93796.12</v>
+        <v>88202.24000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>97537.22</v>
+        <v>90400.78</v>
       </c>
       <c r="N25" t="n">
-        <v>101278.32</v>
+        <v>92599.31</v>
       </c>
       <c r="O25" t="n">
-        <v>105666.18</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
+        <v>101317.95</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
@@ -2644,8 +2640,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2653,89 +2651,81 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>86566.52</v>
+        <v>76968.88</v>
       </c>
       <c r="C26" t="n">
-        <v>90439.28999999999</v>
+        <v>79258.61</v>
       </c>
       <c r="D26" t="n">
-        <v>75698.89999999999</v>
+        <v>60074.2</v>
       </c>
       <c r="E26" t="n">
-        <v>76974.45</v>
+        <v>70264.73</v>
       </c>
       <c r="F26" t="n">
-        <v>-9597.77</v>
+        <v>-6709.72</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.1109</v>
+        <v>-0.0872</v>
       </c>
       <c r="H26" t="n">
-        <v>14740.39</v>
+        <v>19184.41</v>
       </c>
       <c r="I26" t="n">
-        <v>78346.59</v>
+        <v>60958.51</v>
       </c>
       <c r="J26" t="n">
-        <v>77285.08</v>
+        <v>59186.73</v>
       </c>
       <c r="K26" t="n">
-        <v>82743.66</v>
+        <v>69604.25</v>
       </c>
       <c r="L26" t="n">
-        <v>88202.24000000001</v>
+        <v>80021.77</v>
       </c>
       <c r="M26" t="n">
-        <v>90400.78</v>
+        <v>84344.64</v>
       </c>
       <c r="N26" t="n">
-        <v>92599.31</v>
+        <v>88667.50999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>101317.95</v>
+        <v>105179.68</v>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2753,67 +2743,63 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>76968.88</v>
+        <v>70243.33</v>
       </c>
       <c r="C27" t="n">
-        <v>79258.61</v>
+        <v>71369.97</v>
       </c>
       <c r="D27" t="n">
-        <v>60074.2</v>
+        <v>65092.11</v>
       </c>
       <c r="E27" t="n">
-        <v>70264.73</v>
+        <v>68788.19</v>
       </c>
       <c r="F27" t="n">
-        <v>-6709.72</v>
+        <v>-1476.54</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0872</v>
+        <v>-0.021</v>
       </c>
       <c r="H27" t="n">
-        <v>19184.41</v>
+        <v>6277.86</v>
       </c>
       <c r="I27" t="n">
-        <v>60958.51</v>
+        <v>40889.8</v>
       </c>
       <c r="J27" t="n">
-        <v>59186.73</v>
+        <v>51379.48</v>
       </c>
       <c r="K27" t="n">
-        <v>69604.25</v>
+        <v>60672.52</v>
       </c>
       <c r="L27" t="n">
-        <v>80021.77</v>
+        <v>69965.57000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>84344.64</v>
+        <v>79856.92999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>88667.50999999999</v>
+        <v>89748.28999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>105179.68</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>98443.02</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
       </c>
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2830,55 +2816,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>70243.33</v>
+        <v>68782.39999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>71369.97</v>
+        <v>70067.23</v>
       </c>
       <c r="D28" t="n">
-        <v>65092.11</v>
+        <v>65637.42999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>68788.19</v>
+        <v>67659.39</v>
       </c>
       <c r="F28" t="n">
-        <v>-1476.54</v>
+        <v>-1128.8</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.021</v>
+        <v>-0.0164</v>
       </c>
       <c r="H28" t="n">
-        <v>6277.86</v>
+        <v>4429.8</v>
       </c>
       <c r="I28" t="n">
-        <v>40889.8</v>
+        <v>58814.25</v>
       </c>
       <c r="J28" t="n">
-        <v>51379.48</v>
+        <v>62788.9</v>
       </c>
       <c r="K28" t="n">
-        <v>60672.52</v>
+        <v>65649.25999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>69965.57000000001</v>
+        <v>68509.61</v>
       </c>
       <c r="M28" t="n">
-        <v>79856.92999999999</v>
+        <v>71927.12</v>
       </c>
       <c r="N28" t="n">
-        <v>89748.28999999999</v>
+        <v>75344.62</v>
       </c>
       <c r="O28" t="n">
-        <v>98443.02</v>
+        <v>77647.83</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2886,8 +2876,10 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
@@ -2917,70 +2909,74 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>68782.39999999999</v>
+        <v>67668.42999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>70067.23</v>
+        <v>69953.53</v>
       </c>
       <c r="D29" t="n">
-        <v>65637.42999999999</v>
+        <v>62553.19</v>
       </c>
       <c r="E29" t="n">
-        <v>67659.39</v>
+        <v>65738.10000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>-1128.8</v>
+        <v>-1921.29</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0164</v>
+        <v>-0.0284</v>
       </c>
       <c r="H29" t="n">
-        <v>4429.8</v>
+        <v>7400.34</v>
       </c>
       <c r="I29" t="n">
-        <v>58814.25</v>
+        <v>61207.62</v>
       </c>
       <c r="J29" t="n">
-        <v>62788.9</v>
+        <v>63133.12</v>
       </c>
       <c r="K29" t="n">
-        <v>65649.25999999999</v>
+        <v>65444.49</v>
       </c>
       <c r="L29" t="n">
-        <v>68509.61</v>
+        <v>67755.86</v>
       </c>
       <c r="M29" t="n">
-        <v>71927.12</v>
+        <v>69874.28999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>75344.62</v>
+        <v>71992.72</v>
       </c>
       <c r="O29" t="n">
-        <v>77647.83</v>
+        <v>74497.03999999999</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
@@ -2992,86 +2988,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>67668.42999999999</v>
+        <v>65734.08</v>
       </c>
       <c r="C30" t="n">
-        <v>69953.53</v>
+        <v>74051.8</v>
       </c>
       <c r="D30" t="n">
-        <v>62553.19</v>
+        <v>65303.14</v>
       </c>
       <c r="E30" t="n">
-        <v>65738.10000000001</v>
+        <v>65969.78</v>
       </c>
       <c r="F30" t="n">
-        <v>-1921.29</v>
+        <v>231.68</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0284</v>
+        <v>0.0035</v>
       </c>
       <c r="H30" t="n">
-        <v>7400.34</v>
+        <v>8748.67</v>
       </c>
       <c r="I30" t="n">
-        <v>61207.62</v>
+        <v>55152.84</v>
       </c>
       <c r="J30" t="n">
-        <v>63133.12</v>
+        <v>58080.13</v>
       </c>
       <c r="K30" t="n">
-        <v>65444.49</v>
+        <v>62037.93</v>
       </c>
       <c r="L30" t="n">
-        <v>67755.86</v>
+        <v>65995.73</v>
       </c>
       <c r="M30" t="n">
-        <v>69874.28999999999</v>
+        <v>69438.27</v>
       </c>
       <c r="N30" t="n">
-        <v>71992.72</v>
+        <v>72880.82000000001</v>
       </c>
       <c r="O30" t="n">
-        <v>74497.03999999999</v>
+        <v>77353.88</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
+      <c r="U30" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
@@ -3080,55 +3070,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>65734.08</v>
+        <v>65969.59</v>
       </c>
       <c r="C31" t="n">
-        <v>74051.8</v>
+        <v>73927.33</v>
       </c>
       <c r="D31" t="n">
-        <v>65303.14</v>
+        <v>65858.00999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>65969.78</v>
+        <v>72789.91</v>
       </c>
       <c r="F31" t="n">
-        <v>231.68</v>
+        <v>6820.13</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.1034</v>
       </c>
       <c r="H31" t="n">
-        <v>8748.67</v>
+        <v>8069.32</v>
       </c>
       <c r="I31" t="n">
-        <v>55152.84</v>
+        <v>56554.47</v>
       </c>
       <c r="J31" t="n">
-        <v>58080.13</v>
+        <v>55367.27</v>
       </c>
       <c r="K31" t="n">
-        <v>62037.93</v>
+        <v>61595.45</v>
       </c>
       <c r="L31" t="n">
-        <v>65995.73</v>
+        <v>67823.63</v>
       </c>
       <c r="M31" t="n">
-        <v>69438.27</v>
+        <v>70344.12</v>
       </c>
       <c r="N31" t="n">
-        <v>72880.82000000001</v>
+        <v>72864.60000000001</v>
       </c>
       <c r="O31" t="n">
-        <v>77353.88</v>
+        <v>82800.47</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3139,9 +3133,9 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
@@ -3151,7 +3145,7 @@
       </c>
       <c r="U31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V31" s="8" t="n">
@@ -3164,57 +3158,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>65969.59</v>
+        <v>72798.17</v>
       </c>
       <c r="C32" t="n">
-        <v>73927.33</v>
+        <v>75988.39999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>65858.00999999999</v>
+        <v>67372.88</v>
       </c>
       <c r="E32" t="n">
-        <v>72789.91</v>
+        <v>67845.21000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>6820.13</v>
+        <v>-4944.7</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.1034</v>
+        <v>-0.0679</v>
       </c>
       <c r="H32" t="n">
-        <v>8069.32</v>
+        <v>8615.52</v>
       </c>
       <c r="I32" t="n">
-        <v>56554.47</v>
+        <v>57788.69</v>
       </c>
       <c r="J32" t="n">
-        <v>55367.27</v>
+        <v>66169.22</v>
       </c>
       <c r="K32" t="n">
-        <v>61595.45</v>
+        <v>68755.25</v>
       </c>
       <c r="L32" t="n">
-        <v>67823.63</v>
+        <v>71341.28999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>70344.12</v>
+        <v>76824.57000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>72864.60000000001</v>
+        <v>82307.86</v>
       </c>
       <c r="O32" t="n">
-        <v>82800.47</v>
+        <v>81996.64999999999</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3222,23 +3216,21 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3257,50 +3249,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>72798.17</v>
+        <v>67843</v>
       </c>
       <c r="C33" t="n">
-        <v>75988.39999999999</v>
+        <v>71985.74000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>67372.88</v>
+        <v>64971.71</v>
       </c>
       <c r="E33" t="n">
-        <v>67845.21000000001</v>
+        <v>65954.92</v>
       </c>
       <c r="F33" t="n">
-        <v>-4944.7</v>
+        <v>-1890.29</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0679</v>
+        <v>-0.0279</v>
       </c>
       <c r="H33" t="n">
-        <v>8615.52</v>
+        <v>7014.04</v>
       </c>
       <c r="I33" t="n">
-        <v>57788.69</v>
+        <v>58757.35</v>
       </c>
       <c r="J33" t="n">
-        <v>66169.22</v>
+        <v>57311.97</v>
       </c>
       <c r="K33" t="n">
-        <v>68755.25</v>
+        <v>63537.45</v>
       </c>
       <c r="L33" t="n">
-        <v>71341.28999999999</v>
+        <v>69762.92</v>
       </c>
       <c r="M33" t="n">
-        <v>76824.57000000001</v>
+        <v>72152.97</v>
       </c>
       <c r="N33" t="n">
-        <v>82307.86</v>
+        <v>74543.02</v>
       </c>
       <c r="O33" t="n">
-        <v>81996.64999999999</v>
+        <v>84603.92</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3332,59 +3324,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>67843</v>
+        <v>65958.35000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>71985.74000000001</v>
+        <v>69230.36</v>
       </c>
       <c r="D34" t="n">
-        <v>64971.71</v>
+        <v>65725.25999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>65954.92</v>
+        <v>68981.89999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>-1890.29</v>
+        <v>3026.98</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0279</v>
+        <v>0.0459</v>
       </c>
       <c r="H34" t="n">
-        <v>7014.04</v>
+        <v>3505.1</v>
       </c>
       <c r="I34" t="n">
-        <v>58757.35</v>
+        <v>57957.67</v>
       </c>
       <c r="J34" t="n">
-        <v>57311.97</v>
+        <v>57678.99</v>
       </c>
       <c r="K34" t="n">
-        <v>63537.45</v>
+        <v>62447.9</v>
       </c>
       <c r="L34" t="n">
-        <v>69762.92</v>
+        <v>67216.82000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>72152.97</v>
+        <v>69461.94</v>
       </c>
       <c r="N34" t="n">
-        <v>74543.02</v>
+        <v>71707.06</v>
       </c>
       <c r="O34" t="n">
-        <v>84603.92</v>
+        <v>78999.78</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3392,19 +3380,19 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3416,55 +3404,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>65958.35000000001</v>
+        <v>68982.91</v>
       </c>
       <c r="C35" t="n">
-        <v>69230.36</v>
+        <v>73784.23</v>
       </c>
       <c r="D35" t="n">
-        <v>65725.25999999999</v>
+        <v>67740.50999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>68981.89999999999</v>
+        <v>70753.41</v>
       </c>
       <c r="F35" t="n">
-        <v>3026.98</v>
+        <v>1771.51</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0459</v>
+        <v>0.0257</v>
       </c>
       <c r="H35" t="n">
-        <v>3505.1</v>
+        <v>6043.73</v>
       </c>
       <c r="I35" t="n">
-        <v>57957.67</v>
+        <v>62220.16</v>
       </c>
       <c r="J35" t="n">
-        <v>57678.99</v>
+        <v>66228.84</v>
       </c>
       <c r="K35" t="n">
-        <v>62447.9</v>
+        <v>67229.35000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>67216.82000000001</v>
+        <v>68229.85000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>69461.94</v>
+        <v>70734.45</v>
       </c>
       <c r="N35" t="n">
-        <v>71707.06</v>
+        <v>73239.03999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>78999.78</v>
+        <v>72735.46000000001</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3485,11 +3477,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W35" s="11" t="inlineStr">
         <is>
@@ -3498,57 +3494,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>68982.91</v>
+        <v>70757.62</v>
       </c>
       <c r="C36" t="n">
-        <v>73784.23</v>
+        <v>78320.67999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>67740.50999999999</v>
+        <v>70588.52</v>
       </c>
       <c r="E36" t="n">
-        <v>70753.41</v>
+        <v>73856.35000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>1771.51</v>
+        <v>3102.95</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0257</v>
+        <v>0.0439</v>
       </c>
       <c r="H36" t="n">
-        <v>6043.73</v>
+        <v>7732.16</v>
       </c>
       <c r="I36" t="n">
-        <v>62220.16</v>
+        <v>61696.78</v>
       </c>
       <c r="J36" t="n">
-        <v>66228.84</v>
+        <v>64705.2</v>
       </c>
       <c r="K36" t="n">
-        <v>67229.35000000001</v>
+        <v>67731.53999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>68229.85000000001</v>
+        <v>70757.89</v>
       </c>
       <c r="M36" t="n">
-        <v>70734.45</v>
+        <v>73775.27</v>
       </c>
       <c r="N36" t="n">
-        <v>73239.03999999999</v>
+        <v>76792.64999999999</v>
       </c>
       <c r="O36" t="n">
-        <v>72735.46000000001</v>
+        <v>79827.96000000001</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3574,10 +3570,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="11" t="inlineStr">
         <is>
@@ -3593,50 +3587,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>70757.62</v>
+        <v>73854.25</v>
       </c>
       <c r="C37" t="n">
-        <v>78320.67999999999</v>
+        <v>79468</v>
       </c>
       <c r="D37" t="n">
-        <v>70588.52</v>
+        <v>73775.57000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>73856.35000000001</v>
+        <v>78657.53999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>3102.95</v>
+        <v>4801.19</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0439</v>
+        <v>0.065</v>
       </c>
       <c r="H37" t="n">
-        <v>7732.16</v>
+        <v>5692.43</v>
       </c>
       <c r="I37" t="n">
-        <v>61696.78</v>
+        <v>62856.37</v>
       </c>
       <c r="J37" t="n">
-        <v>64705.2</v>
+        <v>65825.07000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>67731.53999999999</v>
+        <v>69990.27</v>
       </c>
       <c r="L37" t="n">
-        <v>70757.89</v>
+        <v>74155.48</v>
       </c>
       <c r="M37" t="n">
-        <v>73775.27</v>
+        <v>77722.42999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>76792.64999999999</v>
+        <v>81289.38</v>
       </c>
       <c r="O37" t="n">
-        <v>79827.96000000001</v>
+        <v>86052.84</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3657,10 +3651,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3679,50 +3671,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>73854.25</v>
+        <v>78661.02</v>
       </c>
       <c r="C38" t="n">
-        <v>79468</v>
+        <v>79488.17</v>
       </c>
       <c r="D38" t="n">
-        <v>73775.57000000001</v>
+        <v>74958.57000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>78657.53999999999</v>
+        <v>78538.23</v>
       </c>
       <c r="F38" t="n">
-        <v>4801.19</v>
+        <v>-119.31</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.065</v>
+        <v>-0.0015</v>
       </c>
       <c r="H38" t="n">
-        <v>5692.43</v>
+        <v>4529.6</v>
       </c>
       <c r="I38" t="n">
-        <v>62856.37</v>
+        <v>68083.14</v>
       </c>
       <c r="J38" t="n">
-        <v>65825.07000000001</v>
+        <v>73982.99000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>69990.27</v>
+        <v>75811.32000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>74155.48</v>
+        <v>77639.66</v>
       </c>
       <c r="M38" t="n">
-        <v>77722.42999999999</v>
+        <v>81503.75</v>
       </c>
       <c r="N38" t="n">
-        <v>81289.38</v>
+        <v>85367.85000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>86052.84</v>
+        <v>85160.42999999999</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3730,18 +3722,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3756,57 +3748,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>78661.02</v>
+        <v>78540.28999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>79488.17</v>
+        <v>82792.21000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>74958.57000000001</v>
+        <v>78217.96000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>78538.23</v>
+        <v>82138.92999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>-119.31</v>
+        <v>3600.7</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0458</v>
       </c>
       <c r="H39" t="n">
-        <v>4529.6</v>
+        <v>4574.25</v>
       </c>
       <c r="I39" t="n">
-        <v>68083.14</v>
+        <v>70428.97</v>
       </c>
       <c r="J39" t="n">
-        <v>73982.99000000001</v>
+        <v>74666.05</v>
       </c>
       <c r="K39" t="n">
-        <v>75811.32000000001</v>
+        <v>76273.42999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>77639.66</v>
+        <v>77880.8</v>
       </c>
       <c r="M39" t="n">
-        <v>81503.75</v>
+        <v>80803.03</v>
       </c>
       <c r="N39" t="n">
-        <v>85367.85000000001</v>
+        <v>83725.25999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>85160.42999999999</v>
+        <v>84017.77</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3814,18 +3806,18 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3840,77 +3832,79 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>78540.28999999999</v>
+        <v>82139.05</v>
       </c>
       <c r="C40" t="n">
-        <v>82792.21000000001</v>
+        <v>82326.23</v>
       </c>
       <c r="D40" t="n">
-        <v>78217.96000000001</v>
+        <v>76783.41</v>
       </c>
       <c r="E40" t="n">
-        <v>82138.92999999999</v>
+        <v>77429.35000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>3600.7</v>
+        <v>-4709.58</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0458</v>
+        <v>-0.0573</v>
       </c>
       <c r="H40" t="n">
-        <v>4574.25</v>
+        <v>5542.82</v>
       </c>
       <c r="I40" t="n">
-        <v>70428.97</v>
+        <v>73643.71000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>74666.05</v>
+        <v>78381.60000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>76273.42999999999</v>
+        <v>79851.8</v>
       </c>
       <c r="L40" t="n">
-        <v>77880.8</v>
+        <v>81322.00999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>80803.03</v>
+        <v>84426.05</v>
       </c>
       <c r="N40" t="n">
-        <v>83725.25999999999</v>
+        <v>87530.10000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>84017.77</v>
+        <v>87366.46000000001</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
+      <c r="Q40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3922,67 +3916,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>82139.05</v>
+        <v>77426.34</v>
       </c>
       <c r="C41" t="n">
-        <v>82326.23</v>
+        <v>78100.56</v>
       </c>
       <c r="D41" t="n">
-        <v>76783.41</v>
+        <v>74255.23</v>
       </c>
       <c r="E41" t="n">
-        <v>77429.35000000001</v>
+        <v>76981.12</v>
       </c>
       <c r="F41" t="n">
-        <v>-4709.58</v>
+        <v>-448.23</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0573</v>
+        <v>-0.0058</v>
       </c>
       <c r="H41" t="n">
-        <v>5542.82</v>
+        <v>3845.33</v>
       </c>
       <c r="I41" t="n">
-        <v>73643.71000000001</v>
+        <v>71240.59</v>
       </c>
       <c r="J41" t="n">
-        <v>78381.60000000001</v>
+        <v>70823.78999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>79851.8</v>
+        <v>74657.94</v>
       </c>
       <c r="L41" t="n">
-        <v>81322.00999999999</v>
+        <v>78492.09</v>
       </c>
       <c r="M41" t="n">
-        <v>84426.05</v>
+        <v>80200.75999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>87530.10000000001</v>
+        <v>81909.44</v>
       </c>
       <c r="O41" t="n">
-        <v>87366.46000000001</v>
+        <v>87869.05</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q41" s="6" t="n">
+        <v/>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
@@ -3991,7 +3979,7 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -4013,56 +4001,58 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>77426.34</v>
+        <v>76981.12</v>
       </c>
       <c r="C42" t="n">
-        <v>78100.56</v>
+        <v>77990.87</v>
       </c>
       <c r="D42" t="n">
-        <v>74255.23</v>
+        <v>72435.62</v>
       </c>
       <c r="E42" t="n">
-        <v>76981.12</v>
+        <v>73579.69</v>
       </c>
       <c r="F42" t="n">
-        <v>-448.23</v>
+        <v>-3401.44</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0442</v>
       </c>
       <c r="H42" t="n">
-        <v>3845.33</v>
+        <v>5555.24</v>
       </c>
       <c r="I42" t="n">
-        <v>71240.59</v>
+        <v>70409.91</v>
       </c>
       <c r="J42" t="n">
-        <v>70823.78999999999</v>
+        <v>73537.41</v>
       </c>
       <c r="K42" t="n">
-        <v>74657.94</v>
+        <v>75058.46000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>78492.09</v>
+        <v>76579.50999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>80200.75999999999</v>
+        <v>78903.78999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>81909.44</v>
+        <v>81228.07000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>87869.05</v>
+        <v>81945.89</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
@@ -4071,7 +4061,7 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4093,57 +4083,59 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>76981.12</v>
+        <v>73580.21000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>77990.87</v>
+        <v>73969.57000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>72435.62</v>
+        <v>59108.92</v>
       </c>
       <c r="E43" t="n">
-        <v>73579.69</v>
+        <v>63239.52</v>
       </c>
       <c r="F43" t="n">
-        <v>-3401.44</v>
+        <v>-10340.17</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0442</v>
+        <v>-0.1405</v>
       </c>
       <c r="H43" t="n">
-        <v>5555.24</v>
+        <v>14860.65</v>
       </c>
       <c r="I43" t="n">
-        <v>70409.91</v>
+        <v>66880.38</v>
       </c>
       <c r="J43" t="n">
-        <v>73537.41</v>
+        <v>67207.67</v>
       </c>
       <c r="K43" t="n">
-        <v>75058.46000000001</v>
+        <v>70802.07000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>76579.50999999999</v>
+        <v>74396.47</v>
       </c>
       <c r="M43" t="n">
-        <v>78903.78999999999</v>
+        <v>76357.31</v>
       </c>
       <c r="N43" t="n">
-        <v>81228.07000000001</v>
+        <v>78318.14999999999</v>
       </c>
       <c r="O43" t="n">
-        <v>81945.89</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
+        <v>83546.11</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
@@ -4175,69 +4167,63 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>73580.21000000001</v>
+        <v>63244.09</v>
       </c>
       <c r="C44" t="n">
-        <v>73969.57000000001</v>
+        <v>65749.78</v>
       </c>
       <c r="D44" t="n">
-        <v>59108.92</v>
+        <v>60756.69</v>
       </c>
       <c r="E44" t="n">
-        <v>63239.52</v>
+        <v>65710.39999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>-10340.17</v>
+        <v>2470.88</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.1405</v>
+        <v>0.0391</v>
       </c>
       <c r="H44" t="n">
-        <v>14860.65</v>
+        <v>4993.09</v>
       </c>
       <c r="I44" t="n">
-        <v>66880.38</v>
+        <v>44248.27</v>
       </c>
       <c r="J44" t="n">
-        <v>67207.67</v>
+        <v>46729</v>
       </c>
       <c r="K44" t="n">
-        <v>70802.07000000001</v>
+        <v>55809.19</v>
       </c>
       <c r="L44" t="n">
-        <v>74396.47</v>
+        <v>64889.38</v>
       </c>
       <c r="M44" t="n">
-        <v>76357.31</v>
+        <v>70669.85000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>78318.14999999999</v>
+        <v>76450.31</v>
       </c>
       <c r="O44" t="n">
-        <v>83546.11</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>88830.22</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4254,55 +4240,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>63244.09</v>
+        <v>65711.11</v>
       </c>
       <c r="C45" t="n">
-        <v>65749.78</v>
+        <v>67248.13</v>
       </c>
       <c r="D45" t="n">
-        <v>60756.69</v>
+        <v>62201.14</v>
       </c>
       <c r="E45" t="n">
-        <v>65710.39999999999</v>
+        <v>63237.54</v>
       </c>
       <c r="F45" t="n">
-        <v>2470.88</v>
+        <v>-2472.86</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0391</v>
+        <v>-0.0376</v>
       </c>
       <c r="H45" t="n">
-        <v>4993.09</v>
+        <v>5046.99</v>
       </c>
       <c r="I45" t="n">
-        <v>44248.27</v>
+        <v>55763.59</v>
       </c>
       <c r="J45" t="n">
-        <v>46729</v>
+        <v>61945.89</v>
       </c>
       <c r="K45" t="n">
-        <v>55809.19</v>
+        <v>63213.85</v>
       </c>
       <c r="L45" t="n">
-        <v>64889.38</v>
+        <v>64481.82</v>
       </c>
       <c r="M45" t="n">
-        <v>70669.85000000001</v>
+        <v>68206.95</v>
       </c>
       <c r="N45" t="n">
-        <v>76450.31</v>
+        <v>71932.07000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>88830.22</v>
+        <v>70742.88</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4310,12 +4300,14 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4341,50 +4333,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>65711.11</v>
+        <v>63240.79</v>
       </c>
       <c r="C46" t="n">
-        <v>67248.13</v>
+        <v>65544</v>
       </c>
       <c r="D46" t="n">
-        <v>62201.14</v>
+        <v>58075.92</v>
       </c>
       <c r="E46" t="n">
-        <v>63237.54</v>
+        <v>59532.34</v>
       </c>
       <c r="F46" t="n">
-        <v>-2472.86</v>
+        <v>-3705.2</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0376</v>
+        <v>-0.0586</v>
       </c>
       <c r="H46" t="n">
-        <v>5046.99</v>
+        <v>7468.08</v>
       </c>
       <c r="I46" t="n">
-        <v>55763.59</v>
+        <v>57154.16</v>
       </c>
       <c r="J46" t="n">
-        <v>61945.89</v>
+        <v>57447</v>
       </c>
       <c r="K46" t="n">
-        <v>63213.85</v>
+        <v>60714.04</v>
       </c>
       <c r="L46" t="n">
-        <v>64481.82</v>
+        <v>63981.09</v>
       </c>
       <c r="M46" t="n">
-        <v>68206.95</v>
+        <v>65761.03</v>
       </c>
       <c r="N46" t="n">
-        <v>71932.07000000001</v>
+        <v>67540.98</v>
       </c>
       <c r="O46" t="n">
-        <v>70742.88</v>
+        <v>72295.12</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4416,59 +4408,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>63240.79</v>
+        <v>59522.79</v>
       </c>
       <c r="C47" t="n">
-        <v>65544</v>
+        <v>63935.85</v>
       </c>
       <c r="D47" t="n">
-        <v>58075.92</v>
+        <v>57747.77</v>
       </c>
       <c r="E47" t="n">
-        <v>59532.34</v>
+        <v>63547.88</v>
       </c>
       <c r="F47" t="n">
-        <v>-3705.2</v>
+        <v>4015.54</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0586</v>
+        <v>0.0675</v>
       </c>
       <c r="H47" t="n">
-        <v>7468.08</v>
+        <v>6188.08</v>
       </c>
       <c r="I47" t="n">
-        <v>57154.16</v>
+        <v>50607.84</v>
       </c>
       <c r="J47" t="n">
-        <v>57447</v>
+        <v>50925.45</v>
       </c>
       <c r="K47" t="n">
-        <v>60714.04</v>
+        <v>55798.3</v>
       </c>
       <c r="L47" t="n">
-        <v>63981.09</v>
+        <v>60671.15</v>
       </c>
       <c r="M47" t="n">
-        <v>65761.03</v>
+        <v>63266.38</v>
       </c>
       <c r="N47" t="n">
-        <v>67540.98</v>
+        <v>65861.61</v>
       </c>
       <c r="O47" t="n">
-        <v>72295.12</v>
+        <v>73012.08</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4476,19 +4464,19 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4500,55 +4488,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>59522.79</v>
+        <v>63551.02</v>
       </c>
       <c r="C48" t="n">
-        <v>63935.85</v>
+        <v>64658.97</v>
       </c>
       <c r="D48" t="n">
-        <v>57747.77</v>
+        <v>61275.83</v>
       </c>
       <c r="E48" t="n">
-        <v>63547.88</v>
+        <v>63758.22</v>
       </c>
       <c r="F48" t="n">
-        <v>4015.54</v>
+        <v>210.34</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0675</v>
+        <v>0.0033</v>
       </c>
       <c r="H48" t="n">
-        <v>6188.08</v>
+        <v>3383.14</v>
       </c>
       <c r="I48" t="n">
-        <v>50607.84</v>
+        <v>51559.68</v>
       </c>
       <c r="J48" t="n">
-        <v>50925.45</v>
+        <v>58712.84</v>
       </c>
       <c r="K48" t="n">
-        <v>55798.3</v>
+        <v>60453.84</v>
       </c>
       <c r="L48" t="n">
-        <v>60671.15</v>
+        <v>62194.84</v>
       </c>
       <c r="M48" t="n">
-        <v>63266.38</v>
+        <v>66641.92</v>
       </c>
       <c r="N48" t="n">
-        <v>65861.61</v>
+        <v>71089</v>
       </c>
       <c r="O48" t="n">
-        <v>73012.08</v>
+        <v>70123.92999999999</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4561,13 +4553,11 @@
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4582,57 +4572,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>63551.02</v>
+        <v>63757.17</v>
       </c>
       <c r="C49" t="n">
-        <v>64658.97</v>
+        <v>65507.59</v>
       </c>
       <c r="D49" t="n">
-        <v>61275.83</v>
+        <v>61769</v>
       </c>
       <c r="E49" t="n">
-        <v>63758.22</v>
+        <v>64690.8</v>
       </c>
       <c r="F49" t="n">
-        <v>210.34</v>
+        <v>932.59</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0146</v>
       </c>
       <c r="H49" t="n">
-        <v>3383.14</v>
+        <v>3738.59</v>
       </c>
       <c r="I49" t="n">
-        <v>51559.68</v>
+        <v>57892.69</v>
       </c>
       <c r="J49" t="n">
-        <v>58712.84</v>
+        <v>60770.49</v>
       </c>
       <c r="K49" t="n">
-        <v>60453.84</v>
+        <v>62066.65</v>
       </c>
       <c r="L49" t="n">
-        <v>62194.84</v>
+        <v>63362.81</v>
       </c>
       <c r="M49" t="n">
-        <v>66641.92</v>
+        <v>65449.79</v>
       </c>
       <c r="N49" t="n">
-        <v>71089</v>
+        <v>67536.77</v>
       </c>
       <c r="O49" t="n">
-        <v>70123.92999999999</v>
+        <v>68042.11</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4640,16 +4630,20 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4671,50 +4665,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>63757.17</v>
+        <v>64684.42</v>
       </c>
       <c r="C50" t="n">
-        <v>65507.59</v>
+        <v>66910.06</v>
       </c>
       <c r="D50" t="n">
-        <v>61769</v>
+        <v>63686.04</v>
       </c>
       <c r="E50" t="n">
-        <v>64690.8</v>
+        <v>65340.3</v>
       </c>
       <c r="F50" t="n">
-        <v>932.59</v>
+        <v>649.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.01</v>
       </c>
       <c r="H50" t="n">
-        <v>3738.59</v>
+        <v>3224.03</v>
       </c>
       <c r="I50" t="n">
-        <v>57892.69</v>
+        <v>58030.41</v>
       </c>
       <c r="J50" t="n">
-        <v>60770.49</v>
+        <v>61478.46</v>
       </c>
       <c r="K50" t="n">
-        <v>62066.65</v>
+        <v>62821.51</v>
       </c>
       <c r="L50" t="n">
-        <v>63362.81</v>
+        <v>64164.55</v>
       </c>
       <c r="M50" t="n">
-        <v>65449.79</v>
+        <v>66560.10000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>67536.77</v>
+        <v>68955.64999999999</v>
       </c>
       <c r="O50" t="n">
-        <v>68042.11</v>
+        <v>69246.19</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4722,19 +4716,17 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="U50" s="8" t="n">
@@ -4757,50 +4749,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>64684.42</v>
+        <v>65340.59</v>
       </c>
       <c r="C51" t="n">
-        <v>66910.06</v>
+        <v>65658.34</v>
       </c>
       <c r="D51" t="n">
-        <v>63686.04</v>
+        <v>62233.01</v>
       </c>
       <c r="E51" t="n">
-        <v>65340.3</v>
+        <v>63482</v>
       </c>
       <c r="F51" t="n">
-        <v>649.5</v>
+        <v>-1858.3</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.0284</v>
       </c>
       <c r="H51" t="n">
-        <v>3224.03</v>
+        <v>3425.32</v>
       </c>
       <c r="I51" t="n">
-        <v>58030.41</v>
+        <v>60462.01</v>
       </c>
       <c r="J51" t="n">
-        <v>61478.46</v>
+        <v>62137.4</v>
       </c>
       <c r="K51" t="n">
-        <v>62821.51</v>
+        <v>63728.29</v>
       </c>
       <c r="L51" t="n">
-        <v>64164.55</v>
+        <v>65319.17</v>
       </c>
       <c r="M51" t="n">
-        <v>66560.10000000001</v>
+        <v>66952.31</v>
       </c>
       <c r="N51" t="n">
-        <v>68955.64999999999</v>
+        <v>68585.45</v>
       </c>
       <c r="O51" t="n">
-        <v>69246.19</v>
+        <v>70134.09</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4808,18 +4800,18 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4832,59 +4824,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>65340.59</v>
+        <v>63485.44</v>
       </c>
       <c r="C52" t="n">
-        <v>65658.34</v>
+        <v>65401.69</v>
       </c>
       <c r="D52" t="n">
-        <v>62233.01</v>
+        <v>62226.58</v>
       </c>
       <c r="E52" t="n">
-        <v>63482</v>
+        <v>64844.89</v>
       </c>
       <c r="F52" t="n">
-        <v>-1858.3</v>
+        <v>1362.89</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0284</v>
+        <v>0.0215</v>
       </c>
       <c r="H52" t="n">
-        <v>3425.32</v>
+        <v>3175.11</v>
       </c>
       <c r="I52" t="n">
-        <v>60462.01</v>
+        <v>58807.69</v>
       </c>
       <c r="J52" t="n">
-        <v>62137.4</v>
+        <v>59824.84</v>
       </c>
       <c r="K52" t="n">
-        <v>63728.29</v>
+        <v>61769.34</v>
       </c>
       <c r="L52" t="n">
-        <v>65319.17</v>
+        <v>63713.84</v>
       </c>
       <c r="M52" t="n">
-        <v>66952.31</v>
+        <v>65194.66</v>
       </c>
       <c r="N52" t="n">
-        <v>68585.45</v>
+        <v>66675.49000000001</v>
       </c>
       <c r="O52" t="n">
-        <v>70134.09</v>
+        <v>69083.66</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4892,19 +4880,19 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
@@ -4916,55 +4904,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>63485.44</v>
+        <v>64845.38</v>
       </c>
       <c r="C53" t="n">
-        <v>65401.69</v>
+        <v>65321.84</v>
       </c>
       <c r="D53" t="n">
-        <v>62226.58</v>
+        <v>62487.7</v>
       </c>
       <c r="E53" t="n">
-        <v>64844.89</v>
+        <v>62818.65</v>
       </c>
       <c r="F53" t="n">
-        <v>1362.89</v>
+        <v>-2026.23</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0215</v>
+        <v>-0.0312</v>
       </c>
       <c r="H53" t="n">
-        <v>3175.11</v>
+        <v>2834.14</v>
       </c>
       <c r="I53" t="n">
-        <v>58807.69</v>
+        <v>59051.46</v>
       </c>
       <c r="J53" t="n">
-        <v>59824.84</v>
+        <v>62185.15</v>
       </c>
       <c r="K53" t="n">
-        <v>61769.34</v>
+        <v>63257.33</v>
       </c>
       <c r="L53" t="n">
-        <v>63713.84</v>
+        <v>64329.51</v>
       </c>
       <c r="M53" t="n">
-        <v>65194.66</v>
+        <v>66432.44</v>
       </c>
       <c r="N53" t="n">
-        <v>66675.49000000001</v>
+        <v>68535.38</v>
       </c>
       <c r="O53" t="n">
-        <v>69083.66</v>
+        <v>68576.8</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4972,18 +4964,18 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -5005,50 +4997,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>64845.38</v>
+        <v>62819.38</v>
       </c>
       <c r="C54" t="n">
-        <v>65321.84</v>
+        <v>79463.71000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>62487.7</v>
+        <v>62687.1</v>
       </c>
       <c r="E54" t="n">
-        <v>62818.65</v>
+        <v>77755.27</v>
       </c>
       <c r="F54" t="n">
-        <v>-2026.23</v>
+        <v>14936.61</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0312</v>
+        <v>0.2378</v>
       </c>
       <c r="H54" t="n">
-        <v>2834.14</v>
+        <v>16776.61</v>
       </c>
       <c r="I54" t="n">
-        <v>59051.46</v>
+        <v>59653.56</v>
       </c>
       <c r="J54" t="n">
-        <v>62185.15</v>
+        <v>59441.45</v>
       </c>
       <c r="K54" t="n">
-        <v>63257.33</v>
+        <v>61401.58</v>
       </c>
       <c r="L54" t="n">
-        <v>64329.51</v>
+        <v>63361.71</v>
       </c>
       <c r="M54" t="n">
-        <v>66432.44</v>
+        <v>64235.72</v>
       </c>
       <c r="N54" t="n">
-        <v>68535.38</v>
+        <v>65109.73</v>
       </c>
       <c r="O54" t="n">
-        <v>68576.8</v>
+        <v>68155.98</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5056,83 +5048,83 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W54" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W54" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>62819.38</v>
+        <v>77748.88</v>
       </c>
       <c r="C55" t="n">
-        <v>79463.71000000001</v>
+        <v>81346.95</v>
       </c>
       <c r="D55" t="n">
-        <v>62687.1</v>
+        <v>76688.83</v>
       </c>
       <c r="E55" t="n">
-        <v>77755.27</v>
+        <v>77667.57000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>14936.61</v>
+        <v>-87.7</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.2378</v>
+        <v>-0.0011</v>
       </c>
       <c r="H55" t="n">
-        <v>16776.61</v>
+        <v>4658.12</v>
       </c>
       <c r="I55" t="n">
-        <v>59653.56</v>
+        <v>45910.49</v>
       </c>
       <c r="J55" t="n">
-        <v>59441.45</v>
+        <v>64318.59</v>
       </c>
       <c r="K55" t="n">
-        <v>61401.58</v>
+        <v>69366.96000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>63361.71</v>
+        <v>74415.34</v>
       </c>
       <c r="M55" t="n">
-        <v>64235.72</v>
+        <v>86143.57000000001</v>
       </c>
       <c r="N55" t="n">
-        <v>65109.73</v>
+        <v>97871.8</v>
       </c>
       <c r="O55" t="n">
-        <v>68155.98</v>
+        <v>96240.32000000001</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5145,78 +5137,76 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
       </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>77748.88</v>
+        <v>77673.7</v>
       </c>
       <c r="C56" t="n">
-        <v>81346.95</v>
+        <v>82262.21000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>76688.83</v>
+        <v>76248.3</v>
       </c>
       <c r="E56" t="n">
-        <v>77667.57000000001</v>
+        <v>80350.05</v>
       </c>
       <c r="F56" t="n">
-        <v>-87.7</v>
+        <v>2682.48</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0345</v>
       </c>
       <c r="H56" t="n">
-        <v>4658.12</v>
+        <v>6013.91</v>
       </c>
       <c r="I56" t="n">
-        <v>45910.49</v>
+        <v>72030.7</v>
       </c>
       <c r="J56" t="n">
-        <v>64318.59</v>
+        <v>72334.28999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>69366.96000000001</v>
+        <v>75338.50999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>74415.34</v>
+        <v>78342.73</v>
       </c>
       <c r="M56" t="n">
-        <v>86143.57000000001</v>
+        <v>79996.63</v>
       </c>
       <c r="N56" t="n">
-        <v>97871.8</v>
+        <v>81650.53999999999</v>
       </c>
       <c r="O56" t="n">
-        <v>96240.32000000001</v>
+        <v>86005.08</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5229,14 +5219,18 @@
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5255,50 +5249,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>77673.7</v>
+        <v>80349.2</v>
       </c>
       <c r="C57" t="n">
-        <v>82262.21000000001</v>
+        <v>80432.31</v>
       </c>
       <c r="D57" t="n">
-        <v>76248.3</v>
+        <v>76162.91</v>
       </c>
       <c r="E57" t="n">
-        <v>80350.05</v>
+        <v>76838.16</v>
       </c>
       <c r="F57" t="n">
-        <v>2682.48</v>
+        <v>-3511.89</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0345</v>
+        <v>-0.0437</v>
       </c>
       <c r="H57" t="n">
-        <v>6013.91</v>
+        <v>4269.4</v>
       </c>
       <c r="I57" t="n">
-        <v>72030.7</v>
+        <v>70234.39999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>72334.28999999999</v>
+        <v>74883.53999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>75338.50999999999</v>
+        <v>77343.09</v>
       </c>
       <c r="L57" t="n">
-        <v>78342.73</v>
+        <v>79802.64999999999</v>
       </c>
       <c r="M57" t="n">
-        <v>79996.63</v>
+        <v>83357</v>
       </c>
       <c r="N57" t="n">
-        <v>81650.53999999999</v>
+        <v>86911.35000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>86005.08</v>
+        <v>88276.12</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5306,23 +5300,21 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5334,57 +5326,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>80349.2</v>
+        <v>76806.19</v>
       </c>
       <c r="C58" t="n">
-        <v>80432.31</v>
+        <v>79435.67999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>76162.91</v>
+        <v>76452.55</v>
       </c>
       <c r="E58" t="n">
-        <v>76983.95</v>
+        <v>78740.3</v>
       </c>
       <c r="F58" t="n">
-        <v>-3366.09</v>
+        <v>1902.14</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0419</v>
+        <v>0.0248</v>
       </c>
       <c r="H58" t="n">
-        <v>4269.4</v>
+        <v>2983.13</v>
       </c>
       <c r="I58" t="n">
-        <v>70234.39999999999</v>
+        <v>71893.52</v>
       </c>
       <c r="J58" t="n">
-        <v>74883.53999999999</v>
+        <v>71839.03</v>
       </c>
       <c r="K58" t="n">
-        <v>77343.09</v>
+        <v>74703.46000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>79802.64999999999</v>
+        <v>77567.88</v>
       </c>
       <c r="M58" t="n">
-        <v>83357</v>
+        <v>78972.86</v>
       </c>
       <c r="N58" t="n">
-        <v>86911.35000000001</v>
+        <v>80377.83</v>
       </c>
       <c r="O58" t="n">
-        <v>88276.12</v>
+        <v>84701.71000000001</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5392,19 +5384,19 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5418,7 +5410,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -5429,25 +5421,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>71893.52</v>
+        <v>73469.41</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>72057.72</v>
+        <v>76155.25999999999</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>74849.25</v>
+        <v>77248.73</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>77640.78</v>
+        <v>78342.21000000001</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>79118.64999999999</v>
+        <v>80231.86</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>80596.52</v>
+        <v>82121.52</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>84701.71000000001</v>
+        <v>82418.81</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5337,25 +5337,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>76806.19</v>
+        <v>78181.33</v>
       </c>
       <c r="C58" t="n">
-        <v>79435.67999999999</v>
+        <v>78232.38</v>
       </c>
       <c r="D58" t="n">
-        <v>76452.55</v>
+        <v>77752.48</v>
       </c>
       <c r="E58" t="n">
-        <v>78740.3</v>
+        <v>77967.62</v>
       </c>
       <c r="F58" t="n">
-        <v>1902.14</v>
+        <v>1129.46</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0248</v>
+        <v>0.0147</v>
       </c>
       <c r="H58" t="n">
-        <v>2983.13</v>
+        <v>479.89</v>
       </c>
       <c r="I58" t="n">
         <v>71893.52</v>
@@ -5389,13 +5389,11 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5421,25 +5419,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>73469.41</v>
+        <v>77272.59</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>76155.25999999999</v>
+        <v>77475.32000000001</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>77248.73</v>
+        <v>77727.67</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>78342.21000000001</v>
+        <v>77980.02</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>80231.86</v>
+        <v>78207.56</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>82121.52</v>
+        <v>78435.10000000001</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>82418.81</v>
+        <v>78712.27</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5346,13 +5346,13 @@
         <v>77752.48</v>
       </c>
       <c r="E58" t="n">
-        <v>77967.62</v>
+        <v>77908.46000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>1129.46</v>
+        <v>1070.3</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0139</v>
       </c>
       <c r="H58" t="n">
         <v>479.89</v>
@@ -5422,19 +5422,19 @@
         <v>77272.59</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>77475.32000000001</v>
+        <v>77386.59</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>77727.67</v>
+        <v>77668.52</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>77980.02</v>
+        <v>77950.45</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>78207.56</v>
+        <v>78148.41</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>78435.10000000001</v>
+        <v>78346.37</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>78712.27</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5343,19 +5343,19 @@
         <v>78232.38</v>
       </c>
       <c r="D58" t="n">
-        <v>77752.48</v>
+        <v>77703.44</v>
       </c>
       <c r="E58" t="n">
-        <v>77908.46000000001</v>
+        <v>77736.21000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>1070.3</v>
+        <v>898.05</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0139</v>
+        <v>0.0117</v>
       </c>
       <c r="H58" t="n">
-        <v>479.89</v>
+        <v>528.9400000000001</v>
       </c>
       <c r="I58" t="n">
         <v>71893.52</v>
@@ -5419,25 +5419,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>77272.59</v>
+        <v>77174.5</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>77386.59</v>
+        <v>77091.42999999999</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>77668.52</v>
+        <v>77471.74000000001</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>77950.45</v>
+        <v>77852.06</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>78148.41</v>
+        <v>78000.67999999999</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>78346.37</v>
+        <v>78149.3</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>78712.27</v>
+        <v>78761.31</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5343,19 +5343,19 @@
         <v>78232.38</v>
       </c>
       <c r="D58" t="n">
-        <v>77703.44</v>
+        <v>77638.84</v>
       </c>
       <c r="E58" t="n">
-        <v>77736.21000000001</v>
+        <v>77620.53999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>898.05</v>
+        <v>782.38</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0102</v>
       </c>
       <c r="H58" t="n">
-        <v>528.9400000000001</v>
+        <v>593.53</v>
       </c>
       <c r="I58" t="n">
         <v>71893.52</v>
@@ -5419,25 +5419,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>77174.5</v>
+        <v>77045.31</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>77091.42999999999</v>
+        <v>76869.47</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>77471.74000000001</v>
+        <v>77323.77</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>77852.06</v>
+        <v>77778.07000000001</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>78000.67999999999</v>
+        <v>77917.3</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>78149.3</v>
+        <v>78056.53999999999</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>78761.31</v>
+        <v>78825.91</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5337,25 +5337,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>78181.33</v>
+        <v>76830.28</v>
       </c>
       <c r="C58" t="n">
-        <v>78232.38</v>
+        <v>79568.95</v>
       </c>
       <c r="D58" t="n">
-        <v>77638.84</v>
+        <v>74984.84</v>
       </c>
       <c r="E58" t="n">
-        <v>77620.53999999999</v>
+        <v>75377.52</v>
       </c>
       <c r="F58" t="n">
-        <v>782.38</v>
+        <v>-1460.63</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.019</v>
       </c>
       <c r="H58" t="n">
-        <v>593.53</v>
+        <v>4584.11</v>
       </c>
       <c r="I58" t="n">
         <v>71893.52</v>
@@ -5384,16 +5384,20 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5408,7 +5412,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
@@ -5419,25 +5423,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>77045.31</v>
+        <v>70400.73</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>76869.47</v>
+        <v>69843.73</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>77323.77</v>
+        <v>73085.47</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>77778.07000000001</v>
+        <v>76327.21000000001</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>77917.3</v>
+        <v>77669.58</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>78056.53999999999</v>
+        <v>79011.95</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>78825.91</v>
+        <v>84153.06</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5343,19 +5343,19 @@
         <v>79568.95</v>
       </c>
       <c r="D58" t="n">
-        <v>74984.84</v>
+        <v>75404.10000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>75377.52</v>
+        <v>75456.36</v>
       </c>
       <c r="F58" t="n">
-        <v>-1460.63</v>
+        <v>-1381.8</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.019</v>
+        <v>-0.018</v>
       </c>
       <c r="H58" t="n">
-        <v>4584.11</v>
+        <v>4164.85</v>
       </c>
       <c r="I58" t="n">
         <v>71893.52</v>
@@ -5423,25 +5423,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>70400.73</v>
+        <v>71239.25</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>69843.73</v>
+        <v>70276.42</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>73085.47</v>
+        <v>73373.92999999999</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>76327.21000000001</v>
+        <v>76471.44</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>77669.58</v>
+        <v>77538.78999999999</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>79011.95</v>
+        <v>78606.13</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>84153.06</v>
+        <v>83733.8</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5343,19 +5343,19 @@
         <v>79568.95</v>
       </c>
       <c r="D58" t="n">
-        <v>75404.10000000001</v>
+        <v>75417.87</v>
       </c>
       <c r="E58" t="n">
-        <v>75456.36</v>
+        <v>75949.36</v>
       </c>
       <c r="F58" t="n">
-        <v>-1381.8</v>
+        <v>-888.8</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.018</v>
+        <v>-0.0116</v>
       </c>
       <c r="H58" t="n">
-        <v>4164.85</v>
+        <v>4151.09</v>
       </c>
       <c r="I58" t="n">
         <v>71893.52</v>
@@ -5423,25 +5423,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>71239.25</v>
+        <v>71266.78</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>70276.42</v>
+        <v>71026.25</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>73373.92999999999</v>
+        <v>73873.82000000001</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>76471.44</v>
+        <v>76721.38</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>77538.78999999999</v>
+        <v>78024.89999999999</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>78606.13</v>
+        <v>79328.42</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>83733.8</v>
+        <v>83720.03999999999</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5343,19 +5343,19 @@
         <v>79568.95</v>
       </c>
       <c r="D58" t="n">
-        <v>75417.87</v>
+        <v>74944.59</v>
       </c>
       <c r="E58" t="n">
-        <v>75949.36</v>
+        <v>75941.33</v>
       </c>
       <c r="F58" t="n">
-        <v>-888.8</v>
+        <v>-896.83</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0117</v>
       </c>
       <c r="H58" t="n">
-        <v>4151.09</v>
+        <v>4624.36</v>
       </c>
       <c r="I58" t="n">
         <v>71893.52</v>
@@ -5423,25 +5423,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>71266.78</v>
+        <v>70320.23</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>71026.25</v>
+        <v>70659.25</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>73873.82000000001</v>
+        <v>73629.14999999999</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>76721.38</v>
+        <v>76599.05</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>78024.89999999999</v>
+        <v>78253.50999999999</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>79328.42</v>
+        <v>79907.96000000001</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>83720.03999999999</v>
+        <v>84193.31</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5346,13 +5346,13 @@
         <v>74944.59</v>
       </c>
       <c r="E58" t="n">
-        <v>75941.33</v>
+        <v>76176.73</v>
       </c>
       <c r="F58" t="n">
-        <v>-896.83</v>
+        <v>-661.4299999999999</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.0086</v>
       </c>
       <c r="H58" t="n">
         <v>4624.36</v>
@@ -5384,14 +5384,12 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5426,19 +5424,19 @@
         <v>70320.23</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>70659.25</v>
+        <v>71012.34</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>73629.14999999999</v>
+        <v>73864.55</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>76599.05</v>
+        <v>76716.75</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>78253.50999999999</v>
+        <v>78488.91</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>79907.96000000001</v>
+        <v>80261.06</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>84193.31</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5346,13 +5346,13 @@
         <v>74944.59</v>
       </c>
       <c r="E58" t="n">
-        <v>76176.73</v>
+        <v>76028.89</v>
       </c>
       <c r="F58" t="n">
-        <v>-661.4299999999999</v>
+        <v>-809.27</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0086</v>
+        <v>-0.0105</v>
       </c>
       <c r="H58" t="n">
         <v>4624.36</v>
@@ -5384,12 +5384,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5424,19 +5426,19 @@
         <v>70320.23</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>71012.34</v>
+        <v>70790.59</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>73864.55</v>
+        <v>73716.71000000001</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>76716.75</v>
+        <v>76642.83</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>78488.91</v>
+        <v>78341.07000000001</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>80261.06</v>
+        <v>80039.31</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>84193.31</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5346,13 +5346,13 @@
         <v>74944.59</v>
       </c>
       <c r="E58" t="n">
-        <v>76028.89</v>
+        <v>75816.42</v>
       </c>
       <c r="F58" t="n">
-        <v>-809.27</v>
+        <v>-1021.73</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0105</v>
+        <v>-0.0133</v>
       </c>
       <c r="H58" t="n">
         <v>4624.36</v>
@@ -5426,19 +5426,19 @@
         <v>70320.23</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>70790.59</v>
+        <v>70471.89</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>73716.71000000001</v>
+        <v>73504.24000000001</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>76642.83</v>
+        <v>76536.60000000001</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>78341.07000000001</v>
+        <v>78128.60000000001</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>80039.31</v>
+        <v>79720.61</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>84193.31</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5346,13 +5346,13 @@
         <v>74944.59</v>
       </c>
       <c r="E58" t="n">
-        <v>75816.42</v>
+        <v>76161.10000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-1021.73</v>
+        <v>-677.05</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0133</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H58" t="n">
         <v>4624.36</v>
@@ -5384,14 +5384,12 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5426,19 +5424,19 @@
         <v>70320.23</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>70471.89</v>
+        <v>70988.91</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>73504.24000000001</v>
+        <v>73848.92</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>76536.60000000001</v>
+        <v>76708.94</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>78128.60000000001</v>
+        <v>78473.28</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>79720.61</v>
+        <v>80237.62</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>84193.31</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5346,13 +5346,13 @@
         <v>74944.59</v>
       </c>
       <c r="E58" t="n">
-        <v>76161.10000000001</v>
+        <v>76301.81</v>
       </c>
       <c r="F58" t="n">
-        <v>-677.05</v>
+        <v>-536.34</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.007</v>
       </c>
       <c r="H58" t="n">
         <v>4624.36</v>
@@ -5424,19 +5424,19 @@
         <v>70320.23</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>70988.91</v>
+        <v>71199.97</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>73848.92</v>
+        <v>73989.63</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>76708.94</v>
+        <v>76779.28999999999</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>78473.28</v>
+        <v>78613.99000000001</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>80237.62</v>
+        <v>80448.69</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>84193.31</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5346,13 +5346,13 @@
         <v>74944.59</v>
       </c>
       <c r="E58" t="n">
-        <v>76301.81</v>
+        <v>76368.75</v>
       </c>
       <c r="F58" t="n">
-        <v>-536.34</v>
+        <v>-469.41</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0061</v>
       </c>
       <c r="H58" t="n">
         <v>4624.36</v>
@@ -5424,19 +5424,19 @@
         <v>70320.23</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>71199.97</v>
+        <v>71300.38</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>73989.63</v>
+        <v>74056.57000000001</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>76779.28999999999</v>
+        <v>76812.75999999999</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>78613.99000000001</v>
+        <v>78680.92999999999</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>80448.69</v>
+        <v>80549.10000000001</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>84193.31</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,13 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X59"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -666,35 +659,39 @@
         <v>6553.62</v>
       </c>
       <c r="I2" t="n">
-        <v>109272.02</v>
+        <v>114396.83</v>
       </c>
       <c r="J2" t="n">
-        <v>108256.62</v>
+        <v>114662.63</v>
       </c>
       <c r="K2" t="n">
-        <v>113656.79</v>
+        <v>116219.19</v>
       </c>
       <c r="L2" t="n">
-        <v>119056.95</v>
+        <v>117775.75</v>
       </c>
       <c r="M2" t="n">
-        <v>121249.34</v>
+        <v>118686.93</v>
       </c>
       <c r="N2" t="n">
-        <v>123441.72</v>
+        <v>119598.12</v>
       </c>
       <c r="O2" t="n">
-        <v>132049.66</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>121800.05</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -713,14 +710,10 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -799,14 +792,10 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -885,12 +874,12 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -969,10 +958,14 @@
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1047,12 +1040,12 @@
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1128,10 @@
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1221,7 +1210,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1303,7 +1292,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1387,7 +1376,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1471,7 +1460,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1557,7 +1546,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1643,7 +1632,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1729,7 +1718,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1813,7 +1802,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1895,7 +1884,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1979,7 +1968,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2061,7 +2050,7 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2145,7 +2134,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2227,7 +2216,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2313,7 +2302,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2393,7 +2382,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2479,7 +2468,7 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2561,7 +2550,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2651,7 +2640,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2733,7 +2722,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2811,7 +2800,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2895,7 +2884,7 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2983,7 +2972,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3065,7 +3054,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3151,7 +3140,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3235,7 +3224,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3319,7 +3308,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3399,7 +3388,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3487,7 +3476,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3573,7 +3562,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3657,7 +3646,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3741,7 +3730,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3825,7 +3814,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3911,7 +3900,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3991,7 +3980,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4073,7 +4062,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4157,7 +4146,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4235,7 +4224,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4319,7 +4308,7 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4403,7 +4392,7 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4483,7 +4472,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4565,7 +4554,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4651,7 +4640,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4735,7 +4724,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4819,7 +4808,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4899,7 +4888,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4983,7 +4972,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5071,7 +5060,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5149,7 +5138,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5235,7 +5224,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5319,7 +5308,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5346,13 +5335,13 @@
         <v>74944.59</v>
       </c>
       <c r="E58" t="n">
-        <v>76368.75</v>
+        <v>76307.59</v>
       </c>
       <c r="F58" t="n">
-        <v>-469.41</v>
+        <v>-530.5599999999999</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0069</v>
       </c>
       <c r="H58" t="n">
         <v>4624.36</v>
@@ -5403,7 +5392,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5412,34 +5401,6 @@
         <is>
           <t>強警訊</t>
         </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>下週預測</t>
-        </is>
-      </c>
-      <c r="I59" s="13" t="n">
-        <v>70320.23</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>71300.38</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>74056.57000000001</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>76812.75999999999</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>78680.92999999999</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>80549.10000000001</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>84193.31</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5335,13 +5335,13 @@
         <v>74944.59</v>
       </c>
       <c r="E58" t="n">
-        <v>76307.59</v>
+        <v>76503.82000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-530.5599999999999</v>
+        <v>-334.34</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0069</v>
+        <v>-0.0044</v>
       </c>
       <c r="H58" t="n">
         <v>4624.36</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -659,34 +659,34 @@
         <v>6553.62</v>
       </c>
       <c r="I2" t="n">
-        <v>114396.83</v>
+        <v>115963.27</v>
       </c>
       <c r="J2" t="n">
-        <v>114662.63</v>
+        <v>115894.52</v>
       </c>
       <c r="K2" t="n">
-        <v>116219.19</v>
+        <v>116794.94</v>
       </c>
       <c r="L2" t="n">
-        <v>117775.75</v>
+        <v>117695.36</v>
       </c>
       <c r="M2" t="n">
-        <v>118686.93</v>
+        <v>118111.19</v>
       </c>
       <c r="N2" t="n">
-        <v>119598.12</v>
+        <v>118527.02</v>
       </c>
       <c r="O2" t="n">
-        <v>121800.05</v>
+        <v>119912.02</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -5329,22 +5329,22 @@
         <v>76830.28</v>
       </c>
       <c r="C58" t="n">
-        <v>79568.95</v>
+        <v>81911.14</v>
       </c>
       <c r="D58" t="n">
         <v>74944.59</v>
       </c>
       <c r="E58" t="n">
-        <v>76503.82000000001</v>
+        <v>81254.85000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-334.34</v>
+        <v>4416.7</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0575</v>
       </c>
       <c r="H58" t="n">
-        <v>4624.36</v>
+        <v>6966.55</v>
       </c>
       <c r="I58" t="n">
         <v>71893.52</v>
@@ -5376,9 +5376,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5386,8 +5386,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U58" s="8" t="n">
-        <v/>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5399,7 +5401,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,66 +634,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>117453.91</v>
+        <v>113456.9</v>
       </c>
       <c r="C2" t="n">
-        <v>117614.17</v>
+        <v>113637.84</v>
       </c>
       <c r="D2" t="n">
-        <v>111060.55</v>
+        <v>107444.45</v>
       </c>
       <c r="E2" t="n">
-        <v>113458.43</v>
+        <v>108236.71</v>
       </c>
       <c r="F2" t="n">
-        <v>-3994.63</v>
+        <v>-5221.72</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.034</v>
+        <v>-0.046</v>
       </c>
       <c r="H2" t="n">
-        <v>6553.62</v>
+        <v>6193.4</v>
       </c>
       <c r="I2" t="n">
-        <v>115963.27</v>
+        <v>104506.92</v>
       </c>
       <c r="J2" t="n">
-        <v>115894.52</v>
+        <v>106465.34</v>
       </c>
       <c r="K2" t="n">
-        <v>116794.94</v>
+        <v>110181.62</v>
       </c>
       <c r="L2" t="n">
-        <v>117695.36</v>
+        <v>113897.89</v>
       </c>
       <c r="M2" t="n">
-        <v>118111.19</v>
+        <v>116735.24</v>
       </c>
       <c r="N2" t="n">
-        <v>118527.02</v>
+        <v>119572.59</v>
       </c>
       <c r="O2" t="n">
-        <v>119912.02</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>124167.8</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -710,140 +708,148 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>113456.9</v>
+        <v>108228.75</v>
       </c>
       <c r="C3" t="n">
-        <v>113637.84</v>
+        <v>113357.49</v>
       </c>
       <c r="D3" t="n">
-        <v>107444.45</v>
+        <v>107271.18</v>
       </c>
       <c r="E3" t="n">
-        <v>108236.71</v>
+        <v>111167.62</v>
       </c>
       <c r="F3" t="n">
-        <v>-5221.72</v>
+        <v>2930.91</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.046</v>
+        <v>0.0271</v>
       </c>
       <c r="H3" t="n">
-        <v>6193.4</v>
+        <v>6086.31</v>
       </c>
       <c r="I3" t="n">
-        <v>104506.92</v>
+        <v>101251.05</v>
       </c>
       <c r="J3" t="n">
-        <v>106465.34</v>
+        <v>100891.1</v>
       </c>
       <c r="K3" t="n">
-        <v>110181.62</v>
+        <v>105140.01</v>
       </c>
       <c r="L3" t="n">
-        <v>113897.89</v>
+        <v>109388.93</v>
       </c>
       <c r="M3" t="n">
-        <v>116735.24</v>
+        <v>111333.41</v>
       </c>
       <c r="N3" t="n">
-        <v>119572.59</v>
+        <v>113277.89</v>
       </c>
       <c r="O3" t="n">
-        <v>124167.8</v>
+        <v>119831.24</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="U3" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>108228.75</v>
+        <v>111163.02</v>
       </c>
       <c r="C4" t="n">
-        <v>113357.49</v>
+        <v>116769.38</v>
       </c>
       <c r="D4" t="n">
-        <v>107271.18</v>
+        <v>110630.61</v>
       </c>
       <c r="E4" t="n">
-        <v>111167.62</v>
+        <v>115407.66</v>
       </c>
       <c r="F4" t="n">
-        <v>2930.91</v>
+        <v>4240.04</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0271</v>
+        <v>0.0381</v>
       </c>
       <c r="H4" t="n">
-        <v>6086.31</v>
+        <v>6138.77</v>
       </c>
       <c r="I4" t="n">
-        <v>101251.05</v>
+        <v>101184.87</v>
       </c>
       <c r="J4" t="n">
-        <v>100891.1</v>
+        <v>105507.95</v>
       </c>
       <c r="K4" t="n">
-        <v>105140.01</v>
+        <v>108124.46</v>
       </c>
       <c r="L4" t="n">
-        <v>109388.93</v>
+        <v>110740.98</v>
       </c>
       <c r="M4" t="n">
-        <v>111333.41</v>
+        <v>114210.77</v>
       </c>
       <c r="N4" t="n">
-        <v>113277.89</v>
+        <v>117680.57</v>
       </c>
       <c r="O4" t="n">
-        <v>119831.24</v>
+        <v>119443.8</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -864,72 +870,66 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>111163.02</v>
+        <v>115399.63</v>
       </c>
       <c r="C5" t="n">
-        <v>116769.38</v>
+        <v>117911.79</v>
       </c>
       <c r="D5" t="n">
-        <v>110630.61</v>
+        <v>114461.06</v>
       </c>
       <c r="E5" t="n">
-        <v>115407.66</v>
+        <v>115306.09</v>
       </c>
       <c r="F5" t="n">
-        <v>4240.04</v>
+        <v>-101.56</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0381</v>
+        <v>-0.0009</v>
       </c>
       <c r="H5" t="n">
-        <v>6138.77</v>
+        <v>3450.73</v>
       </c>
       <c r="I5" t="n">
-        <v>101184.87</v>
+        <v>104491.84</v>
       </c>
       <c r="J5" t="n">
-        <v>105507.95</v>
+        <v>110122.71</v>
       </c>
       <c r="K5" t="n">
-        <v>108124.46</v>
+        <v>112338.27</v>
       </c>
       <c r="L5" t="n">
-        <v>110740.98</v>
+        <v>114553.83</v>
       </c>
       <c r="M5" t="n">
-        <v>114210.77</v>
+        <v>118477.04</v>
       </c>
       <c r="N5" t="n">
-        <v>117680.57</v>
+        <v>122400.26</v>
       </c>
       <c r="O5" t="n">
-        <v>119443.8</v>
+        <v>122908.16</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -942,13 +942,11 @@
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -958,75 +956,81 @@
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>115399.63</v>
+        <v>115309.22</v>
       </c>
       <c r="C6" t="n">
-        <v>117911.79</v>
+        <v>115431.31</v>
       </c>
       <c r="D6" t="n">
-        <v>114461.06</v>
+        <v>108713.4</v>
       </c>
       <c r="E6" t="n">
-        <v>115306.09</v>
+        <v>112122.64</v>
       </c>
       <c r="F6" t="n">
-        <v>-101.56</v>
+        <v>-3183.45</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0276</v>
       </c>
       <c r="H6" t="n">
-        <v>3450.73</v>
+        <v>6717.91</v>
       </c>
       <c r="I6" t="n">
-        <v>104491.84</v>
+        <v>111010.34</v>
       </c>
       <c r="J6" t="n">
-        <v>110122.71</v>
+        <v>111415.2</v>
       </c>
       <c r="K6" t="n">
-        <v>112338.27</v>
+        <v>113580.73</v>
       </c>
       <c r="L6" t="n">
-        <v>114553.83</v>
+        <v>115746.26</v>
       </c>
       <c r="M6" t="n">
-        <v>118477.04</v>
+        <v>117031.46</v>
       </c>
       <c r="N6" t="n">
-        <v>122400.26</v>
+        <v>118316.65</v>
       </c>
       <c r="O6" t="n">
-        <v>122908.16</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>121362.52</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1040,95 +1044,95 @@
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>115309.22</v>
+        <v>112117.88</v>
       </c>
       <c r="C7" t="n">
-        <v>115431.31</v>
+        <v>125559.21</v>
       </c>
       <c r="D7" t="n">
-        <v>108713.4</v>
+        <v>111589.95</v>
       </c>
       <c r="E7" t="n">
-        <v>112122.64</v>
+        <v>123513.48</v>
       </c>
       <c r="F7" t="n">
-        <v>-3183.45</v>
+        <v>11390.84</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0276</v>
+        <v>0.1016</v>
       </c>
       <c r="H7" t="n">
-        <v>6717.91</v>
+        <v>13969.26</v>
       </c>
       <c r="I7" t="n">
-        <v>111010.34</v>
+        <v>101995.48</v>
       </c>
       <c r="J7" t="n">
-        <v>111415.2</v>
+        <v>105429.87</v>
       </c>
       <c r="K7" t="n">
-        <v>113580.73</v>
+        <v>108763.68</v>
       </c>
       <c r="L7" t="n">
-        <v>115746.26</v>
+        <v>112097.5</v>
       </c>
       <c r="M7" t="n">
-        <v>117031.46</v>
+        <v>115481.6</v>
       </c>
       <c r="N7" t="n">
-        <v>118316.65</v>
+        <v>118865.7</v>
       </c>
       <c r="O7" t="n">
-        <v>121362.52</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
+        <v>122149.23</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
-      </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1136,142 +1140,142 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>112117.88</v>
+        <v>123510.45</v>
       </c>
       <c r="C8" t="n">
-        <v>125559.21</v>
+        <v>126198.07</v>
       </c>
       <c r="D8" t="n">
-        <v>111589.95</v>
+        <v>104582.41</v>
       </c>
       <c r="E8" t="n">
-        <v>123513.48</v>
+        <v>115169.77</v>
       </c>
       <c r="F8" t="n">
-        <v>11390.84</v>
+        <v>-8343.709999999999</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.1016</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>13969.26</v>
+        <v>21615.66</v>
       </c>
       <c r="I8" t="n">
-        <v>101995.48</v>
+        <v>97620.7</v>
       </c>
       <c r="J8" t="n">
-        <v>105429.87</v>
+        <v>112013.67</v>
       </c>
       <c r="K8" t="n">
-        <v>108763.68</v>
+        <v>116528.85</v>
       </c>
       <c r="L8" t="n">
-        <v>112097.5</v>
+        <v>121044.03</v>
       </c>
       <c r="M8" t="n">
-        <v>115481.6</v>
+        <v>130498.11</v>
       </c>
       <c r="N8" t="n">
-        <v>118865.7</v>
+        <v>139952.18</v>
       </c>
       <c r="O8" t="n">
-        <v>122149.23</v>
+        <v>139528.47</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+      <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>123510.45</v>
+        <v>115161.68</v>
       </c>
       <c r="C9" t="n">
-        <v>126198.07</v>
+        <v>116020.48</v>
       </c>
       <c r="D9" t="n">
-        <v>104582.41</v>
+        <v>103598.43</v>
       </c>
       <c r="E9" t="n">
-        <v>115169.77</v>
+        <v>108666.71</v>
       </c>
       <c r="F9" t="n">
-        <v>-8343.709999999999</v>
+        <v>-6503.05</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0565</v>
       </c>
       <c r="H9" t="n">
-        <v>21615.66</v>
+        <v>12422.05</v>
       </c>
       <c r="I9" t="n">
-        <v>97620.7</v>
+        <v>82966.75999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>112013.67</v>
+        <v>93443.87</v>
       </c>
       <c r="K9" t="n">
-        <v>116528.85</v>
+        <v>104361.94</v>
       </c>
       <c r="L9" t="n">
-        <v>121044.03</v>
+        <v>115280</v>
       </c>
       <c r="M9" t="n">
-        <v>130498.11</v>
+        <v>125977.59</v>
       </c>
       <c r="N9" t="n">
-        <v>139952.18</v>
+        <v>136675.18</v>
       </c>
       <c r="O9" t="n">
-        <v>139528.47</v>
+        <v>147813.73</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q9" s="6" t="n">
+        <v/>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
@@ -1292,64 +1296,64 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>115161.68</v>
+        <v>108667.45</v>
       </c>
       <c r="C10" t="n">
-        <v>116020.48</v>
+        <v>115260.91</v>
       </c>
       <c r="D10" t="n">
-        <v>103598.43</v>
+        <v>106778</v>
       </c>
       <c r="E10" t="n">
-        <v>108666.71</v>
+        <v>114472.45</v>
       </c>
       <c r="F10" t="n">
-        <v>-6503.05</v>
+        <v>5805.73</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0565</v>
+        <v>0.0534</v>
       </c>
       <c r="H10" t="n">
-        <v>12422.05</v>
+        <v>8482.91</v>
       </c>
       <c r="I10" t="n">
-        <v>82966.75999999999</v>
+        <v>91176.38</v>
       </c>
       <c r="J10" t="n">
-        <v>93443.87</v>
+        <v>95673.28</v>
       </c>
       <c r="K10" t="n">
-        <v>104361.94</v>
+        <v>102455.68</v>
       </c>
       <c r="L10" t="n">
-        <v>115280</v>
+        <v>109238.08</v>
       </c>
       <c r="M10" t="n">
-        <v>125977.59</v>
+        <v>114877.74</v>
       </c>
       <c r="N10" t="n">
-        <v>136675.18</v>
+        <v>120517.39</v>
       </c>
       <c r="O10" t="n">
-        <v>147813.73</v>
+        <v>128442.54</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1357,167 +1361,169 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>108667.45</v>
+        <v>114479.85</v>
       </c>
       <c r="C11" t="n">
-        <v>115260.91</v>
+        <v>116273.31</v>
       </c>
       <c r="D11" t="n">
-        <v>106778</v>
+        <v>106376.69</v>
       </c>
       <c r="E11" t="n">
-        <v>114472.45</v>
+        <v>110639.62</v>
       </c>
       <c r="F11" t="n">
-        <v>5805.73</v>
+        <v>-3832.82</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0534</v>
+        <v>-0.0335</v>
       </c>
       <c r="H11" t="n">
-        <v>8482.91</v>
+        <v>9896.620000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>91176.38</v>
+        <v>98295.09</v>
       </c>
       <c r="J11" t="n">
-        <v>95673.28</v>
+        <v>107716.04</v>
       </c>
       <c r="K11" t="n">
-        <v>102455.68</v>
+        <v>110230.99</v>
       </c>
       <c r="L11" t="n">
-        <v>109238.08</v>
+        <v>112745.95</v>
       </c>
       <c r="M11" t="n">
-        <v>114877.74</v>
+        <v>118713.9</v>
       </c>
       <c r="N11" t="n">
-        <v>120517.39</v>
+        <v>124681.85</v>
       </c>
       <c r="O11" t="n">
-        <v>128442.54</v>
+        <v>123743.81</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>114479.85</v>
+        <v>110646.91</v>
       </c>
       <c r="C12" t="n">
-        <v>116273.31</v>
+        <v>110764.91</v>
       </c>
       <c r="D12" t="n">
-        <v>106376.69</v>
+        <v>98962.06</v>
       </c>
       <c r="E12" t="n">
-        <v>110639.62</v>
+        <v>104719.64</v>
       </c>
       <c r="F12" t="n">
-        <v>-3832.82</v>
+        <v>-5919.98</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0335</v>
+        <v>-0.0535</v>
       </c>
       <c r="H12" t="n">
-        <v>9896.620000000001</v>
+        <v>11802.85</v>
       </c>
       <c r="I12" t="n">
-        <v>98295.09</v>
+        <v>96480.06</v>
       </c>
       <c r="J12" t="n">
-        <v>107716.04</v>
+        <v>100400.31</v>
       </c>
       <c r="K12" t="n">
-        <v>110230.99</v>
+        <v>105691.31</v>
       </c>
       <c r="L12" t="n">
-        <v>112745.95</v>
+        <v>110982.31</v>
       </c>
       <c r="M12" t="n">
-        <v>118713.9</v>
+        <v>115587.94</v>
       </c>
       <c r="N12" t="n">
-        <v>124681.85</v>
+        <v>120193.56</v>
       </c>
       <c r="O12" t="n">
-        <v>123743.81</v>
+        <v>126169.94</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1546,78 +1552,78 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>110646.91</v>
+        <v>104723.77</v>
       </c>
       <c r="C13" t="n">
-        <v>110764.91</v>
+        <v>107428.26</v>
       </c>
       <c r="D13" t="n">
-        <v>98962.06</v>
+        <v>92971.16</v>
       </c>
       <c r="E13" t="n">
-        <v>104719.64</v>
+        <v>94177.08</v>
       </c>
       <c r="F13" t="n">
-        <v>-5919.98</v>
+        <v>-10542.56</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0535</v>
+        <v>-0.1007</v>
       </c>
       <c r="H13" t="n">
-        <v>11802.85</v>
+        <v>14457.09</v>
       </c>
       <c r="I13" t="n">
-        <v>96480.06</v>
+        <v>87159.21000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>100400.31</v>
+        <v>92844.87</v>
       </c>
       <c r="K13" t="n">
-        <v>105691.31</v>
+        <v>98818.21000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>110982.31</v>
+        <v>104791.56</v>
       </c>
       <c r="M13" t="n">
-        <v>115587.94</v>
+        <v>110621.07</v>
       </c>
       <c r="N13" t="n">
-        <v>120193.56</v>
+        <v>116450.57</v>
       </c>
       <c r="O13" t="n">
-        <v>126169.94</v>
+        <v>122567.77</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1632,7 +1638,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1646,64 +1652,62 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>104723.77</v>
+        <v>94180.88</v>
       </c>
       <c r="C14" t="n">
-        <v>107428.26</v>
+        <v>95928.37</v>
       </c>
       <c r="D14" t="n">
-        <v>92971.16</v>
+        <v>80659.81</v>
       </c>
       <c r="E14" t="n">
-        <v>94177.08</v>
+        <v>86805.00999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-10542.56</v>
+        <v>-7372.07</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.1007</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>14457.09</v>
+        <v>15268.55</v>
       </c>
       <c r="I14" t="n">
-        <v>87159.21000000001</v>
+        <v>78514.07000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>92844.87</v>
+        <v>76708.67</v>
       </c>
       <c r="K14" t="n">
-        <v>98818.21000000001</v>
+        <v>86948.53</v>
       </c>
       <c r="L14" t="n">
-        <v>104791.56</v>
+        <v>97188.39</v>
       </c>
       <c r="M14" t="n">
-        <v>110621.07</v>
+        <v>101405.62</v>
       </c>
       <c r="N14" t="n">
-        <v>116450.57</v>
+        <v>105622.86</v>
       </c>
       <c r="O14" t="n">
-        <v>122567.77</v>
+        <v>121885.35</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1718,7 +1722,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1732,50 +1736,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>94180.88</v>
+        <v>86798.77</v>
       </c>
       <c r="C15" t="n">
-        <v>95928.37</v>
+        <v>92969.09</v>
       </c>
       <c r="D15" t="n">
-        <v>80659.81</v>
+        <v>85272.2</v>
       </c>
       <c r="E15" t="n">
-        <v>86805.00999999999</v>
+        <v>90394.31</v>
       </c>
       <c r="F15" t="n">
-        <v>-7372.07</v>
+        <v>3589.3</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.0413</v>
       </c>
       <c r="H15" t="n">
-        <v>15268.55</v>
+        <v>7696.89</v>
       </c>
       <c r="I15" t="n">
-        <v>78514.07000000001</v>
+        <v>65391.26</v>
       </c>
       <c r="J15" t="n">
-        <v>76708.67</v>
+        <v>70791.91</v>
       </c>
       <c r="K15" t="n">
-        <v>86948.53</v>
+        <v>79170.73</v>
       </c>
       <c r="L15" t="n">
-        <v>97188.39</v>
+        <v>87549.55</v>
       </c>
       <c r="M15" t="n">
-        <v>101405.62</v>
+        <v>94439.28999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>105622.86</v>
+        <v>101329.02</v>
       </c>
       <c r="O15" t="n">
-        <v>121885.35</v>
+        <v>111196.92</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1783,14 +1787,12 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1802,64 +1804,64 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>86798.77</v>
+        <v>90389.11</v>
       </c>
       <c r="C16" t="n">
-        <v>92969.09</v>
+        <v>94060.77</v>
       </c>
       <c r="D16" t="n">
-        <v>85272.2</v>
+        <v>83862.25</v>
       </c>
       <c r="E16" t="n">
-        <v>90394.31</v>
+        <v>90405.64</v>
       </c>
       <c r="F16" t="n">
-        <v>3589.3</v>
+        <v>11.33</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0413</v>
+        <v>0.0001</v>
       </c>
       <c r="H16" t="n">
-        <v>7696.89</v>
+        <v>10198.52</v>
       </c>
       <c r="I16" t="n">
-        <v>65391.26</v>
+        <v>77575.3</v>
       </c>
       <c r="J16" t="n">
-        <v>70791.91</v>
+        <v>83334.25999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>79170.73</v>
+        <v>86545.87</v>
       </c>
       <c r="L16" t="n">
-        <v>87549.55</v>
+        <v>89757.48</v>
       </c>
       <c r="M16" t="n">
-        <v>94439.28999999999</v>
+        <v>94242.75999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>101329.02</v>
+        <v>98728.03999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>111196.92</v>
+        <v>100665.98</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1867,8 +1869,10 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
@@ -1884,7 +1888,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1898,50 +1902,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>90389.11</v>
+        <v>90424.59</v>
       </c>
       <c r="C17" t="n">
-        <v>94060.77</v>
+        <v>94601.57000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>83862.25</v>
+        <v>87634.94</v>
       </c>
       <c r="E17" t="n">
-        <v>90405.64</v>
+        <v>88175.17999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>11.33</v>
+        <v>-2230.46</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0247</v>
       </c>
       <c r="H17" t="n">
-        <v>10198.52</v>
+        <v>6966.63</v>
       </c>
       <c r="I17" t="n">
-        <v>77575.3</v>
+        <v>73663.73</v>
       </c>
       <c r="J17" t="n">
-        <v>83334.25999999999</v>
+        <v>80929.17999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>86545.87</v>
+        <v>85306.38</v>
       </c>
       <c r="L17" t="n">
-        <v>89757.48</v>
+        <v>89683.58</v>
       </c>
       <c r="M17" t="n">
-        <v>94242.75999999999</v>
+        <v>95504.89999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>98728.03999999999</v>
+        <v>101326.23</v>
       </c>
       <c r="O17" t="n">
-        <v>100665.98</v>
+        <v>104259.3</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1949,14 +1953,12 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1968,7 +1970,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1982,50 +1984,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>90424.59</v>
+        <v>88171.08</v>
       </c>
       <c r="C18" t="n">
-        <v>94601.57000000001</v>
+        <v>90264.57000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>87634.94</v>
+        <v>84436.31</v>
       </c>
       <c r="E18" t="n">
-        <v>88175.17999999999</v>
+        <v>88621.75</v>
       </c>
       <c r="F18" t="n">
-        <v>-2230.46</v>
+        <v>446.57</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0051</v>
       </c>
       <c r="H18" t="n">
-        <v>6966.63</v>
+        <v>5828.26</v>
       </c>
       <c r="I18" t="n">
-        <v>73663.73</v>
+        <v>80668.3</v>
       </c>
       <c r="J18" t="n">
-        <v>80929.17999999999</v>
+        <v>79737.00999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>85306.38</v>
+        <v>84691.86</v>
       </c>
       <c r="L18" t="n">
-        <v>89683.58</v>
+        <v>89646.72</v>
       </c>
       <c r="M18" t="n">
-        <v>95504.89999999999</v>
+        <v>91658.5</v>
       </c>
       <c r="N18" t="n">
-        <v>101326.23</v>
+        <v>93670.28</v>
       </c>
       <c r="O18" t="n">
-        <v>104259.3</v>
+        <v>101568.2</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2033,8 +2035,10 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
@@ -2050,64 +2054,64 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>88171.08</v>
+        <v>88621.39999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>90264.57000000001</v>
+        <v>90501.92999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>84436.31</v>
+        <v>86411.8</v>
       </c>
       <c r="E19" t="n">
-        <v>88621.75</v>
+        <v>87835.84</v>
       </c>
       <c r="F19" t="n">
-        <v>446.57</v>
+        <v>-785.91</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0051</v>
+        <v>-0.0089</v>
       </c>
       <c r="H19" t="n">
-        <v>5828.26</v>
+        <v>4090.13</v>
       </c>
       <c r="I19" t="n">
-        <v>80668.3</v>
+        <v>78608.05</v>
       </c>
       <c r="J19" t="n">
-        <v>79737.00999999999</v>
+        <v>83429.14999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>84691.86</v>
+        <v>85707.62</v>
       </c>
       <c r="L19" t="n">
-        <v>89646.72</v>
+        <v>87986.10000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>91658.5</v>
+        <v>91535.88</v>
       </c>
       <c r="N19" t="n">
-        <v>93670.28</v>
+        <v>95085.66</v>
       </c>
       <c r="O19" t="n">
-        <v>101568.2</v>
+        <v>96092.83</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2115,10 +2119,8 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R19" s="6" t="n">
+        <v/>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
@@ -2134,64 +2136,64 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>88621.39999999999</v>
+        <v>87835.78999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>90501.92999999999</v>
+        <v>91712.59</v>
       </c>
       <c r="D20" t="n">
-        <v>86411.8</v>
+        <v>86717.91</v>
       </c>
       <c r="E20" t="n">
-        <v>87835.84</v>
+        <v>91413.49000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-785.91</v>
+        <v>3577.66</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0089</v>
+        <v>0.0407</v>
       </c>
       <c r="H20" t="n">
-        <v>4090.13</v>
+        <v>4994.67</v>
       </c>
       <c r="I20" t="n">
-        <v>78608.05</v>
+        <v>82321.66</v>
       </c>
       <c r="J20" t="n">
-        <v>83429.14999999999</v>
+        <v>83435.19</v>
       </c>
       <c r="K20" t="n">
-        <v>85707.62</v>
+        <v>85790.77</v>
       </c>
       <c r="L20" t="n">
-        <v>87986.10000000001</v>
+        <v>88146.35000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>91535.88</v>
+        <v>89880.89999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>95085.66</v>
+        <v>91615.46000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>96092.83</v>
+        <v>94592.06</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2202,78 +2204,78 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>87835.78999999999</v>
+        <v>91414.62</v>
       </c>
       <c r="C21" t="n">
-        <v>91712.59</v>
+        <v>94762.07000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>86717.91</v>
+        <v>89233.88</v>
       </c>
       <c r="E21" t="n">
-        <v>91413.49000000001</v>
+        <v>90827.46000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>3577.66</v>
+        <v>-586.03</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0407</v>
+        <v>-0.0064</v>
       </c>
       <c r="H21" t="n">
-        <v>4994.67</v>
+        <v>5528.2</v>
       </c>
       <c r="I21" t="n">
-        <v>82321.66</v>
+        <v>81723.24000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>83435.19</v>
+        <v>87517.94</v>
       </c>
       <c r="K21" t="n">
-        <v>85790.77</v>
+        <v>88916.16</v>
       </c>
       <c r="L21" t="n">
-        <v>88146.35000000001</v>
+        <v>90314.37</v>
       </c>
       <c r="M21" t="n">
-        <v>89880.89999999999</v>
+        <v>93910.83</v>
       </c>
       <c r="N21" t="n">
-        <v>91615.46000000001</v>
+        <v>97507.28999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>94592.06</v>
+        <v>96707.25999999999</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2286,7 +2288,7 @@
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2294,68 +2296,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>91414.62</v>
+        <v>90825.86</v>
       </c>
       <c r="C22" t="n">
-        <v>94762.07000000001</v>
+        <v>97860.60000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>89233.88</v>
+        <v>90055.02</v>
       </c>
       <c r="E22" t="n">
-        <v>90827.46000000001</v>
+        <v>93634.42999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-586.03</v>
+        <v>2806.97</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0064</v>
+        <v>0.0309</v>
       </c>
       <c r="H22" t="n">
-        <v>5528.2</v>
+        <v>7805.58</v>
       </c>
       <c r="I22" t="n">
-        <v>81723.24000000001</v>
+        <v>83705.67999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>87517.94</v>
+        <v>84714.00999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>88916.16</v>
+        <v>88063.36</v>
       </c>
       <c r="L22" t="n">
-        <v>90314.37</v>
+        <v>91412.72</v>
       </c>
       <c r="M22" t="n">
-        <v>93910.83</v>
+        <v>93591.56</v>
       </c>
       <c r="N22" t="n">
-        <v>97507.28999999999</v>
+        <v>95770.39999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>96707.25999999999</v>
+        <v>100290.27</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2368,163 +2372,167 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>90825.86</v>
+        <v>93655.67</v>
       </c>
       <c r="C23" t="n">
-        <v>97860.60000000001</v>
+        <v>93660.83</v>
       </c>
       <c r="D23" t="n">
-        <v>90055.02</v>
+        <v>86003.71000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>93634.42999999999</v>
+        <v>86572.22</v>
       </c>
       <c r="F23" t="n">
-        <v>2806.97</v>
+        <v>-7062.21</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0309</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>7805.58</v>
+        <v>7657.12</v>
       </c>
       <c r="I23" t="n">
-        <v>83705.67999999999</v>
+        <v>82249.45</v>
       </c>
       <c r="J23" t="n">
-        <v>84714.00999999999</v>
+        <v>85667.16</v>
       </c>
       <c r="K23" t="n">
-        <v>88063.36</v>
+        <v>89731.64</v>
       </c>
       <c r="L23" t="n">
-        <v>91412.72</v>
+        <v>93796.12</v>
       </c>
       <c r="M23" t="n">
-        <v>93591.56</v>
+        <v>97537.22</v>
       </c>
       <c r="N23" t="n">
-        <v>95770.39999999999</v>
+        <v>101278.32</v>
       </c>
       <c r="O23" t="n">
-        <v>100290.27</v>
+        <v>105666.18</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
+      <c r="Q23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U23" s="8" t="inlineStr">
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>93655.67</v>
+        <v>86566.52</v>
       </c>
       <c r="C24" t="n">
-        <v>93660.83</v>
+        <v>90439.28999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>86003.71000000001</v>
+        <v>75698.89999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>86572.22</v>
+        <v>76974.45</v>
       </c>
       <c r="F24" t="n">
-        <v>-7062.21</v>
+        <v>-9597.77</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.1109</v>
       </c>
       <c r="H24" t="n">
-        <v>7657.12</v>
+        <v>14740.39</v>
       </c>
       <c r="I24" t="n">
-        <v>82249.45</v>
+        <v>78346.59</v>
       </c>
       <c r="J24" t="n">
-        <v>85667.16</v>
+        <v>77285.08</v>
       </c>
       <c r="K24" t="n">
-        <v>89731.64</v>
+        <v>82743.66</v>
       </c>
       <c r="L24" t="n">
-        <v>93796.12</v>
+        <v>88202.24000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>97537.22</v>
+        <v>90400.78</v>
       </c>
       <c r="N24" t="n">
-        <v>101278.32</v>
+        <v>92599.31</v>
       </c>
       <c r="O24" t="n">
-        <v>105666.18</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
+        <v>101317.95</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q24" s="6" t="inlineStr">
         <is>
@@ -2541,8 +2549,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2552,87 +2562,79 @@
       </c>
       <c r="W24" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>86566.52</v>
+        <v>76968.88</v>
       </c>
       <c r="C25" t="n">
-        <v>90439.28999999999</v>
+        <v>79258.61</v>
       </c>
       <c r="D25" t="n">
-        <v>75698.89999999999</v>
+        <v>60074.2</v>
       </c>
       <c r="E25" t="n">
-        <v>76974.45</v>
+        <v>70264.73</v>
       </c>
       <c r="F25" t="n">
-        <v>-9597.77</v>
+        <v>-6709.72</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.1109</v>
+        <v>-0.0872</v>
       </c>
       <c r="H25" t="n">
-        <v>14740.39</v>
+        <v>19184.41</v>
       </c>
       <c r="I25" t="n">
-        <v>78346.59</v>
+        <v>60958.51</v>
       </c>
       <c r="J25" t="n">
-        <v>77285.08</v>
+        <v>59186.73</v>
       </c>
       <c r="K25" t="n">
-        <v>82743.66</v>
+        <v>69604.25</v>
       </c>
       <c r="L25" t="n">
-        <v>88202.24000000001</v>
+        <v>80021.77</v>
       </c>
       <c r="M25" t="n">
-        <v>90400.78</v>
+        <v>84344.64</v>
       </c>
       <c r="N25" t="n">
-        <v>92599.31</v>
+        <v>88667.50999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>101317.95</v>
+        <v>105179.68</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2640,7 +2642,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2650,67 +2652,63 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>76968.88</v>
+        <v>70243.33</v>
       </c>
       <c r="C26" t="n">
-        <v>79258.61</v>
+        <v>71369.97</v>
       </c>
       <c r="D26" t="n">
-        <v>60074.2</v>
+        <v>65092.11</v>
       </c>
       <c r="E26" t="n">
-        <v>70264.73</v>
+        <v>68788.19</v>
       </c>
       <c r="F26" t="n">
-        <v>-6709.72</v>
+        <v>-1476.54</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0872</v>
+        <v>-0.021</v>
       </c>
       <c r="H26" t="n">
-        <v>19184.41</v>
+        <v>6277.86</v>
       </c>
       <c r="I26" t="n">
-        <v>60958.51</v>
+        <v>40889.8</v>
       </c>
       <c r="J26" t="n">
-        <v>59186.73</v>
+        <v>51379.48</v>
       </c>
       <c r="K26" t="n">
-        <v>69604.25</v>
+        <v>60672.52</v>
       </c>
       <c r="L26" t="n">
-        <v>80021.77</v>
+        <v>69965.57000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>84344.64</v>
+        <v>79856.92999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>88667.50999999999</v>
+        <v>89748.28999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>105179.68</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>98443.02</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
       </c>
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2722,60 +2720,64 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>70243.33</v>
+        <v>68782.39999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>71369.97</v>
+        <v>70067.23</v>
       </c>
       <c r="D27" t="n">
-        <v>65092.11</v>
+        <v>65637.42999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>68788.19</v>
+        <v>67659.39</v>
       </c>
       <c r="F27" t="n">
-        <v>-1476.54</v>
+        <v>-1128.8</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.021</v>
+        <v>-0.0164</v>
       </c>
       <c r="H27" t="n">
-        <v>6277.86</v>
+        <v>4429.8</v>
       </c>
       <c r="I27" t="n">
-        <v>40889.8</v>
+        <v>58814.25</v>
       </c>
       <c r="J27" t="n">
-        <v>51379.48</v>
+        <v>62788.9</v>
       </c>
       <c r="K27" t="n">
-        <v>60672.52</v>
+        <v>65649.25999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>69965.57000000001</v>
+        <v>68509.61</v>
       </c>
       <c r="M27" t="n">
-        <v>79856.92999999999</v>
+        <v>71927.12</v>
       </c>
       <c r="N27" t="n">
-        <v>89748.28999999999</v>
+        <v>75344.62</v>
       </c>
       <c r="O27" t="n">
-        <v>98443.02</v>
+        <v>77647.83</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2783,8 +2785,10 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
@@ -2800,7 +2804,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2814,218 +2818,220 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>68782.39999999999</v>
+        <v>67668.42999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>70067.23</v>
+        <v>69953.53</v>
       </c>
       <c r="D28" t="n">
-        <v>65637.42999999999</v>
+        <v>62553.19</v>
       </c>
       <c r="E28" t="n">
-        <v>67659.39</v>
+        <v>65738.10000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-1128.8</v>
+        <v>-1921.29</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0164</v>
+        <v>-0.0284</v>
       </c>
       <c r="H28" t="n">
-        <v>4429.8</v>
+        <v>7400.34</v>
       </c>
       <c r="I28" t="n">
-        <v>58814.25</v>
+        <v>61207.62</v>
       </c>
       <c r="J28" t="n">
-        <v>62788.9</v>
+        <v>63133.12</v>
       </c>
       <c r="K28" t="n">
-        <v>65649.25999999999</v>
+        <v>65444.49</v>
       </c>
       <c r="L28" t="n">
-        <v>68509.61</v>
+        <v>67755.86</v>
       </c>
       <c r="M28" t="n">
-        <v>71927.12</v>
+        <v>69874.28999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>75344.62</v>
+        <v>71992.72</v>
       </c>
       <c r="O28" t="n">
-        <v>77647.83</v>
+        <v>74497.03999999999</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>67668.42999999999</v>
+        <v>65734.08</v>
       </c>
       <c r="C29" t="n">
-        <v>69953.53</v>
+        <v>74051.8</v>
       </c>
       <c r="D29" t="n">
-        <v>62553.19</v>
+        <v>65303.14</v>
       </c>
       <c r="E29" t="n">
-        <v>65738.10000000001</v>
+        <v>65969.78</v>
       </c>
       <c r="F29" t="n">
-        <v>-1921.29</v>
+        <v>231.68</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0284</v>
+        <v>0.0035</v>
       </c>
       <c r="H29" t="n">
-        <v>7400.34</v>
+        <v>8748.67</v>
       </c>
       <c r="I29" t="n">
-        <v>61207.62</v>
+        <v>55152.84</v>
       </c>
       <c r="J29" t="n">
-        <v>63133.12</v>
+        <v>58080.13</v>
       </c>
       <c r="K29" t="n">
-        <v>65444.49</v>
+        <v>62037.93</v>
       </c>
       <c r="L29" t="n">
-        <v>67755.86</v>
+        <v>65995.73</v>
       </c>
       <c r="M29" t="n">
-        <v>69874.28999999999</v>
+        <v>69438.27</v>
       </c>
       <c r="N29" t="n">
-        <v>71992.72</v>
+        <v>72880.82000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>74497.03999999999</v>
+        <v>77353.88</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>65734.08</v>
+        <v>65969.59</v>
       </c>
       <c r="C30" t="n">
-        <v>74051.8</v>
+        <v>73927.33</v>
       </c>
       <c r="D30" t="n">
-        <v>65303.14</v>
+        <v>65858.00999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>65969.78</v>
+        <v>72789.91</v>
       </c>
       <c r="F30" t="n">
-        <v>231.68</v>
+        <v>6820.13</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.1034</v>
       </c>
       <c r="H30" t="n">
-        <v>8748.67</v>
+        <v>8069.32</v>
       </c>
       <c r="I30" t="n">
-        <v>55152.84</v>
+        <v>56554.47</v>
       </c>
       <c r="J30" t="n">
-        <v>58080.13</v>
+        <v>55367.27</v>
       </c>
       <c r="K30" t="n">
-        <v>62037.93</v>
+        <v>61595.45</v>
       </c>
       <c r="L30" t="n">
-        <v>65995.73</v>
+        <v>67823.63</v>
       </c>
       <c r="M30" t="n">
-        <v>69438.27</v>
+        <v>70344.12</v>
       </c>
       <c r="N30" t="n">
-        <v>72880.82000000001</v>
+        <v>72864.60000000001</v>
       </c>
       <c r="O30" t="n">
-        <v>77353.88</v>
+        <v>82800.47</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3036,9 +3042,9 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -3048,70 +3054,70 @@
       </c>
       <c r="U30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>65969.59</v>
+        <v>72798.17</v>
       </c>
       <c r="C31" t="n">
-        <v>73927.33</v>
+        <v>75988.39999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>65858.00999999999</v>
+        <v>67372.88</v>
       </c>
       <c r="E31" t="n">
-        <v>72789.91</v>
+        <v>67845.21000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>6820.13</v>
+        <v>-4944.7</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.1034</v>
+        <v>-0.0679</v>
       </c>
       <c r="H31" t="n">
-        <v>8069.32</v>
+        <v>8615.52</v>
       </c>
       <c r="I31" t="n">
-        <v>56554.47</v>
+        <v>57788.69</v>
       </c>
       <c r="J31" t="n">
-        <v>55367.27</v>
+        <v>66169.22</v>
       </c>
       <c r="K31" t="n">
-        <v>61595.45</v>
+        <v>68755.25</v>
       </c>
       <c r="L31" t="n">
-        <v>67823.63</v>
+        <v>71341.28999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>70344.12</v>
+        <v>76824.57000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>72864.60000000001</v>
+        <v>82307.86</v>
       </c>
       <c r="O31" t="n">
-        <v>82800.47</v>
+        <v>81996.64999999999</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3119,28 +3125,26 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3154,50 +3158,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>72798.17</v>
+        <v>67843</v>
       </c>
       <c r="C32" t="n">
-        <v>75988.39999999999</v>
+        <v>71985.74000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>67372.88</v>
+        <v>64971.71</v>
       </c>
       <c r="E32" t="n">
-        <v>67845.21000000001</v>
+        <v>65954.92</v>
       </c>
       <c r="F32" t="n">
-        <v>-4944.7</v>
+        <v>-1890.29</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0679</v>
+        <v>-0.0279</v>
       </c>
       <c r="H32" t="n">
-        <v>8615.52</v>
+        <v>7014.04</v>
       </c>
       <c r="I32" t="n">
-        <v>57788.69</v>
+        <v>58757.35</v>
       </c>
       <c r="J32" t="n">
-        <v>66169.22</v>
+        <v>57311.97</v>
       </c>
       <c r="K32" t="n">
-        <v>68755.25</v>
+        <v>63537.45</v>
       </c>
       <c r="L32" t="n">
-        <v>71341.28999999999</v>
+        <v>69762.92</v>
       </c>
       <c r="M32" t="n">
-        <v>76824.57000000001</v>
+        <v>72152.97</v>
       </c>
       <c r="N32" t="n">
-        <v>82307.86</v>
+        <v>74543.02</v>
       </c>
       <c r="O32" t="n">
-        <v>81996.64999999999</v>
+        <v>84603.92</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3224,64 +3228,60 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>67843</v>
+        <v>65958.35000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>71985.74000000001</v>
+        <v>69230.36</v>
       </c>
       <c r="D33" t="n">
-        <v>64971.71</v>
+        <v>65725.25999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>65954.92</v>
+        <v>68981.89999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>-1890.29</v>
+        <v>3026.98</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0279</v>
+        <v>0.0459</v>
       </c>
       <c r="H33" t="n">
-        <v>7014.04</v>
+        <v>3505.1</v>
       </c>
       <c r="I33" t="n">
-        <v>58757.35</v>
+        <v>57957.67</v>
       </c>
       <c r="J33" t="n">
-        <v>57311.97</v>
+        <v>57678.99</v>
       </c>
       <c r="K33" t="n">
-        <v>63537.45</v>
+        <v>62447.9</v>
       </c>
       <c r="L33" t="n">
-        <v>69762.92</v>
+        <v>67216.82000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>72152.97</v>
+        <v>69461.94</v>
       </c>
       <c r="N33" t="n">
-        <v>74543.02</v>
+        <v>71707.06</v>
       </c>
       <c r="O33" t="n">
-        <v>84603.92</v>
+        <v>78999.78</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3289,79 +3289,83 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>65958.35000000001</v>
+        <v>68982.91</v>
       </c>
       <c r="C34" t="n">
-        <v>69230.36</v>
+        <v>73784.23</v>
       </c>
       <c r="D34" t="n">
-        <v>65725.25999999999</v>
+        <v>67740.50999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>68981.89999999999</v>
+        <v>70753.41</v>
       </c>
       <c r="F34" t="n">
-        <v>3026.98</v>
+        <v>1771.51</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0459</v>
+        <v>0.0257</v>
       </c>
       <c r="H34" t="n">
-        <v>3505.1</v>
+        <v>6043.73</v>
       </c>
       <c r="I34" t="n">
-        <v>57957.67</v>
+        <v>62220.16</v>
       </c>
       <c r="J34" t="n">
-        <v>57678.99</v>
+        <v>66228.84</v>
       </c>
       <c r="K34" t="n">
-        <v>62447.9</v>
+        <v>67229.35000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>67216.82000000001</v>
+        <v>68229.85000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>69461.94</v>
+        <v>70734.45</v>
       </c>
       <c r="N34" t="n">
-        <v>71707.06</v>
+        <v>73239.03999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>78999.78</v>
+        <v>72735.46000000001</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3382,70 +3386,74 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>68982.91</v>
+        <v>70757.62</v>
       </c>
       <c r="C35" t="n">
-        <v>73784.23</v>
+        <v>78320.67999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>67740.50999999999</v>
+        <v>70588.52</v>
       </c>
       <c r="E35" t="n">
-        <v>70753.41</v>
+        <v>73856.35000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>1771.51</v>
+        <v>3102.95</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0257</v>
+        <v>0.0439</v>
       </c>
       <c r="H35" t="n">
-        <v>6043.73</v>
+        <v>7732.16</v>
       </c>
       <c r="I35" t="n">
-        <v>62220.16</v>
+        <v>61696.78</v>
       </c>
       <c r="J35" t="n">
-        <v>66228.84</v>
+        <v>64705.2</v>
       </c>
       <c r="K35" t="n">
-        <v>67229.35000000001</v>
+        <v>67731.53999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>68229.85000000001</v>
+        <v>70757.89</v>
       </c>
       <c r="M35" t="n">
-        <v>70734.45</v>
+        <v>73775.27</v>
       </c>
       <c r="N35" t="n">
-        <v>73239.03999999999</v>
+        <v>76792.64999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>72735.46000000001</v>
+        <v>79827.96000000001</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3471,12 +3479,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3490,50 +3496,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>70757.62</v>
+        <v>73854.25</v>
       </c>
       <c r="C36" t="n">
-        <v>78320.67999999999</v>
+        <v>79468</v>
       </c>
       <c r="D36" t="n">
-        <v>70588.52</v>
+        <v>73775.57000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>73856.35000000001</v>
+        <v>78657.53999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>3102.95</v>
+        <v>4801.19</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0439</v>
+        <v>0.065</v>
       </c>
       <c r="H36" t="n">
-        <v>7732.16</v>
+        <v>5692.43</v>
       </c>
       <c r="I36" t="n">
-        <v>61696.78</v>
+        <v>62856.37</v>
       </c>
       <c r="J36" t="n">
-        <v>64705.2</v>
+        <v>65825.07000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>67731.53999999999</v>
+        <v>69990.27</v>
       </c>
       <c r="L36" t="n">
-        <v>70757.89</v>
+        <v>74155.48</v>
       </c>
       <c r="M36" t="n">
-        <v>73775.27</v>
+        <v>77722.42999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>76792.64999999999</v>
+        <v>81289.38</v>
       </c>
       <c r="O36" t="n">
-        <v>79827.96000000001</v>
+        <v>86052.84</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3554,15 +3560,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3576,50 +3580,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>73854.25</v>
+        <v>78661.02</v>
       </c>
       <c r="C37" t="n">
-        <v>79468</v>
+        <v>79488.17</v>
       </c>
       <c r="D37" t="n">
-        <v>73775.57000000001</v>
+        <v>74958.57000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>78657.53999999999</v>
+        <v>78538.23</v>
       </c>
       <c r="F37" t="n">
-        <v>4801.19</v>
+        <v>-119.31</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.065</v>
+        <v>-0.0015</v>
       </c>
       <c r="H37" t="n">
-        <v>5692.43</v>
+        <v>4529.6</v>
       </c>
       <c r="I37" t="n">
-        <v>62856.37</v>
+        <v>68083.14</v>
       </c>
       <c r="J37" t="n">
-        <v>65825.07000000001</v>
+        <v>73982.99000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>69990.27</v>
+        <v>75811.32000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>74155.48</v>
+        <v>77639.66</v>
       </c>
       <c r="M37" t="n">
-        <v>77722.42999999999</v>
+        <v>81503.75</v>
       </c>
       <c r="N37" t="n">
-        <v>81289.38</v>
+        <v>85367.85000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>86052.84</v>
+        <v>85160.42999999999</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3627,18 +3631,18 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3646,64 +3650,64 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>78661.02</v>
+        <v>78540.28999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>79488.17</v>
+        <v>82792.21000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>74958.57000000001</v>
+        <v>78217.96000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>78538.23</v>
+        <v>82138.92999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>-119.31</v>
+        <v>3600.7</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0458</v>
       </c>
       <c r="H38" t="n">
-        <v>4529.6</v>
+        <v>4574.25</v>
       </c>
       <c r="I38" t="n">
-        <v>68083.14</v>
+        <v>70428.97</v>
       </c>
       <c r="J38" t="n">
-        <v>73982.99000000001</v>
+        <v>74666.05</v>
       </c>
       <c r="K38" t="n">
-        <v>75811.32000000001</v>
+        <v>76273.42999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>77639.66</v>
+        <v>77880.8</v>
       </c>
       <c r="M38" t="n">
-        <v>81503.75</v>
+        <v>80803.03</v>
       </c>
       <c r="N38" t="n">
-        <v>85367.85000000001</v>
+        <v>83725.25999999999</v>
       </c>
       <c r="O38" t="n">
-        <v>85160.42999999999</v>
+        <v>84017.77</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3711,18 +3715,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3730,156 +3734,152 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>78540.28999999999</v>
+        <v>82139.05</v>
       </c>
       <c r="C39" t="n">
-        <v>82792.21000000001</v>
+        <v>82326.23</v>
       </c>
       <c r="D39" t="n">
-        <v>78217.96000000001</v>
+        <v>76783.41</v>
       </c>
       <c r="E39" t="n">
-        <v>82138.92999999999</v>
+        <v>77429.35000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>3600.7</v>
+        <v>-4709.58</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0458</v>
+        <v>-0.0573</v>
       </c>
       <c r="H39" t="n">
-        <v>4574.25</v>
+        <v>5542.82</v>
       </c>
       <c r="I39" t="n">
-        <v>70428.97</v>
+        <v>73643.71000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>74666.05</v>
+        <v>78381.60000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>76273.42999999999</v>
+        <v>79851.8</v>
       </c>
       <c r="L39" t="n">
-        <v>77880.8</v>
+        <v>81322.00999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>80803.03</v>
+        <v>84426.05</v>
       </c>
       <c r="N39" t="n">
-        <v>83725.25999999999</v>
+        <v>87530.10000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>84017.77</v>
+        <v>87366.46000000001</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+      <c r="Q39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>82139.05</v>
+        <v>77426.34</v>
       </c>
       <c r="C40" t="n">
-        <v>82326.23</v>
+        <v>78100.56</v>
       </c>
       <c r="D40" t="n">
-        <v>76783.41</v>
+        <v>74255.23</v>
       </c>
       <c r="E40" t="n">
-        <v>77429.35000000001</v>
+        <v>76981.12</v>
       </c>
       <c r="F40" t="n">
-        <v>-4709.58</v>
+        <v>-448.23</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0573</v>
+        <v>-0.0058</v>
       </c>
       <c r="H40" t="n">
-        <v>5542.82</v>
+        <v>3845.33</v>
       </c>
       <c r="I40" t="n">
-        <v>73643.71000000001</v>
+        <v>71240.59</v>
       </c>
       <c r="J40" t="n">
-        <v>78381.60000000001</v>
+        <v>70823.78999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>79851.8</v>
+        <v>74657.94</v>
       </c>
       <c r="L40" t="n">
-        <v>81322.00999999999</v>
+        <v>78492.09</v>
       </c>
       <c r="M40" t="n">
-        <v>84426.05</v>
+        <v>80200.75999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>87530.10000000001</v>
+        <v>81909.44</v>
       </c>
       <c r="O40" t="n">
-        <v>87366.46000000001</v>
+        <v>87869.05</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q40" s="6" t="n">
+        <v/>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3900,7 +3900,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3910,56 +3910,58 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>77426.34</v>
+        <v>76981.12</v>
       </c>
       <c r="C41" t="n">
-        <v>78100.56</v>
+        <v>77990.87</v>
       </c>
       <c r="D41" t="n">
-        <v>74255.23</v>
+        <v>72435.62</v>
       </c>
       <c r="E41" t="n">
-        <v>76981.12</v>
+        <v>73579.69</v>
       </c>
       <c r="F41" t="n">
-        <v>-448.23</v>
+        <v>-3401.44</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0442</v>
       </c>
       <c r="H41" t="n">
-        <v>3845.33</v>
+        <v>5555.24</v>
       </c>
       <c r="I41" t="n">
-        <v>71240.59</v>
+        <v>70409.91</v>
       </c>
       <c r="J41" t="n">
-        <v>70823.78999999999</v>
+        <v>73537.41</v>
       </c>
       <c r="K41" t="n">
-        <v>74657.94</v>
+        <v>75058.46000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>78492.09</v>
+        <v>76579.50999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>80200.75999999999</v>
+        <v>78903.78999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>81909.44</v>
+        <v>81228.07000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>87869.05</v>
+        <v>81945.89</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
@@ -3968,7 +3970,7 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3980,7 +3982,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3990,57 +3992,59 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>76981.12</v>
+        <v>73580.21000000001</v>
       </c>
       <c r="C42" t="n">
-        <v>77990.87</v>
+        <v>73969.57000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>72435.62</v>
+        <v>59108.92</v>
       </c>
       <c r="E42" t="n">
-        <v>73579.69</v>
+        <v>63239.52</v>
       </c>
       <c r="F42" t="n">
-        <v>-3401.44</v>
+        <v>-10340.17</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0442</v>
+        <v>-0.1405</v>
       </c>
       <c r="H42" t="n">
-        <v>5555.24</v>
+        <v>14860.65</v>
       </c>
       <c r="I42" t="n">
-        <v>70409.91</v>
+        <v>66880.38</v>
       </c>
       <c r="J42" t="n">
-        <v>73537.41</v>
+        <v>67207.67</v>
       </c>
       <c r="K42" t="n">
-        <v>75058.46000000001</v>
+        <v>70802.07000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>76579.50999999999</v>
+        <v>74396.47</v>
       </c>
       <c r="M42" t="n">
-        <v>78903.78999999999</v>
+        <v>76357.31</v>
       </c>
       <c r="N42" t="n">
-        <v>81228.07000000001</v>
+        <v>78318.14999999999</v>
       </c>
       <c r="O42" t="n">
-        <v>81945.89</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
+        <v>83546.11</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
@@ -4062,7 +4066,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4072,69 +4076,63 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>73580.21000000001</v>
+        <v>63244.09</v>
       </c>
       <c r="C43" t="n">
-        <v>73969.57000000001</v>
+        <v>65749.78</v>
       </c>
       <c r="D43" t="n">
-        <v>59108.92</v>
+        <v>60756.69</v>
       </c>
       <c r="E43" t="n">
-        <v>63239.52</v>
+        <v>65710.39999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>-10340.17</v>
+        <v>2470.88</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.1405</v>
+        <v>0.0391</v>
       </c>
       <c r="H43" t="n">
-        <v>14860.65</v>
+        <v>4993.09</v>
       </c>
       <c r="I43" t="n">
-        <v>66880.38</v>
+        <v>44248.27</v>
       </c>
       <c r="J43" t="n">
-        <v>67207.67</v>
+        <v>46729</v>
       </c>
       <c r="K43" t="n">
-        <v>70802.07000000001</v>
+        <v>55809.19</v>
       </c>
       <c r="L43" t="n">
-        <v>74396.47</v>
+        <v>64889.38</v>
       </c>
       <c r="M43" t="n">
-        <v>76357.31</v>
+        <v>70669.85000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>78318.14999999999</v>
+        <v>76450.31</v>
       </c>
       <c r="O43" t="n">
-        <v>83546.11</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>88830.22</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4146,60 +4144,64 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>63244.09</v>
+        <v>65711.11</v>
       </c>
       <c r="C44" t="n">
-        <v>65749.78</v>
+        <v>67248.13</v>
       </c>
       <c r="D44" t="n">
-        <v>60756.69</v>
+        <v>62201.14</v>
       </c>
       <c r="E44" t="n">
-        <v>65710.39999999999</v>
+        <v>63237.54</v>
       </c>
       <c r="F44" t="n">
-        <v>2470.88</v>
+        <v>-2472.86</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0391</v>
+        <v>-0.0376</v>
       </c>
       <c r="H44" t="n">
-        <v>4993.09</v>
+        <v>5046.99</v>
       </c>
       <c r="I44" t="n">
-        <v>44248.27</v>
+        <v>55763.59</v>
       </c>
       <c r="J44" t="n">
-        <v>46729</v>
+        <v>61945.89</v>
       </c>
       <c r="K44" t="n">
-        <v>55809.19</v>
+        <v>63213.85</v>
       </c>
       <c r="L44" t="n">
-        <v>64889.38</v>
+        <v>64481.82</v>
       </c>
       <c r="M44" t="n">
-        <v>70669.85000000001</v>
+        <v>68206.95</v>
       </c>
       <c r="N44" t="n">
-        <v>76450.31</v>
+        <v>71932.07000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>88830.22</v>
+        <v>70742.88</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4207,12 +4209,14 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4224,7 +4228,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4238,50 +4242,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>65711.11</v>
+        <v>63240.79</v>
       </c>
       <c r="C45" t="n">
-        <v>67248.13</v>
+        <v>65544</v>
       </c>
       <c r="D45" t="n">
-        <v>62201.14</v>
+        <v>58075.92</v>
       </c>
       <c r="E45" t="n">
-        <v>63237.54</v>
+        <v>59532.34</v>
       </c>
       <c r="F45" t="n">
-        <v>-2472.86</v>
+        <v>-3705.2</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0376</v>
+        <v>-0.0586</v>
       </c>
       <c r="H45" t="n">
-        <v>5046.99</v>
+        <v>7468.08</v>
       </c>
       <c r="I45" t="n">
-        <v>55763.59</v>
+        <v>57154.16</v>
       </c>
       <c r="J45" t="n">
-        <v>61945.89</v>
+        <v>57447</v>
       </c>
       <c r="K45" t="n">
-        <v>63213.85</v>
+        <v>60714.04</v>
       </c>
       <c r="L45" t="n">
-        <v>64481.82</v>
+        <v>63981.09</v>
       </c>
       <c r="M45" t="n">
-        <v>68206.95</v>
+        <v>65761.03</v>
       </c>
       <c r="N45" t="n">
-        <v>71932.07000000001</v>
+        <v>67540.98</v>
       </c>
       <c r="O45" t="n">
-        <v>70742.88</v>
+        <v>72295.12</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4308,64 +4312,60 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>63240.79</v>
+        <v>59522.79</v>
       </c>
       <c r="C46" t="n">
-        <v>65544</v>
+        <v>63935.85</v>
       </c>
       <c r="D46" t="n">
-        <v>58075.92</v>
+        <v>57747.77</v>
       </c>
       <c r="E46" t="n">
-        <v>59532.34</v>
+        <v>63547.88</v>
       </c>
       <c r="F46" t="n">
-        <v>-3705.2</v>
+        <v>4015.54</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0586</v>
+        <v>0.0675</v>
       </c>
       <c r="H46" t="n">
-        <v>7468.08</v>
+        <v>6188.08</v>
       </c>
       <c r="I46" t="n">
-        <v>57154.16</v>
+        <v>50607.84</v>
       </c>
       <c r="J46" t="n">
-        <v>57447</v>
+        <v>50925.45</v>
       </c>
       <c r="K46" t="n">
-        <v>60714.04</v>
+        <v>55798.3</v>
       </c>
       <c r="L46" t="n">
-        <v>63981.09</v>
+        <v>60671.15</v>
       </c>
       <c r="M46" t="n">
-        <v>65761.03</v>
+        <v>63266.38</v>
       </c>
       <c r="N46" t="n">
-        <v>67540.98</v>
+        <v>65861.61</v>
       </c>
       <c r="O46" t="n">
-        <v>72295.12</v>
+        <v>73012.08</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4373,79 +4373,83 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>59522.79</v>
+        <v>63551.02</v>
       </c>
       <c r="C47" t="n">
-        <v>63935.85</v>
+        <v>64658.97</v>
       </c>
       <c r="D47" t="n">
-        <v>57747.77</v>
+        <v>61275.83</v>
       </c>
       <c r="E47" t="n">
-        <v>63547.88</v>
+        <v>63758.22</v>
       </c>
       <c r="F47" t="n">
-        <v>4015.54</v>
+        <v>210.34</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0675</v>
+        <v>0.0033</v>
       </c>
       <c r="H47" t="n">
-        <v>6188.08</v>
+        <v>3383.14</v>
       </c>
       <c r="I47" t="n">
-        <v>50607.84</v>
+        <v>51559.68</v>
       </c>
       <c r="J47" t="n">
-        <v>50925.45</v>
+        <v>58712.84</v>
       </c>
       <c r="K47" t="n">
-        <v>55798.3</v>
+        <v>60453.84</v>
       </c>
       <c r="L47" t="n">
-        <v>60671.15</v>
+        <v>62194.84</v>
       </c>
       <c r="M47" t="n">
-        <v>63266.38</v>
+        <v>66641.92</v>
       </c>
       <c r="N47" t="n">
-        <v>65861.61</v>
+        <v>71089</v>
       </c>
       <c r="O47" t="n">
-        <v>73012.08</v>
+        <v>70123.92999999999</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4458,13 +4462,11 @@
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4472,64 +4474,64 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>63551.02</v>
+        <v>63757.17</v>
       </c>
       <c r="C48" t="n">
-        <v>64658.97</v>
+        <v>65507.59</v>
       </c>
       <c r="D48" t="n">
-        <v>61275.83</v>
+        <v>61769</v>
       </c>
       <c r="E48" t="n">
-        <v>63758.22</v>
+        <v>64690.8</v>
       </c>
       <c r="F48" t="n">
-        <v>210.34</v>
+        <v>932.59</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0146</v>
       </c>
       <c r="H48" t="n">
-        <v>3383.14</v>
+        <v>3738.59</v>
       </c>
       <c r="I48" t="n">
-        <v>51559.68</v>
+        <v>57892.69</v>
       </c>
       <c r="J48" t="n">
-        <v>58712.84</v>
+        <v>60770.49</v>
       </c>
       <c r="K48" t="n">
-        <v>60453.84</v>
+        <v>62066.65</v>
       </c>
       <c r="L48" t="n">
-        <v>62194.84</v>
+        <v>63362.81</v>
       </c>
       <c r="M48" t="n">
-        <v>66641.92</v>
+        <v>65449.79</v>
       </c>
       <c r="N48" t="n">
-        <v>71089</v>
+        <v>67536.77</v>
       </c>
       <c r="O48" t="n">
-        <v>70123.92999999999</v>
+        <v>68042.11</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4537,16 +4539,20 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4554,7 +4560,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4568,50 +4574,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>63757.17</v>
+        <v>64684.42</v>
       </c>
       <c r="C49" t="n">
-        <v>65507.59</v>
+        <v>66910.06</v>
       </c>
       <c r="D49" t="n">
-        <v>61769</v>
+        <v>63686.04</v>
       </c>
       <c r="E49" t="n">
-        <v>64690.8</v>
+        <v>65340.3</v>
       </c>
       <c r="F49" t="n">
-        <v>932.59</v>
+        <v>649.5</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.01</v>
       </c>
       <c r="H49" t="n">
-        <v>3738.59</v>
+        <v>3224.03</v>
       </c>
       <c r="I49" t="n">
-        <v>57892.69</v>
+        <v>58030.41</v>
       </c>
       <c r="J49" t="n">
-        <v>60770.49</v>
+        <v>61478.46</v>
       </c>
       <c r="K49" t="n">
-        <v>62066.65</v>
+        <v>62821.51</v>
       </c>
       <c r="L49" t="n">
-        <v>63362.81</v>
+        <v>64164.55</v>
       </c>
       <c r="M49" t="n">
-        <v>65449.79</v>
+        <v>66560.10000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>67536.77</v>
+        <v>68955.64999999999</v>
       </c>
       <c r="O49" t="n">
-        <v>68042.11</v>
+        <v>69246.19</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4619,28 +4625,26 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4654,50 +4658,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>64684.42</v>
+        <v>65340.59</v>
       </c>
       <c r="C50" t="n">
-        <v>66910.06</v>
+        <v>65658.34</v>
       </c>
       <c r="D50" t="n">
-        <v>63686.04</v>
+        <v>62233.01</v>
       </c>
       <c r="E50" t="n">
-        <v>65340.3</v>
+        <v>63482</v>
       </c>
       <c r="F50" t="n">
-        <v>649.5</v>
+        <v>-1858.3</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.0284</v>
       </c>
       <c r="H50" t="n">
-        <v>3224.03</v>
+        <v>3425.32</v>
       </c>
       <c r="I50" t="n">
-        <v>58030.41</v>
+        <v>60462.01</v>
       </c>
       <c r="J50" t="n">
-        <v>61478.46</v>
+        <v>62137.4</v>
       </c>
       <c r="K50" t="n">
-        <v>62821.51</v>
+        <v>63728.29</v>
       </c>
       <c r="L50" t="n">
-        <v>64164.55</v>
+        <v>65319.17</v>
       </c>
       <c r="M50" t="n">
-        <v>66560.10000000001</v>
+        <v>66952.31</v>
       </c>
       <c r="N50" t="n">
-        <v>68955.64999999999</v>
+        <v>68585.45</v>
       </c>
       <c r="O50" t="n">
-        <v>69246.19</v>
+        <v>70134.09</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4705,18 +4709,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4724,64 +4728,60 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>65340.59</v>
+        <v>63485.44</v>
       </c>
       <c r="C51" t="n">
-        <v>65658.34</v>
+        <v>65401.69</v>
       </c>
       <c r="D51" t="n">
-        <v>62233.01</v>
+        <v>62226.58</v>
       </c>
       <c r="E51" t="n">
-        <v>63482</v>
+        <v>64844.89</v>
       </c>
       <c r="F51" t="n">
-        <v>-1858.3</v>
+        <v>1362.89</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0284</v>
+        <v>0.0215</v>
       </c>
       <c r="H51" t="n">
-        <v>3425.32</v>
+        <v>3175.11</v>
       </c>
       <c r="I51" t="n">
-        <v>60462.01</v>
+        <v>58807.69</v>
       </c>
       <c r="J51" t="n">
-        <v>62137.4</v>
+        <v>59824.84</v>
       </c>
       <c r="K51" t="n">
-        <v>63728.29</v>
+        <v>61769.34</v>
       </c>
       <c r="L51" t="n">
-        <v>65319.17</v>
+        <v>63713.84</v>
       </c>
       <c r="M51" t="n">
-        <v>66952.31</v>
+        <v>65194.66</v>
       </c>
       <c r="N51" t="n">
-        <v>68585.45</v>
+        <v>66675.49000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>70134.09</v>
+        <v>69083.66</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4789,79 +4789,83 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>63485.44</v>
+        <v>64845.38</v>
       </c>
       <c r="C52" t="n">
-        <v>65401.69</v>
+        <v>65321.84</v>
       </c>
       <c r="D52" t="n">
-        <v>62226.58</v>
+        <v>62487.7</v>
       </c>
       <c r="E52" t="n">
-        <v>64844.89</v>
+        <v>62818.65</v>
       </c>
       <c r="F52" t="n">
-        <v>1362.89</v>
+        <v>-2026.23</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0215</v>
+        <v>-0.0312</v>
       </c>
       <c r="H52" t="n">
-        <v>3175.11</v>
+        <v>2834.14</v>
       </c>
       <c r="I52" t="n">
-        <v>58807.69</v>
+        <v>59051.46</v>
       </c>
       <c r="J52" t="n">
-        <v>59824.84</v>
+        <v>62185.15</v>
       </c>
       <c r="K52" t="n">
-        <v>61769.34</v>
+        <v>63257.33</v>
       </c>
       <c r="L52" t="n">
-        <v>63713.84</v>
+        <v>64329.51</v>
       </c>
       <c r="M52" t="n">
-        <v>65194.66</v>
+        <v>66432.44</v>
       </c>
       <c r="N52" t="n">
-        <v>66675.49000000001</v>
+        <v>68535.38</v>
       </c>
       <c r="O52" t="n">
-        <v>69083.66</v>
+        <v>68576.8</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4869,26 +4873,26 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4902,50 +4906,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>64845.38</v>
+        <v>62819.38</v>
       </c>
       <c r="C53" t="n">
-        <v>65321.84</v>
+        <v>79463.71000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>62487.7</v>
+        <v>62687.1</v>
       </c>
       <c r="E53" t="n">
-        <v>62818.65</v>
+        <v>77755.27</v>
       </c>
       <c r="F53" t="n">
-        <v>-2026.23</v>
+        <v>14936.61</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0312</v>
+        <v>0.2378</v>
       </c>
       <c r="H53" t="n">
-        <v>2834.14</v>
+        <v>16776.61</v>
       </c>
       <c r="I53" t="n">
-        <v>59051.46</v>
+        <v>59653.56</v>
       </c>
       <c r="J53" t="n">
-        <v>62185.15</v>
+        <v>59441.45</v>
       </c>
       <c r="K53" t="n">
-        <v>63257.33</v>
+        <v>61401.58</v>
       </c>
       <c r="L53" t="n">
-        <v>64329.51</v>
+        <v>63361.71</v>
       </c>
       <c r="M53" t="n">
-        <v>66432.44</v>
+        <v>64235.72</v>
       </c>
       <c r="N53" t="n">
-        <v>68535.38</v>
+        <v>65109.73</v>
       </c>
       <c r="O53" t="n">
-        <v>68576.8</v>
+        <v>68155.98</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4953,83 +4957,83 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
-      </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>62819.38</v>
+        <v>77748.88</v>
       </c>
       <c r="C54" t="n">
-        <v>79463.71000000001</v>
+        <v>81346.95</v>
       </c>
       <c r="D54" t="n">
-        <v>62687.1</v>
+        <v>76688.83</v>
       </c>
       <c r="E54" t="n">
-        <v>77755.27</v>
+        <v>77667.57000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>14936.61</v>
+        <v>-87.7</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.2378</v>
+        <v>-0.0011</v>
       </c>
       <c r="H54" t="n">
-        <v>16776.61</v>
+        <v>4658.12</v>
       </c>
       <c r="I54" t="n">
-        <v>59653.56</v>
+        <v>45910.49</v>
       </c>
       <c r="J54" t="n">
-        <v>59441.45</v>
+        <v>64318.59</v>
       </c>
       <c r="K54" t="n">
-        <v>61401.58</v>
+        <v>69366.96000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>63361.71</v>
+        <v>74415.34</v>
       </c>
       <c r="M54" t="n">
-        <v>64235.72</v>
+        <v>86143.57000000001</v>
       </c>
       <c r="N54" t="n">
-        <v>65109.73</v>
+        <v>97871.8</v>
       </c>
       <c r="O54" t="n">
-        <v>68155.98</v>
+        <v>96240.32000000001</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5042,78 +5046,76 @@
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W54" s="11" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>77748.88</v>
+        <v>77673.7</v>
       </c>
       <c r="C55" t="n">
-        <v>81346.95</v>
+        <v>82262.21000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>76688.83</v>
+        <v>76248.3</v>
       </c>
       <c r="E55" t="n">
-        <v>77667.57000000001</v>
+        <v>80350.05</v>
       </c>
       <c r="F55" t="n">
-        <v>-87.7</v>
+        <v>2682.48</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0345</v>
       </c>
       <c r="H55" t="n">
-        <v>4658.12</v>
+        <v>6013.91</v>
       </c>
       <c r="I55" t="n">
-        <v>45910.49</v>
+        <v>72030.7</v>
       </c>
       <c r="J55" t="n">
-        <v>64318.59</v>
+        <v>72334.28999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>69366.96000000001</v>
+        <v>75338.50999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>74415.34</v>
+        <v>78342.73</v>
       </c>
       <c r="M55" t="n">
-        <v>86143.57000000001</v>
+        <v>79996.63</v>
       </c>
       <c r="N55" t="n">
-        <v>97871.8</v>
+        <v>81650.53999999999</v>
       </c>
       <c r="O55" t="n">
-        <v>96240.32000000001</v>
+        <v>86005.08</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5126,19 +5128,23 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5152,50 +5158,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>77673.7</v>
+        <v>80349.2</v>
       </c>
       <c r="C56" t="n">
-        <v>82262.21000000001</v>
+        <v>80432.31</v>
       </c>
       <c r="D56" t="n">
-        <v>76248.3</v>
+        <v>76162.91</v>
       </c>
       <c r="E56" t="n">
-        <v>80350.05</v>
+        <v>76838.16</v>
       </c>
       <c r="F56" t="n">
-        <v>2682.48</v>
+        <v>-3511.89</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0345</v>
+        <v>-0.0437</v>
       </c>
       <c r="H56" t="n">
-        <v>6013.91</v>
+        <v>4269.4</v>
       </c>
       <c r="I56" t="n">
-        <v>72030.7</v>
+        <v>70234.39999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>72334.28999999999</v>
+        <v>74883.53999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>75338.50999999999</v>
+        <v>77343.09</v>
       </c>
       <c r="L56" t="n">
-        <v>78342.73</v>
+        <v>79802.64999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>79996.63</v>
+        <v>83357</v>
       </c>
       <c r="N56" t="n">
-        <v>81650.53999999999</v>
+        <v>86911.35000000001</v>
       </c>
       <c r="O56" t="n">
-        <v>86005.08</v>
+        <v>88276.12</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5203,85 +5209,83 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>80349.2</v>
+        <v>76830.28</v>
       </c>
       <c r="C57" t="n">
-        <v>80432.31</v>
+        <v>81911.14</v>
       </c>
       <c r="D57" t="n">
-        <v>76162.91</v>
+        <v>74944.59</v>
       </c>
       <c r="E57" t="n">
-        <v>76838.16</v>
+        <v>81142.61</v>
       </c>
       <c r="F57" t="n">
-        <v>-3511.89</v>
+        <v>4304.45</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0437</v>
+        <v>0.056</v>
       </c>
       <c r="H57" t="n">
-        <v>4269.4</v>
+        <v>6966.55</v>
       </c>
       <c r="I57" t="n">
-        <v>70234.39999999999</v>
+        <v>71893.52</v>
       </c>
       <c r="J57" t="n">
-        <v>74883.53999999999</v>
+        <v>71839.03</v>
       </c>
       <c r="K57" t="n">
-        <v>77343.09</v>
+        <v>74703.46000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>79802.64999999999</v>
+        <v>77567.88</v>
       </c>
       <c r="M57" t="n">
-        <v>83357</v>
+        <v>78972.86</v>
       </c>
       <c r="N57" t="n">
-        <v>86911.35000000001</v>
+        <v>80377.83</v>
       </c>
       <c r="O57" t="n">
-        <v>88276.12</v>
+        <v>84701.71000000001</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5289,83 +5293,85 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>76830.28</v>
+        <v>81162.17999999999</v>
       </c>
       <c r="C58" t="n">
-        <v>81911.14</v>
+        <v>87281.16</v>
       </c>
       <c r="D58" t="n">
-        <v>74944.59</v>
+        <v>80933.07000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>81254.85000000001</v>
+        <v>86555.13</v>
       </c>
       <c r="F58" t="n">
-        <v>4416.7</v>
+        <v>5412.52</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0575</v>
+        <v>0.0667</v>
       </c>
       <c r="H58" t="n">
-        <v>6966.55</v>
+        <v>6348.09</v>
       </c>
       <c r="I58" t="n">
-        <v>71893.52</v>
+        <v>67978.05</v>
       </c>
       <c r="J58" t="n">
-        <v>71839.03</v>
+        <v>75533.42999999999</v>
       </c>
       <c r="K58" t="n">
-        <v>74703.46000000001</v>
+        <v>77659.34</v>
       </c>
       <c r="L58" t="n">
-        <v>77567.88</v>
+        <v>79785.24000000001</v>
       </c>
       <c r="M58" t="n">
-        <v>78972.86</v>
+        <v>84625.88</v>
       </c>
       <c r="N58" t="n">
-        <v>80377.83</v>
+        <v>89466.53</v>
       </c>
       <c r="O58" t="n">
-        <v>84701.71000000001</v>
+        <v>88877.69</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5383,27 +5389,21 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>6193.4</v>
       </c>
       <c r="I2" t="n">
-        <v>104506.92</v>
+        <v>104743.7</v>
       </c>
       <c r="J2" t="n">
-        <v>106465.34</v>
+        <v>106761.31</v>
       </c>
       <c r="K2" t="n">
-        <v>110181.62</v>
+        <v>110300</v>
       </c>
       <c r="L2" t="n">
-        <v>113897.89</v>
+        <v>113838.7</v>
       </c>
       <c r="M2" t="n">
-        <v>116735.24</v>
+        <v>116616.86</v>
       </c>
       <c r="N2" t="n">
-        <v>119572.59</v>
+        <v>119395.01</v>
       </c>
       <c r="O2" t="n">
-        <v>124167.8</v>
+        <v>123694.25</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5332,25 +5332,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>81162.17999999999</v>
+        <v>81143.62</v>
       </c>
       <c r="C58" t="n">
-        <v>87281.16</v>
+        <v>87363.75999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>80933.07000000001</v>
+        <v>80867.09</v>
       </c>
       <c r="E58" t="n">
-        <v>86555.13</v>
+        <v>86217.53</v>
       </c>
       <c r="F58" t="n">
-        <v>5412.52</v>
+        <v>5074.92</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0667</v>
+        <v>0.0625</v>
       </c>
       <c r="H58" t="n">
-        <v>6348.09</v>
+        <v>6496.67</v>
       </c>
       <c r="I58" t="n">
         <v>67978.05</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5341,13 +5341,13 @@
         <v>80867.09</v>
       </c>
       <c r="E58" t="n">
-        <v>86217.53</v>
+        <v>86200.89999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>5074.92</v>
+        <v>5058.29</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.0623</v>
       </c>
       <c r="H58" t="n">
         <v>6496.67</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5341,13 +5341,13 @@
         <v>80867.09</v>
       </c>
       <c r="E58" t="n">
-        <v>86200.89999999999</v>
+        <v>86030.86</v>
       </c>
       <c r="F58" t="n">
-        <v>5058.29</v>
+        <v>4888.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0623</v>
+        <v>0.0602</v>
       </c>
       <c r="H58" t="n">
         <v>6496.67</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5341,13 +5341,13 @@
         <v>80867.09</v>
       </c>
       <c r="E58" t="n">
-        <v>86030.86</v>
+        <v>86402.27</v>
       </c>
       <c r="F58" t="n">
-        <v>4888.25</v>
+        <v>5259.66</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0602</v>
+        <v>0.0648</v>
       </c>
       <c r="H58" t="n">
         <v>6496.67</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5341,13 +5341,13 @@
         <v>80867.09</v>
       </c>
       <c r="E58" t="n">
-        <v>86402.27</v>
+        <v>86187.53999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>5259.66</v>
+        <v>5044.93</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0648</v>
+        <v>0.0622</v>
       </c>
       <c r="H58" t="n">
         <v>6496.67</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5341,13 +5341,13 @@
         <v>80867.09</v>
       </c>
       <c r="E58" t="n">
-        <v>86187.53999999999</v>
+        <v>86465.98</v>
       </c>
       <c r="F58" t="n">
-        <v>5044.93</v>
+        <v>5323.37</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0622</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H58" t="n">
         <v>6496.67</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5341,13 +5341,13 @@
         <v>80867.09</v>
       </c>
       <c r="E58" t="n">
-        <v>86465.98</v>
+        <v>86716.46000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>5323.37</v>
+        <v>5573.85</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0687</v>
       </c>
       <c r="H58" t="n">
         <v>6496.67</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5341,13 +5341,13 @@
         <v>80867.09</v>
       </c>
       <c r="E58" t="n">
-        <v>86716.46000000001</v>
+        <v>85449.99000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>5573.85</v>
+        <v>4307.38</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0687</v>
+        <v>0.0531</v>
       </c>
       <c r="H58" t="n">
         <v>6496.67</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5341,13 +5341,13 @@
         <v>80867.09</v>
       </c>
       <c r="E58" t="n">
-        <v>85449.99000000001</v>
+        <v>84547.02</v>
       </c>
       <c r="F58" t="n">
-        <v>4307.38</v>
+        <v>3404.41</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0531</v>
+        <v>0.042</v>
       </c>
       <c r="H58" t="n">
         <v>6496.67</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5341,13 +5341,13 @@
         <v>80867.09</v>
       </c>
       <c r="E58" t="n">
-        <v>84547.02</v>
+        <v>84315.32000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>3404.41</v>
+        <v>3172.71</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.042</v>
+        <v>0.0391</v>
       </c>
       <c r="H58" t="n">
         <v>6496.67</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -659,25 +659,25 @@
         <v>6193.4</v>
       </c>
       <c r="I2" t="n">
-        <v>104743.7</v>
+        <v>106506.01</v>
       </c>
       <c r="J2" t="n">
-        <v>106761.31</v>
+        <v>108964.2</v>
       </c>
       <c r="K2" t="n">
-        <v>110300</v>
+        <v>111181.16</v>
       </c>
       <c r="L2" t="n">
-        <v>113838.7</v>
+        <v>113398.12</v>
       </c>
       <c r="M2" t="n">
-        <v>116616.86</v>
+        <v>115735.7</v>
       </c>
       <c r="N2" t="n">
-        <v>119395.01</v>
+        <v>118073.28</v>
       </c>
       <c r="O2" t="n">
-        <v>123694.25</v>
+        <v>120169.62</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -708,14 +708,10 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -794,12 +790,12 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -878,10 +874,14 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -1044,14 +1044,10 @@
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1130,7 +1126,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1212,7 +1208,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1296,7 +1292,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1380,7 +1376,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1466,7 +1462,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1552,7 +1548,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1638,7 +1634,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1722,7 +1718,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1804,7 +1800,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1888,7 +1884,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1970,7 +1966,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2054,7 +2050,7 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2136,7 +2132,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2222,7 +2218,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2302,7 +2298,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2388,7 +2384,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2470,7 +2466,7 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2560,7 +2556,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2642,7 +2638,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2720,7 +2716,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2804,7 +2800,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2892,7 +2888,7 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2974,7 +2970,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3060,7 +3056,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3144,7 +3140,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3228,7 +3224,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3308,7 +3304,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3396,7 +3392,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3482,7 +3478,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3566,7 +3562,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3650,7 +3646,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3734,7 +3730,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3820,7 +3816,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3900,7 +3896,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3982,7 +3978,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4066,7 +4062,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4144,7 +4140,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4228,7 +4224,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4312,7 +4308,7 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4392,7 +4388,7 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4474,7 +4470,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4560,7 +4556,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4644,7 +4640,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4728,7 +4724,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4808,7 +4804,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4892,7 +4888,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4980,7 +4976,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5058,7 +5054,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5144,7 +5140,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5228,7 +5224,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5314,7 +5310,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5341,13 +5337,13 @@
         <v>80867.09</v>
       </c>
       <c r="E58" t="n">
-        <v>84315.32000000001</v>
+        <v>84326.42</v>
       </c>
       <c r="F58" t="n">
-        <v>3172.71</v>
+        <v>3183.81</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0391</v>
+        <v>0.0392</v>
       </c>
       <c r="H58" t="n">
         <v>6496.67</v>
@@ -5398,7 +5394,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,132 +634,136 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>113456.9</v>
+        <v>108228.75</v>
       </c>
       <c r="C2" t="n">
-        <v>113637.84</v>
+        <v>113357.49</v>
       </c>
       <c r="D2" t="n">
-        <v>107444.45</v>
+        <v>107271.18</v>
       </c>
       <c r="E2" t="n">
-        <v>108236.71</v>
+        <v>111167.62</v>
       </c>
       <c r="F2" t="n">
-        <v>-5221.72</v>
+        <v>2930.91</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.046</v>
+        <v>0.0271</v>
       </c>
       <c r="H2" t="n">
-        <v>6193.4</v>
+        <v>6086.31</v>
       </c>
       <c r="I2" t="n">
-        <v>106506.01</v>
+        <v>101251.05</v>
       </c>
       <c r="J2" t="n">
-        <v>108964.2</v>
+        <v>100891.1</v>
       </c>
       <c r="K2" t="n">
-        <v>111181.16</v>
+        <v>105140.01</v>
       </c>
       <c r="L2" t="n">
-        <v>113398.12</v>
+        <v>109388.93</v>
       </c>
       <c r="M2" t="n">
-        <v>115735.7</v>
+        <v>111333.41</v>
       </c>
       <c r="N2" t="n">
-        <v>118073.28</v>
+        <v>113277.89</v>
       </c>
       <c r="O2" t="n">
-        <v>120169.62</v>
+        <v>119831.24</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="U2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>108228.75</v>
+        <v>111163.02</v>
       </c>
       <c r="C3" t="n">
-        <v>113357.49</v>
+        <v>116769.38</v>
       </c>
       <c r="D3" t="n">
-        <v>107271.18</v>
+        <v>110630.61</v>
       </c>
       <c r="E3" t="n">
-        <v>111167.62</v>
+        <v>115407.66</v>
       </c>
       <c r="F3" t="n">
-        <v>2930.91</v>
+        <v>4240.04</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0271</v>
+        <v>0.0381</v>
       </c>
       <c r="H3" t="n">
-        <v>6086.31</v>
+        <v>6138.77</v>
       </c>
       <c r="I3" t="n">
-        <v>101251.05</v>
+        <v>101184.87</v>
       </c>
       <c r="J3" t="n">
-        <v>100891.1</v>
+        <v>105507.95</v>
       </c>
       <c r="K3" t="n">
-        <v>105140.01</v>
+        <v>108124.46</v>
       </c>
       <c r="L3" t="n">
-        <v>109388.93</v>
+        <v>110740.98</v>
       </c>
       <c r="M3" t="n">
-        <v>111333.41</v>
+        <v>114210.77</v>
       </c>
       <c r="N3" t="n">
-        <v>113277.89</v>
+        <v>117680.57</v>
       </c>
       <c r="O3" t="n">
-        <v>119831.24</v>
+        <v>119443.8</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -770,7 +774,7 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -780,72 +784,66 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>111163.02</v>
+        <v>115399.63</v>
       </c>
       <c r="C4" t="n">
-        <v>116769.38</v>
+        <v>117911.79</v>
       </c>
       <c r="D4" t="n">
-        <v>110630.61</v>
+        <v>114461.06</v>
       </c>
       <c r="E4" t="n">
-        <v>115407.66</v>
+        <v>115306.09</v>
       </c>
       <c r="F4" t="n">
-        <v>4240.04</v>
+        <v>-101.56</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0381</v>
+        <v>-0.0009</v>
       </c>
       <c r="H4" t="n">
-        <v>6138.77</v>
+        <v>3450.73</v>
       </c>
       <c r="I4" t="n">
-        <v>101184.87</v>
+        <v>104491.84</v>
       </c>
       <c r="J4" t="n">
-        <v>105507.95</v>
+        <v>110122.71</v>
       </c>
       <c r="K4" t="n">
-        <v>108124.46</v>
+        <v>112338.27</v>
       </c>
       <c r="L4" t="n">
-        <v>110740.98</v>
+        <v>114553.83</v>
       </c>
       <c r="M4" t="n">
-        <v>114210.77</v>
+        <v>118477.04</v>
       </c>
       <c r="N4" t="n">
-        <v>117680.57</v>
+        <v>122400.26</v>
       </c>
       <c r="O4" t="n">
-        <v>119443.8</v>
+        <v>122908.16</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -856,15 +854,13 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -874,75 +870,81 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>115399.63</v>
+        <v>115309.22</v>
       </c>
       <c r="C5" t="n">
-        <v>117911.79</v>
+        <v>115431.31</v>
       </c>
       <c r="D5" t="n">
-        <v>114461.06</v>
+        <v>108713.4</v>
       </c>
       <c r="E5" t="n">
-        <v>115306.09</v>
+        <v>112122.64</v>
       </c>
       <c r="F5" t="n">
-        <v>-101.56</v>
+        <v>-3183.45</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0276</v>
       </c>
       <c r="H5" t="n">
-        <v>3450.73</v>
+        <v>6717.91</v>
       </c>
       <c r="I5" t="n">
-        <v>104491.84</v>
+        <v>111010.34</v>
       </c>
       <c r="J5" t="n">
-        <v>110122.71</v>
+        <v>111415.2</v>
       </c>
       <c r="K5" t="n">
-        <v>112338.27</v>
+        <v>113580.73</v>
       </c>
       <c r="L5" t="n">
-        <v>114553.83</v>
+        <v>115746.26</v>
       </c>
       <c r="M5" t="n">
-        <v>118477.04</v>
+        <v>117031.46</v>
       </c>
       <c r="N5" t="n">
-        <v>122400.26</v>
+        <v>118316.65</v>
       </c>
       <c r="O5" t="n">
-        <v>122908.16</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+        <v>121362.52</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -956,95 +958,95 @@
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>115309.22</v>
+        <v>112117.88</v>
       </c>
       <c r="C6" t="n">
-        <v>115431.31</v>
+        <v>125559.21</v>
       </c>
       <c r="D6" t="n">
-        <v>108713.4</v>
+        <v>111589.95</v>
       </c>
       <c r="E6" t="n">
-        <v>112122.64</v>
+        <v>123513.48</v>
       </c>
       <c r="F6" t="n">
-        <v>-3183.45</v>
+        <v>11390.84</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0276</v>
+        <v>0.1016</v>
       </c>
       <c r="H6" t="n">
-        <v>6717.91</v>
+        <v>13969.26</v>
       </c>
       <c r="I6" t="n">
-        <v>111010.34</v>
+        <v>101995.48</v>
       </c>
       <c r="J6" t="n">
-        <v>111415.2</v>
+        <v>105429.87</v>
       </c>
       <c r="K6" t="n">
-        <v>113580.73</v>
+        <v>108763.68</v>
       </c>
       <c r="L6" t="n">
-        <v>115746.26</v>
+        <v>112097.5</v>
       </c>
       <c r="M6" t="n">
-        <v>117031.46</v>
+        <v>115481.6</v>
       </c>
       <c r="N6" t="n">
-        <v>118316.65</v>
+        <v>118865.7</v>
       </c>
       <c r="O6" t="n">
-        <v>121362.52</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
+        <v>122149.23</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
-      </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1052,149 +1054,149 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112117.88</v>
+        <v>123510.45</v>
       </c>
       <c r="C7" t="n">
-        <v>125559.21</v>
+        <v>126198.07</v>
       </c>
       <c r="D7" t="n">
-        <v>111589.95</v>
+        <v>104582.41</v>
       </c>
       <c r="E7" t="n">
-        <v>123513.48</v>
+        <v>115169.77</v>
       </c>
       <c r="F7" t="n">
-        <v>11390.84</v>
+        <v>-8343.709999999999</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.1016</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>13969.26</v>
+        <v>21615.66</v>
       </c>
       <c r="I7" t="n">
-        <v>101995.48</v>
+        <v>97620.7</v>
       </c>
       <c r="J7" t="n">
-        <v>105429.87</v>
+        <v>112013.67</v>
       </c>
       <c r="K7" t="n">
-        <v>108763.68</v>
+        <v>116528.85</v>
       </c>
       <c r="L7" t="n">
-        <v>112097.5</v>
+        <v>121044.03</v>
       </c>
       <c r="M7" t="n">
-        <v>115481.6</v>
+        <v>130498.11</v>
       </c>
       <c r="N7" t="n">
-        <v>118865.7</v>
+        <v>139952.18</v>
       </c>
       <c r="O7" t="n">
-        <v>122149.23</v>
+        <v>139528.47</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W7" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>123510.45</v>
+        <v>115161.68</v>
       </c>
       <c r="C8" t="n">
-        <v>126198.07</v>
+        <v>116020.48</v>
       </c>
       <c r="D8" t="n">
-        <v>104582.41</v>
+        <v>103598.43</v>
       </c>
       <c r="E8" t="n">
-        <v>115169.77</v>
+        <v>108666.71</v>
       </c>
       <c r="F8" t="n">
-        <v>-8343.709999999999</v>
+        <v>-6503.05</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0565</v>
       </c>
       <c r="H8" t="n">
-        <v>21615.66</v>
+        <v>12422.05</v>
       </c>
       <c r="I8" t="n">
-        <v>97620.7</v>
+        <v>82966.75999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>112013.67</v>
+        <v>93443.87</v>
       </c>
       <c r="K8" t="n">
-        <v>116528.85</v>
+        <v>104361.94</v>
       </c>
       <c r="L8" t="n">
-        <v>121044.03</v>
+        <v>115280</v>
       </c>
       <c r="M8" t="n">
-        <v>130498.11</v>
+        <v>125977.59</v>
       </c>
       <c r="N8" t="n">
-        <v>139952.18</v>
+        <v>136675.18</v>
       </c>
       <c r="O8" t="n">
-        <v>139528.47</v>
+        <v>147813.73</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q8" s="6" t="n">
+        <v/>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1208,64 +1210,64 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>115161.68</v>
+        <v>108667.45</v>
       </c>
       <c r="C9" t="n">
-        <v>116020.48</v>
+        <v>115260.91</v>
       </c>
       <c r="D9" t="n">
-        <v>103598.43</v>
+        <v>106778</v>
       </c>
       <c r="E9" t="n">
-        <v>108666.71</v>
+        <v>114472.45</v>
       </c>
       <c r="F9" t="n">
-        <v>-6503.05</v>
+        <v>5805.73</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0565</v>
+        <v>0.0534</v>
       </c>
       <c r="H9" t="n">
-        <v>12422.05</v>
+        <v>8482.91</v>
       </c>
       <c r="I9" t="n">
-        <v>82966.75999999999</v>
+        <v>91176.38</v>
       </c>
       <c r="J9" t="n">
-        <v>93443.87</v>
+        <v>95673.28</v>
       </c>
       <c r="K9" t="n">
-        <v>104361.94</v>
+        <v>102455.68</v>
       </c>
       <c r="L9" t="n">
-        <v>115280</v>
+        <v>109238.08</v>
       </c>
       <c r="M9" t="n">
-        <v>125977.59</v>
+        <v>114877.74</v>
       </c>
       <c r="N9" t="n">
-        <v>136675.18</v>
+        <v>120517.39</v>
       </c>
       <c r="O9" t="n">
-        <v>147813.73</v>
+        <v>128442.54</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1273,102 +1275,104 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>108667.45</v>
+        <v>114479.85</v>
       </c>
       <c r="C10" t="n">
-        <v>115260.91</v>
+        <v>116273.31</v>
       </c>
       <c r="D10" t="n">
-        <v>106778</v>
+        <v>106376.69</v>
       </c>
       <c r="E10" t="n">
-        <v>114472.45</v>
+        <v>110639.62</v>
       </c>
       <c r="F10" t="n">
-        <v>5805.73</v>
+        <v>-3832.82</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0534</v>
+        <v>-0.0335</v>
       </c>
       <c r="H10" t="n">
-        <v>8482.91</v>
+        <v>9896.620000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>91176.38</v>
+        <v>98295.09</v>
       </c>
       <c r="J10" t="n">
-        <v>95673.28</v>
+        <v>107716.04</v>
       </c>
       <c r="K10" t="n">
-        <v>102455.68</v>
+        <v>110230.99</v>
       </c>
       <c r="L10" t="n">
-        <v>109238.08</v>
+        <v>112745.95</v>
       </c>
       <c r="M10" t="n">
-        <v>114877.74</v>
+        <v>118713.9</v>
       </c>
       <c r="N10" t="n">
-        <v>120517.39</v>
+        <v>124681.85</v>
       </c>
       <c r="O10" t="n">
-        <v>128442.54</v>
+        <v>123743.81</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1376,64 +1380,64 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>114479.85</v>
+        <v>110646.91</v>
       </c>
       <c r="C11" t="n">
-        <v>116273.31</v>
+        <v>110764.91</v>
       </c>
       <c r="D11" t="n">
-        <v>106376.69</v>
+        <v>98962.06</v>
       </c>
       <c r="E11" t="n">
-        <v>110639.62</v>
+        <v>104719.64</v>
       </c>
       <c r="F11" t="n">
-        <v>-3832.82</v>
+        <v>-5919.98</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0335</v>
+        <v>-0.0535</v>
       </c>
       <c r="H11" t="n">
-        <v>9896.620000000001</v>
+        <v>11802.85</v>
       </c>
       <c r="I11" t="n">
-        <v>98295.09</v>
+        <v>96480.06</v>
       </c>
       <c r="J11" t="n">
-        <v>107716.04</v>
+        <v>100400.31</v>
       </c>
       <c r="K11" t="n">
-        <v>110230.99</v>
+        <v>105691.31</v>
       </c>
       <c r="L11" t="n">
-        <v>112745.95</v>
+        <v>110982.31</v>
       </c>
       <c r="M11" t="n">
-        <v>118713.9</v>
+        <v>115587.94</v>
       </c>
       <c r="N11" t="n">
-        <v>124681.85</v>
+        <v>120193.56</v>
       </c>
       <c r="O11" t="n">
-        <v>123743.81</v>
+        <v>126169.94</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1448,7 +1452,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1462,79 +1466,79 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>110646.91</v>
+        <v>104723.77</v>
       </c>
       <c r="C12" t="n">
-        <v>110764.91</v>
+        <v>107428.26</v>
       </c>
       <c r="D12" t="n">
-        <v>98962.06</v>
+        <v>92971.16</v>
       </c>
       <c r="E12" t="n">
-        <v>104719.64</v>
+        <v>94177.08</v>
       </c>
       <c r="F12" t="n">
-        <v>-5919.98</v>
+        <v>-10542.56</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0535</v>
+        <v>-0.1007</v>
       </c>
       <c r="H12" t="n">
-        <v>11802.85</v>
+        <v>14457.09</v>
       </c>
       <c r="I12" t="n">
-        <v>96480.06</v>
+        <v>87159.21000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>100400.31</v>
+        <v>92844.87</v>
       </c>
       <c r="K12" t="n">
-        <v>105691.31</v>
+        <v>98818.21000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>110982.31</v>
+        <v>104791.56</v>
       </c>
       <c r="M12" t="n">
-        <v>115587.94</v>
+        <v>110621.07</v>
       </c>
       <c r="N12" t="n">
-        <v>120193.56</v>
+        <v>116450.57</v>
       </c>
       <c r="O12" t="n">
-        <v>126169.94</v>
+        <v>122567.77</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1548,7 +1552,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1562,65 +1566,63 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>104723.77</v>
+        <v>94180.88</v>
       </c>
       <c r="C13" t="n">
-        <v>107428.26</v>
+        <v>95928.37</v>
       </c>
       <c r="D13" t="n">
-        <v>92971.16</v>
+        <v>80659.81</v>
       </c>
       <c r="E13" t="n">
-        <v>94177.08</v>
+        <v>86805.00999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-10542.56</v>
+        <v>-7372.07</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.1007</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>14457.09</v>
+        <v>15268.55</v>
       </c>
       <c r="I13" t="n">
-        <v>87159.21000000001</v>
+        <v>78514.07000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>92844.87</v>
+        <v>76708.67</v>
       </c>
       <c r="K13" t="n">
-        <v>98818.21000000001</v>
+        <v>86948.53</v>
       </c>
       <c r="L13" t="n">
-        <v>104791.56</v>
+        <v>97188.39</v>
       </c>
       <c r="M13" t="n">
-        <v>110621.07</v>
+        <v>101405.62</v>
       </c>
       <c r="N13" t="n">
-        <v>116450.57</v>
+        <v>105622.86</v>
       </c>
       <c r="O13" t="n">
-        <v>122567.77</v>
+        <v>121885.35</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1634,7 +1636,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1648,50 +1650,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>94180.88</v>
+        <v>86798.77</v>
       </c>
       <c r="C14" t="n">
-        <v>95928.37</v>
+        <v>92969.09</v>
       </c>
       <c r="D14" t="n">
-        <v>80659.81</v>
+        <v>85272.2</v>
       </c>
       <c r="E14" t="n">
-        <v>86805.00999999999</v>
+        <v>90394.31</v>
       </c>
       <c r="F14" t="n">
-        <v>-7372.07</v>
+        <v>3589.3</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.0413</v>
       </c>
       <c r="H14" t="n">
-        <v>15268.55</v>
+        <v>7696.89</v>
       </c>
       <c r="I14" t="n">
-        <v>78514.07000000001</v>
+        <v>65391.26</v>
       </c>
       <c r="J14" t="n">
-        <v>76708.67</v>
+        <v>70791.91</v>
       </c>
       <c r="K14" t="n">
-        <v>86948.53</v>
+        <v>79170.73</v>
       </c>
       <c r="L14" t="n">
-        <v>97188.39</v>
+        <v>87549.55</v>
       </c>
       <c r="M14" t="n">
-        <v>101405.62</v>
+        <v>94439.28999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>105622.86</v>
+        <v>101329.02</v>
       </c>
       <c r="O14" t="n">
-        <v>121885.35</v>
+        <v>111196.92</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1699,14 +1701,12 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1718,64 +1718,64 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>86798.77</v>
+        <v>90389.11</v>
       </c>
       <c r="C15" t="n">
-        <v>92969.09</v>
+        <v>94060.77</v>
       </c>
       <c r="D15" t="n">
-        <v>85272.2</v>
+        <v>83862.25</v>
       </c>
       <c r="E15" t="n">
-        <v>90394.31</v>
+        <v>90405.64</v>
       </c>
       <c r="F15" t="n">
-        <v>3589.3</v>
+        <v>11.33</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0413</v>
+        <v>0.0001</v>
       </c>
       <c r="H15" t="n">
-        <v>7696.89</v>
+        <v>10198.52</v>
       </c>
       <c r="I15" t="n">
-        <v>65391.26</v>
+        <v>77575.3</v>
       </c>
       <c r="J15" t="n">
-        <v>70791.91</v>
+        <v>83334.25999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>79170.73</v>
+        <v>86545.87</v>
       </c>
       <c r="L15" t="n">
-        <v>87549.55</v>
+        <v>89757.48</v>
       </c>
       <c r="M15" t="n">
-        <v>94439.28999999999</v>
+        <v>94242.75999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>101329.02</v>
+        <v>98728.03999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>111196.92</v>
+        <v>100665.98</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1783,10 +1783,12 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1800,7 +1802,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1814,50 +1816,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>90389.11</v>
+        <v>90424.59</v>
       </c>
       <c r="C16" t="n">
-        <v>94060.77</v>
+        <v>94601.57000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>83862.25</v>
+        <v>87634.94</v>
       </c>
       <c r="E16" t="n">
-        <v>90405.64</v>
+        <v>88175.17999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>11.33</v>
+        <v>-2230.46</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0247</v>
       </c>
       <c r="H16" t="n">
-        <v>10198.52</v>
+        <v>6966.63</v>
       </c>
       <c r="I16" t="n">
-        <v>77575.3</v>
+        <v>73663.73</v>
       </c>
       <c r="J16" t="n">
-        <v>83334.25999999999</v>
+        <v>80929.17999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>86545.87</v>
+        <v>85306.38</v>
       </c>
       <c r="L16" t="n">
-        <v>89757.48</v>
+        <v>89683.58</v>
       </c>
       <c r="M16" t="n">
-        <v>94242.75999999999</v>
+        <v>95504.89999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>98728.03999999999</v>
+        <v>101326.23</v>
       </c>
       <c r="O16" t="n">
-        <v>100665.98</v>
+        <v>104259.3</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1865,14 +1867,12 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R16" s="6" t="n">
+        <v/>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1884,7 +1884,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1898,50 +1898,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>90424.59</v>
+        <v>88171.08</v>
       </c>
       <c r="C17" t="n">
-        <v>94601.57000000001</v>
+        <v>90264.57000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>87634.94</v>
+        <v>84436.31</v>
       </c>
       <c r="E17" t="n">
-        <v>88175.17999999999</v>
+        <v>88621.75</v>
       </c>
       <c r="F17" t="n">
-        <v>-2230.46</v>
+        <v>446.57</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0051</v>
       </c>
       <c r="H17" t="n">
-        <v>6966.63</v>
+        <v>5828.26</v>
       </c>
       <c r="I17" t="n">
-        <v>73663.73</v>
+        <v>80668.3</v>
       </c>
       <c r="J17" t="n">
-        <v>80929.17999999999</v>
+        <v>79737.00999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>85306.38</v>
+        <v>84691.86</v>
       </c>
       <c r="L17" t="n">
-        <v>89683.58</v>
+        <v>89646.72</v>
       </c>
       <c r="M17" t="n">
-        <v>95504.89999999999</v>
+        <v>91658.5</v>
       </c>
       <c r="N17" t="n">
-        <v>101326.23</v>
+        <v>93670.28</v>
       </c>
       <c r="O17" t="n">
-        <v>104259.3</v>
+        <v>101568.2</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1949,10 +1949,12 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1966,64 +1968,64 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>88171.08</v>
+        <v>88621.39999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>90264.57000000001</v>
+        <v>90501.92999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>84436.31</v>
+        <v>86411.8</v>
       </c>
       <c r="E18" t="n">
-        <v>88621.75</v>
+        <v>87835.84</v>
       </c>
       <c r="F18" t="n">
-        <v>446.57</v>
+        <v>-785.91</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0051</v>
+        <v>-0.0089</v>
       </c>
       <c r="H18" t="n">
-        <v>5828.26</v>
+        <v>4090.13</v>
       </c>
       <c r="I18" t="n">
-        <v>80668.3</v>
+        <v>78608.05</v>
       </c>
       <c r="J18" t="n">
-        <v>79737.00999999999</v>
+        <v>83429.14999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>84691.86</v>
+        <v>85707.62</v>
       </c>
       <c r="L18" t="n">
-        <v>89646.72</v>
+        <v>87986.10000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>91658.5</v>
+        <v>91535.88</v>
       </c>
       <c r="N18" t="n">
-        <v>93670.28</v>
+        <v>95085.66</v>
       </c>
       <c r="O18" t="n">
-        <v>101568.2</v>
+        <v>96092.83</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2031,12 +2033,10 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2050,64 +2050,64 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>88621.39999999999</v>
+        <v>87835.78999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>90501.92999999999</v>
+        <v>91712.59</v>
       </c>
       <c r="D19" t="n">
-        <v>86411.8</v>
+        <v>86717.91</v>
       </c>
       <c r="E19" t="n">
-        <v>87835.84</v>
+        <v>91413.49000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-785.91</v>
+        <v>3577.66</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0089</v>
+        <v>0.0407</v>
       </c>
       <c r="H19" t="n">
-        <v>4090.13</v>
+        <v>4994.67</v>
       </c>
       <c r="I19" t="n">
-        <v>78608.05</v>
+        <v>82321.66</v>
       </c>
       <c r="J19" t="n">
-        <v>83429.14999999999</v>
+        <v>83435.19</v>
       </c>
       <c r="K19" t="n">
-        <v>85707.62</v>
+        <v>85790.77</v>
       </c>
       <c r="L19" t="n">
-        <v>87986.10000000001</v>
+        <v>88146.35000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>91535.88</v>
+        <v>89880.89999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>95085.66</v>
+        <v>91615.46000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>96092.83</v>
+        <v>94592.06</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2120,76 +2120,76 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>87835.78999999999</v>
+        <v>91414.62</v>
       </c>
       <c r="C20" t="n">
-        <v>91712.59</v>
+        <v>94762.07000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>86717.91</v>
+        <v>89233.88</v>
       </c>
       <c r="E20" t="n">
-        <v>91413.49000000001</v>
+        <v>90827.46000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>3577.66</v>
+        <v>-586.03</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0407</v>
+        <v>-0.0064</v>
       </c>
       <c r="H20" t="n">
-        <v>4994.67</v>
+        <v>5528.2</v>
       </c>
       <c r="I20" t="n">
-        <v>82321.66</v>
+        <v>81723.24000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>83435.19</v>
+        <v>87517.94</v>
       </c>
       <c r="K20" t="n">
-        <v>85790.77</v>
+        <v>88916.16</v>
       </c>
       <c r="L20" t="n">
-        <v>88146.35000000001</v>
+        <v>90314.37</v>
       </c>
       <c r="M20" t="n">
-        <v>89880.89999999999</v>
+        <v>93910.83</v>
       </c>
       <c r="N20" t="n">
-        <v>91615.46000000001</v>
+        <v>97507.28999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>94592.06</v>
+        <v>96707.25999999999</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2200,9 +2200,9 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2210,68 +2210,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>91414.62</v>
+        <v>90825.86</v>
       </c>
       <c r="C21" t="n">
-        <v>94762.07000000001</v>
+        <v>97860.60000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>89233.88</v>
+        <v>90055.02</v>
       </c>
       <c r="E21" t="n">
-        <v>90827.46000000001</v>
+        <v>93634.42999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-586.03</v>
+        <v>2806.97</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0064</v>
+        <v>0.0309</v>
       </c>
       <c r="H21" t="n">
-        <v>5528.2</v>
+        <v>7805.58</v>
       </c>
       <c r="I21" t="n">
-        <v>81723.24000000001</v>
+        <v>83705.67999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>87517.94</v>
+        <v>84714.00999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>88916.16</v>
+        <v>88063.36</v>
       </c>
       <c r="L21" t="n">
-        <v>90314.37</v>
+        <v>91412.72</v>
       </c>
       <c r="M21" t="n">
-        <v>93910.83</v>
+        <v>93591.56</v>
       </c>
       <c r="N21" t="n">
-        <v>97507.28999999999</v>
+        <v>95770.39999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>96707.25999999999</v>
+        <v>100290.27</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2282,165 +2284,169 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>90825.86</v>
+        <v>93655.67</v>
       </c>
       <c r="C22" t="n">
-        <v>97860.60000000001</v>
+        <v>93660.83</v>
       </c>
       <c r="D22" t="n">
-        <v>90055.02</v>
+        <v>86003.71000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>93634.42999999999</v>
+        <v>86572.22</v>
       </c>
       <c r="F22" t="n">
-        <v>2806.97</v>
+        <v>-7062.21</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0309</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>7805.58</v>
+        <v>7657.12</v>
       </c>
       <c r="I22" t="n">
-        <v>83705.67999999999</v>
+        <v>82249.45</v>
       </c>
       <c r="J22" t="n">
-        <v>84714.00999999999</v>
+        <v>85667.16</v>
       </c>
       <c r="K22" t="n">
-        <v>88063.36</v>
+        <v>89731.64</v>
       </c>
       <c r="L22" t="n">
-        <v>91412.72</v>
+        <v>93796.12</v>
       </c>
       <c r="M22" t="n">
-        <v>93591.56</v>
+        <v>97537.22</v>
       </c>
       <c r="N22" t="n">
-        <v>95770.39999999999</v>
+        <v>101278.32</v>
       </c>
       <c r="O22" t="n">
-        <v>100290.27</v>
+        <v>105666.18</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>93655.67</v>
+        <v>86566.52</v>
       </c>
       <c r="C23" t="n">
-        <v>93660.83</v>
+        <v>90439.28999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>86003.71000000001</v>
+        <v>75698.89999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>86572.22</v>
+        <v>76974.45</v>
       </c>
       <c r="F23" t="n">
-        <v>-7062.21</v>
+        <v>-9597.77</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.1109</v>
       </c>
       <c r="H23" t="n">
-        <v>7657.12</v>
+        <v>14740.39</v>
       </c>
       <c r="I23" t="n">
-        <v>82249.45</v>
+        <v>78346.59</v>
       </c>
       <c r="J23" t="n">
-        <v>85667.16</v>
+        <v>77285.08</v>
       </c>
       <c r="K23" t="n">
-        <v>89731.64</v>
+        <v>82743.66</v>
       </c>
       <c r="L23" t="n">
-        <v>93796.12</v>
+        <v>88202.24000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>97537.22</v>
+        <v>90400.78</v>
       </c>
       <c r="N23" t="n">
-        <v>101278.32</v>
+        <v>92599.31</v>
       </c>
       <c r="O23" t="n">
-        <v>105666.18</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
+        <v>101317.95</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
@@ -2452,13 +2458,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2468,87 +2476,79 @@
       </c>
       <c r="W23" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>86566.52</v>
+        <v>76968.88</v>
       </c>
       <c r="C24" t="n">
-        <v>90439.28999999999</v>
+        <v>79258.61</v>
       </c>
       <c r="D24" t="n">
-        <v>75698.89999999999</v>
+        <v>60074.2</v>
       </c>
       <c r="E24" t="n">
-        <v>76974.45</v>
+        <v>70264.73</v>
       </c>
       <c r="F24" t="n">
-        <v>-9597.77</v>
+        <v>-6709.72</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.1109</v>
+        <v>-0.0872</v>
       </c>
       <c r="H24" t="n">
-        <v>14740.39</v>
+        <v>19184.41</v>
       </c>
       <c r="I24" t="n">
-        <v>78346.59</v>
+        <v>60958.51</v>
       </c>
       <c r="J24" t="n">
-        <v>77285.08</v>
+        <v>59186.73</v>
       </c>
       <c r="K24" t="n">
-        <v>82743.66</v>
+        <v>69604.25</v>
       </c>
       <c r="L24" t="n">
-        <v>88202.24000000001</v>
+        <v>80021.77</v>
       </c>
       <c r="M24" t="n">
-        <v>90400.78</v>
+        <v>84344.64</v>
       </c>
       <c r="N24" t="n">
-        <v>92599.31</v>
+        <v>88667.50999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>101317.95</v>
+        <v>105179.68</v>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2556,7 +2556,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2566,67 +2566,63 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>76968.88</v>
+        <v>70243.33</v>
       </c>
       <c r="C25" t="n">
-        <v>79258.61</v>
+        <v>71369.97</v>
       </c>
       <c r="D25" t="n">
-        <v>60074.2</v>
+        <v>65092.11</v>
       </c>
       <c r="E25" t="n">
-        <v>70264.73</v>
+        <v>68788.19</v>
       </c>
       <c r="F25" t="n">
-        <v>-6709.72</v>
+        <v>-1476.54</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0872</v>
+        <v>-0.021</v>
       </c>
       <c r="H25" t="n">
-        <v>19184.41</v>
+        <v>6277.86</v>
       </c>
       <c r="I25" t="n">
-        <v>60958.51</v>
+        <v>40889.8</v>
       </c>
       <c r="J25" t="n">
-        <v>59186.73</v>
+        <v>51379.48</v>
       </c>
       <c r="K25" t="n">
-        <v>69604.25</v>
+        <v>60672.52</v>
       </c>
       <c r="L25" t="n">
-        <v>80021.77</v>
+        <v>69965.57000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>84344.64</v>
+        <v>79856.92999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>88667.50999999999</v>
+        <v>89748.28999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>105179.68</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>98443.02</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
       </c>
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2638,60 +2634,64 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>70243.33</v>
+        <v>68782.39999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>71369.97</v>
+        <v>70067.23</v>
       </c>
       <c r="D26" t="n">
-        <v>65092.11</v>
+        <v>65637.42999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>68788.19</v>
+        <v>67659.39</v>
       </c>
       <c r="F26" t="n">
-        <v>-1476.54</v>
+        <v>-1128.8</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.021</v>
+        <v>-0.0164</v>
       </c>
       <c r="H26" t="n">
-        <v>6277.86</v>
+        <v>4429.8</v>
       </c>
       <c r="I26" t="n">
-        <v>40889.8</v>
+        <v>58814.25</v>
       </c>
       <c r="J26" t="n">
-        <v>51379.48</v>
+        <v>62788.9</v>
       </c>
       <c r="K26" t="n">
-        <v>60672.52</v>
+        <v>65649.25999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>69965.57000000001</v>
+        <v>68509.61</v>
       </c>
       <c r="M26" t="n">
-        <v>79856.92999999999</v>
+        <v>71927.12</v>
       </c>
       <c r="N26" t="n">
-        <v>89748.28999999999</v>
+        <v>75344.62</v>
       </c>
       <c r="O26" t="n">
-        <v>98443.02</v>
+        <v>77647.83</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2699,10 +2699,12 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2716,7 +2718,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2730,218 +2732,220 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>68782.39999999999</v>
+        <v>67668.42999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>70067.23</v>
+        <v>69953.53</v>
       </c>
       <c r="D27" t="n">
-        <v>65637.42999999999</v>
+        <v>62553.19</v>
       </c>
       <c r="E27" t="n">
-        <v>67659.39</v>
+        <v>65738.10000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-1128.8</v>
+        <v>-1921.29</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0164</v>
+        <v>-0.0284</v>
       </c>
       <c r="H27" t="n">
-        <v>4429.8</v>
+        <v>7400.34</v>
       </c>
       <c r="I27" t="n">
-        <v>58814.25</v>
+        <v>61207.62</v>
       </c>
       <c r="J27" t="n">
-        <v>62788.9</v>
+        <v>63133.12</v>
       </c>
       <c r="K27" t="n">
-        <v>65649.25999999999</v>
+        <v>65444.49</v>
       </c>
       <c r="L27" t="n">
-        <v>68509.61</v>
+        <v>67755.86</v>
       </c>
       <c r="M27" t="n">
-        <v>71927.12</v>
+        <v>69874.28999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>75344.62</v>
+        <v>71992.72</v>
       </c>
       <c r="O27" t="n">
-        <v>77647.83</v>
+        <v>74497.03999999999</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>67668.42999999999</v>
+        <v>65734.08</v>
       </c>
       <c r="C28" t="n">
-        <v>69953.53</v>
+        <v>74051.8</v>
       </c>
       <c r="D28" t="n">
-        <v>62553.19</v>
+        <v>65303.14</v>
       </c>
       <c r="E28" t="n">
-        <v>65738.10000000001</v>
+        <v>65969.78</v>
       </c>
       <c r="F28" t="n">
-        <v>-1921.29</v>
+        <v>231.68</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0284</v>
+        <v>0.0035</v>
       </c>
       <c r="H28" t="n">
-        <v>7400.34</v>
+        <v>8748.67</v>
       </c>
       <c r="I28" t="n">
-        <v>61207.62</v>
+        <v>55152.84</v>
       </c>
       <c r="J28" t="n">
-        <v>63133.12</v>
+        <v>58080.13</v>
       </c>
       <c r="K28" t="n">
-        <v>65444.49</v>
+        <v>62037.93</v>
       </c>
       <c r="L28" t="n">
-        <v>67755.86</v>
+        <v>65995.73</v>
       </c>
       <c r="M28" t="n">
-        <v>69874.28999999999</v>
+        <v>69438.27</v>
       </c>
       <c r="N28" t="n">
-        <v>71992.72</v>
+        <v>72880.82000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>74497.03999999999</v>
+        <v>77353.88</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>65734.08</v>
+        <v>65969.59</v>
       </c>
       <c r="C29" t="n">
-        <v>74051.8</v>
+        <v>73927.33</v>
       </c>
       <c r="D29" t="n">
-        <v>65303.14</v>
+        <v>65858.00999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>65969.78</v>
+        <v>72789.91</v>
       </c>
       <c r="F29" t="n">
-        <v>231.68</v>
+        <v>6820.13</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.1034</v>
       </c>
       <c r="H29" t="n">
-        <v>8748.67</v>
+        <v>8069.32</v>
       </c>
       <c r="I29" t="n">
-        <v>55152.84</v>
+        <v>56554.47</v>
       </c>
       <c r="J29" t="n">
-        <v>58080.13</v>
+        <v>55367.27</v>
       </c>
       <c r="K29" t="n">
-        <v>62037.93</v>
+        <v>61595.45</v>
       </c>
       <c r="L29" t="n">
-        <v>65995.73</v>
+        <v>67823.63</v>
       </c>
       <c r="M29" t="n">
-        <v>69438.27</v>
+        <v>70344.12</v>
       </c>
       <c r="N29" t="n">
-        <v>72880.82000000001</v>
+        <v>72864.60000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>77353.88</v>
+        <v>82800.47</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2954,7 +2958,7 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -2964,70 +2968,70 @@
       </c>
       <c r="U29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>65969.59</v>
+        <v>72798.17</v>
       </c>
       <c r="C30" t="n">
-        <v>73927.33</v>
+        <v>75988.39999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>65858.00999999999</v>
+        <v>67372.88</v>
       </c>
       <c r="E30" t="n">
-        <v>72789.91</v>
+        <v>67845.21000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>6820.13</v>
+        <v>-4944.7</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.1034</v>
+        <v>-0.0679</v>
       </c>
       <c r="H30" t="n">
-        <v>8069.32</v>
+        <v>8615.52</v>
       </c>
       <c r="I30" t="n">
-        <v>56554.47</v>
+        <v>57788.69</v>
       </c>
       <c r="J30" t="n">
-        <v>55367.27</v>
+        <v>66169.22</v>
       </c>
       <c r="K30" t="n">
-        <v>61595.45</v>
+        <v>68755.25</v>
       </c>
       <c r="L30" t="n">
-        <v>67823.63</v>
+        <v>71341.28999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>70344.12</v>
+        <v>76824.57000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>72864.60000000001</v>
+        <v>82307.86</v>
       </c>
       <c r="O30" t="n">
-        <v>82800.47</v>
+        <v>81996.64999999999</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3035,28 +3039,26 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3070,50 +3072,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>72798.17</v>
+        <v>67843</v>
       </c>
       <c r="C31" t="n">
-        <v>75988.39999999999</v>
+        <v>71985.74000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>67372.88</v>
+        <v>64971.71</v>
       </c>
       <c r="E31" t="n">
-        <v>67845.21000000001</v>
+        <v>65954.92</v>
       </c>
       <c r="F31" t="n">
-        <v>-4944.7</v>
+        <v>-1890.29</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0679</v>
+        <v>-0.0279</v>
       </c>
       <c r="H31" t="n">
-        <v>8615.52</v>
+        <v>7014.04</v>
       </c>
       <c r="I31" t="n">
-        <v>57788.69</v>
+        <v>58757.35</v>
       </c>
       <c r="J31" t="n">
-        <v>66169.22</v>
+        <v>57311.97</v>
       </c>
       <c r="K31" t="n">
-        <v>68755.25</v>
+        <v>63537.45</v>
       </c>
       <c r="L31" t="n">
-        <v>71341.28999999999</v>
+        <v>69762.92</v>
       </c>
       <c r="M31" t="n">
-        <v>76824.57000000001</v>
+        <v>72152.97</v>
       </c>
       <c r="N31" t="n">
-        <v>82307.86</v>
+        <v>74543.02</v>
       </c>
       <c r="O31" t="n">
-        <v>81996.64999999999</v>
+        <v>84603.92</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3126,7 +3128,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3140,64 +3142,60 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>67843</v>
+        <v>65958.35000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>71985.74000000001</v>
+        <v>69230.36</v>
       </c>
       <c r="D32" t="n">
-        <v>64971.71</v>
+        <v>65725.25999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>65954.92</v>
+        <v>68981.89999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>-1890.29</v>
+        <v>3026.98</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0279</v>
+        <v>0.0459</v>
       </c>
       <c r="H32" t="n">
-        <v>7014.04</v>
+        <v>3505.1</v>
       </c>
       <c r="I32" t="n">
-        <v>58757.35</v>
+        <v>57957.67</v>
       </c>
       <c r="J32" t="n">
-        <v>57311.97</v>
+        <v>57678.99</v>
       </c>
       <c r="K32" t="n">
-        <v>63537.45</v>
+        <v>62447.9</v>
       </c>
       <c r="L32" t="n">
-        <v>69762.92</v>
+        <v>67216.82000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>72152.97</v>
+        <v>69461.94</v>
       </c>
       <c r="N32" t="n">
-        <v>74543.02</v>
+        <v>71707.06</v>
       </c>
       <c r="O32" t="n">
-        <v>84603.92</v>
+        <v>78999.78</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3205,79 +3203,83 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>65958.35000000001</v>
+        <v>68982.91</v>
       </c>
       <c r="C33" t="n">
-        <v>69230.36</v>
+        <v>73784.23</v>
       </c>
       <c r="D33" t="n">
-        <v>65725.25999999999</v>
+        <v>67740.50999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>68981.89999999999</v>
+        <v>70753.41</v>
       </c>
       <c r="F33" t="n">
-        <v>3026.98</v>
+        <v>1771.51</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0459</v>
+        <v>0.0257</v>
       </c>
       <c r="H33" t="n">
-        <v>3505.1</v>
+        <v>6043.73</v>
       </c>
       <c r="I33" t="n">
-        <v>57957.67</v>
+        <v>62220.16</v>
       </c>
       <c r="J33" t="n">
-        <v>57678.99</v>
+        <v>66228.84</v>
       </c>
       <c r="K33" t="n">
-        <v>62447.9</v>
+        <v>67229.35000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>67216.82000000001</v>
+        <v>68229.85000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>69461.94</v>
+        <v>70734.45</v>
       </c>
       <c r="N33" t="n">
-        <v>71707.06</v>
+        <v>73239.03999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>78999.78</v>
+        <v>72735.46000000001</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3288,7 +3290,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3298,70 +3300,74 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>68982.91</v>
+        <v>70757.62</v>
       </c>
       <c r="C34" t="n">
-        <v>73784.23</v>
+        <v>78320.67999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>67740.50999999999</v>
+        <v>70588.52</v>
       </c>
       <c r="E34" t="n">
-        <v>70753.41</v>
+        <v>73856.35000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>1771.51</v>
+        <v>3102.95</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0257</v>
+        <v>0.0439</v>
       </c>
       <c r="H34" t="n">
-        <v>6043.73</v>
+        <v>7732.16</v>
       </c>
       <c r="I34" t="n">
-        <v>62220.16</v>
+        <v>61696.78</v>
       </c>
       <c r="J34" t="n">
-        <v>66228.84</v>
+        <v>64705.2</v>
       </c>
       <c r="K34" t="n">
-        <v>67229.35000000001</v>
+        <v>67731.53999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>68229.85000000001</v>
+        <v>70757.89</v>
       </c>
       <c r="M34" t="n">
-        <v>70734.45</v>
+        <v>73775.27</v>
       </c>
       <c r="N34" t="n">
-        <v>73239.03999999999</v>
+        <v>76792.64999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>72735.46000000001</v>
+        <v>79827.96000000001</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3372,7 +3378,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3387,12 +3393,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="V34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3406,50 +3410,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>70757.62</v>
+        <v>73854.25</v>
       </c>
       <c r="C35" t="n">
-        <v>78320.67999999999</v>
+        <v>79468</v>
       </c>
       <c r="D35" t="n">
-        <v>70588.52</v>
+        <v>73775.57000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>73856.35000000001</v>
+        <v>78657.53999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>3102.95</v>
+        <v>4801.19</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0439</v>
+        <v>0.065</v>
       </c>
       <c r="H35" t="n">
-        <v>7732.16</v>
+        <v>5692.43</v>
       </c>
       <c r="I35" t="n">
-        <v>61696.78</v>
+        <v>62856.37</v>
       </c>
       <c r="J35" t="n">
-        <v>64705.2</v>
+        <v>65825.07000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>67731.53999999999</v>
+        <v>69990.27</v>
       </c>
       <c r="L35" t="n">
-        <v>70757.89</v>
+        <v>74155.48</v>
       </c>
       <c r="M35" t="n">
-        <v>73775.27</v>
+        <v>77722.42999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>76792.64999999999</v>
+        <v>81289.38</v>
       </c>
       <c r="O35" t="n">
-        <v>79827.96000000001</v>
+        <v>86052.84</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3460,7 +3464,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3470,15 +3474,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3492,50 +3494,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>73854.25</v>
+        <v>78661.02</v>
       </c>
       <c r="C36" t="n">
-        <v>79468</v>
+        <v>79488.17</v>
       </c>
       <c r="D36" t="n">
-        <v>73775.57000000001</v>
+        <v>74958.57000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>78657.53999999999</v>
+        <v>78538.23</v>
       </c>
       <c r="F36" t="n">
-        <v>4801.19</v>
+        <v>-119.31</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.065</v>
+        <v>-0.0015</v>
       </c>
       <c r="H36" t="n">
-        <v>5692.43</v>
+        <v>4529.6</v>
       </c>
       <c r="I36" t="n">
-        <v>62856.37</v>
+        <v>68083.14</v>
       </c>
       <c r="J36" t="n">
-        <v>65825.07000000001</v>
+        <v>73982.99000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>69990.27</v>
+        <v>75811.32000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>74155.48</v>
+        <v>77639.66</v>
       </c>
       <c r="M36" t="n">
-        <v>77722.42999999999</v>
+        <v>81503.75</v>
       </c>
       <c r="N36" t="n">
-        <v>81289.38</v>
+        <v>85367.85000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>86052.84</v>
+        <v>85160.42999999999</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3543,18 +3545,18 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3562,64 +3564,64 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>78661.02</v>
+        <v>78540.28999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>79488.17</v>
+        <v>82792.21000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>74958.57000000001</v>
+        <v>78217.96000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>78538.23</v>
+        <v>82138.92999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>-119.31</v>
+        <v>3600.7</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0458</v>
       </c>
       <c r="H37" t="n">
-        <v>4529.6</v>
+        <v>4574.25</v>
       </c>
       <c r="I37" t="n">
-        <v>68083.14</v>
+        <v>70428.97</v>
       </c>
       <c r="J37" t="n">
-        <v>73982.99000000001</v>
+        <v>74666.05</v>
       </c>
       <c r="K37" t="n">
-        <v>75811.32000000001</v>
+        <v>76273.42999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>77639.66</v>
+        <v>77880.8</v>
       </c>
       <c r="M37" t="n">
-        <v>81503.75</v>
+        <v>80803.03</v>
       </c>
       <c r="N37" t="n">
-        <v>85367.85000000001</v>
+        <v>83725.25999999999</v>
       </c>
       <c r="O37" t="n">
-        <v>85160.42999999999</v>
+        <v>84017.77</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3627,18 +3629,18 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3646,83 +3648,85 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>78540.28999999999</v>
+        <v>82139.05</v>
       </c>
       <c r="C38" t="n">
-        <v>82792.21000000001</v>
+        <v>82326.23</v>
       </c>
       <c r="D38" t="n">
-        <v>78217.96000000001</v>
+        <v>76783.41</v>
       </c>
       <c r="E38" t="n">
-        <v>82138.92999999999</v>
+        <v>77429.35000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>3600.7</v>
+        <v>-4709.58</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0458</v>
+        <v>-0.0573</v>
       </c>
       <c r="H38" t="n">
-        <v>4574.25</v>
+        <v>5542.82</v>
       </c>
       <c r="I38" t="n">
-        <v>70428.97</v>
+        <v>73643.71000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>74666.05</v>
+        <v>78381.60000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>76273.42999999999</v>
+        <v>79851.8</v>
       </c>
       <c r="L38" t="n">
-        <v>77880.8</v>
+        <v>81322.00999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>80803.03</v>
+        <v>84426.05</v>
       </c>
       <c r="N38" t="n">
-        <v>83725.25999999999</v>
+        <v>87530.10000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>84017.77</v>
+        <v>87366.46000000001</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3730,81 +3734,75 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>82139.05</v>
+        <v>77426.34</v>
       </c>
       <c r="C39" t="n">
-        <v>82326.23</v>
+        <v>78100.56</v>
       </c>
       <c r="D39" t="n">
-        <v>76783.41</v>
+        <v>74255.23</v>
       </c>
       <c r="E39" t="n">
-        <v>77429.35000000001</v>
+        <v>76981.12</v>
       </c>
       <c r="F39" t="n">
-        <v>-4709.58</v>
+        <v>-448.23</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0573</v>
+        <v>-0.0058</v>
       </c>
       <c r="H39" t="n">
-        <v>5542.82</v>
+        <v>3845.33</v>
       </c>
       <c r="I39" t="n">
-        <v>73643.71000000001</v>
+        <v>71240.59</v>
       </c>
       <c r="J39" t="n">
-        <v>78381.60000000001</v>
+        <v>70823.78999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>79851.8</v>
+        <v>74657.94</v>
       </c>
       <c r="L39" t="n">
-        <v>81322.00999999999</v>
+        <v>78492.09</v>
       </c>
       <c r="M39" t="n">
-        <v>84426.05</v>
+        <v>80200.75999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>87530.10000000001</v>
+        <v>81909.44</v>
       </c>
       <c r="O39" t="n">
-        <v>87366.46000000001</v>
+        <v>87869.05</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q39" s="6" t="n">
+        <v/>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3816,7 +3814,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3826,65 +3824,67 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>77426.34</v>
+        <v>76981.12</v>
       </c>
       <c r="C40" t="n">
-        <v>78100.56</v>
+        <v>77990.87</v>
       </c>
       <c r="D40" t="n">
-        <v>74255.23</v>
+        <v>72435.62</v>
       </c>
       <c r="E40" t="n">
-        <v>76981.12</v>
+        <v>73579.69</v>
       </c>
       <c r="F40" t="n">
-        <v>-448.23</v>
+        <v>-3401.44</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0442</v>
       </c>
       <c r="H40" t="n">
-        <v>3845.33</v>
+        <v>5555.24</v>
       </c>
       <c r="I40" t="n">
-        <v>71240.59</v>
+        <v>70409.91</v>
       </c>
       <c r="J40" t="n">
-        <v>70823.78999999999</v>
+        <v>73537.41</v>
       </c>
       <c r="K40" t="n">
-        <v>74657.94</v>
+        <v>75058.46000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>78492.09</v>
+        <v>76579.50999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>80200.75999999999</v>
+        <v>78903.78999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>81909.44</v>
+        <v>81228.07000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>87869.05</v>
+        <v>81945.89</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3896,7 +3896,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3906,57 +3906,59 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>76981.12</v>
+        <v>73580.21000000001</v>
       </c>
       <c r="C41" t="n">
-        <v>77990.87</v>
+        <v>73969.57000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>72435.62</v>
+        <v>59108.92</v>
       </c>
       <c r="E41" t="n">
-        <v>73579.69</v>
+        <v>63239.52</v>
       </c>
       <c r="F41" t="n">
-        <v>-3401.44</v>
+        <v>-10340.17</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0442</v>
+        <v>-0.1405</v>
       </c>
       <c r="H41" t="n">
-        <v>5555.24</v>
+        <v>14860.65</v>
       </c>
       <c r="I41" t="n">
-        <v>70409.91</v>
+        <v>66880.38</v>
       </c>
       <c r="J41" t="n">
-        <v>73537.41</v>
+        <v>67207.67</v>
       </c>
       <c r="K41" t="n">
-        <v>75058.46000000001</v>
+        <v>70802.07000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>76579.50999999999</v>
+        <v>74396.47</v>
       </c>
       <c r="M41" t="n">
-        <v>78903.78999999999</v>
+        <v>76357.31</v>
       </c>
       <c r="N41" t="n">
-        <v>81228.07000000001</v>
+        <v>78318.14999999999</v>
       </c>
       <c r="O41" t="n">
-        <v>81945.89</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
+        <v>83546.11</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
@@ -3964,7 +3966,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3978,7 +3980,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3988,69 +3990,63 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>73580.21000000001</v>
+        <v>63244.09</v>
       </c>
       <c r="C42" t="n">
-        <v>73969.57000000001</v>
+        <v>65749.78</v>
       </c>
       <c r="D42" t="n">
-        <v>59108.92</v>
+        <v>60756.69</v>
       </c>
       <c r="E42" t="n">
-        <v>63239.52</v>
+        <v>65710.39999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>-10340.17</v>
+        <v>2470.88</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.1405</v>
+        <v>0.0391</v>
       </c>
       <c r="H42" t="n">
-        <v>14860.65</v>
+        <v>4993.09</v>
       </c>
       <c r="I42" t="n">
-        <v>66880.38</v>
+        <v>44248.27</v>
       </c>
       <c r="J42" t="n">
-        <v>67207.67</v>
+        <v>46729</v>
       </c>
       <c r="K42" t="n">
-        <v>70802.07000000001</v>
+        <v>55809.19</v>
       </c>
       <c r="L42" t="n">
-        <v>74396.47</v>
+        <v>64889.38</v>
       </c>
       <c r="M42" t="n">
-        <v>76357.31</v>
+        <v>70669.85000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>78318.14999999999</v>
+        <v>76450.31</v>
       </c>
       <c r="O42" t="n">
-        <v>83546.11</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>88830.22</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4062,60 +4058,64 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>63244.09</v>
+        <v>65711.11</v>
       </c>
       <c r="C43" t="n">
-        <v>65749.78</v>
+        <v>67248.13</v>
       </c>
       <c r="D43" t="n">
-        <v>60756.69</v>
+        <v>62201.14</v>
       </c>
       <c r="E43" t="n">
-        <v>65710.39999999999</v>
+        <v>63237.54</v>
       </c>
       <c r="F43" t="n">
-        <v>2470.88</v>
+        <v>-2472.86</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0391</v>
+        <v>-0.0376</v>
       </c>
       <c r="H43" t="n">
-        <v>4993.09</v>
+        <v>5046.99</v>
       </c>
       <c r="I43" t="n">
-        <v>44248.27</v>
+        <v>55763.59</v>
       </c>
       <c r="J43" t="n">
-        <v>46729</v>
+        <v>61945.89</v>
       </c>
       <c r="K43" t="n">
-        <v>55809.19</v>
+        <v>63213.85</v>
       </c>
       <c r="L43" t="n">
-        <v>64889.38</v>
+        <v>64481.82</v>
       </c>
       <c r="M43" t="n">
-        <v>70669.85000000001</v>
+        <v>68206.95</v>
       </c>
       <c r="N43" t="n">
-        <v>76450.31</v>
+        <v>71932.07000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>88830.22</v>
+        <v>70742.88</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4123,12 +4123,14 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4140,7 +4142,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4154,50 +4156,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>65711.11</v>
+        <v>63240.79</v>
       </c>
       <c r="C44" t="n">
-        <v>67248.13</v>
+        <v>65544</v>
       </c>
       <c r="D44" t="n">
-        <v>62201.14</v>
+        <v>58075.92</v>
       </c>
       <c r="E44" t="n">
-        <v>63237.54</v>
+        <v>59532.34</v>
       </c>
       <c r="F44" t="n">
-        <v>-2472.86</v>
+        <v>-3705.2</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0376</v>
+        <v>-0.0586</v>
       </c>
       <c r="H44" t="n">
-        <v>5046.99</v>
+        <v>7468.08</v>
       </c>
       <c r="I44" t="n">
-        <v>55763.59</v>
+        <v>57154.16</v>
       </c>
       <c r="J44" t="n">
-        <v>61945.89</v>
+        <v>57447</v>
       </c>
       <c r="K44" t="n">
-        <v>63213.85</v>
+        <v>60714.04</v>
       </c>
       <c r="L44" t="n">
-        <v>64481.82</v>
+        <v>63981.09</v>
       </c>
       <c r="M44" t="n">
-        <v>68206.95</v>
+        <v>65761.03</v>
       </c>
       <c r="N44" t="n">
-        <v>71932.07000000001</v>
+        <v>67540.98</v>
       </c>
       <c r="O44" t="n">
-        <v>70742.88</v>
+        <v>72295.12</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4210,7 +4212,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4224,64 +4226,60 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>63240.79</v>
+        <v>59522.79</v>
       </c>
       <c r="C45" t="n">
-        <v>65544</v>
+        <v>63935.85</v>
       </c>
       <c r="D45" t="n">
-        <v>58075.92</v>
+        <v>57747.77</v>
       </c>
       <c r="E45" t="n">
-        <v>59532.34</v>
+        <v>63547.88</v>
       </c>
       <c r="F45" t="n">
-        <v>-3705.2</v>
+        <v>4015.54</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0586</v>
+        <v>0.0675</v>
       </c>
       <c r="H45" t="n">
-        <v>7468.08</v>
+        <v>6188.08</v>
       </c>
       <c r="I45" t="n">
-        <v>57154.16</v>
+        <v>50607.84</v>
       </c>
       <c r="J45" t="n">
-        <v>57447</v>
+        <v>50925.45</v>
       </c>
       <c r="K45" t="n">
-        <v>60714.04</v>
+        <v>55798.3</v>
       </c>
       <c r="L45" t="n">
-        <v>63981.09</v>
+        <v>60671.15</v>
       </c>
       <c r="M45" t="n">
-        <v>65761.03</v>
+        <v>63266.38</v>
       </c>
       <c r="N45" t="n">
-        <v>67540.98</v>
+        <v>65861.61</v>
       </c>
       <c r="O45" t="n">
-        <v>72295.12</v>
+        <v>73012.08</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4289,79 +4287,83 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>59522.79</v>
+        <v>63551.02</v>
       </c>
       <c r="C46" t="n">
-        <v>63935.85</v>
+        <v>64658.97</v>
       </c>
       <c r="D46" t="n">
-        <v>57747.77</v>
+        <v>61275.83</v>
       </c>
       <c r="E46" t="n">
-        <v>63547.88</v>
+        <v>63758.22</v>
       </c>
       <c r="F46" t="n">
-        <v>4015.54</v>
+        <v>210.34</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0675</v>
+        <v>0.0033</v>
       </c>
       <c r="H46" t="n">
-        <v>6188.08</v>
+        <v>3383.14</v>
       </c>
       <c r="I46" t="n">
-        <v>50607.84</v>
+        <v>51559.68</v>
       </c>
       <c r="J46" t="n">
-        <v>50925.45</v>
+        <v>58712.84</v>
       </c>
       <c r="K46" t="n">
-        <v>55798.3</v>
+        <v>60453.84</v>
       </c>
       <c r="L46" t="n">
-        <v>60671.15</v>
+        <v>62194.84</v>
       </c>
       <c r="M46" t="n">
-        <v>63266.38</v>
+        <v>66641.92</v>
       </c>
       <c r="N46" t="n">
-        <v>65861.61</v>
+        <v>71089</v>
       </c>
       <c r="O46" t="n">
-        <v>73012.08</v>
+        <v>70123.92999999999</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4372,15 +4374,13 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4388,64 +4388,64 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>63551.02</v>
+        <v>63757.17</v>
       </c>
       <c r="C47" t="n">
-        <v>64658.97</v>
+        <v>65507.59</v>
       </c>
       <c r="D47" t="n">
-        <v>61275.83</v>
+        <v>61769</v>
       </c>
       <c r="E47" t="n">
-        <v>63758.22</v>
+        <v>64690.8</v>
       </c>
       <c r="F47" t="n">
-        <v>210.34</v>
+        <v>932.59</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0146</v>
       </c>
       <c r="H47" t="n">
-        <v>3383.14</v>
+        <v>3738.59</v>
       </c>
       <c r="I47" t="n">
-        <v>51559.68</v>
+        <v>57892.69</v>
       </c>
       <c r="J47" t="n">
-        <v>58712.84</v>
+        <v>60770.49</v>
       </c>
       <c r="K47" t="n">
-        <v>60453.84</v>
+        <v>62066.65</v>
       </c>
       <c r="L47" t="n">
-        <v>62194.84</v>
+        <v>63362.81</v>
       </c>
       <c r="M47" t="n">
-        <v>66641.92</v>
+        <v>65449.79</v>
       </c>
       <c r="N47" t="n">
-        <v>71089</v>
+        <v>67536.77</v>
       </c>
       <c r="O47" t="n">
-        <v>70123.92999999999</v>
+        <v>68042.11</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4453,16 +4453,20 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4470,7 +4474,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4484,50 +4488,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>63757.17</v>
+        <v>64684.42</v>
       </c>
       <c r="C48" t="n">
-        <v>65507.59</v>
+        <v>66910.06</v>
       </c>
       <c r="D48" t="n">
-        <v>61769</v>
+        <v>63686.04</v>
       </c>
       <c r="E48" t="n">
-        <v>64690.8</v>
+        <v>65340.3</v>
       </c>
       <c r="F48" t="n">
-        <v>932.59</v>
+        <v>649.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.01</v>
       </c>
       <c r="H48" t="n">
-        <v>3738.59</v>
+        <v>3224.03</v>
       </c>
       <c r="I48" t="n">
-        <v>57892.69</v>
+        <v>58030.41</v>
       </c>
       <c r="J48" t="n">
-        <v>60770.49</v>
+        <v>61478.46</v>
       </c>
       <c r="K48" t="n">
-        <v>62066.65</v>
+        <v>62821.51</v>
       </c>
       <c r="L48" t="n">
-        <v>63362.81</v>
+        <v>64164.55</v>
       </c>
       <c r="M48" t="n">
-        <v>65449.79</v>
+        <v>66560.10000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>67536.77</v>
+        <v>68955.64999999999</v>
       </c>
       <c r="O48" t="n">
-        <v>68042.11</v>
+        <v>69246.19</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4535,28 +4539,26 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4570,50 +4572,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>64684.42</v>
+        <v>65340.59</v>
       </c>
       <c r="C49" t="n">
-        <v>66910.06</v>
+        <v>65658.34</v>
       </c>
       <c r="D49" t="n">
-        <v>63686.04</v>
+        <v>62233.01</v>
       </c>
       <c r="E49" t="n">
-        <v>65340.3</v>
+        <v>63482</v>
       </c>
       <c r="F49" t="n">
-        <v>649.5</v>
+        <v>-1858.3</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.0284</v>
       </c>
       <c r="H49" t="n">
-        <v>3224.03</v>
+        <v>3425.32</v>
       </c>
       <c r="I49" t="n">
-        <v>58030.41</v>
+        <v>60462.01</v>
       </c>
       <c r="J49" t="n">
-        <v>61478.46</v>
+        <v>62137.4</v>
       </c>
       <c r="K49" t="n">
-        <v>62821.51</v>
+        <v>63728.29</v>
       </c>
       <c r="L49" t="n">
-        <v>64164.55</v>
+        <v>65319.17</v>
       </c>
       <c r="M49" t="n">
-        <v>66560.10000000001</v>
+        <v>66952.31</v>
       </c>
       <c r="N49" t="n">
-        <v>68955.64999999999</v>
+        <v>68585.45</v>
       </c>
       <c r="O49" t="n">
-        <v>69246.19</v>
+        <v>70134.09</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4621,18 +4623,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4640,64 +4642,60 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>65340.59</v>
+        <v>63485.44</v>
       </c>
       <c r="C50" t="n">
-        <v>65658.34</v>
+        <v>65401.69</v>
       </c>
       <c r="D50" t="n">
-        <v>62233.01</v>
+        <v>62226.58</v>
       </c>
       <c r="E50" t="n">
-        <v>63482</v>
+        <v>64844.89</v>
       </c>
       <c r="F50" t="n">
-        <v>-1858.3</v>
+        <v>1362.89</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0284</v>
+        <v>0.0215</v>
       </c>
       <c r="H50" t="n">
-        <v>3425.32</v>
+        <v>3175.11</v>
       </c>
       <c r="I50" t="n">
-        <v>60462.01</v>
+        <v>58807.69</v>
       </c>
       <c r="J50" t="n">
-        <v>62137.4</v>
+        <v>59824.84</v>
       </c>
       <c r="K50" t="n">
-        <v>63728.29</v>
+        <v>61769.34</v>
       </c>
       <c r="L50" t="n">
-        <v>65319.17</v>
+        <v>63713.84</v>
       </c>
       <c r="M50" t="n">
-        <v>66952.31</v>
+        <v>65194.66</v>
       </c>
       <c r="N50" t="n">
-        <v>68585.45</v>
+        <v>66675.49000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>70134.09</v>
+        <v>69083.66</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4705,79 +4703,83 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
       <c r="U50" s="8" t="n">
         <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>63485.44</v>
+        <v>64845.38</v>
       </c>
       <c r="C51" t="n">
-        <v>65401.69</v>
+        <v>65321.84</v>
       </c>
       <c r="D51" t="n">
-        <v>62226.58</v>
+        <v>62487.7</v>
       </c>
       <c r="E51" t="n">
-        <v>64844.89</v>
+        <v>62818.65</v>
       </c>
       <c r="F51" t="n">
-        <v>1362.89</v>
+        <v>-2026.23</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0215</v>
+        <v>-0.0312</v>
       </c>
       <c r="H51" t="n">
-        <v>3175.11</v>
+        <v>2834.14</v>
       </c>
       <c r="I51" t="n">
-        <v>58807.69</v>
+        <v>59051.46</v>
       </c>
       <c r="J51" t="n">
-        <v>59824.84</v>
+        <v>62185.15</v>
       </c>
       <c r="K51" t="n">
-        <v>61769.34</v>
+        <v>63257.33</v>
       </c>
       <c r="L51" t="n">
-        <v>63713.84</v>
+        <v>64329.51</v>
       </c>
       <c r="M51" t="n">
-        <v>65194.66</v>
+        <v>66432.44</v>
       </c>
       <c r="N51" t="n">
-        <v>66675.49000000001</v>
+        <v>68535.38</v>
       </c>
       <c r="O51" t="n">
-        <v>69083.66</v>
+        <v>68576.8</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4785,18 +4787,18 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4804,7 +4806,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4818,50 +4820,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>64845.38</v>
+        <v>62819.38</v>
       </c>
       <c r="C52" t="n">
-        <v>65321.84</v>
+        <v>79463.71000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>62487.7</v>
+        <v>62687.1</v>
       </c>
       <c r="E52" t="n">
-        <v>62818.65</v>
+        <v>77755.27</v>
       </c>
       <c r="F52" t="n">
-        <v>-2026.23</v>
+        <v>14936.61</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0312</v>
+        <v>0.2378</v>
       </c>
       <c r="H52" t="n">
-        <v>2834.14</v>
+        <v>16776.61</v>
       </c>
       <c r="I52" t="n">
-        <v>59051.46</v>
+        <v>59653.56</v>
       </c>
       <c r="J52" t="n">
-        <v>62185.15</v>
+        <v>59441.45</v>
       </c>
       <c r="K52" t="n">
-        <v>63257.33</v>
+        <v>61401.58</v>
       </c>
       <c r="L52" t="n">
-        <v>64329.51</v>
+        <v>63361.71</v>
       </c>
       <c r="M52" t="n">
-        <v>66432.44</v>
+        <v>64235.72</v>
       </c>
       <c r="N52" t="n">
-        <v>68535.38</v>
+        <v>65109.73</v>
       </c>
       <c r="O52" t="n">
-        <v>68576.8</v>
+        <v>68155.98</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4869,83 +4871,83 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
-      </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>62819.38</v>
+        <v>77748.88</v>
       </c>
       <c r="C53" t="n">
-        <v>79463.71000000001</v>
+        <v>81346.95</v>
       </c>
       <c r="D53" t="n">
-        <v>62687.1</v>
+        <v>76688.83</v>
       </c>
       <c r="E53" t="n">
-        <v>77755.27</v>
+        <v>77667.57000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>14936.61</v>
+        <v>-87.7</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.2378</v>
+        <v>-0.0011</v>
       </c>
       <c r="H53" t="n">
-        <v>16776.61</v>
+        <v>4658.12</v>
       </c>
       <c r="I53" t="n">
-        <v>59653.56</v>
+        <v>45910.49</v>
       </c>
       <c r="J53" t="n">
-        <v>59441.45</v>
+        <v>64318.59</v>
       </c>
       <c r="K53" t="n">
-        <v>61401.58</v>
+        <v>69366.96000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>63361.71</v>
+        <v>74415.34</v>
       </c>
       <c r="M53" t="n">
-        <v>64235.72</v>
+        <v>86143.57000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>65109.73</v>
+        <v>97871.8</v>
       </c>
       <c r="O53" t="n">
-        <v>68155.98</v>
+        <v>96240.32000000001</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4956,80 +4958,78 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>77748.88</v>
+        <v>77673.7</v>
       </c>
       <c r="C54" t="n">
-        <v>81346.95</v>
+        <v>82262.21000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>76688.83</v>
+        <v>76248.3</v>
       </c>
       <c r="E54" t="n">
-        <v>77667.57000000001</v>
+        <v>80350.05</v>
       </c>
       <c r="F54" t="n">
-        <v>-87.7</v>
+        <v>2682.48</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0345</v>
       </c>
       <c r="H54" t="n">
-        <v>4658.12</v>
+        <v>6013.91</v>
       </c>
       <c r="I54" t="n">
-        <v>45910.49</v>
+        <v>72030.7</v>
       </c>
       <c r="J54" t="n">
-        <v>64318.59</v>
+        <v>72334.28999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>69366.96000000001</v>
+        <v>75338.50999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>74415.34</v>
+        <v>78342.73</v>
       </c>
       <c r="M54" t="n">
-        <v>86143.57000000001</v>
+        <v>79996.63</v>
       </c>
       <c r="N54" t="n">
-        <v>97871.8</v>
+        <v>81650.53999999999</v>
       </c>
       <c r="O54" t="n">
-        <v>96240.32000000001</v>
+        <v>86005.08</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5040,21 +5040,25 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5068,50 +5072,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>77673.7</v>
+        <v>80349.2</v>
       </c>
       <c r="C55" t="n">
-        <v>82262.21000000001</v>
+        <v>80432.31</v>
       </c>
       <c r="D55" t="n">
-        <v>76248.3</v>
+        <v>76162.91</v>
       </c>
       <c r="E55" t="n">
-        <v>80350.05</v>
+        <v>76838.16</v>
       </c>
       <c r="F55" t="n">
-        <v>2682.48</v>
+        <v>-3511.89</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0345</v>
+        <v>-0.0437</v>
       </c>
       <c r="H55" t="n">
-        <v>6013.91</v>
+        <v>4269.4</v>
       </c>
       <c r="I55" t="n">
-        <v>72030.7</v>
+        <v>70234.39999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>72334.28999999999</v>
+        <v>74883.53999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>75338.50999999999</v>
+        <v>77343.09</v>
       </c>
       <c r="L55" t="n">
-        <v>78342.73</v>
+        <v>79802.64999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>79996.63</v>
+        <v>83357</v>
       </c>
       <c r="N55" t="n">
-        <v>81650.53999999999</v>
+        <v>86911.35000000001</v>
       </c>
       <c r="O55" t="n">
-        <v>86005.08</v>
+        <v>88276.12</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5119,85 +5123,83 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>80349.2</v>
+        <v>76830.28</v>
       </c>
       <c r="C56" t="n">
-        <v>80432.31</v>
+        <v>81911.14</v>
       </c>
       <c r="D56" t="n">
-        <v>76162.91</v>
+        <v>74944.59</v>
       </c>
       <c r="E56" t="n">
-        <v>76838.16</v>
+        <v>81142.61</v>
       </c>
       <c r="F56" t="n">
-        <v>-3511.89</v>
+        <v>4304.45</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0437</v>
+        <v>0.056</v>
       </c>
       <c r="H56" t="n">
-        <v>4269.4</v>
+        <v>6966.55</v>
       </c>
       <c r="I56" t="n">
-        <v>70234.39999999999</v>
+        <v>71893.52</v>
       </c>
       <c r="J56" t="n">
-        <v>74883.53999999999</v>
+        <v>71839.03</v>
       </c>
       <c r="K56" t="n">
-        <v>77343.09</v>
+        <v>74703.46000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>79802.64999999999</v>
+        <v>77567.88</v>
       </c>
       <c r="M56" t="n">
-        <v>83357</v>
+        <v>78972.86</v>
       </c>
       <c r="N56" t="n">
-        <v>86911.35000000001</v>
+        <v>80377.83</v>
       </c>
       <c r="O56" t="n">
-        <v>88276.12</v>
+        <v>84701.71000000001</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5205,83 +5207,85 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>76830.28</v>
+        <v>81143.62</v>
       </c>
       <c r="C57" t="n">
-        <v>81911.14</v>
+        <v>87363.75999999999</v>
       </c>
       <c r="D57" t="n">
-        <v>74944.59</v>
+        <v>80867.09</v>
       </c>
       <c r="E57" t="n">
-        <v>81142.61</v>
+        <v>84458.09</v>
       </c>
       <c r="F57" t="n">
-        <v>4304.45</v>
+        <v>3315.48</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.056</v>
+        <v>0.0409</v>
       </c>
       <c r="H57" t="n">
-        <v>6966.55</v>
+        <v>6496.67</v>
       </c>
       <c r="I57" t="n">
-        <v>71893.52</v>
+        <v>67978.05</v>
       </c>
       <c r="J57" t="n">
-        <v>71839.03</v>
+        <v>75533.42999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>74703.46000000001</v>
+        <v>77659.34</v>
       </c>
       <c r="L57" t="n">
-        <v>77567.88</v>
+        <v>79785.24000000001</v>
       </c>
       <c r="M57" t="n">
-        <v>78972.86</v>
+        <v>84625.88</v>
       </c>
       <c r="N57" t="n">
-        <v>80377.83</v>
+        <v>89466.53</v>
       </c>
       <c r="O57" t="n">
-        <v>84701.71000000001</v>
+        <v>88877.69</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5292,82 +5296,76 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>81143.62</v>
+        <v>84457.3</v>
       </c>
       <c r="C58" t="n">
-        <v>87363.75999999999</v>
+        <v>84846.03999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>80867.09</v>
+        <v>82580.83</v>
       </c>
       <c r="E58" t="n">
-        <v>84326.42</v>
+        <v>83128.56</v>
       </c>
       <c r="F58" t="n">
-        <v>3183.81</v>
+        <v>-1329.52</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0392</v>
+        <v>-0.0157</v>
       </c>
       <c r="H58" t="n">
-        <v>6496.67</v>
+        <v>2265.21</v>
       </c>
       <c r="I58" t="n">
-        <v>67978.05</v>
+        <v>74370.41</v>
       </c>
       <c r="J58" t="n">
-        <v>75533.42999999999</v>
+        <v>78132.75</v>
       </c>
       <c r="K58" t="n">
-        <v>77659.34</v>
+        <v>81209.75</v>
       </c>
       <c r="L58" t="n">
-        <v>79785.24000000001</v>
+        <v>84286.75</v>
       </c>
       <c r="M58" t="n">
-        <v>84625.88</v>
+        <v>87706.42</v>
       </c>
       <c r="N58" t="n">
-        <v>89466.53</v>
+        <v>91126.09</v>
       </c>
       <c r="O58" t="n">
-        <v>88877.69</v>
+        <v>93860.42999999999</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5380,13 +5378,11 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5394,12 +5390,16 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>6086.31</v>
       </c>
       <c r="I2" t="n">
-        <v>101251.05</v>
+        <v>101438.81</v>
       </c>
       <c r="J2" t="n">
-        <v>100891.1</v>
+        <v>101125.8</v>
       </c>
       <c r="K2" t="n">
-        <v>105140.01</v>
+        <v>105233.89</v>
       </c>
       <c r="L2" t="n">
-        <v>109388.93</v>
+        <v>109341.99</v>
       </c>
       <c r="M2" t="n">
-        <v>111333.41</v>
+        <v>111239.53</v>
       </c>
       <c r="N2" t="n">
-        <v>113277.89</v>
+        <v>113137.07</v>
       </c>
       <c r="O2" t="n">
-        <v>119831.24</v>
+        <v>119455.71</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5326,25 +5326,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>84457.3</v>
+        <v>84454.12</v>
       </c>
       <c r="C58" t="n">
-        <v>84846.03999999999</v>
+        <v>84972.66</v>
       </c>
       <c r="D58" t="n">
-        <v>82580.83</v>
+        <v>82570.72</v>
       </c>
       <c r="E58" t="n">
-        <v>83128.56</v>
+        <v>83581.52</v>
       </c>
       <c r="F58" t="n">
-        <v>-1329.52</v>
+        <v>-876.5599999999999</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0104</v>
       </c>
       <c r="H58" t="n">
-        <v>2265.21</v>
+        <v>2401.95</v>
       </c>
       <c r="I58" t="n">
         <v>74370.41</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5329,22 +5329,22 @@
         <v>84454.12</v>
       </c>
       <c r="C58" t="n">
-        <v>84972.66</v>
+        <v>85581.34</v>
       </c>
       <c r="D58" t="n">
         <v>82570.72</v>
       </c>
       <c r="E58" t="n">
-        <v>83581.52</v>
+        <v>83694.34</v>
       </c>
       <c r="F58" t="n">
-        <v>-876.5599999999999</v>
+        <v>-763.74</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0104</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>2401.95</v>
+        <v>3010.62</v>
       </c>
       <c r="I58" t="n">
         <v>74370.41</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5329,22 +5329,22 @@
         <v>84454.12</v>
       </c>
       <c r="C58" t="n">
-        <v>85581.34</v>
+        <v>85599.8</v>
       </c>
       <c r="D58" t="n">
         <v>82570.72</v>
       </c>
       <c r="E58" t="n">
-        <v>83694.34</v>
+        <v>84728.34</v>
       </c>
       <c r="F58" t="n">
-        <v>-763.74</v>
+        <v>270.26</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.0032</v>
       </c>
       <c r="H58" t="n">
-        <v>3010.62</v>
+        <v>3029.09</v>
       </c>
       <c r="I58" t="n">
         <v>74370.41</v>
@@ -5376,9 +5376,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>6086.31</v>
       </c>
       <c r="I2" t="n">
-        <v>101438.81</v>
+        <v>106718.31</v>
       </c>
       <c r="J2" t="n">
-        <v>101125.8</v>
+        <v>106569.81</v>
       </c>
       <c r="K2" t="n">
-        <v>105233.89</v>
+        <v>107543.54</v>
       </c>
       <c r="L2" t="n">
-        <v>109341.99</v>
+        <v>108517.27</v>
       </c>
       <c r="M2" t="n">
-        <v>111239.53</v>
+        <v>108929.88</v>
       </c>
       <c r="N2" t="n">
-        <v>113137.07</v>
+        <v>109342.5</v>
       </c>
       <c r="O2" t="n">
-        <v>119455.71</v>
+        <v>110877.34</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -695,17 +697,19 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
-      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
@@ -713,7 +717,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -5329,22 +5333,22 @@
         <v>84454.12</v>
       </c>
       <c r="C58" t="n">
-        <v>85599.8</v>
+        <v>87146.35000000001</v>
       </c>
       <c r="D58" t="n">
         <v>82570.72</v>
       </c>
       <c r="E58" t="n">
-        <v>84728.34</v>
+        <v>86329.17</v>
       </c>
       <c r="F58" t="n">
-        <v>270.26</v>
+        <v>1871.09</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0222</v>
       </c>
       <c r="H58" t="n">
-        <v>3029.09</v>
+        <v>4575.63</v>
       </c>
       <c r="I58" t="n">
         <v>74370.41</v>
@@ -5378,11 +5382,13 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108228.75</v>
+        <v>111163.02</v>
       </c>
       <c r="C2" t="n">
-        <v>113357.49</v>
+        <v>116769.38</v>
       </c>
       <c r="D2" t="n">
-        <v>107271.18</v>
+        <v>110630.61</v>
       </c>
       <c r="E2" t="n">
-        <v>111167.62</v>
+        <v>115407.66</v>
       </c>
       <c r="F2" t="n">
-        <v>2930.91</v>
+        <v>4240.04</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0271</v>
+        <v>0.0381</v>
       </c>
       <c r="H2" t="n">
-        <v>6086.31</v>
+        <v>6138.77</v>
       </c>
       <c r="I2" t="n">
-        <v>106718.31</v>
+        <v>101184.87</v>
       </c>
       <c r="J2" t="n">
-        <v>106569.81</v>
+        <v>105507.95</v>
       </c>
       <c r="K2" t="n">
-        <v>107543.54</v>
+        <v>108124.46</v>
       </c>
       <c r="L2" t="n">
-        <v>108517.27</v>
+        <v>110740.98</v>
       </c>
       <c r="M2" t="n">
-        <v>108929.88</v>
+        <v>114210.77</v>
       </c>
       <c r="N2" t="n">
-        <v>109342.5</v>
+        <v>117680.57</v>
       </c>
       <c r="O2" t="n">
-        <v>110877.34</v>
+        <v>119443.8</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,10 +685,8 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -697,77 +695,69 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
+      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>111163.02</v>
+        <v>115399.63</v>
       </c>
       <c r="C3" t="n">
-        <v>116769.38</v>
+        <v>117911.79</v>
       </c>
       <c r="D3" t="n">
-        <v>110630.61</v>
+        <v>114461.06</v>
       </c>
       <c r="E3" t="n">
-        <v>115407.66</v>
+        <v>115306.09</v>
       </c>
       <c r="F3" t="n">
-        <v>4240.04</v>
+        <v>-101.56</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0381</v>
+        <v>-0.0009</v>
       </c>
       <c r="H3" t="n">
-        <v>6138.77</v>
+        <v>3450.73</v>
       </c>
       <c r="I3" t="n">
-        <v>101184.87</v>
+        <v>104491.84</v>
       </c>
       <c r="J3" t="n">
-        <v>105507.95</v>
+        <v>110122.71</v>
       </c>
       <c r="K3" t="n">
-        <v>108124.46</v>
+        <v>112338.27</v>
       </c>
       <c r="L3" t="n">
-        <v>110740.98</v>
+        <v>114553.83</v>
       </c>
       <c r="M3" t="n">
-        <v>114210.77</v>
+        <v>118477.04</v>
       </c>
       <c r="N3" t="n">
-        <v>117680.57</v>
+        <v>122400.26</v>
       </c>
       <c r="O3" t="n">
-        <v>119443.8</v>
+        <v>122908.16</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -780,13 +770,11 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -799,68 +787,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>115399.63</v>
+        <v>115309.22</v>
       </c>
       <c r="C4" t="n">
-        <v>117911.79</v>
+        <v>115431.31</v>
       </c>
       <c r="D4" t="n">
-        <v>114461.06</v>
+        <v>108713.4</v>
       </c>
       <c r="E4" t="n">
-        <v>115306.09</v>
+        <v>112122.64</v>
       </c>
       <c r="F4" t="n">
-        <v>-101.56</v>
+        <v>-3183.45</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0276</v>
       </c>
       <c r="H4" t="n">
-        <v>3450.73</v>
+        <v>6717.91</v>
       </c>
       <c r="I4" t="n">
-        <v>104491.84</v>
+        <v>111010.34</v>
       </c>
       <c r="J4" t="n">
-        <v>110122.71</v>
+        <v>111415.2</v>
       </c>
       <c r="K4" t="n">
-        <v>112338.27</v>
+        <v>113580.73</v>
       </c>
       <c r="L4" t="n">
-        <v>114553.83</v>
+        <v>115746.26</v>
       </c>
       <c r="M4" t="n">
-        <v>118477.04</v>
+        <v>117031.46</v>
       </c>
       <c r="N4" t="n">
-        <v>122400.26</v>
+        <v>118316.65</v>
       </c>
       <c r="O4" t="n">
-        <v>122908.16</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>121362.52</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -879,237 +877,233 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>115309.22</v>
+        <v>112117.88</v>
       </c>
       <c r="C5" t="n">
-        <v>115431.31</v>
+        <v>125559.21</v>
       </c>
       <c r="D5" t="n">
-        <v>108713.4</v>
+        <v>111589.95</v>
       </c>
       <c r="E5" t="n">
-        <v>112122.64</v>
+        <v>123513.48</v>
       </c>
       <c r="F5" t="n">
-        <v>-3183.45</v>
+        <v>11390.84</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0276</v>
+        <v>0.1016</v>
       </c>
       <c r="H5" t="n">
-        <v>6717.91</v>
+        <v>13969.26</v>
       </c>
       <c r="I5" t="n">
-        <v>111010.34</v>
+        <v>101995.48</v>
       </c>
       <c r="J5" t="n">
-        <v>111415.2</v>
+        <v>105429.87</v>
       </c>
       <c r="K5" t="n">
-        <v>113580.73</v>
+        <v>108763.68</v>
       </c>
       <c r="L5" t="n">
-        <v>115746.26</v>
+        <v>112097.5</v>
       </c>
       <c r="M5" t="n">
-        <v>117031.46</v>
+        <v>115481.6</v>
       </c>
       <c r="N5" t="n">
-        <v>118316.65</v>
+        <v>118865.7</v>
       </c>
       <c r="O5" t="n">
-        <v>121362.52</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
+        <v>122149.23</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
-      </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>112117.88</v>
+        <v>123510.45</v>
       </c>
       <c r="C6" t="n">
-        <v>125559.21</v>
+        <v>126198.07</v>
       </c>
       <c r="D6" t="n">
-        <v>111589.95</v>
+        <v>104582.41</v>
       </c>
       <c r="E6" t="n">
-        <v>123513.48</v>
+        <v>115169.77</v>
       </c>
       <c r="F6" t="n">
-        <v>11390.84</v>
+        <v>-8343.709999999999</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.1016</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>13969.26</v>
+        <v>21615.66</v>
       </c>
       <c r="I6" t="n">
-        <v>101995.48</v>
+        <v>97620.7</v>
       </c>
       <c r="J6" t="n">
-        <v>105429.87</v>
+        <v>112013.67</v>
       </c>
       <c r="K6" t="n">
-        <v>108763.68</v>
+        <v>116528.85</v>
       </c>
       <c r="L6" t="n">
-        <v>112097.5</v>
+        <v>121044.03</v>
       </c>
       <c r="M6" t="n">
-        <v>115481.6</v>
+        <v>130498.11</v>
       </c>
       <c r="N6" t="n">
-        <v>118865.7</v>
+        <v>139952.18</v>
       </c>
       <c r="O6" t="n">
-        <v>122149.23</v>
+        <v>139528.47</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
+      </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>123510.45</v>
+        <v>115161.68</v>
       </c>
       <c r="C7" t="n">
-        <v>126198.07</v>
+        <v>116020.48</v>
       </c>
       <c r="D7" t="n">
-        <v>104582.41</v>
+        <v>103598.43</v>
       </c>
       <c r="E7" t="n">
-        <v>115169.77</v>
+        <v>108666.71</v>
       </c>
       <c r="F7" t="n">
-        <v>-8343.709999999999</v>
+        <v>-6503.05</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0565</v>
       </c>
       <c r="H7" t="n">
-        <v>21615.66</v>
+        <v>12422.05</v>
       </c>
       <c r="I7" t="n">
-        <v>97620.7</v>
+        <v>82966.75999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>112013.67</v>
+        <v>93443.87</v>
       </c>
       <c r="K7" t="n">
-        <v>116528.85</v>
+        <v>104361.94</v>
       </c>
       <c r="L7" t="n">
-        <v>121044.03</v>
+        <v>115280</v>
       </c>
       <c r="M7" t="n">
-        <v>130498.11</v>
+        <v>125977.59</v>
       </c>
       <c r="N7" t="n">
-        <v>139952.18</v>
+        <v>136675.18</v>
       </c>
       <c r="O7" t="n">
-        <v>139528.47</v>
+        <v>147813.73</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q7" s="6" t="n">
+        <v/>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
@@ -1137,57 +1131,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>115161.68</v>
+        <v>108667.45</v>
       </c>
       <c r="C8" t="n">
-        <v>116020.48</v>
+        <v>115260.91</v>
       </c>
       <c r="D8" t="n">
-        <v>103598.43</v>
+        <v>106778</v>
       </c>
       <c r="E8" t="n">
-        <v>108666.71</v>
+        <v>114472.45</v>
       </c>
       <c r="F8" t="n">
-        <v>-6503.05</v>
+        <v>5805.73</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0565</v>
+        <v>0.0534</v>
       </c>
       <c r="H8" t="n">
-        <v>12422.05</v>
+        <v>8482.91</v>
       </c>
       <c r="I8" t="n">
-        <v>82966.75999999999</v>
+        <v>91176.38</v>
       </c>
       <c r="J8" t="n">
-        <v>93443.87</v>
+        <v>95673.28</v>
       </c>
       <c r="K8" t="n">
-        <v>104361.94</v>
+        <v>102455.68</v>
       </c>
       <c r="L8" t="n">
-        <v>115280</v>
+        <v>109238.08</v>
       </c>
       <c r="M8" t="n">
-        <v>125977.59</v>
+        <v>114877.74</v>
       </c>
       <c r="N8" t="n">
-        <v>136675.18</v>
+        <v>120517.39</v>
       </c>
       <c r="O8" t="n">
-        <v>147813.73</v>
+        <v>128442.54</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1195,19 +1189,19 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1221,77 +1215,79 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>108667.45</v>
+        <v>114479.85</v>
       </c>
       <c r="C9" t="n">
-        <v>115260.91</v>
+        <v>116273.31</v>
       </c>
       <c r="D9" t="n">
-        <v>106778</v>
+        <v>106376.69</v>
       </c>
       <c r="E9" t="n">
-        <v>114472.45</v>
+        <v>110639.62</v>
       </c>
       <c r="F9" t="n">
-        <v>5805.73</v>
+        <v>-3832.82</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0534</v>
+        <v>-0.0335</v>
       </c>
       <c r="H9" t="n">
-        <v>8482.91</v>
+        <v>9896.620000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>91176.38</v>
+        <v>98295.09</v>
       </c>
       <c r="J9" t="n">
-        <v>95673.28</v>
+        <v>107716.04</v>
       </c>
       <c r="K9" t="n">
-        <v>102455.68</v>
+        <v>110230.99</v>
       </c>
       <c r="L9" t="n">
-        <v>109238.08</v>
+        <v>112745.95</v>
       </c>
       <c r="M9" t="n">
-        <v>114877.74</v>
+        <v>118713.9</v>
       </c>
       <c r="N9" t="n">
-        <v>120517.39</v>
+        <v>124681.85</v>
       </c>
       <c r="O9" t="n">
-        <v>128442.54</v>
+        <v>123743.81</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1305,57 +1301,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>114479.85</v>
+        <v>110646.91</v>
       </c>
       <c r="C10" t="n">
-        <v>116273.31</v>
+        <v>110764.91</v>
       </c>
       <c r="D10" t="n">
-        <v>106376.69</v>
+        <v>98962.06</v>
       </c>
       <c r="E10" t="n">
-        <v>110639.62</v>
+        <v>104719.64</v>
       </c>
       <c r="F10" t="n">
-        <v>-3832.82</v>
+        <v>-5919.98</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0335</v>
+        <v>-0.0535</v>
       </c>
       <c r="H10" t="n">
-        <v>9896.620000000001</v>
+        <v>11802.85</v>
       </c>
       <c r="I10" t="n">
-        <v>98295.09</v>
+        <v>96480.06</v>
       </c>
       <c r="J10" t="n">
-        <v>107716.04</v>
+        <v>100400.31</v>
       </c>
       <c r="K10" t="n">
-        <v>110230.99</v>
+        <v>105691.31</v>
       </c>
       <c r="L10" t="n">
-        <v>112745.95</v>
+        <v>110982.31</v>
       </c>
       <c r="M10" t="n">
-        <v>118713.9</v>
+        <v>115587.94</v>
       </c>
       <c r="N10" t="n">
-        <v>124681.85</v>
+        <v>120193.56</v>
       </c>
       <c r="O10" t="n">
-        <v>123743.81</v>
+        <v>126169.94</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1391,69 +1387,69 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>110646.91</v>
+        <v>104723.77</v>
       </c>
       <c r="C11" t="n">
-        <v>110764.91</v>
+        <v>107428.26</v>
       </c>
       <c r="D11" t="n">
-        <v>98962.06</v>
+        <v>92971.16</v>
       </c>
       <c r="E11" t="n">
-        <v>104719.64</v>
+        <v>94177.08</v>
       </c>
       <c r="F11" t="n">
-        <v>-5919.98</v>
+        <v>-10542.56</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0535</v>
+        <v>-0.1007</v>
       </c>
       <c r="H11" t="n">
-        <v>11802.85</v>
+        <v>14457.09</v>
       </c>
       <c r="I11" t="n">
-        <v>96480.06</v>
+        <v>87159.21000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>100400.31</v>
+        <v>92844.87</v>
       </c>
       <c r="K11" t="n">
-        <v>105691.31</v>
+        <v>98818.21000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>110982.31</v>
+        <v>104791.56</v>
       </c>
       <c r="M11" t="n">
-        <v>115587.94</v>
+        <v>110621.07</v>
       </c>
       <c r="N11" t="n">
-        <v>120193.56</v>
+        <v>116450.57</v>
       </c>
       <c r="O11" t="n">
-        <v>126169.94</v>
+        <v>122567.77</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
       <c r="Q11" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
@@ -1484,62 +1480,60 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>104723.77</v>
+        <v>94180.88</v>
       </c>
       <c r="C12" t="n">
-        <v>107428.26</v>
+        <v>95928.37</v>
       </c>
       <c r="D12" t="n">
-        <v>92971.16</v>
+        <v>80659.81</v>
       </c>
       <c r="E12" t="n">
-        <v>94177.08</v>
+        <v>86805.00999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-10542.56</v>
+        <v>-7372.07</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.1007</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>14457.09</v>
+        <v>15268.55</v>
       </c>
       <c r="I12" t="n">
-        <v>87159.21000000001</v>
+        <v>78514.07000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>92844.87</v>
+        <v>76708.67</v>
       </c>
       <c r="K12" t="n">
-        <v>98818.21000000001</v>
+        <v>86948.53</v>
       </c>
       <c r="L12" t="n">
-        <v>104791.56</v>
+        <v>97188.39</v>
       </c>
       <c r="M12" t="n">
-        <v>110621.07</v>
+        <v>101405.62</v>
       </c>
       <c r="N12" t="n">
-        <v>116450.57</v>
+        <v>105622.86</v>
       </c>
       <c r="O12" t="n">
-        <v>122567.77</v>
+        <v>121885.35</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
@@ -1570,50 +1564,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>94180.88</v>
+        <v>86798.77</v>
       </c>
       <c r="C13" t="n">
-        <v>95928.37</v>
+        <v>92969.09</v>
       </c>
       <c r="D13" t="n">
-        <v>80659.81</v>
+        <v>85272.2</v>
       </c>
       <c r="E13" t="n">
-        <v>86805.00999999999</v>
+        <v>90394.31</v>
       </c>
       <c r="F13" t="n">
-        <v>-7372.07</v>
+        <v>3589.3</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.0413</v>
       </c>
       <c r="H13" t="n">
-        <v>15268.55</v>
+        <v>7696.89</v>
       </c>
       <c r="I13" t="n">
-        <v>78514.07000000001</v>
+        <v>65391.26</v>
       </c>
       <c r="J13" t="n">
-        <v>76708.67</v>
+        <v>70791.91</v>
       </c>
       <c r="K13" t="n">
-        <v>86948.53</v>
+        <v>79170.73</v>
       </c>
       <c r="L13" t="n">
-        <v>97188.39</v>
+        <v>87549.55</v>
       </c>
       <c r="M13" t="n">
-        <v>101405.62</v>
+        <v>94439.28999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>105622.86</v>
+        <v>101329.02</v>
       </c>
       <c r="O13" t="n">
-        <v>121885.35</v>
+        <v>111196.92</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1621,14 +1615,12 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1647,57 +1639,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>86798.77</v>
+        <v>90389.11</v>
       </c>
       <c r="C14" t="n">
-        <v>92969.09</v>
+        <v>94060.77</v>
       </c>
       <c r="D14" t="n">
-        <v>85272.2</v>
+        <v>83862.25</v>
       </c>
       <c r="E14" t="n">
-        <v>90394.31</v>
+        <v>90405.64</v>
       </c>
       <c r="F14" t="n">
-        <v>3589.3</v>
+        <v>11.33</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0413</v>
+        <v>0.0001</v>
       </c>
       <c r="H14" t="n">
-        <v>7696.89</v>
+        <v>10198.52</v>
       </c>
       <c r="I14" t="n">
-        <v>65391.26</v>
+        <v>77575.3</v>
       </c>
       <c r="J14" t="n">
-        <v>70791.91</v>
+        <v>83334.25999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>79170.73</v>
+        <v>86545.87</v>
       </c>
       <c r="L14" t="n">
-        <v>87549.55</v>
+        <v>89757.48</v>
       </c>
       <c r="M14" t="n">
-        <v>94439.28999999999</v>
+        <v>94242.75999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>101329.02</v>
+        <v>98728.03999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>111196.92</v>
+        <v>100665.98</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1705,8 +1697,10 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
@@ -1736,50 +1730,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>90389.11</v>
+        <v>90424.59</v>
       </c>
       <c r="C15" t="n">
-        <v>94060.77</v>
+        <v>94601.57000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>83862.25</v>
+        <v>87634.94</v>
       </c>
       <c r="E15" t="n">
-        <v>90405.64</v>
+        <v>88175.17999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>11.33</v>
+        <v>-2230.46</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0247</v>
       </c>
       <c r="H15" t="n">
-        <v>10198.52</v>
+        <v>6966.63</v>
       </c>
       <c r="I15" t="n">
-        <v>77575.3</v>
+        <v>73663.73</v>
       </c>
       <c r="J15" t="n">
-        <v>83334.25999999999</v>
+        <v>80929.17999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>86545.87</v>
+        <v>85306.38</v>
       </c>
       <c r="L15" t="n">
-        <v>89757.48</v>
+        <v>89683.58</v>
       </c>
       <c r="M15" t="n">
-        <v>94242.75999999999</v>
+        <v>95504.89999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>98728.03999999999</v>
+        <v>101326.23</v>
       </c>
       <c r="O15" t="n">
-        <v>100665.98</v>
+        <v>104259.3</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1787,14 +1781,12 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1820,50 +1812,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>90424.59</v>
+        <v>88171.08</v>
       </c>
       <c r="C16" t="n">
-        <v>94601.57000000001</v>
+        <v>90264.57000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>87634.94</v>
+        <v>84436.31</v>
       </c>
       <c r="E16" t="n">
-        <v>88175.17999999999</v>
+        <v>88621.75</v>
       </c>
       <c r="F16" t="n">
-        <v>-2230.46</v>
+        <v>446.57</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0051</v>
       </c>
       <c r="H16" t="n">
-        <v>6966.63</v>
+        <v>5828.26</v>
       </c>
       <c r="I16" t="n">
-        <v>73663.73</v>
+        <v>80668.3</v>
       </c>
       <c r="J16" t="n">
-        <v>80929.17999999999</v>
+        <v>79737.00999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>85306.38</v>
+        <v>84691.86</v>
       </c>
       <c r="L16" t="n">
-        <v>89683.58</v>
+        <v>89646.72</v>
       </c>
       <c r="M16" t="n">
-        <v>95504.89999999999</v>
+        <v>91658.5</v>
       </c>
       <c r="N16" t="n">
-        <v>101326.23</v>
+        <v>93670.28</v>
       </c>
       <c r="O16" t="n">
-        <v>104259.3</v>
+        <v>101568.2</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1871,8 +1863,10 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
@@ -1895,57 +1889,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>88171.08</v>
+        <v>88621.39999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>90264.57000000001</v>
+        <v>90501.92999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>84436.31</v>
+        <v>86411.8</v>
       </c>
       <c r="E17" t="n">
-        <v>88621.75</v>
+        <v>87835.84</v>
       </c>
       <c r="F17" t="n">
-        <v>446.57</v>
+        <v>-785.91</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0051</v>
+        <v>-0.0089</v>
       </c>
       <c r="H17" t="n">
-        <v>5828.26</v>
+        <v>4090.13</v>
       </c>
       <c r="I17" t="n">
-        <v>80668.3</v>
+        <v>78608.05</v>
       </c>
       <c r="J17" t="n">
-        <v>79737.00999999999</v>
+        <v>83429.14999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>84691.86</v>
+        <v>85707.62</v>
       </c>
       <c r="L17" t="n">
-        <v>89646.72</v>
+        <v>87986.10000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>91658.5</v>
+        <v>91535.88</v>
       </c>
       <c r="N17" t="n">
-        <v>93670.28</v>
+        <v>95085.66</v>
       </c>
       <c r="O17" t="n">
-        <v>101568.2</v>
+        <v>96092.83</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1953,10 +1947,8 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R17" s="6" t="n">
+        <v/>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
@@ -1979,57 +1971,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>88621.39999999999</v>
+        <v>87835.78999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>90501.92999999999</v>
+        <v>91712.59</v>
       </c>
       <c r="D18" t="n">
-        <v>86411.8</v>
+        <v>86717.91</v>
       </c>
       <c r="E18" t="n">
-        <v>87835.84</v>
+        <v>91413.49000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-785.91</v>
+        <v>3577.66</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0089</v>
+        <v>0.0407</v>
       </c>
       <c r="H18" t="n">
-        <v>4090.13</v>
+        <v>4994.67</v>
       </c>
       <c r="I18" t="n">
-        <v>78608.05</v>
+        <v>82321.66</v>
       </c>
       <c r="J18" t="n">
-        <v>83429.14999999999</v>
+        <v>83435.19</v>
       </c>
       <c r="K18" t="n">
-        <v>85707.62</v>
+        <v>85790.77</v>
       </c>
       <c r="L18" t="n">
-        <v>87986.10000000001</v>
+        <v>88146.35000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>91535.88</v>
+        <v>89880.89999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>95085.66</v>
+        <v>91615.46000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>96092.83</v>
+        <v>94592.06</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2040,16 +2032,20 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2059,59 +2055,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>87835.78999999999</v>
+        <v>91414.62</v>
       </c>
       <c r="C19" t="n">
-        <v>91712.59</v>
+        <v>94762.07000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>86717.91</v>
+        <v>89233.88</v>
       </c>
       <c r="E19" t="n">
-        <v>91413.49000000001</v>
+        <v>90827.46000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>3577.66</v>
+        <v>-586.03</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0407</v>
+        <v>-0.0064</v>
       </c>
       <c r="H19" t="n">
-        <v>4994.67</v>
+        <v>5528.2</v>
       </c>
       <c r="I19" t="n">
-        <v>82321.66</v>
+        <v>81723.24000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>83435.19</v>
+        <v>87517.94</v>
       </c>
       <c r="K19" t="n">
-        <v>85790.77</v>
+        <v>88916.16</v>
       </c>
       <c r="L19" t="n">
-        <v>88146.35000000001</v>
+        <v>90314.37</v>
       </c>
       <c r="M19" t="n">
-        <v>89880.89999999999</v>
+        <v>93910.83</v>
       </c>
       <c r="N19" t="n">
-        <v>91615.46000000001</v>
+        <v>97507.28999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>94592.06</v>
+        <v>96707.25999999999</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2124,7 +2116,7 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2132,10 +2124,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2145,55 +2135,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>91414.62</v>
+        <v>90825.86</v>
       </c>
       <c r="C20" t="n">
-        <v>94762.07000000001</v>
+        <v>97860.60000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>89233.88</v>
+        <v>90055.02</v>
       </c>
       <c r="E20" t="n">
-        <v>90827.46000000001</v>
+        <v>93634.42999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-586.03</v>
+        <v>2806.97</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0064</v>
+        <v>0.0309</v>
       </c>
       <c r="H20" t="n">
-        <v>5528.2</v>
+        <v>7805.58</v>
       </c>
       <c r="I20" t="n">
-        <v>81723.24000000001</v>
+        <v>83705.67999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>87517.94</v>
+        <v>84714.00999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>88916.16</v>
+        <v>88063.36</v>
       </c>
       <c r="L20" t="n">
-        <v>90314.37</v>
+        <v>91412.72</v>
       </c>
       <c r="M20" t="n">
-        <v>93910.83</v>
+        <v>93591.56</v>
       </c>
       <c r="N20" t="n">
-        <v>97507.28999999999</v>
+        <v>95770.39999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>96707.25999999999</v>
+        <v>100290.27</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2206,17 +2200,19 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2225,84 +2221,80 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>90825.86</v>
+        <v>93655.67</v>
       </c>
       <c r="C21" t="n">
-        <v>97860.60000000001</v>
+        <v>93660.83</v>
       </c>
       <c r="D21" t="n">
-        <v>90055.02</v>
+        <v>86003.71000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>93634.42999999999</v>
+        <v>86572.22</v>
       </c>
       <c r="F21" t="n">
-        <v>2806.97</v>
+        <v>-7062.21</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0309</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>7805.58</v>
+        <v>7657.12</v>
       </c>
       <c r="I21" t="n">
-        <v>83705.67999999999</v>
+        <v>82249.45</v>
       </c>
       <c r="J21" t="n">
-        <v>84714.00999999999</v>
+        <v>85667.16</v>
       </c>
       <c r="K21" t="n">
-        <v>88063.36</v>
+        <v>89731.64</v>
       </c>
       <c r="L21" t="n">
-        <v>91412.72</v>
+        <v>93796.12</v>
       </c>
       <c r="M21" t="n">
-        <v>93591.56</v>
+        <v>97537.22</v>
       </c>
       <c r="N21" t="n">
-        <v>95770.39999999999</v>
+        <v>101278.32</v>
       </c>
       <c r="O21" t="n">
-        <v>100290.27</v>
+        <v>105666.18</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
+      <c r="Q21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
@@ -2311,58 +2303,64 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>93655.67</v>
+        <v>86566.52</v>
       </c>
       <c r="C22" t="n">
-        <v>93660.83</v>
+        <v>90439.28999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>86003.71000000001</v>
+        <v>75698.89999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>86572.22</v>
+        <v>76974.45</v>
       </c>
       <c r="F22" t="n">
-        <v>-7062.21</v>
+        <v>-9597.77</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.1109</v>
       </c>
       <c r="H22" t="n">
-        <v>7657.12</v>
+        <v>14740.39</v>
       </c>
       <c r="I22" t="n">
-        <v>82249.45</v>
+        <v>78346.59</v>
       </c>
       <c r="J22" t="n">
-        <v>85667.16</v>
+        <v>77285.08</v>
       </c>
       <c r="K22" t="n">
-        <v>89731.64</v>
+        <v>82743.66</v>
       </c>
       <c r="L22" t="n">
-        <v>93796.12</v>
+        <v>88202.24000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>97537.22</v>
+        <v>90400.78</v>
       </c>
       <c r="N22" t="n">
-        <v>101278.32</v>
+        <v>92599.31</v>
       </c>
       <c r="O22" t="n">
-        <v>105666.18</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
+        <v>101317.95</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
@@ -2379,8 +2377,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2388,89 +2388,81 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W22" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>86566.52</v>
+        <v>76968.88</v>
       </c>
       <c r="C23" t="n">
-        <v>90439.28999999999</v>
+        <v>79258.61</v>
       </c>
       <c r="D23" t="n">
-        <v>75698.89999999999</v>
+        <v>60074.2</v>
       </c>
       <c r="E23" t="n">
-        <v>76974.45</v>
+        <v>70264.73</v>
       </c>
       <c r="F23" t="n">
-        <v>-9597.77</v>
+        <v>-6709.72</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.1109</v>
+        <v>-0.0872</v>
       </c>
       <c r="H23" t="n">
-        <v>14740.39</v>
+        <v>19184.41</v>
       </c>
       <c r="I23" t="n">
-        <v>78346.59</v>
+        <v>60958.51</v>
       </c>
       <c r="J23" t="n">
-        <v>77285.08</v>
+        <v>59186.73</v>
       </c>
       <c r="K23" t="n">
-        <v>82743.66</v>
+        <v>69604.25</v>
       </c>
       <c r="L23" t="n">
-        <v>88202.24000000001</v>
+        <v>80021.77</v>
       </c>
       <c r="M23" t="n">
-        <v>90400.78</v>
+        <v>84344.64</v>
       </c>
       <c r="N23" t="n">
-        <v>92599.31</v>
+        <v>88667.50999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>101317.95</v>
+        <v>105179.68</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2488,67 +2480,63 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>76968.88</v>
+        <v>70243.33</v>
       </c>
       <c r="C24" t="n">
-        <v>79258.61</v>
+        <v>71369.97</v>
       </c>
       <c r="D24" t="n">
-        <v>60074.2</v>
+        <v>65092.11</v>
       </c>
       <c r="E24" t="n">
-        <v>70264.73</v>
+        <v>68788.19</v>
       </c>
       <c r="F24" t="n">
-        <v>-6709.72</v>
+        <v>-1476.54</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0872</v>
+        <v>-0.021</v>
       </c>
       <c r="H24" t="n">
-        <v>19184.41</v>
+        <v>6277.86</v>
       </c>
       <c r="I24" t="n">
-        <v>60958.51</v>
+        <v>40889.8</v>
       </c>
       <c r="J24" t="n">
-        <v>59186.73</v>
+        <v>51379.48</v>
       </c>
       <c r="K24" t="n">
-        <v>69604.25</v>
+        <v>60672.52</v>
       </c>
       <c r="L24" t="n">
-        <v>80021.77</v>
+        <v>69965.57000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>84344.64</v>
+        <v>79856.92999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>88667.50999999999</v>
+        <v>89748.28999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>105179.68</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>98443.02</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
       </c>
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2565,55 +2553,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>70243.33</v>
+        <v>68782.39999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>71369.97</v>
+        <v>70067.23</v>
       </c>
       <c r="D25" t="n">
-        <v>65092.11</v>
+        <v>65637.42999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>68788.19</v>
+        <v>67659.39</v>
       </c>
       <c r="F25" t="n">
-        <v>-1476.54</v>
+        <v>-1128.8</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.021</v>
+        <v>-0.0164</v>
       </c>
       <c r="H25" t="n">
-        <v>6277.86</v>
+        <v>4429.8</v>
       </c>
       <c r="I25" t="n">
-        <v>40889.8</v>
+        <v>58814.25</v>
       </c>
       <c r="J25" t="n">
-        <v>51379.48</v>
+        <v>62788.9</v>
       </c>
       <c r="K25" t="n">
-        <v>60672.52</v>
+        <v>65649.25999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>69965.57000000001</v>
+        <v>68509.61</v>
       </c>
       <c r="M25" t="n">
-        <v>79856.92999999999</v>
+        <v>71927.12</v>
       </c>
       <c r="N25" t="n">
-        <v>89748.28999999999</v>
+        <v>75344.62</v>
       </c>
       <c r="O25" t="n">
-        <v>98443.02</v>
+        <v>77647.83</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2621,8 +2613,10 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
@@ -2652,70 +2646,74 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>68782.39999999999</v>
+        <v>67668.42999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>70067.23</v>
+        <v>69953.53</v>
       </c>
       <c r="D26" t="n">
-        <v>65637.42999999999</v>
+        <v>62553.19</v>
       </c>
       <c r="E26" t="n">
-        <v>67659.39</v>
+        <v>65738.10000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-1128.8</v>
+        <v>-1921.29</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0164</v>
+        <v>-0.0284</v>
       </c>
       <c r="H26" t="n">
-        <v>4429.8</v>
+        <v>7400.34</v>
       </c>
       <c r="I26" t="n">
-        <v>58814.25</v>
+        <v>61207.62</v>
       </c>
       <c r="J26" t="n">
-        <v>62788.9</v>
+        <v>63133.12</v>
       </c>
       <c r="K26" t="n">
-        <v>65649.25999999999</v>
+        <v>65444.49</v>
       </c>
       <c r="L26" t="n">
-        <v>68509.61</v>
+        <v>67755.86</v>
       </c>
       <c r="M26" t="n">
-        <v>71927.12</v>
+        <v>69874.28999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>75344.62</v>
+        <v>71992.72</v>
       </c>
       <c r="O26" t="n">
-        <v>77647.83</v>
+        <v>74497.03999999999</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
@@ -2727,86 +2725,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>67668.42999999999</v>
+        <v>65734.08</v>
       </c>
       <c r="C27" t="n">
-        <v>69953.53</v>
+        <v>74051.8</v>
       </c>
       <c r="D27" t="n">
-        <v>62553.19</v>
+        <v>65303.14</v>
       </c>
       <c r="E27" t="n">
-        <v>65738.10000000001</v>
+        <v>65969.78</v>
       </c>
       <c r="F27" t="n">
-        <v>-1921.29</v>
+        <v>231.68</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0284</v>
+        <v>0.0035</v>
       </c>
       <c r="H27" t="n">
-        <v>7400.34</v>
+        <v>8748.67</v>
       </c>
       <c r="I27" t="n">
-        <v>61207.62</v>
+        <v>55152.84</v>
       </c>
       <c r="J27" t="n">
-        <v>63133.12</v>
+        <v>58080.13</v>
       </c>
       <c r="K27" t="n">
-        <v>65444.49</v>
+        <v>62037.93</v>
       </c>
       <c r="L27" t="n">
-        <v>67755.86</v>
+        <v>65995.73</v>
       </c>
       <c r="M27" t="n">
-        <v>69874.28999999999</v>
+        <v>69438.27</v>
       </c>
       <c r="N27" t="n">
-        <v>71992.72</v>
+        <v>72880.82000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>74497.03999999999</v>
+        <v>77353.88</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
@@ -2815,55 +2807,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>65734.08</v>
+        <v>65969.59</v>
       </c>
       <c r="C28" t="n">
-        <v>74051.8</v>
+        <v>73927.33</v>
       </c>
       <c r="D28" t="n">
-        <v>65303.14</v>
+        <v>65858.00999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>65969.78</v>
+        <v>72789.91</v>
       </c>
       <c r="F28" t="n">
-        <v>231.68</v>
+        <v>6820.13</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.1034</v>
       </c>
       <c r="H28" t="n">
-        <v>8748.67</v>
+        <v>8069.32</v>
       </c>
       <c r="I28" t="n">
-        <v>55152.84</v>
+        <v>56554.47</v>
       </c>
       <c r="J28" t="n">
-        <v>58080.13</v>
+        <v>55367.27</v>
       </c>
       <c r="K28" t="n">
-        <v>62037.93</v>
+        <v>61595.45</v>
       </c>
       <c r="L28" t="n">
-        <v>65995.73</v>
+        <v>67823.63</v>
       </c>
       <c r="M28" t="n">
-        <v>69438.27</v>
+        <v>70344.12</v>
       </c>
       <c r="N28" t="n">
-        <v>72880.82000000001</v>
+        <v>72864.60000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>77353.88</v>
+        <v>82800.47</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2874,9 +2870,9 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -2886,7 +2882,7 @@
       </c>
       <c r="U28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V28" s="8" t="n">
@@ -2899,57 +2895,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>65969.59</v>
+        <v>72798.17</v>
       </c>
       <c r="C29" t="n">
-        <v>73927.33</v>
+        <v>75988.39999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>65858.00999999999</v>
+        <v>67372.88</v>
       </c>
       <c r="E29" t="n">
-        <v>72789.91</v>
+        <v>67845.21000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>6820.13</v>
+        <v>-4944.7</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.1034</v>
+        <v>-0.0679</v>
       </c>
       <c r="H29" t="n">
-        <v>8069.32</v>
+        <v>8615.52</v>
       </c>
       <c r="I29" t="n">
-        <v>56554.47</v>
+        <v>57788.69</v>
       </c>
       <c r="J29" t="n">
-        <v>55367.27</v>
+        <v>66169.22</v>
       </c>
       <c r="K29" t="n">
-        <v>61595.45</v>
+        <v>68755.25</v>
       </c>
       <c r="L29" t="n">
-        <v>67823.63</v>
+        <v>71341.28999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>70344.12</v>
+        <v>76824.57000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>72864.60000000001</v>
+        <v>82307.86</v>
       </c>
       <c r="O29" t="n">
-        <v>82800.47</v>
+        <v>81996.64999999999</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2957,23 +2953,21 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2992,50 +2986,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>72798.17</v>
+        <v>67843</v>
       </c>
       <c r="C30" t="n">
-        <v>75988.39999999999</v>
+        <v>71985.74000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>67372.88</v>
+        <v>64971.71</v>
       </c>
       <c r="E30" t="n">
-        <v>67845.21000000001</v>
+        <v>65954.92</v>
       </c>
       <c r="F30" t="n">
-        <v>-4944.7</v>
+        <v>-1890.29</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0679</v>
+        <v>-0.0279</v>
       </c>
       <c r="H30" t="n">
-        <v>8615.52</v>
+        <v>7014.04</v>
       </c>
       <c r="I30" t="n">
-        <v>57788.69</v>
+        <v>58757.35</v>
       </c>
       <c r="J30" t="n">
-        <v>66169.22</v>
+        <v>57311.97</v>
       </c>
       <c r="K30" t="n">
-        <v>68755.25</v>
+        <v>63537.45</v>
       </c>
       <c r="L30" t="n">
-        <v>71341.28999999999</v>
+        <v>69762.92</v>
       </c>
       <c r="M30" t="n">
-        <v>76824.57000000001</v>
+        <v>72152.97</v>
       </c>
       <c r="N30" t="n">
-        <v>82307.86</v>
+        <v>74543.02</v>
       </c>
       <c r="O30" t="n">
-        <v>81996.64999999999</v>
+        <v>84603.92</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3067,59 +3061,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>67843</v>
+        <v>65958.35000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>71985.74000000001</v>
+        <v>69230.36</v>
       </c>
       <c r="D31" t="n">
-        <v>64971.71</v>
+        <v>65725.25999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>65954.92</v>
+        <v>68981.89999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>-1890.29</v>
+        <v>3026.98</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0279</v>
+        <v>0.0459</v>
       </c>
       <c r="H31" t="n">
-        <v>7014.04</v>
+        <v>3505.1</v>
       </c>
       <c r="I31" t="n">
-        <v>58757.35</v>
+        <v>57957.67</v>
       </c>
       <c r="J31" t="n">
-        <v>57311.97</v>
+        <v>57678.99</v>
       </c>
       <c r="K31" t="n">
-        <v>63537.45</v>
+        <v>62447.9</v>
       </c>
       <c r="L31" t="n">
-        <v>69762.92</v>
+        <v>67216.82000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>72152.97</v>
+        <v>69461.94</v>
       </c>
       <c r="N31" t="n">
-        <v>74543.02</v>
+        <v>71707.06</v>
       </c>
       <c r="O31" t="n">
-        <v>84603.92</v>
+        <v>78999.78</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3127,19 +3117,19 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3151,55 +3141,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>65958.35000000001</v>
+        <v>68982.91</v>
       </c>
       <c r="C32" t="n">
-        <v>69230.36</v>
+        <v>73784.23</v>
       </c>
       <c r="D32" t="n">
-        <v>65725.25999999999</v>
+        <v>67740.50999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>68981.89999999999</v>
+        <v>70753.41</v>
       </c>
       <c r="F32" t="n">
-        <v>3026.98</v>
+        <v>1771.51</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0459</v>
+        <v>0.0257</v>
       </c>
       <c r="H32" t="n">
-        <v>3505.1</v>
+        <v>6043.73</v>
       </c>
       <c r="I32" t="n">
-        <v>57957.67</v>
+        <v>62220.16</v>
       </c>
       <c r="J32" t="n">
-        <v>57678.99</v>
+        <v>66228.84</v>
       </c>
       <c r="K32" t="n">
-        <v>62447.9</v>
+        <v>67229.35000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>67216.82000000001</v>
+        <v>68229.85000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>69461.94</v>
+        <v>70734.45</v>
       </c>
       <c r="N32" t="n">
-        <v>71707.06</v>
+        <v>73239.03999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>78999.78</v>
+        <v>72735.46000000001</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3220,11 +3214,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W32" s="11" t="inlineStr">
         <is>
@@ -3233,57 +3231,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>68982.91</v>
+        <v>70757.62</v>
       </c>
       <c r="C33" t="n">
-        <v>73784.23</v>
+        <v>78320.67999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>67740.50999999999</v>
+        <v>70588.52</v>
       </c>
       <c r="E33" t="n">
-        <v>70753.41</v>
+        <v>73856.35000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>1771.51</v>
+        <v>3102.95</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0257</v>
+        <v>0.0439</v>
       </c>
       <c r="H33" t="n">
-        <v>6043.73</v>
+        <v>7732.16</v>
       </c>
       <c r="I33" t="n">
-        <v>62220.16</v>
+        <v>61696.78</v>
       </c>
       <c r="J33" t="n">
-        <v>66228.84</v>
+        <v>64705.2</v>
       </c>
       <c r="K33" t="n">
-        <v>67229.35000000001</v>
+        <v>67731.53999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>68229.85000000001</v>
+        <v>70757.89</v>
       </c>
       <c r="M33" t="n">
-        <v>70734.45</v>
+        <v>73775.27</v>
       </c>
       <c r="N33" t="n">
-        <v>73239.03999999999</v>
+        <v>76792.64999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>72735.46000000001</v>
+        <v>79827.96000000001</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3309,10 +3307,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="11" t="inlineStr">
         <is>
@@ -3328,50 +3324,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>70757.62</v>
+        <v>73854.25</v>
       </c>
       <c r="C34" t="n">
-        <v>78320.67999999999</v>
+        <v>79468</v>
       </c>
       <c r="D34" t="n">
-        <v>70588.52</v>
+        <v>73775.57000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>73856.35000000001</v>
+        <v>78657.53999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>3102.95</v>
+        <v>4801.19</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0439</v>
+        <v>0.065</v>
       </c>
       <c r="H34" t="n">
-        <v>7732.16</v>
+        <v>5692.43</v>
       </c>
       <c r="I34" t="n">
-        <v>61696.78</v>
+        <v>62856.37</v>
       </c>
       <c r="J34" t="n">
-        <v>64705.2</v>
+        <v>65825.07000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>67731.53999999999</v>
+        <v>69990.27</v>
       </c>
       <c r="L34" t="n">
-        <v>70757.89</v>
+        <v>74155.48</v>
       </c>
       <c r="M34" t="n">
-        <v>73775.27</v>
+        <v>77722.42999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>76792.64999999999</v>
+        <v>81289.38</v>
       </c>
       <c r="O34" t="n">
-        <v>79827.96000000001</v>
+        <v>86052.84</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3392,10 +3388,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3414,50 +3408,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>73854.25</v>
+        <v>78661.02</v>
       </c>
       <c r="C35" t="n">
-        <v>79468</v>
+        <v>79488.17</v>
       </c>
       <c r="D35" t="n">
-        <v>73775.57000000001</v>
+        <v>74958.57000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>78657.53999999999</v>
+        <v>78538.23</v>
       </c>
       <c r="F35" t="n">
-        <v>4801.19</v>
+        <v>-119.31</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.065</v>
+        <v>-0.0015</v>
       </c>
       <c r="H35" t="n">
-        <v>5692.43</v>
+        <v>4529.6</v>
       </c>
       <c r="I35" t="n">
-        <v>62856.37</v>
+        <v>68083.14</v>
       </c>
       <c r="J35" t="n">
-        <v>65825.07000000001</v>
+        <v>73982.99000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>69990.27</v>
+        <v>75811.32000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>74155.48</v>
+        <v>77639.66</v>
       </c>
       <c r="M35" t="n">
-        <v>77722.42999999999</v>
+        <v>81503.75</v>
       </c>
       <c r="N35" t="n">
-        <v>81289.38</v>
+        <v>85367.85000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>86052.84</v>
+        <v>85160.42999999999</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3465,18 +3459,18 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3491,57 +3485,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>78661.02</v>
+        <v>78540.28999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>79488.17</v>
+        <v>82792.21000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>74958.57000000001</v>
+        <v>78217.96000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>78538.23</v>
+        <v>82138.92999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>-119.31</v>
+        <v>3600.7</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0458</v>
       </c>
       <c r="H36" t="n">
-        <v>4529.6</v>
+        <v>4574.25</v>
       </c>
       <c r="I36" t="n">
-        <v>68083.14</v>
+        <v>70428.97</v>
       </c>
       <c r="J36" t="n">
-        <v>73982.99000000001</v>
+        <v>74666.05</v>
       </c>
       <c r="K36" t="n">
-        <v>75811.32000000001</v>
+        <v>76273.42999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>77639.66</v>
+        <v>77880.8</v>
       </c>
       <c r="M36" t="n">
-        <v>81503.75</v>
+        <v>80803.03</v>
       </c>
       <c r="N36" t="n">
-        <v>85367.85000000001</v>
+        <v>83725.25999999999</v>
       </c>
       <c r="O36" t="n">
-        <v>85160.42999999999</v>
+        <v>84017.77</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3549,18 +3543,18 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3575,77 +3569,79 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>78540.28999999999</v>
+        <v>82139.05</v>
       </c>
       <c r="C37" t="n">
-        <v>82792.21000000001</v>
+        <v>82326.23</v>
       </c>
       <c r="D37" t="n">
-        <v>78217.96000000001</v>
+        <v>76783.41</v>
       </c>
       <c r="E37" t="n">
-        <v>82138.92999999999</v>
+        <v>77429.35000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>3600.7</v>
+        <v>-4709.58</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0458</v>
+        <v>-0.0573</v>
       </c>
       <c r="H37" t="n">
-        <v>4574.25</v>
+        <v>5542.82</v>
       </c>
       <c r="I37" t="n">
-        <v>70428.97</v>
+        <v>73643.71000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>74666.05</v>
+        <v>78381.60000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>76273.42999999999</v>
+        <v>79851.8</v>
       </c>
       <c r="L37" t="n">
-        <v>77880.8</v>
+        <v>81322.00999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>80803.03</v>
+        <v>84426.05</v>
       </c>
       <c r="N37" t="n">
-        <v>83725.25999999999</v>
+        <v>87530.10000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>84017.77</v>
+        <v>87366.46000000001</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
+      <c r="Q37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3657,67 +3653,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>82139.05</v>
+        <v>77426.34</v>
       </c>
       <c r="C38" t="n">
-        <v>82326.23</v>
+        <v>78100.56</v>
       </c>
       <c r="D38" t="n">
-        <v>76783.41</v>
+        <v>74255.23</v>
       </c>
       <c r="E38" t="n">
-        <v>77429.35000000001</v>
+        <v>76981.12</v>
       </c>
       <c r="F38" t="n">
-        <v>-4709.58</v>
+        <v>-448.23</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0573</v>
+        <v>-0.0058</v>
       </c>
       <c r="H38" t="n">
-        <v>5542.82</v>
+        <v>3845.33</v>
       </c>
       <c r="I38" t="n">
-        <v>73643.71000000001</v>
+        <v>71240.59</v>
       </c>
       <c r="J38" t="n">
-        <v>78381.60000000001</v>
+        <v>70823.78999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>79851.8</v>
+        <v>74657.94</v>
       </c>
       <c r="L38" t="n">
-        <v>81322.00999999999</v>
+        <v>78492.09</v>
       </c>
       <c r="M38" t="n">
-        <v>84426.05</v>
+        <v>80200.75999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>87530.10000000001</v>
+        <v>81909.44</v>
       </c>
       <c r="O38" t="n">
-        <v>87366.46000000001</v>
+        <v>87869.05</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q38" s="6" t="n">
+        <v/>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
@@ -3726,7 +3716,7 @@
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3748,56 +3738,58 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>77426.34</v>
+        <v>76981.12</v>
       </c>
       <c r="C39" t="n">
-        <v>78100.56</v>
+        <v>77990.87</v>
       </c>
       <c r="D39" t="n">
-        <v>74255.23</v>
+        <v>72435.62</v>
       </c>
       <c r="E39" t="n">
-        <v>76981.12</v>
+        <v>73579.69</v>
       </c>
       <c r="F39" t="n">
-        <v>-448.23</v>
+        <v>-3401.44</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0442</v>
       </c>
       <c r="H39" t="n">
-        <v>3845.33</v>
+        <v>5555.24</v>
       </c>
       <c r="I39" t="n">
-        <v>71240.59</v>
+        <v>70409.91</v>
       </c>
       <c r="J39" t="n">
-        <v>70823.78999999999</v>
+        <v>73537.41</v>
       </c>
       <c r="K39" t="n">
-        <v>74657.94</v>
+        <v>75058.46000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>78492.09</v>
+        <v>76579.50999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>80200.75999999999</v>
+        <v>78903.78999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>81909.44</v>
+        <v>81228.07000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>87869.05</v>
+        <v>81945.89</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
@@ -3806,7 +3798,7 @@
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3828,57 +3820,59 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>76981.12</v>
+        <v>73580.21000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>77990.87</v>
+        <v>73969.57000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>72435.62</v>
+        <v>59108.92</v>
       </c>
       <c r="E40" t="n">
-        <v>73579.69</v>
+        <v>63239.52</v>
       </c>
       <c r="F40" t="n">
-        <v>-3401.44</v>
+        <v>-10340.17</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0442</v>
+        <v>-0.1405</v>
       </c>
       <c r="H40" t="n">
-        <v>5555.24</v>
+        <v>14860.65</v>
       </c>
       <c r="I40" t="n">
-        <v>70409.91</v>
+        <v>66880.38</v>
       </c>
       <c r="J40" t="n">
-        <v>73537.41</v>
+        <v>67207.67</v>
       </c>
       <c r="K40" t="n">
-        <v>75058.46000000001</v>
+        <v>70802.07000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>76579.50999999999</v>
+        <v>74396.47</v>
       </c>
       <c r="M40" t="n">
-        <v>78903.78999999999</v>
+        <v>76357.31</v>
       </c>
       <c r="N40" t="n">
-        <v>81228.07000000001</v>
+        <v>78318.14999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>81945.89</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
+        <v>83546.11</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
@@ -3910,69 +3904,63 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>73580.21000000001</v>
+        <v>63244.09</v>
       </c>
       <c r="C41" t="n">
-        <v>73969.57000000001</v>
+        <v>65749.78</v>
       </c>
       <c r="D41" t="n">
-        <v>59108.92</v>
+        <v>60756.69</v>
       </c>
       <c r="E41" t="n">
-        <v>63239.52</v>
+        <v>65710.39999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>-10340.17</v>
+        <v>2470.88</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.1405</v>
+        <v>0.0391</v>
       </c>
       <c r="H41" t="n">
-        <v>14860.65</v>
+        <v>4993.09</v>
       </c>
       <c r="I41" t="n">
-        <v>66880.38</v>
+        <v>44248.27</v>
       </c>
       <c r="J41" t="n">
-        <v>67207.67</v>
+        <v>46729</v>
       </c>
       <c r="K41" t="n">
-        <v>70802.07000000001</v>
+        <v>55809.19</v>
       </c>
       <c r="L41" t="n">
-        <v>74396.47</v>
+        <v>64889.38</v>
       </c>
       <c r="M41" t="n">
-        <v>76357.31</v>
+        <v>70669.85000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>78318.14999999999</v>
+        <v>76450.31</v>
       </c>
       <c r="O41" t="n">
-        <v>83546.11</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>88830.22</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3989,55 +3977,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>63244.09</v>
+        <v>65711.11</v>
       </c>
       <c r="C42" t="n">
-        <v>65749.78</v>
+        <v>67248.13</v>
       </c>
       <c r="D42" t="n">
-        <v>60756.69</v>
+        <v>62201.14</v>
       </c>
       <c r="E42" t="n">
-        <v>65710.39999999999</v>
+        <v>63237.54</v>
       </c>
       <c r="F42" t="n">
-        <v>2470.88</v>
+        <v>-2472.86</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0391</v>
+        <v>-0.0376</v>
       </c>
       <c r="H42" t="n">
-        <v>4993.09</v>
+        <v>5046.99</v>
       </c>
       <c r="I42" t="n">
-        <v>44248.27</v>
+        <v>55763.59</v>
       </c>
       <c r="J42" t="n">
-        <v>46729</v>
+        <v>61945.89</v>
       </c>
       <c r="K42" t="n">
-        <v>55809.19</v>
+        <v>63213.85</v>
       </c>
       <c r="L42" t="n">
-        <v>64889.38</v>
+        <v>64481.82</v>
       </c>
       <c r="M42" t="n">
-        <v>70669.85000000001</v>
+        <v>68206.95</v>
       </c>
       <c r="N42" t="n">
-        <v>76450.31</v>
+        <v>71932.07000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>88830.22</v>
+        <v>70742.88</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4045,12 +4037,14 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4076,50 +4070,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>65711.11</v>
+        <v>63240.79</v>
       </c>
       <c r="C43" t="n">
-        <v>67248.13</v>
+        <v>65544</v>
       </c>
       <c r="D43" t="n">
-        <v>62201.14</v>
+        <v>58075.92</v>
       </c>
       <c r="E43" t="n">
-        <v>63237.54</v>
+        <v>59532.34</v>
       </c>
       <c r="F43" t="n">
-        <v>-2472.86</v>
+        <v>-3705.2</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0376</v>
+        <v>-0.0586</v>
       </c>
       <c r="H43" t="n">
-        <v>5046.99</v>
+        <v>7468.08</v>
       </c>
       <c r="I43" t="n">
-        <v>55763.59</v>
+        <v>57154.16</v>
       </c>
       <c r="J43" t="n">
-        <v>61945.89</v>
+        <v>57447</v>
       </c>
       <c r="K43" t="n">
-        <v>63213.85</v>
+        <v>60714.04</v>
       </c>
       <c r="L43" t="n">
-        <v>64481.82</v>
+        <v>63981.09</v>
       </c>
       <c r="M43" t="n">
-        <v>68206.95</v>
+        <v>65761.03</v>
       </c>
       <c r="N43" t="n">
-        <v>71932.07000000001</v>
+        <v>67540.98</v>
       </c>
       <c r="O43" t="n">
-        <v>70742.88</v>
+        <v>72295.12</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4151,59 +4145,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>63240.79</v>
+        <v>59522.79</v>
       </c>
       <c r="C44" t="n">
-        <v>65544</v>
+        <v>63935.85</v>
       </c>
       <c r="D44" t="n">
-        <v>58075.92</v>
+        <v>57747.77</v>
       </c>
       <c r="E44" t="n">
-        <v>59532.34</v>
+        <v>63547.88</v>
       </c>
       <c r="F44" t="n">
-        <v>-3705.2</v>
+        <v>4015.54</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0586</v>
+        <v>0.0675</v>
       </c>
       <c r="H44" t="n">
-        <v>7468.08</v>
+        <v>6188.08</v>
       </c>
       <c r="I44" t="n">
-        <v>57154.16</v>
+        <v>50607.84</v>
       </c>
       <c r="J44" t="n">
-        <v>57447</v>
+        <v>50925.45</v>
       </c>
       <c r="K44" t="n">
-        <v>60714.04</v>
+        <v>55798.3</v>
       </c>
       <c r="L44" t="n">
-        <v>63981.09</v>
+        <v>60671.15</v>
       </c>
       <c r="M44" t="n">
-        <v>65761.03</v>
+        <v>63266.38</v>
       </c>
       <c r="N44" t="n">
-        <v>67540.98</v>
+        <v>65861.61</v>
       </c>
       <c r="O44" t="n">
-        <v>72295.12</v>
+        <v>73012.08</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4211,19 +4201,19 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4235,55 +4225,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>59522.79</v>
+        <v>63551.02</v>
       </c>
       <c r="C45" t="n">
-        <v>63935.85</v>
+        <v>64658.97</v>
       </c>
       <c r="D45" t="n">
-        <v>57747.77</v>
+        <v>61275.83</v>
       </c>
       <c r="E45" t="n">
-        <v>63547.88</v>
+        <v>63758.22</v>
       </c>
       <c r="F45" t="n">
-        <v>4015.54</v>
+        <v>210.34</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0675</v>
+        <v>0.0033</v>
       </c>
       <c r="H45" t="n">
-        <v>6188.08</v>
+        <v>3383.14</v>
       </c>
       <c r="I45" t="n">
-        <v>50607.84</v>
+        <v>51559.68</v>
       </c>
       <c r="J45" t="n">
-        <v>50925.45</v>
+        <v>58712.84</v>
       </c>
       <c r="K45" t="n">
-        <v>55798.3</v>
+        <v>60453.84</v>
       </c>
       <c r="L45" t="n">
-        <v>60671.15</v>
+        <v>62194.84</v>
       </c>
       <c r="M45" t="n">
-        <v>63266.38</v>
+        <v>66641.92</v>
       </c>
       <c r="N45" t="n">
-        <v>65861.61</v>
+        <v>71089</v>
       </c>
       <c r="O45" t="n">
-        <v>73012.08</v>
+        <v>70123.92999999999</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4296,13 +4290,11 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4317,57 +4309,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>63551.02</v>
+        <v>63757.17</v>
       </c>
       <c r="C46" t="n">
-        <v>64658.97</v>
+        <v>65507.59</v>
       </c>
       <c r="D46" t="n">
-        <v>61275.83</v>
+        <v>61769</v>
       </c>
       <c r="E46" t="n">
-        <v>63758.22</v>
+        <v>64690.8</v>
       </c>
       <c r="F46" t="n">
-        <v>210.34</v>
+        <v>932.59</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0146</v>
       </c>
       <c r="H46" t="n">
-        <v>3383.14</v>
+        <v>3738.59</v>
       </c>
       <c r="I46" t="n">
-        <v>51559.68</v>
+        <v>57892.69</v>
       </c>
       <c r="J46" t="n">
-        <v>58712.84</v>
+        <v>60770.49</v>
       </c>
       <c r="K46" t="n">
-        <v>60453.84</v>
+        <v>62066.65</v>
       </c>
       <c r="L46" t="n">
-        <v>62194.84</v>
+        <v>63362.81</v>
       </c>
       <c r="M46" t="n">
-        <v>66641.92</v>
+        <v>65449.79</v>
       </c>
       <c r="N46" t="n">
-        <v>71089</v>
+        <v>67536.77</v>
       </c>
       <c r="O46" t="n">
-        <v>70123.92999999999</v>
+        <v>68042.11</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4375,16 +4367,20 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4406,50 +4402,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>63757.17</v>
+        <v>64684.42</v>
       </c>
       <c r="C47" t="n">
-        <v>65507.59</v>
+        <v>66910.06</v>
       </c>
       <c r="D47" t="n">
-        <v>61769</v>
+        <v>63686.04</v>
       </c>
       <c r="E47" t="n">
-        <v>64690.8</v>
+        <v>65340.3</v>
       </c>
       <c r="F47" t="n">
-        <v>932.59</v>
+        <v>649.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.01</v>
       </c>
       <c r="H47" t="n">
-        <v>3738.59</v>
+        <v>3224.03</v>
       </c>
       <c r="I47" t="n">
-        <v>57892.69</v>
+        <v>58030.41</v>
       </c>
       <c r="J47" t="n">
-        <v>60770.49</v>
+        <v>61478.46</v>
       </c>
       <c r="K47" t="n">
-        <v>62066.65</v>
+        <v>62821.51</v>
       </c>
       <c r="L47" t="n">
-        <v>63362.81</v>
+        <v>64164.55</v>
       </c>
       <c r="M47" t="n">
-        <v>65449.79</v>
+        <v>66560.10000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>67536.77</v>
+        <v>68955.64999999999</v>
       </c>
       <c r="O47" t="n">
-        <v>68042.11</v>
+        <v>69246.19</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4457,19 +4453,17 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="U47" s="8" t="n">
@@ -4492,50 +4486,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>64684.42</v>
+        <v>65340.59</v>
       </c>
       <c r="C48" t="n">
-        <v>66910.06</v>
+        <v>65658.34</v>
       </c>
       <c r="D48" t="n">
-        <v>63686.04</v>
+        <v>62233.01</v>
       </c>
       <c r="E48" t="n">
-        <v>65340.3</v>
+        <v>63482</v>
       </c>
       <c r="F48" t="n">
-        <v>649.5</v>
+        <v>-1858.3</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.0284</v>
       </c>
       <c r="H48" t="n">
-        <v>3224.03</v>
+        <v>3425.32</v>
       </c>
       <c r="I48" t="n">
-        <v>58030.41</v>
+        <v>60462.01</v>
       </c>
       <c r="J48" t="n">
-        <v>61478.46</v>
+        <v>62137.4</v>
       </c>
       <c r="K48" t="n">
-        <v>62821.51</v>
+        <v>63728.29</v>
       </c>
       <c r="L48" t="n">
-        <v>64164.55</v>
+        <v>65319.17</v>
       </c>
       <c r="M48" t="n">
-        <v>66560.10000000001</v>
+        <v>66952.31</v>
       </c>
       <c r="N48" t="n">
-        <v>68955.64999999999</v>
+        <v>68585.45</v>
       </c>
       <c r="O48" t="n">
-        <v>69246.19</v>
+        <v>70134.09</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4543,18 +4537,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4567,59 +4561,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>65340.59</v>
+        <v>63485.44</v>
       </c>
       <c r="C49" t="n">
-        <v>65658.34</v>
+        <v>65401.69</v>
       </c>
       <c r="D49" t="n">
-        <v>62233.01</v>
+        <v>62226.58</v>
       </c>
       <c r="E49" t="n">
-        <v>63482</v>
+        <v>64844.89</v>
       </c>
       <c r="F49" t="n">
-        <v>-1858.3</v>
+        <v>1362.89</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0284</v>
+        <v>0.0215</v>
       </c>
       <c r="H49" t="n">
-        <v>3425.32</v>
+        <v>3175.11</v>
       </c>
       <c r="I49" t="n">
-        <v>60462.01</v>
+        <v>58807.69</v>
       </c>
       <c r="J49" t="n">
-        <v>62137.4</v>
+        <v>59824.84</v>
       </c>
       <c r="K49" t="n">
-        <v>63728.29</v>
+        <v>61769.34</v>
       </c>
       <c r="L49" t="n">
-        <v>65319.17</v>
+        <v>63713.84</v>
       </c>
       <c r="M49" t="n">
-        <v>66952.31</v>
+        <v>65194.66</v>
       </c>
       <c r="N49" t="n">
-        <v>68585.45</v>
+        <v>66675.49000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>70134.09</v>
+        <v>69083.66</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4627,19 +4617,19 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
@@ -4651,55 +4641,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>63485.44</v>
+        <v>64845.38</v>
       </c>
       <c r="C50" t="n">
-        <v>65401.69</v>
+        <v>65321.84</v>
       </c>
       <c r="D50" t="n">
-        <v>62226.58</v>
+        <v>62487.7</v>
       </c>
       <c r="E50" t="n">
-        <v>64844.89</v>
+        <v>62818.65</v>
       </c>
       <c r="F50" t="n">
-        <v>1362.89</v>
+        <v>-2026.23</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0215</v>
+        <v>-0.0312</v>
       </c>
       <c r="H50" t="n">
-        <v>3175.11</v>
+        <v>2834.14</v>
       </c>
       <c r="I50" t="n">
-        <v>58807.69</v>
+        <v>59051.46</v>
       </c>
       <c r="J50" t="n">
-        <v>59824.84</v>
+        <v>62185.15</v>
       </c>
       <c r="K50" t="n">
-        <v>61769.34</v>
+        <v>63257.33</v>
       </c>
       <c r="L50" t="n">
-        <v>63713.84</v>
+        <v>64329.51</v>
       </c>
       <c r="M50" t="n">
-        <v>65194.66</v>
+        <v>66432.44</v>
       </c>
       <c r="N50" t="n">
-        <v>66675.49000000001</v>
+        <v>68535.38</v>
       </c>
       <c r="O50" t="n">
-        <v>69083.66</v>
+        <v>68576.8</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4707,18 +4701,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4740,50 +4734,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>64845.38</v>
+        <v>62819.38</v>
       </c>
       <c r="C51" t="n">
-        <v>65321.84</v>
+        <v>79463.71000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>62487.7</v>
+        <v>62687.1</v>
       </c>
       <c r="E51" t="n">
-        <v>62818.65</v>
+        <v>77755.27</v>
       </c>
       <c r="F51" t="n">
-        <v>-2026.23</v>
+        <v>14936.61</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0312</v>
+        <v>0.2378</v>
       </c>
       <c r="H51" t="n">
-        <v>2834.14</v>
+        <v>16776.61</v>
       </c>
       <c r="I51" t="n">
-        <v>59051.46</v>
+        <v>59653.56</v>
       </c>
       <c r="J51" t="n">
-        <v>62185.15</v>
+        <v>59441.45</v>
       </c>
       <c r="K51" t="n">
-        <v>63257.33</v>
+        <v>61401.58</v>
       </c>
       <c r="L51" t="n">
-        <v>64329.51</v>
+        <v>63361.71</v>
       </c>
       <c r="M51" t="n">
-        <v>66432.44</v>
+        <v>64235.72</v>
       </c>
       <c r="N51" t="n">
-        <v>68535.38</v>
+        <v>65109.73</v>
       </c>
       <c r="O51" t="n">
-        <v>68576.8</v>
+        <v>68155.98</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4791,83 +4785,83 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W51" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W51" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>62819.38</v>
+        <v>77748.88</v>
       </c>
       <c r="C52" t="n">
-        <v>79463.71000000001</v>
+        <v>81346.95</v>
       </c>
       <c r="D52" t="n">
-        <v>62687.1</v>
+        <v>76688.83</v>
       </c>
       <c r="E52" t="n">
-        <v>77755.27</v>
+        <v>77667.57000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>14936.61</v>
+        <v>-87.7</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.2378</v>
+        <v>-0.0011</v>
       </c>
       <c r="H52" t="n">
-        <v>16776.61</v>
+        <v>4658.12</v>
       </c>
       <c r="I52" t="n">
-        <v>59653.56</v>
+        <v>45910.49</v>
       </c>
       <c r="J52" t="n">
-        <v>59441.45</v>
+        <v>64318.59</v>
       </c>
       <c r="K52" t="n">
-        <v>61401.58</v>
+        <v>69366.96000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>63361.71</v>
+        <v>74415.34</v>
       </c>
       <c r="M52" t="n">
-        <v>64235.72</v>
+        <v>86143.57000000001</v>
       </c>
       <c r="N52" t="n">
-        <v>65109.73</v>
+        <v>97871.8</v>
       </c>
       <c r="O52" t="n">
-        <v>68155.98</v>
+        <v>96240.32000000001</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4880,78 +4874,76 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
       </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>77748.88</v>
+        <v>77673.7</v>
       </c>
       <c r="C53" t="n">
-        <v>81346.95</v>
+        <v>82262.21000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>76688.83</v>
+        <v>76248.3</v>
       </c>
       <c r="E53" t="n">
-        <v>77667.57000000001</v>
+        <v>80350.05</v>
       </c>
       <c r="F53" t="n">
-        <v>-87.7</v>
+        <v>2682.48</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0345</v>
       </c>
       <c r="H53" t="n">
-        <v>4658.12</v>
+        <v>6013.91</v>
       </c>
       <c r="I53" t="n">
-        <v>45910.49</v>
+        <v>72030.7</v>
       </c>
       <c r="J53" t="n">
-        <v>64318.59</v>
+        <v>72334.28999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>69366.96000000001</v>
+        <v>75338.50999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>74415.34</v>
+        <v>78342.73</v>
       </c>
       <c r="M53" t="n">
-        <v>86143.57000000001</v>
+        <v>79996.63</v>
       </c>
       <c r="N53" t="n">
-        <v>97871.8</v>
+        <v>81650.53999999999</v>
       </c>
       <c r="O53" t="n">
-        <v>96240.32000000001</v>
+        <v>86005.08</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4964,14 +4956,18 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4990,50 +4986,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>77673.7</v>
+        <v>80349.2</v>
       </c>
       <c r="C54" t="n">
-        <v>82262.21000000001</v>
+        <v>80432.31</v>
       </c>
       <c r="D54" t="n">
-        <v>76248.3</v>
+        <v>76162.91</v>
       </c>
       <c r="E54" t="n">
-        <v>80350.05</v>
+        <v>76838.16</v>
       </c>
       <c r="F54" t="n">
-        <v>2682.48</v>
+        <v>-3511.89</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0345</v>
+        <v>-0.0437</v>
       </c>
       <c r="H54" t="n">
-        <v>6013.91</v>
+        <v>4269.4</v>
       </c>
       <c r="I54" t="n">
-        <v>72030.7</v>
+        <v>70234.39999999999</v>
       </c>
       <c r="J54" t="n">
-        <v>72334.28999999999</v>
+        <v>74883.53999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>75338.50999999999</v>
+        <v>77343.09</v>
       </c>
       <c r="L54" t="n">
-        <v>78342.73</v>
+        <v>79802.64999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>79996.63</v>
+        <v>83357</v>
       </c>
       <c r="N54" t="n">
-        <v>81650.53999999999</v>
+        <v>86911.35000000001</v>
       </c>
       <c r="O54" t="n">
-        <v>86005.08</v>
+        <v>88276.12</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5041,23 +5037,21 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5069,57 +5063,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>80349.2</v>
+        <v>76830.28</v>
       </c>
       <c r="C55" t="n">
-        <v>80432.31</v>
+        <v>81911.14</v>
       </c>
       <c r="D55" t="n">
-        <v>76162.91</v>
+        <v>74944.59</v>
       </c>
       <c r="E55" t="n">
-        <v>76838.16</v>
+        <v>81142.61</v>
       </c>
       <c r="F55" t="n">
-        <v>-3511.89</v>
+        <v>4304.45</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0437</v>
+        <v>0.056</v>
       </c>
       <c r="H55" t="n">
-        <v>4269.4</v>
+        <v>6966.55</v>
       </c>
       <c r="I55" t="n">
-        <v>70234.39999999999</v>
+        <v>71893.52</v>
       </c>
       <c r="J55" t="n">
-        <v>74883.53999999999</v>
+        <v>71839.03</v>
       </c>
       <c r="K55" t="n">
-        <v>77343.09</v>
+        <v>74703.46000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>79802.64999999999</v>
+        <v>77567.88</v>
       </c>
       <c r="M55" t="n">
-        <v>83357</v>
+        <v>78972.86</v>
       </c>
       <c r="N55" t="n">
-        <v>86911.35000000001</v>
+        <v>80377.83</v>
       </c>
       <c r="O55" t="n">
-        <v>88276.12</v>
+        <v>84701.71000000001</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5127,22 +5121,24 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
@@ -5153,57 +5149,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>76830.28</v>
+        <v>81143.62</v>
       </c>
       <c r="C56" t="n">
-        <v>81911.14</v>
+        <v>87363.75999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>74944.59</v>
+        <v>80867.09</v>
       </c>
       <c r="E56" t="n">
-        <v>81142.61</v>
+        <v>84458.09</v>
       </c>
       <c r="F56" t="n">
-        <v>4304.45</v>
+        <v>3315.48</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.056</v>
+        <v>0.0409</v>
       </c>
       <c r="H56" t="n">
-        <v>6966.55</v>
+        <v>6496.67</v>
       </c>
       <c r="I56" t="n">
-        <v>71893.52</v>
+        <v>67978.05</v>
       </c>
       <c r="J56" t="n">
-        <v>71839.03</v>
+        <v>75533.42999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>74703.46000000001</v>
+        <v>77659.34</v>
       </c>
       <c r="L56" t="n">
-        <v>77567.88</v>
+        <v>79785.24000000001</v>
       </c>
       <c r="M56" t="n">
-        <v>78972.86</v>
+        <v>84625.88</v>
       </c>
       <c r="N56" t="n">
-        <v>80377.83</v>
+        <v>89466.53</v>
       </c>
       <c r="O56" t="n">
-        <v>84701.71000000001</v>
+        <v>88877.69</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5221,14 +5217,12 @@
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
@@ -5237,59 +5231,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>81143.62</v>
+        <v>84454.12</v>
       </c>
       <c r="C57" t="n">
-        <v>87363.75999999999</v>
+        <v>87146.35000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>80867.09</v>
+        <v>82570.72</v>
       </c>
       <c r="E57" t="n">
-        <v>84458.09</v>
+        <v>86480.3</v>
       </c>
       <c r="F57" t="n">
-        <v>3315.48</v>
+        <v>2022.22</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0409</v>
+        <v>0.0239</v>
       </c>
       <c r="H57" t="n">
-        <v>6496.67</v>
+        <v>4575.63</v>
       </c>
       <c r="I57" t="n">
-        <v>67978.05</v>
+        <v>74370.41</v>
       </c>
       <c r="J57" t="n">
-        <v>75533.42999999999</v>
+        <v>78132.75</v>
       </c>
       <c r="K57" t="n">
-        <v>77659.34</v>
+        <v>81209.75</v>
       </c>
       <c r="L57" t="n">
-        <v>79785.24000000001</v>
+        <v>84286.75</v>
       </c>
       <c r="M57" t="n">
-        <v>84625.88</v>
+        <v>87706.42</v>
       </c>
       <c r="N57" t="n">
-        <v>89466.53</v>
+        <v>91126.09</v>
       </c>
       <c r="O57" t="n">
-        <v>88877.69</v>
+        <v>93860.42999999999</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5321,55 +5311,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>84454.12</v>
+        <v>86513.38</v>
       </c>
       <c r="C58" t="n">
-        <v>87146.35000000001</v>
+        <v>86929.66</v>
       </c>
       <c r="D58" t="n">
-        <v>82570.72</v>
+        <v>85098.8</v>
       </c>
       <c r="E58" t="n">
-        <v>86329.17</v>
+        <v>85979.11</v>
       </c>
       <c r="F58" t="n">
-        <v>1871.09</v>
+        <v>-501.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0222</v>
+        <v>-0.0058</v>
       </c>
       <c r="H58" t="n">
-        <v>4575.63</v>
+        <v>1830.86</v>
       </c>
       <c r="I58" t="n">
-        <v>74370.41</v>
+        <v>77995.09</v>
       </c>
       <c r="J58" t="n">
-        <v>78132.75</v>
+        <v>82715.56</v>
       </c>
       <c r="K58" t="n">
-        <v>81209.75</v>
+        <v>84192.49000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>84286.75</v>
+        <v>85669.42</v>
       </c>
       <c r="M58" t="n">
-        <v>87706.42</v>
+        <v>88768.12</v>
       </c>
       <c r="N58" t="n">
-        <v>91126.09</v>
+        <v>91866.82000000001</v>
       </c>
       <c r="O58" t="n">
-        <v>93860.42999999999</v>
+        <v>91721.98</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5382,13 +5376,11 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5403,7 +5395,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>6138.77</v>
       </c>
       <c r="I2" t="n">
-        <v>101184.87</v>
+        <v>105336.96</v>
       </c>
       <c r="J2" t="n">
-        <v>105507.95</v>
+        <v>107064.98</v>
       </c>
       <c r="K2" t="n">
-        <v>108124.46</v>
+        <v>109162.48</v>
       </c>
       <c r="L2" t="n">
-        <v>110740.98</v>
+        <v>111259.99</v>
       </c>
       <c r="M2" t="n">
-        <v>114210.77</v>
+        <v>113172.75</v>
       </c>
       <c r="N2" t="n">
-        <v>117680.57</v>
+        <v>115085.51</v>
       </c>
       <c r="O2" t="n">
-        <v>119443.8</v>
+        <v>117367.76</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,11 +695,13 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -5324,25 +5326,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>86513.38</v>
+        <v>86480.00999999999</v>
       </c>
       <c r="C58" t="n">
-        <v>86929.66</v>
+        <v>86971.78</v>
       </c>
       <c r="D58" t="n">
-        <v>85098.8</v>
+        <v>84971.87</v>
       </c>
       <c r="E58" t="n">
-        <v>85979.11</v>
+        <v>85385.42999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>-501.2</v>
+        <v>-1094.88</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0127</v>
       </c>
       <c r="H58" t="n">
-        <v>1830.86</v>
+        <v>1999.91</v>
       </c>
       <c r="I58" t="n">
         <v>77995.09</v>
@@ -5374,9 +5376,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5332,19 +5332,19 @@
         <v>86971.78</v>
       </c>
       <c r="D58" t="n">
-        <v>84971.87</v>
+        <v>83199.25</v>
       </c>
       <c r="E58" t="n">
-        <v>85385.42999999999</v>
+        <v>83269.60000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-1094.88</v>
+        <v>-3210.7</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.0371</v>
       </c>
       <c r="H58" t="n">
-        <v>1999.91</v>
+        <v>3772.53</v>
       </c>
       <c r="I58" t="n">
         <v>77995.09</v>
@@ -5370,15 +5370,19 @@
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5332,19 +5332,19 @@
         <v>86971.78</v>
       </c>
       <c r="D58" t="n">
-        <v>83199.25</v>
+        <v>83159.3</v>
       </c>
       <c r="E58" t="n">
-        <v>83269.60000000001</v>
+        <v>83240.78999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>-3210.7</v>
+        <v>-3239.52</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0371</v>
+        <v>-0.0375</v>
       </c>
       <c r="H58" t="n">
-        <v>3772.53</v>
+        <v>3812.48</v>
       </c>
       <c r="I58" t="n">
         <v>77995.09</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>6138.77</v>
       </c>
       <c r="I2" t="n">
-        <v>105336.96</v>
+        <v>106690.68</v>
       </c>
       <c r="J2" t="n">
-        <v>107064.98</v>
+        <v>107572.62</v>
       </c>
       <c r="K2" t="n">
-        <v>109162.48</v>
+        <v>109500.91</v>
       </c>
       <c r="L2" t="n">
-        <v>111259.99</v>
+        <v>111429.2</v>
       </c>
       <c r="M2" t="n">
-        <v>113172.75</v>
+        <v>112834.32</v>
       </c>
       <c r="N2" t="n">
-        <v>115085.51</v>
+        <v>114239.44</v>
       </c>
       <c r="O2" t="n">
-        <v>117367.76</v>
+        <v>116690.9</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -703,8 +703,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5332,19 +5334,19 @@
         <v>86971.78</v>
       </c>
       <c r="D58" t="n">
-        <v>83159.3</v>
+        <v>81602.41</v>
       </c>
       <c r="E58" t="n">
-        <v>83240.78999999999</v>
+        <v>81873.64</v>
       </c>
       <c r="F58" t="n">
-        <v>-3239.52</v>
+        <v>-4606.66</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0375</v>
+        <v>-0.0533</v>
       </c>
       <c r="H58" t="n">
-        <v>3812.48</v>
+        <v>5369.38</v>
       </c>
       <c r="I58" t="n">
         <v>77995.09</v>
@@ -5394,16 +5396,12 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>6138.77</v>
       </c>
       <c r="I2" t="n">
-        <v>106690.68</v>
+        <v>108457.09</v>
       </c>
       <c r="J2" t="n">
-        <v>107572.62</v>
+        <v>109780.64</v>
       </c>
       <c r="K2" t="n">
-        <v>109500.91</v>
+        <v>110384.12</v>
       </c>
       <c r="L2" t="n">
-        <v>111429.2</v>
+        <v>110987.6</v>
       </c>
       <c r="M2" t="n">
-        <v>112834.32</v>
+        <v>111951.11</v>
       </c>
       <c r="N2" t="n">
-        <v>114239.44</v>
+        <v>112914.63</v>
       </c>
       <c r="O2" t="n">
-        <v>116690.9</v>
+        <v>113158.07</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,12 +700,12 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -5334,19 +5334,19 @@
         <v>86971.78</v>
       </c>
       <c r="D58" t="n">
-        <v>81602.41</v>
+        <v>80336.91</v>
       </c>
       <c r="E58" t="n">
-        <v>81873.64</v>
+        <v>82734.96000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-4606.66</v>
+        <v>-3745.34</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0533</v>
+        <v>-0.0433</v>
       </c>
       <c r="H58" t="n">
-        <v>5369.38</v>
+        <v>6634.88</v>
       </c>
       <c r="I58" t="n">
         <v>77995.09</v>
@@ -5396,12 +5396,16 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5337,13 +5337,13 @@
         <v>80336.91</v>
       </c>
       <c r="E58" t="n">
-        <v>82734.96000000001</v>
+        <v>82827.78</v>
       </c>
       <c r="F58" t="n">
-        <v>-3745.34</v>
+        <v>-3652.52</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0433</v>
+        <v>-0.0422</v>
       </c>
       <c r="H58" t="n">
         <v>6634.88</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>111163.02</v>
+        <v>115399.63</v>
       </c>
       <c r="C2" t="n">
-        <v>116769.38</v>
+        <v>117911.79</v>
       </c>
       <c r="D2" t="n">
-        <v>110630.61</v>
+        <v>114461.06</v>
       </c>
       <c r="E2" t="n">
-        <v>115407.66</v>
+        <v>115306.09</v>
       </c>
       <c r="F2" t="n">
-        <v>4240.04</v>
+        <v>-101.56</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0381</v>
+        <v>-0.0009</v>
       </c>
       <c r="H2" t="n">
-        <v>6138.77</v>
+        <v>3450.73</v>
       </c>
       <c r="I2" t="n">
-        <v>108457.09</v>
+        <v>104491.84</v>
       </c>
       <c r="J2" t="n">
-        <v>109780.64</v>
+        <v>110122.71</v>
       </c>
       <c r="K2" t="n">
-        <v>110384.12</v>
+        <v>112338.27</v>
       </c>
       <c r="L2" t="n">
-        <v>110987.6</v>
+        <v>114553.83</v>
       </c>
       <c r="M2" t="n">
-        <v>111951.11</v>
+        <v>118477.04</v>
       </c>
       <c r="N2" t="n">
-        <v>112914.63</v>
+        <v>122400.26</v>
       </c>
       <c r="O2" t="n">
-        <v>113158.07</v>
+        <v>122908.16</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,91 +690,95 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>115399.63</v>
+        <v>115309.22</v>
       </c>
       <c r="C3" t="n">
-        <v>117911.79</v>
+        <v>115431.31</v>
       </c>
       <c r="D3" t="n">
-        <v>114461.06</v>
+        <v>108713.4</v>
       </c>
       <c r="E3" t="n">
-        <v>115306.09</v>
+        <v>112122.64</v>
       </c>
       <c r="F3" t="n">
-        <v>-101.56</v>
+        <v>-3183.45</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0276</v>
       </c>
       <c r="H3" t="n">
-        <v>3450.73</v>
+        <v>6717.91</v>
       </c>
       <c r="I3" t="n">
-        <v>104491.84</v>
+        <v>111010.34</v>
       </c>
       <c r="J3" t="n">
-        <v>110122.71</v>
+        <v>111415.2</v>
       </c>
       <c r="K3" t="n">
-        <v>112338.27</v>
+        <v>113580.73</v>
       </c>
       <c r="L3" t="n">
-        <v>114553.83</v>
+        <v>115746.26</v>
       </c>
       <c r="M3" t="n">
-        <v>118477.04</v>
+        <v>117031.46</v>
       </c>
       <c r="N3" t="n">
-        <v>122400.26</v>
+        <v>118316.65</v>
       </c>
       <c r="O3" t="n">
-        <v>122908.16</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>121362.52</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -793,237 +797,233 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>115309.22</v>
+        <v>112117.88</v>
       </c>
       <c r="C4" t="n">
-        <v>115431.31</v>
+        <v>125559.21</v>
       </c>
       <c r="D4" t="n">
-        <v>108713.4</v>
+        <v>111589.95</v>
       </c>
       <c r="E4" t="n">
-        <v>112122.64</v>
+        <v>123513.48</v>
       </c>
       <c r="F4" t="n">
-        <v>-3183.45</v>
+        <v>11390.84</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0276</v>
+        <v>0.1016</v>
       </c>
       <c r="H4" t="n">
-        <v>6717.91</v>
+        <v>13969.26</v>
       </c>
       <c r="I4" t="n">
-        <v>111010.34</v>
+        <v>101995.48</v>
       </c>
       <c r="J4" t="n">
-        <v>111415.2</v>
+        <v>105429.87</v>
       </c>
       <c r="K4" t="n">
-        <v>113580.73</v>
+        <v>108763.68</v>
       </c>
       <c r="L4" t="n">
-        <v>115746.26</v>
+        <v>112097.5</v>
       </c>
       <c r="M4" t="n">
-        <v>117031.46</v>
+        <v>115481.6</v>
       </c>
       <c r="N4" t="n">
-        <v>118316.65</v>
+        <v>118865.7</v>
       </c>
       <c r="O4" t="n">
-        <v>121362.52</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
+        <v>122149.23</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
-      </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>112117.88</v>
+        <v>123510.45</v>
       </c>
       <c r="C5" t="n">
-        <v>125559.21</v>
+        <v>126198.07</v>
       </c>
       <c r="D5" t="n">
-        <v>111589.95</v>
+        <v>104582.41</v>
       </c>
       <c r="E5" t="n">
-        <v>123513.48</v>
+        <v>115169.77</v>
       </c>
       <c r="F5" t="n">
-        <v>11390.84</v>
+        <v>-8343.709999999999</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.1016</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>13969.26</v>
+        <v>21615.66</v>
       </c>
       <c r="I5" t="n">
-        <v>101995.48</v>
+        <v>97620.7</v>
       </c>
       <c r="J5" t="n">
-        <v>105429.87</v>
+        <v>112013.67</v>
       </c>
       <c r="K5" t="n">
-        <v>108763.68</v>
+        <v>116528.85</v>
       </c>
       <c r="L5" t="n">
-        <v>112097.5</v>
+        <v>121044.03</v>
       </c>
       <c r="M5" t="n">
-        <v>115481.6</v>
+        <v>130498.11</v>
       </c>
       <c r="N5" t="n">
-        <v>118865.7</v>
+        <v>139952.18</v>
       </c>
       <c r="O5" t="n">
-        <v>122149.23</v>
+        <v>139528.47</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
+      </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>123510.45</v>
+        <v>115161.68</v>
       </c>
       <c r="C6" t="n">
-        <v>126198.07</v>
+        <v>116020.48</v>
       </c>
       <c r="D6" t="n">
-        <v>104582.41</v>
+        <v>103598.43</v>
       </c>
       <c r="E6" t="n">
-        <v>115169.77</v>
+        <v>108666.71</v>
       </c>
       <c r="F6" t="n">
-        <v>-8343.709999999999</v>
+        <v>-6503.05</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0565</v>
       </c>
       <c r="H6" t="n">
-        <v>21615.66</v>
+        <v>12422.05</v>
       </c>
       <c r="I6" t="n">
-        <v>97620.7</v>
+        <v>82966.75999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>112013.67</v>
+        <v>93443.87</v>
       </c>
       <c r="K6" t="n">
-        <v>116528.85</v>
+        <v>104361.94</v>
       </c>
       <c r="L6" t="n">
-        <v>121044.03</v>
+        <v>115280</v>
       </c>
       <c r="M6" t="n">
-        <v>130498.11</v>
+        <v>125977.59</v>
       </c>
       <c r="N6" t="n">
-        <v>139952.18</v>
+        <v>136675.18</v>
       </c>
       <c r="O6" t="n">
-        <v>139528.47</v>
+        <v>147813.73</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q6" s="6" t="n">
+        <v/>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
@@ -1051,57 +1051,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>115161.68</v>
+        <v>108667.45</v>
       </c>
       <c r="C7" t="n">
-        <v>116020.48</v>
+        <v>115260.91</v>
       </c>
       <c r="D7" t="n">
-        <v>103598.43</v>
+        <v>106778</v>
       </c>
       <c r="E7" t="n">
-        <v>108666.71</v>
+        <v>114472.45</v>
       </c>
       <c r="F7" t="n">
-        <v>-6503.05</v>
+        <v>5805.73</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0565</v>
+        <v>0.0534</v>
       </c>
       <c r="H7" t="n">
-        <v>12422.05</v>
+        <v>8482.91</v>
       </c>
       <c r="I7" t="n">
-        <v>82966.75999999999</v>
+        <v>91176.38</v>
       </c>
       <c r="J7" t="n">
-        <v>93443.87</v>
+        <v>95673.28</v>
       </c>
       <c r="K7" t="n">
-        <v>104361.94</v>
+        <v>102455.68</v>
       </c>
       <c r="L7" t="n">
-        <v>115280</v>
+        <v>109238.08</v>
       </c>
       <c r="M7" t="n">
-        <v>125977.59</v>
+        <v>114877.74</v>
       </c>
       <c r="N7" t="n">
-        <v>136675.18</v>
+        <v>120517.39</v>
       </c>
       <c r="O7" t="n">
-        <v>147813.73</v>
+        <v>128442.54</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1109,19 +1109,19 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1135,77 +1135,79 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108667.45</v>
+        <v>114479.85</v>
       </c>
       <c r="C8" t="n">
-        <v>115260.91</v>
+        <v>116273.31</v>
       </c>
       <c r="D8" t="n">
-        <v>106778</v>
+        <v>106376.69</v>
       </c>
       <c r="E8" t="n">
-        <v>114472.45</v>
+        <v>110639.62</v>
       </c>
       <c r="F8" t="n">
-        <v>5805.73</v>
+        <v>-3832.82</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0534</v>
+        <v>-0.0335</v>
       </c>
       <c r="H8" t="n">
-        <v>8482.91</v>
+        <v>9896.620000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>91176.38</v>
+        <v>98295.09</v>
       </c>
       <c r="J8" t="n">
-        <v>95673.28</v>
+        <v>107716.04</v>
       </c>
       <c r="K8" t="n">
-        <v>102455.68</v>
+        <v>110230.99</v>
       </c>
       <c r="L8" t="n">
-        <v>109238.08</v>
+        <v>112745.95</v>
       </c>
       <c r="M8" t="n">
-        <v>114877.74</v>
+        <v>118713.9</v>
       </c>
       <c r="N8" t="n">
-        <v>120517.39</v>
+        <v>124681.85</v>
       </c>
       <c r="O8" t="n">
-        <v>128442.54</v>
+        <v>123743.81</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1219,57 +1221,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>114479.85</v>
+        <v>110646.91</v>
       </c>
       <c r="C9" t="n">
-        <v>116273.31</v>
+        <v>110764.91</v>
       </c>
       <c r="D9" t="n">
-        <v>106376.69</v>
+        <v>98962.06</v>
       </c>
       <c r="E9" t="n">
-        <v>110639.62</v>
+        <v>104719.64</v>
       </c>
       <c r="F9" t="n">
-        <v>-3832.82</v>
+        <v>-5919.98</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0335</v>
+        <v>-0.0535</v>
       </c>
       <c r="H9" t="n">
-        <v>9896.620000000001</v>
+        <v>11802.85</v>
       </c>
       <c r="I9" t="n">
-        <v>98295.09</v>
+        <v>96480.06</v>
       </c>
       <c r="J9" t="n">
-        <v>107716.04</v>
+        <v>100400.31</v>
       </c>
       <c r="K9" t="n">
-        <v>110230.99</v>
+        <v>105691.31</v>
       </c>
       <c r="L9" t="n">
-        <v>112745.95</v>
+        <v>110982.31</v>
       </c>
       <c r="M9" t="n">
-        <v>118713.9</v>
+        <v>115587.94</v>
       </c>
       <c r="N9" t="n">
-        <v>124681.85</v>
+        <v>120193.56</v>
       </c>
       <c r="O9" t="n">
-        <v>123743.81</v>
+        <v>126169.94</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1305,69 +1307,69 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>110646.91</v>
+        <v>104723.77</v>
       </c>
       <c r="C10" t="n">
-        <v>110764.91</v>
+        <v>107428.26</v>
       </c>
       <c r="D10" t="n">
-        <v>98962.06</v>
+        <v>92971.16</v>
       </c>
       <c r="E10" t="n">
-        <v>104719.64</v>
+        <v>94177.08</v>
       </c>
       <c r="F10" t="n">
-        <v>-5919.98</v>
+        <v>-10542.56</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0535</v>
+        <v>-0.1007</v>
       </c>
       <c r="H10" t="n">
-        <v>11802.85</v>
+        <v>14457.09</v>
       </c>
       <c r="I10" t="n">
-        <v>96480.06</v>
+        <v>87159.21000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>100400.31</v>
+        <v>92844.87</v>
       </c>
       <c r="K10" t="n">
-        <v>105691.31</v>
+        <v>98818.21000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>110982.31</v>
+        <v>104791.56</v>
       </c>
       <c r="M10" t="n">
-        <v>115587.94</v>
+        <v>110621.07</v>
       </c>
       <c r="N10" t="n">
-        <v>120193.56</v>
+        <v>116450.57</v>
       </c>
       <c r="O10" t="n">
-        <v>126169.94</v>
+        <v>122567.77</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
@@ -1398,62 +1400,60 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>104723.77</v>
+        <v>94180.88</v>
       </c>
       <c r="C11" t="n">
-        <v>107428.26</v>
+        <v>95928.37</v>
       </c>
       <c r="D11" t="n">
-        <v>92971.16</v>
+        <v>80659.81</v>
       </c>
       <c r="E11" t="n">
-        <v>94177.08</v>
+        <v>86805.00999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-10542.56</v>
+        <v>-7372.07</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.1007</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>14457.09</v>
+        <v>15268.55</v>
       </c>
       <c r="I11" t="n">
-        <v>87159.21000000001</v>
+        <v>78514.07000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>92844.87</v>
+        <v>76708.67</v>
       </c>
       <c r="K11" t="n">
-        <v>98818.21000000001</v>
+        <v>86948.53</v>
       </c>
       <c r="L11" t="n">
-        <v>104791.56</v>
+        <v>97188.39</v>
       </c>
       <c r="M11" t="n">
-        <v>110621.07</v>
+        <v>101405.62</v>
       </c>
       <c r="N11" t="n">
-        <v>116450.57</v>
+        <v>105622.86</v>
       </c>
       <c r="O11" t="n">
-        <v>122567.77</v>
+        <v>121885.35</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
@@ -1484,50 +1484,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>94180.88</v>
+        <v>86798.77</v>
       </c>
       <c r="C12" t="n">
-        <v>95928.37</v>
+        <v>92969.09</v>
       </c>
       <c r="D12" t="n">
-        <v>80659.81</v>
+        <v>85272.2</v>
       </c>
       <c r="E12" t="n">
-        <v>86805.00999999999</v>
+        <v>90394.31</v>
       </c>
       <c r="F12" t="n">
-        <v>-7372.07</v>
+        <v>3589.3</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.0413</v>
       </c>
       <c r="H12" t="n">
-        <v>15268.55</v>
+        <v>7696.89</v>
       </c>
       <c r="I12" t="n">
-        <v>78514.07000000001</v>
+        <v>65391.26</v>
       </c>
       <c r="J12" t="n">
-        <v>76708.67</v>
+        <v>70791.91</v>
       </c>
       <c r="K12" t="n">
-        <v>86948.53</v>
+        <v>79170.73</v>
       </c>
       <c r="L12" t="n">
-        <v>97188.39</v>
+        <v>87549.55</v>
       </c>
       <c r="M12" t="n">
-        <v>101405.62</v>
+        <v>94439.28999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>105622.86</v>
+        <v>101329.02</v>
       </c>
       <c r="O12" t="n">
-        <v>121885.35</v>
+        <v>111196.92</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1535,14 +1535,12 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1561,57 +1559,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>86798.77</v>
+        <v>90389.11</v>
       </c>
       <c r="C13" t="n">
-        <v>92969.09</v>
+        <v>94060.77</v>
       </c>
       <c r="D13" t="n">
-        <v>85272.2</v>
+        <v>83862.25</v>
       </c>
       <c r="E13" t="n">
-        <v>90394.31</v>
+        <v>90405.64</v>
       </c>
       <c r="F13" t="n">
-        <v>3589.3</v>
+        <v>11.33</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0413</v>
+        <v>0.0001</v>
       </c>
       <c r="H13" t="n">
-        <v>7696.89</v>
+        <v>10198.52</v>
       </c>
       <c r="I13" t="n">
-        <v>65391.26</v>
+        <v>77575.3</v>
       </c>
       <c r="J13" t="n">
-        <v>70791.91</v>
+        <v>83334.25999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>79170.73</v>
+        <v>86545.87</v>
       </c>
       <c r="L13" t="n">
-        <v>87549.55</v>
+        <v>89757.48</v>
       </c>
       <c r="M13" t="n">
-        <v>94439.28999999999</v>
+        <v>94242.75999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>101329.02</v>
+        <v>98728.03999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>111196.92</v>
+        <v>100665.98</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1619,8 +1617,10 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
@@ -1650,50 +1650,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>90389.11</v>
+        <v>90424.59</v>
       </c>
       <c r="C14" t="n">
-        <v>94060.77</v>
+        <v>94601.57000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>83862.25</v>
+        <v>87634.94</v>
       </c>
       <c r="E14" t="n">
-        <v>90405.64</v>
+        <v>88175.17999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>11.33</v>
+        <v>-2230.46</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0247</v>
       </c>
       <c r="H14" t="n">
-        <v>10198.52</v>
+        <v>6966.63</v>
       </c>
       <c r="I14" t="n">
-        <v>77575.3</v>
+        <v>73663.73</v>
       </c>
       <c r="J14" t="n">
-        <v>83334.25999999999</v>
+        <v>80929.17999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>86545.87</v>
+        <v>85306.38</v>
       </c>
       <c r="L14" t="n">
-        <v>89757.48</v>
+        <v>89683.58</v>
       </c>
       <c r="M14" t="n">
-        <v>94242.75999999999</v>
+        <v>95504.89999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>98728.03999999999</v>
+        <v>101326.23</v>
       </c>
       <c r="O14" t="n">
-        <v>100665.98</v>
+        <v>104259.3</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1701,14 +1701,12 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1734,50 +1732,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>90424.59</v>
+        <v>88171.08</v>
       </c>
       <c r="C15" t="n">
-        <v>94601.57000000001</v>
+        <v>90264.57000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>87634.94</v>
+        <v>84436.31</v>
       </c>
       <c r="E15" t="n">
-        <v>88175.17999999999</v>
+        <v>88621.75</v>
       </c>
       <c r="F15" t="n">
-        <v>-2230.46</v>
+        <v>446.57</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0051</v>
       </c>
       <c r="H15" t="n">
-        <v>6966.63</v>
+        <v>5828.26</v>
       </c>
       <c r="I15" t="n">
-        <v>73663.73</v>
+        <v>80668.3</v>
       </c>
       <c r="J15" t="n">
-        <v>80929.17999999999</v>
+        <v>79737.00999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>85306.38</v>
+        <v>84691.86</v>
       </c>
       <c r="L15" t="n">
-        <v>89683.58</v>
+        <v>89646.72</v>
       </c>
       <c r="M15" t="n">
-        <v>95504.89999999999</v>
+        <v>91658.5</v>
       </c>
       <c r="N15" t="n">
-        <v>101326.23</v>
+        <v>93670.28</v>
       </c>
       <c r="O15" t="n">
-        <v>104259.3</v>
+        <v>101568.2</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1785,8 +1783,10 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
@@ -1809,57 +1809,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>88171.08</v>
+        <v>88621.39999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>90264.57000000001</v>
+        <v>90501.92999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>84436.31</v>
+        <v>86411.8</v>
       </c>
       <c r="E16" t="n">
-        <v>88621.75</v>
+        <v>87835.84</v>
       </c>
       <c r="F16" t="n">
-        <v>446.57</v>
+        <v>-785.91</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0051</v>
+        <v>-0.0089</v>
       </c>
       <c r="H16" t="n">
-        <v>5828.26</v>
+        <v>4090.13</v>
       </c>
       <c r="I16" t="n">
-        <v>80668.3</v>
+        <v>78608.05</v>
       </c>
       <c r="J16" t="n">
-        <v>79737.00999999999</v>
+        <v>83429.14999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>84691.86</v>
+        <v>85707.62</v>
       </c>
       <c r="L16" t="n">
-        <v>89646.72</v>
+        <v>87986.10000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>91658.5</v>
+        <v>91535.88</v>
       </c>
       <c r="N16" t="n">
-        <v>93670.28</v>
+        <v>95085.66</v>
       </c>
       <c r="O16" t="n">
-        <v>101568.2</v>
+        <v>96092.83</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1867,10 +1867,8 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R16" s="6" t="n">
+        <v/>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
@@ -1893,57 +1891,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>88621.39999999999</v>
+        <v>87835.78999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>90501.92999999999</v>
+        <v>91712.59</v>
       </c>
       <c r="D17" t="n">
-        <v>86411.8</v>
+        <v>86717.91</v>
       </c>
       <c r="E17" t="n">
-        <v>87835.84</v>
+        <v>91413.49000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-785.91</v>
+        <v>3577.66</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0089</v>
+        <v>0.0407</v>
       </c>
       <c r="H17" t="n">
-        <v>4090.13</v>
+        <v>4994.67</v>
       </c>
       <c r="I17" t="n">
-        <v>78608.05</v>
+        <v>82321.66</v>
       </c>
       <c r="J17" t="n">
-        <v>83429.14999999999</v>
+        <v>83435.19</v>
       </c>
       <c r="K17" t="n">
-        <v>85707.62</v>
+        <v>85790.77</v>
       </c>
       <c r="L17" t="n">
-        <v>87986.10000000001</v>
+        <v>88146.35000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>91535.88</v>
+        <v>89880.89999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>95085.66</v>
+        <v>91615.46000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>96092.83</v>
+        <v>94592.06</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1954,16 +1952,20 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1973,59 +1975,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>87835.78999999999</v>
+        <v>91414.62</v>
       </c>
       <c r="C18" t="n">
-        <v>91712.59</v>
+        <v>94762.07000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>86717.91</v>
+        <v>89233.88</v>
       </c>
       <c r="E18" t="n">
-        <v>91413.49000000001</v>
+        <v>90827.46000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>3577.66</v>
+        <v>-586.03</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0407</v>
+        <v>-0.0064</v>
       </c>
       <c r="H18" t="n">
-        <v>4994.67</v>
+        <v>5528.2</v>
       </c>
       <c r="I18" t="n">
-        <v>82321.66</v>
+        <v>81723.24000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>83435.19</v>
+        <v>87517.94</v>
       </c>
       <c r="K18" t="n">
-        <v>85790.77</v>
+        <v>88916.16</v>
       </c>
       <c r="L18" t="n">
-        <v>88146.35000000001</v>
+        <v>90314.37</v>
       </c>
       <c r="M18" t="n">
-        <v>89880.89999999999</v>
+        <v>93910.83</v>
       </c>
       <c r="N18" t="n">
-        <v>91615.46000000001</v>
+        <v>97507.28999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>94592.06</v>
+        <v>96707.25999999999</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2038,7 +2036,7 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
@@ -2046,10 +2044,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2059,55 +2055,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>91414.62</v>
+        <v>90825.86</v>
       </c>
       <c r="C19" t="n">
-        <v>94762.07000000001</v>
+        <v>97860.60000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>89233.88</v>
+        <v>90055.02</v>
       </c>
       <c r="E19" t="n">
-        <v>90827.46000000001</v>
+        <v>93634.42999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-586.03</v>
+        <v>2806.97</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0064</v>
+        <v>0.0309</v>
       </c>
       <c r="H19" t="n">
-        <v>5528.2</v>
+        <v>7805.58</v>
       </c>
       <c r="I19" t="n">
-        <v>81723.24000000001</v>
+        <v>83705.67999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>87517.94</v>
+        <v>84714.00999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>88916.16</v>
+        <v>88063.36</v>
       </c>
       <c r="L19" t="n">
-        <v>90314.37</v>
+        <v>91412.72</v>
       </c>
       <c r="M19" t="n">
-        <v>93910.83</v>
+        <v>93591.56</v>
       </c>
       <c r="N19" t="n">
-        <v>97507.28999999999</v>
+        <v>95770.39999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>96707.25999999999</v>
+        <v>100290.27</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2120,17 +2120,19 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
@@ -2139,84 +2141,80 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>90825.86</v>
+        <v>93655.67</v>
       </c>
       <c r="C20" t="n">
-        <v>97860.60000000001</v>
+        <v>93660.83</v>
       </c>
       <c r="D20" t="n">
-        <v>90055.02</v>
+        <v>86003.71000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>93634.42999999999</v>
+        <v>86572.22</v>
       </c>
       <c r="F20" t="n">
-        <v>2806.97</v>
+        <v>-7062.21</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0309</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>7805.58</v>
+        <v>7657.12</v>
       </c>
       <c r="I20" t="n">
-        <v>83705.67999999999</v>
+        <v>82249.45</v>
       </c>
       <c r="J20" t="n">
-        <v>84714.00999999999</v>
+        <v>85667.16</v>
       </c>
       <c r="K20" t="n">
-        <v>88063.36</v>
+        <v>89731.64</v>
       </c>
       <c r="L20" t="n">
-        <v>91412.72</v>
+        <v>93796.12</v>
       </c>
       <c r="M20" t="n">
-        <v>93591.56</v>
+        <v>97537.22</v>
       </c>
       <c r="N20" t="n">
-        <v>95770.39999999999</v>
+        <v>101278.32</v>
       </c>
       <c r="O20" t="n">
-        <v>100290.27</v>
+        <v>105666.18</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="Q20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2225,58 +2223,64 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>93655.67</v>
+        <v>86566.52</v>
       </c>
       <c r="C21" t="n">
-        <v>93660.83</v>
+        <v>90439.28999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>86003.71000000001</v>
+        <v>75698.89999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>86572.22</v>
+        <v>76974.45</v>
       </c>
       <c r="F21" t="n">
-        <v>-7062.21</v>
+        <v>-9597.77</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.1109</v>
       </c>
       <c r="H21" t="n">
-        <v>7657.12</v>
+        <v>14740.39</v>
       </c>
       <c r="I21" t="n">
-        <v>82249.45</v>
+        <v>78346.59</v>
       </c>
       <c r="J21" t="n">
-        <v>85667.16</v>
+        <v>77285.08</v>
       </c>
       <c r="K21" t="n">
-        <v>89731.64</v>
+        <v>82743.66</v>
       </c>
       <c r="L21" t="n">
-        <v>93796.12</v>
+        <v>88202.24000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>97537.22</v>
+        <v>90400.78</v>
       </c>
       <c r="N21" t="n">
-        <v>101278.32</v>
+        <v>92599.31</v>
       </c>
       <c r="O21" t="n">
-        <v>105666.18</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
+        <v>101317.95</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
@@ -2293,8 +2297,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2302,89 +2308,81 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>86566.52</v>
+        <v>76968.88</v>
       </c>
       <c r="C22" t="n">
-        <v>90439.28999999999</v>
+        <v>79258.61</v>
       </c>
       <c r="D22" t="n">
-        <v>75698.89999999999</v>
+        <v>60074.2</v>
       </c>
       <c r="E22" t="n">
-        <v>76974.45</v>
+        <v>70264.73</v>
       </c>
       <c r="F22" t="n">
-        <v>-9597.77</v>
+        <v>-6709.72</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.1109</v>
+        <v>-0.0872</v>
       </c>
       <c r="H22" t="n">
-        <v>14740.39</v>
+        <v>19184.41</v>
       </c>
       <c r="I22" t="n">
-        <v>78346.59</v>
+        <v>60958.51</v>
       </c>
       <c r="J22" t="n">
-        <v>77285.08</v>
+        <v>59186.73</v>
       </c>
       <c r="K22" t="n">
-        <v>82743.66</v>
+        <v>69604.25</v>
       </c>
       <c r="L22" t="n">
-        <v>88202.24000000001</v>
+        <v>80021.77</v>
       </c>
       <c r="M22" t="n">
-        <v>90400.78</v>
+        <v>84344.64</v>
       </c>
       <c r="N22" t="n">
-        <v>92599.31</v>
+        <v>88667.50999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>101317.95</v>
+        <v>105179.68</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2402,67 +2400,63 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>76968.88</v>
+        <v>70243.33</v>
       </c>
       <c r="C23" t="n">
-        <v>79258.61</v>
+        <v>71369.97</v>
       </c>
       <c r="D23" t="n">
-        <v>60074.2</v>
+        <v>65092.11</v>
       </c>
       <c r="E23" t="n">
-        <v>70264.73</v>
+        <v>68788.19</v>
       </c>
       <c r="F23" t="n">
-        <v>-6709.72</v>
+        <v>-1476.54</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0872</v>
+        <v>-0.021</v>
       </c>
       <c r="H23" t="n">
-        <v>19184.41</v>
+        <v>6277.86</v>
       </c>
       <c r="I23" t="n">
-        <v>60958.51</v>
+        <v>40889.8</v>
       </c>
       <c r="J23" t="n">
-        <v>59186.73</v>
+        <v>51379.48</v>
       </c>
       <c r="K23" t="n">
-        <v>69604.25</v>
+        <v>60672.52</v>
       </c>
       <c r="L23" t="n">
-        <v>80021.77</v>
+        <v>69965.57000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>84344.64</v>
+        <v>79856.92999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>88667.50999999999</v>
+        <v>89748.28999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>105179.68</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>98443.02</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
       </c>
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2479,55 +2473,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>70243.33</v>
+        <v>68782.39999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>71369.97</v>
+        <v>70067.23</v>
       </c>
       <c r="D24" t="n">
-        <v>65092.11</v>
+        <v>65637.42999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>68788.19</v>
+        <v>67659.39</v>
       </c>
       <c r="F24" t="n">
-        <v>-1476.54</v>
+        <v>-1128.8</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.021</v>
+        <v>-0.0164</v>
       </c>
       <c r="H24" t="n">
-        <v>6277.86</v>
+        <v>4429.8</v>
       </c>
       <c r="I24" t="n">
-        <v>40889.8</v>
+        <v>58814.25</v>
       </c>
       <c r="J24" t="n">
-        <v>51379.48</v>
+        <v>62788.9</v>
       </c>
       <c r="K24" t="n">
-        <v>60672.52</v>
+        <v>65649.25999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>69965.57000000001</v>
+        <v>68509.61</v>
       </c>
       <c r="M24" t="n">
-        <v>79856.92999999999</v>
+        <v>71927.12</v>
       </c>
       <c r="N24" t="n">
-        <v>89748.28999999999</v>
+        <v>75344.62</v>
       </c>
       <c r="O24" t="n">
-        <v>98443.02</v>
+        <v>77647.83</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2535,8 +2533,10 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
@@ -2566,70 +2566,74 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>68782.39999999999</v>
+        <v>67668.42999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>70067.23</v>
+        <v>69953.53</v>
       </c>
       <c r="D25" t="n">
-        <v>65637.42999999999</v>
+        <v>62553.19</v>
       </c>
       <c r="E25" t="n">
-        <v>67659.39</v>
+        <v>65738.10000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-1128.8</v>
+        <v>-1921.29</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0164</v>
+        <v>-0.0284</v>
       </c>
       <c r="H25" t="n">
-        <v>4429.8</v>
+        <v>7400.34</v>
       </c>
       <c r="I25" t="n">
-        <v>58814.25</v>
+        <v>61207.62</v>
       </c>
       <c r="J25" t="n">
-        <v>62788.9</v>
+        <v>63133.12</v>
       </c>
       <c r="K25" t="n">
-        <v>65649.25999999999</v>
+        <v>65444.49</v>
       </c>
       <c r="L25" t="n">
-        <v>68509.61</v>
+        <v>67755.86</v>
       </c>
       <c r="M25" t="n">
-        <v>71927.12</v>
+        <v>69874.28999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>75344.62</v>
+        <v>71992.72</v>
       </c>
       <c r="O25" t="n">
-        <v>77647.83</v>
+        <v>74497.03999999999</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
@@ -2641,86 +2645,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>67668.42999999999</v>
+        <v>65734.08</v>
       </c>
       <c r="C26" t="n">
-        <v>69953.53</v>
+        <v>74051.8</v>
       </c>
       <c r="D26" t="n">
-        <v>62553.19</v>
+        <v>65303.14</v>
       </c>
       <c r="E26" t="n">
-        <v>65738.10000000001</v>
+        <v>65969.78</v>
       </c>
       <c r="F26" t="n">
-        <v>-1921.29</v>
+        <v>231.68</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0284</v>
+        <v>0.0035</v>
       </c>
       <c r="H26" t="n">
-        <v>7400.34</v>
+        <v>8748.67</v>
       </c>
       <c r="I26" t="n">
-        <v>61207.62</v>
+        <v>55152.84</v>
       </c>
       <c r="J26" t="n">
-        <v>63133.12</v>
+        <v>58080.13</v>
       </c>
       <c r="K26" t="n">
-        <v>65444.49</v>
+        <v>62037.93</v>
       </c>
       <c r="L26" t="n">
-        <v>67755.86</v>
+        <v>65995.73</v>
       </c>
       <c r="M26" t="n">
-        <v>69874.28999999999</v>
+        <v>69438.27</v>
       </c>
       <c r="N26" t="n">
-        <v>71992.72</v>
+        <v>72880.82000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>74497.03999999999</v>
+        <v>77353.88</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
@@ -2729,55 +2727,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>65734.08</v>
+        <v>65969.59</v>
       </c>
       <c r="C27" t="n">
-        <v>74051.8</v>
+        <v>73927.33</v>
       </c>
       <c r="D27" t="n">
-        <v>65303.14</v>
+        <v>65858.00999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>65969.78</v>
+        <v>72789.91</v>
       </c>
       <c r="F27" t="n">
-        <v>231.68</v>
+        <v>6820.13</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.1034</v>
       </c>
       <c r="H27" t="n">
-        <v>8748.67</v>
+        <v>8069.32</v>
       </c>
       <c r="I27" t="n">
-        <v>55152.84</v>
+        <v>56554.47</v>
       </c>
       <c r="J27" t="n">
-        <v>58080.13</v>
+        <v>55367.27</v>
       </c>
       <c r="K27" t="n">
-        <v>62037.93</v>
+        <v>61595.45</v>
       </c>
       <c r="L27" t="n">
-        <v>65995.73</v>
+        <v>67823.63</v>
       </c>
       <c r="M27" t="n">
-        <v>69438.27</v>
+        <v>70344.12</v>
       </c>
       <c r="N27" t="n">
-        <v>72880.82000000001</v>
+        <v>72864.60000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>77353.88</v>
+        <v>82800.47</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2788,9 +2790,9 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -2800,7 +2802,7 @@
       </c>
       <c r="U27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V27" s="8" t="n">
@@ -2813,57 +2815,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>65969.59</v>
+        <v>72798.17</v>
       </c>
       <c r="C28" t="n">
-        <v>73927.33</v>
+        <v>75988.39999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>65858.00999999999</v>
+        <v>67372.88</v>
       </c>
       <c r="E28" t="n">
-        <v>72789.91</v>
+        <v>67845.21000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>6820.13</v>
+        <v>-4944.7</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.1034</v>
+        <v>-0.0679</v>
       </c>
       <c r="H28" t="n">
-        <v>8069.32</v>
+        <v>8615.52</v>
       </c>
       <c r="I28" t="n">
-        <v>56554.47</v>
+        <v>57788.69</v>
       </c>
       <c r="J28" t="n">
-        <v>55367.27</v>
+        <v>66169.22</v>
       </c>
       <c r="K28" t="n">
-        <v>61595.45</v>
+        <v>68755.25</v>
       </c>
       <c r="L28" t="n">
-        <v>67823.63</v>
+        <v>71341.28999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>70344.12</v>
+        <v>76824.57000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>72864.60000000001</v>
+        <v>82307.86</v>
       </c>
       <c r="O28" t="n">
-        <v>82800.47</v>
+        <v>81996.64999999999</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2871,23 +2873,21 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2906,50 +2906,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>72798.17</v>
+        <v>67843</v>
       </c>
       <c r="C29" t="n">
-        <v>75988.39999999999</v>
+        <v>71985.74000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>67372.88</v>
+        <v>64971.71</v>
       </c>
       <c r="E29" t="n">
-        <v>67845.21000000001</v>
+        <v>65954.92</v>
       </c>
       <c r="F29" t="n">
-        <v>-4944.7</v>
+        <v>-1890.29</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0679</v>
+        <v>-0.0279</v>
       </c>
       <c r="H29" t="n">
-        <v>8615.52</v>
+        <v>7014.04</v>
       </c>
       <c r="I29" t="n">
-        <v>57788.69</v>
+        <v>58757.35</v>
       </c>
       <c r="J29" t="n">
-        <v>66169.22</v>
+        <v>57311.97</v>
       </c>
       <c r="K29" t="n">
-        <v>68755.25</v>
+        <v>63537.45</v>
       </c>
       <c r="L29" t="n">
-        <v>71341.28999999999</v>
+        <v>69762.92</v>
       </c>
       <c r="M29" t="n">
-        <v>76824.57000000001</v>
+        <v>72152.97</v>
       </c>
       <c r="N29" t="n">
-        <v>82307.86</v>
+        <v>74543.02</v>
       </c>
       <c r="O29" t="n">
-        <v>81996.64999999999</v>
+        <v>84603.92</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2981,59 +2981,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>67843</v>
+        <v>65958.35000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>71985.74000000001</v>
+        <v>69230.36</v>
       </c>
       <c r="D30" t="n">
-        <v>64971.71</v>
+        <v>65725.25999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>65954.92</v>
+        <v>68981.89999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>-1890.29</v>
+        <v>3026.98</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0279</v>
+        <v>0.0459</v>
       </c>
       <c r="H30" t="n">
-        <v>7014.04</v>
+        <v>3505.1</v>
       </c>
       <c r="I30" t="n">
-        <v>58757.35</v>
+        <v>57957.67</v>
       </c>
       <c r="J30" t="n">
-        <v>57311.97</v>
+        <v>57678.99</v>
       </c>
       <c r="K30" t="n">
-        <v>63537.45</v>
+        <v>62447.9</v>
       </c>
       <c r="L30" t="n">
-        <v>69762.92</v>
+        <v>67216.82000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>72152.97</v>
+        <v>69461.94</v>
       </c>
       <c r="N30" t="n">
-        <v>74543.02</v>
+        <v>71707.06</v>
       </c>
       <c r="O30" t="n">
-        <v>84603.92</v>
+        <v>78999.78</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3041,19 +3037,19 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
@@ -3065,55 +3061,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>65958.35000000001</v>
+        <v>68982.91</v>
       </c>
       <c r="C31" t="n">
-        <v>69230.36</v>
+        <v>73784.23</v>
       </c>
       <c r="D31" t="n">
-        <v>65725.25999999999</v>
+        <v>67740.50999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>68981.89999999999</v>
+        <v>70753.41</v>
       </c>
       <c r="F31" t="n">
-        <v>3026.98</v>
+        <v>1771.51</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0459</v>
+        <v>0.0257</v>
       </c>
       <c r="H31" t="n">
-        <v>3505.1</v>
+        <v>6043.73</v>
       </c>
       <c r="I31" t="n">
-        <v>57957.67</v>
+        <v>62220.16</v>
       </c>
       <c r="J31" t="n">
-        <v>57678.99</v>
+        <v>66228.84</v>
       </c>
       <c r="K31" t="n">
-        <v>62447.9</v>
+        <v>67229.35000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>67216.82000000001</v>
+        <v>68229.85000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>69461.94</v>
+        <v>70734.45</v>
       </c>
       <c r="N31" t="n">
-        <v>71707.06</v>
+        <v>73239.03999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>78999.78</v>
+        <v>72735.46000000001</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3134,11 +3134,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W31" s="11" t="inlineStr">
         <is>
@@ -3147,57 +3151,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>68982.91</v>
+        <v>70757.62</v>
       </c>
       <c r="C32" t="n">
-        <v>73784.23</v>
+        <v>78320.67999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>67740.50999999999</v>
+        <v>70588.52</v>
       </c>
       <c r="E32" t="n">
-        <v>70753.41</v>
+        <v>73856.35000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>1771.51</v>
+        <v>3102.95</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0257</v>
+        <v>0.0439</v>
       </c>
       <c r="H32" t="n">
-        <v>6043.73</v>
+        <v>7732.16</v>
       </c>
       <c r="I32" t="n">
-        <v>62220.16</v>
+        <v>61696.78</v>
       </c>
       <c r="J32" t="n">
-        <v>66228.84</v>
+        <v>64705.2</v>
       </c>
       <c r="K32" t="n">
-        <v>67229.35000000001</v>
+        <v>67731.53999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>68229.85000000001</v>
+        <v>70757.89</v>
       </c>
       <c r="M32" t="n">
-        <v>70734.45</v>
+        <v>73775.27</v>
       </c>
       <c r="N32" t="n">
-        <v>73239.03999999999</v>
+        <v>76792.64999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>72735.46000000001</v>
+        <v>79827.96000000001</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3223,10 +3227,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V32" s="8" t="n">
+        <v/>
       </c>
       <c r="W32" s="11" t="inlineStr">
         <is>
@@ -3242,50 +3244,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>70757.62</v>
+        <v>73854.25</v>
       </c>
       <c r="C33" t="n">
-        <v>78320.67999999999</v>
+        <v>79468</v>
       </c>
       <c r="D33" t="n">
-        <v>70588.52</v>
+        <v>73775.57000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>73856.35000000001</v>
+        <v>78657.53999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>3102.95</v>
+        <v>4801.19</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0439</v>
+        <v>0.065</v>
       </c>
       <c r="H33" t="n">
-        <v>7732.16</v>
+        <v>5692.43</v>
       </c>
       <c r="I33" t="n">
-        <v>61696.78</v>
+        <v>62856.37</v>
       </c>
       <c r="J33" t="n">
-        <v>64705.2</v>
+        <v>65825.07000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>67731.53999999999</v>
+        <v>69990.27</v>
       </c>
       <c r="L33" t="n">
-        <v>70757.89</v>
+        <v>74155.48</v>
       </c>
       <c r="M33" t="n">
-        <v>73775.27</v>
+        <v>77722.42999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>76792.64999999999</v>
+        <v>81289.38</v>
       </c>
       <c r="O33" t="n">
-        <v>79827.96000000001</v>
+        <v>86052.84</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3306,10 +3308,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3328,50 +3328,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>73854.25</v>
+        <v>78661.02</v>
       </c>
       <c r="C34" t="n">
-        <v>79468</v>
+        <v>79488.17</v>
       </c>
       <c r="D34" t="n">
-        <v>73775.57000000001</v>
+        <v>74958.57000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>78657.53999999999</v>
+        <v>78538.23</v>
       </c>
       <c r="F34" t="n">
-        <v>4801.19</v>
+        <v>-119.31</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.065</v>
+        <v>-0.0015</v>
       </c>
       <c r="H34" t="n">
-        <v>5692.43</v>
+        <v>4529.6</v>
       </c>
       <c r="I34" t="n">
-        <v>62856.37</v>
+        <v>68083.14</v>
       </c>
       <c r="J34" t="n">
-        <v>65825.07000000001</v>
+        <v>73982.99000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>69990.27</v>
+        <v>75811.32000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>74155.48</v>
+        <v>77639.66</v>
       </c>
       <c r="M34" t="n">
-        <v>77722.42999999999</v>
+        <v>81503.75</v>
       </c>
       <c r="N34" t="n">
-        <v>81289.38</v>
+        <v>85367.85000000001</v>
       </c>
       <c r="O34" t="n">
-        <v>86052.84</v>
+        <v>85160.42999999999</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3379,18 +3379,18 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3405,57 +3405,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>78661.02</v>
+        <v>78540.28999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>79488.17</v>
+        <v>82792.21000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>74958.57000000001</v>
+        <v>78217.96000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>78538.23</v>
+        <v>82138.92999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>-119.31</v>
+        <v>3600.7</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0458</v>
       </c>
       <c r="H35" t="n">
-        <v>4529.6</v>
+        <v>4574.25</v>
       </c>
       <c r="I35" t="n">
-        <v>68083.14</v>
+        <v>70428.97</v>
       </c>
       <c r="J35" t="n">
-        <v>73982.99000000001</v>
+        <v>74666.05</v>
       </c>
       <c r="K35" t="n">
-        <v>75811.32000000001</v>
+        <v>76273.42999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>77639.66</v>
+        <v>77880.8</v>
       </c>
       <c r="M35" t="n">
-        <v>81503.75</v>
+        <v>80803.03</v>
       </c>
       <c r="N35" t="n">
-        <v>85367.85000000001</v>
+        <v>83725.25999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>85160.42999999999</v>
+        <v>84017.77</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3463,18 +3463,18 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3489,77 +3489,79 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>78540.28999999999</v>
+        <v>82139.05</v>
       </c>
       <c r="C36" t="n">
-        <v>82792.21000000001</v>
+        <v>82326.23</v>
       </c>
       <c r="D36" t="n">
-        <v>78217.96000000001</v>
+        <v>76783.41</v>
       </c>
       <c r="E36" t="n">
-        <v>82138.92999999999</v>
+        <v>77429.35000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>3600.7</v>
+        <v>-4709.58</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0458</v>
+        <v>-0.0573</v>
       </c>
       <c r="H36" t="n">
-        <v>4574.25</v>
+        <v>5542.82</v>
       </c>
       <c r="I36" t="n">
-        <v>70428.97</v>
+        <v>73643.71000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>74666.05</v>
+        <v>78381.60000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>76273.42999999999</v>
+        <v>79851.8</v>
       </c>
       <c r="L36" t="n">
-        <v>77880.8</v>
+        <v>81322.00999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>80803.03</v>
+        <v>84426.05</v>
       </c>
       <c r="N36" t="n">
-        <v>83725.25999999999</v>
+        <v>87530.10000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>84017.77</v>
+        <v>87366.46000000001</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="Q36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3571,67 +3573,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>82139.05</v>
+        <v>77426.34</v>
       </c>
       <c r="C37" t="n">
-        <v>82326.23</v>
+        <v>78100.56</v>
       </c>
       <c r="D37" t="n">
-        <v>76783.41</v>
+        <v>74255.23</v>
       </c>
       <c r="E37" t="n">
-        <v>77429.35000000001</v>
+        <v>76981.12</v>
       </c>
       <c r="F37" t="n">
-        <v>-4709.58</v>
+        <v>-448.23</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0573</v>
+        <v>-0.0058</v>
       </c>
       <c r="H37" t="n">
-        <v>5542.82</v>
+        <v>3845.33</v>
       </c>
       <c r="I37" t="n">
-        <v>73643.71000000001</v>
+        <v>71240.59</v>
       </c>
       <c r="J37" t="n">
-        <v>78381.60000000001</v>
+        <v>70823.78999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>79851.8</v>
+        <v>74657.94</v>
       </c>
       <c r="L37" t="n">
-        <v>81322.00999999999</v>
+        <v>78492.09</v>
       </c>
       <c r="M37" t="n">
-        <v>84426.05</v>
+        <v>80200.75999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>87530.10000000001</v>
+        <v>81909.44</v>
       </c>
       <c r="O37" t="n">
-        <v>87366.46000000001</v>
+        <v>87869.05</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q37" s="6" t="n">
+        <v/>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
@@ -3640,7 +3636,7 @@
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3662,56 +3658,58 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>77426.34</v>
+        <v>76981.12</v>
       </c>
       <c r="C38" t="n">
-        <v>78100.56</v>
+        <v>77990.87</v>
       </c>
       <c r="D38" t="n">
-        <v>74255.23</v>
+        <v>72435.62</v>
       </c>
       <c r="E38" t="n">
-        <v>76981.12</v>
+        <v>73579.69</v>
       </c>
       <c r="F38" t="n">
-        <v>-448.23</v>
+        <v>-3401.44</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0442</v>
       </c>
       <c r="H38" t="n">
-        <v>3845.33</v>
+        <v>5555.24</v>
       </c>
       <c r="I38" t="n">
-        <v>71240.59</v>
+        <v>70409.91</v>
       </c>
       <c r="J38" t="n">
-        <v>70823.78999999999</v>
+        <v>73537.41</v>
       </c>
       <c r="K38" t="n">
-        <v>74657.94</v>
+        <v>75058.46000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>78492.09</v>
+        <v>76579.50999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>80200.75999999999</v>
+        <v>78903.78999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>81909.44</v>
+        <v>81228.07000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>87869.05</v>
+        <v>81945.89</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
@@ -3720,7 +3718,7 @@
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3742,57 +3740,59 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>76981.12</v>
+        <v>73580.21000000001</v>
       </c>
       <c r="C39" t="n">
-        <v>77990.87</v>
+        <v>73969.57000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>72435.62</v>
+        <v>59108.92</v>
       </c>
       <c r="E39" t="n">
-        <v>73579.69</v>
+        <v>63239.52</v>
       </c>
       <c r="F39" t="n">
-        <v>-3401.44</v>
+        <v>-10340.17</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0442</v>
+        <v>-0.1405</v>
       </c>
       <c r="H39" t="n">
-        <v>5555.24</v>
+        <v>14860.65</v>
       </c>
       <c r="I39" t="n">
-        <v>70409.91</v>
+        <v>66880.38</v>
       </c>
       <c r="J39" t="n">
-        <v>73537.41</v>
+        <v>67207.67</v>
       </c>
       <c r="K39" t="n">
-        <v>75058.46000000001</v>
+        <v>70802.07000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>76579.50999999999</v>
+        <v>74396.47</v>
       </c>
       <c r="M39" t="n">
-        <v>78903.78999999999</v>
+        <v>76357.31</v>
       </c>
       <c r="N39" t="n">
-        <v>81228.07000000001</v>
+        <v>78318.14999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>81945.89</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
+        <v>83546.11</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
@@ -3824,69 +3824,63 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>73580.21000000001</v>
+        <v>63244.09</v>
       </c>
       <c r="C40" t="n">
-        <v>73969.57000000001</v>
+        <v>65749.78</v>
       </c>
       <c r="D40" t="n">
-        <v>59108.92</v>
+        <v>60756.69</v>
       </c>
       <c r="E40" t="n">
-        <v>63239.52</v>
+        <v>65710.39999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>-10340.17</v>
+        <v>2470.88</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.1405</v>
+        <v>0.0391</v>
       </c>
       <c r="H40" t="n">
-        <v>14860.65</v>
+        <v>4993.09</v>
       </c>
       <c r="I40" t="n">
-        <v>66880.38</v>
+        <v>44248.27</v>
       </c>
       <c r="J40" t="n">
-        <v>67207.67</v>
+        <v>46729</v>
       </c>
       <c r="K40" t="n">
-        <v>70802.07000000001</v>
+        <v>55809.19</v>
       </c>
       <c r="L40" t="n">
-        <v>74396.47</v>
+        <v>64889.38</v>
       </c>
       <c r="M40" t="n">
-        <v>76357.31</v>
+        <v>70669.85000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>78318.14999999999</v>
+        <v>76450.31</v>
       </c>
       <c r="O40" t="n">
-        <v>83546.11</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>88830.22</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3903,55 +3897,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>63244.09</v>
+        <v>65711.11</v>
       </c>
       <c r="C41" t="n">
-        <v>65749.78</v>
+        <v>67248.13</v>
       </c>
       <c r="D41" t="n">
-        <v>60756.69</v>
+        <v>62201.14</v>
       </c>
       <c r="E41" t="n">
-        <v>65710.39999999999</v>
+        <v>63237.54</v>
       </c>
       <c r="F41" t="n">
-        <v>2470.88</v>
+        <v>-2472.86</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0391</v>
+        <v>-0.0376</v>
       </c>
       <c r="H41" t="n">
-        <v>4993.09</v>
+        <v>5046.99</v>
       </c>
       <c r="I41" t="n">
-        <v>44248.27</v>
+        <v>55763.59</v>
       </c>
       <c r="J41" t="n">
-        <v>46729</v>
+        <v>61945.89</v>
       </c>
       <c r="K41" t="n">
-        <v>55809.19</v>
+        <v>63213.85</v>
       </c>
       <c r="L41" t="n">
-        <v>64889.38</v>
+        <v>64481.82</v>
       </c>
       <c r="M41" t="n">
-        <v>70669.85000000001</v>
+        <v>68206.95</v>
       </c>
       <c r="N41" t="n">
-        <v>76450.31</v>
+        <v>71932.07000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>88830.22</v>
+        <v>70742.88</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3959,12 +3957,14 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3990,50 +3990,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>65711.11</v>
+        <v>63240.79</v>
       </c>
       <c r="C42" t="n">
-        <v>67248.13</v>
+        <v>65544</v>
       </c>
       <c r="D42" t="n">
-        <v>62201.14</v>
+        <v>58075.92</v>
       </c>
       <c r="E42" t="n">
-        <v>63237.54</v>
+        <v>59532.34</v>
       </c>
       <c r="F42" t="n">
-        <v>-2472.86</v>
+        <v>-3705.2</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0376</v>
+        <v>-0.0586</v>
       </c>
       <c r="H42" t="n">
-        <v>5046.99</v>
+        <v>7468.08</v>
       </c>
       <c r="I42" t="n">
-        <v>55763.59</v>
+        <v>57154.16</v>
       </c>
       <c r="J42" t="n">
-        <v>61945.89</v>
+        <v>57447</v>
       </c>
       <c r="K42" t="n">
-        <v>63213.85</v>
+        <v>60714.04</v>
       </c>
       <c r="L42" t="n">
-        <v>64481.82</v>
+        <v>63981.09</v>
       </c>
       <c r="M42" t="n">
-        <v>68206.95</v>
+        <v>65761.03</v>
       </c>
       <c r="N42" t="n">
-        <v>71932.07000000001</v>
+        <v>67540.98</v>
       </c>
       <c r="O42" t="n">
-        <v>70742.88</v>
+        <v>72295.12</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4065,59 +4065,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>63240.79</v>
+        <v>59522.79</v>
       </c>
       <c r="C43" t="n">
-        <v>65544</v>
+        <v>63935.85</v>
       </c>
       <c r="D43" t="n">
-        <v>58075.92</v>
+        <v>57747.77</v>
       </c>
       <c r="E43" t="n">
-        <v>59532.34</v>
+        <v>63547.88</v>
       </c>
       <c r="F43" t="n">
-        <v>-3705.2</v>
+        <v>4015.54</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0586</v>
+        <v>0.0675</v>
       </c>
       <c r="H43" t="n">
-        <v>7468.08</v>
+        <v>6188.08</v>
       </c>
       <c r="I43" t="n">
-        <v>57154.16</v>
+        <v>50607.84</v>
       </c>
       <c r="J43" t="n">
-        <v>57447</v>
+        <v>50925.45</v>
       </c>
       <c r="K43" t="n">
-        <v>60714.04</v>
+        <v>55798.3</v>
       </c>
       <c r="L43" t="n">
-        <v>63981.09</v>
+        <v>60671.15</v>
       </c>
       <c r="M43" t="n">
-        <v>65761.03</v>
+        <v>63266.38</v>
       </c>
       <c r="N43" t="n">
-        <v>67540.98</v>
+        <v>65861.61</v>
       </c>
       <c r="O43" t="n">
-        <v>72295.12</v>
+        <v>73012.08</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4125,19 +4121,19 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4149,55 +4145,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>59522.79</v>
+        <v>63551.02</v>
       </c>
       <c r="C44" t="n">
-        <v>63935.85</v>
+        <v>64658.97</v>
       </c>
       <c r="D44" t="n">
-        <v>57747.77</v>
+        <v>61275.83</v>
       </c>
       <c r="E44" t="n">
-        <v>63547.88</v>
+        <v>63758.22</v>
       </c>
       <c r="F44" t="n">
-        <v>4015.54</v>
+        <v>210.34</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0675</v>
+        <v>0.0033</v>
       </c>
       <c r="H44" t="n">
-        <v>6188.08</v>
+        <v>3383.14</v>
       </c>
       <c r="I44" t="n">
-        <v>50607.84</v>
+        <v>51559.68</v>
       </c>
       <c r="J44" t="n">
-        <v>50925.45</v>
+        <v>58712.84</v>
       </c>
       <c r="K44" t="n">
-        <v>55798.3</v>
+        <v>60453.84</v>
       </c>
       <c r="L44" t="n">
-        <v>60671.15</v>
+        <v>62194.84</v>
       </c>
       <c r="M44" t="n">
-        <v>63266.38</v>
+        <v>66641.92</v>
       </c>
       <c r="N44" t="n">
-        <v>65861.61</v>
+        <v>71089</v>
       </c>
       <c r="O44" t="n">
-        <v>73012.08</v>
+        <v>70123.92999999999</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4210,13 +4210,11 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4231,57 +4229,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>63551.02</v>
+        <v>63757.17</v>
       </c>
       <c r="C45" t="n">
-        <v>64658.97</v>
+        <v>65507.59</v>
       </c>
       <c r="D45" t="n">
-        <v>61275.83</v>
+        <v>61769</v>
       </c>
       <c r="E45" t="n">
-        <v>63758.22</v>
+        <v>64690.8</v>
       </c>
       <c r="F45" t="n">
-        <v>210.34</v>
+        <v>932.59</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0146</v>
       </c>
       <c r="H45" t="n">
-        <v>3383.14</v>
+        <v>3738.59</v>
       </c>
       <c r="I45" t="n">
-        <v>51559.68</v>
+        <v>57892.69</v>
       </c>
       <c r="J45" t="n">
-        <v>58712.84</v>
+        <v>60770.49</v>
       </c>
       <c r="K45" t="n">
-        <v>60453.84</v>
+        <v>62066.65</v>
       </c>
       <c r="L45" t="n">
-        <v>62194.84</v>
+        <v>63362.81</v>
       </c>
       <c r="M45" t="n">
-        <v>66641.92</v>
+        <v>65449.79</v>
       </c>
       <c r="N45" t="n">
-        <v>71089</v>
+        <v>67536.77</v>
       </c>
       <c r="O45" t="n">
-        <v>70123.92999999999</v>
+        <v>68042.11</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4289,16 +4287,20 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4320,50 +4322,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>63757.17</v>
+        <v>64684.42</v>
       </c>
       <c r="C46" t="n">
-        <v>65507.59</v>
+        <v>66910.06</v>
       </c>
       <c r="D46" t="n">
-        <v>61769</v>
+        <v>63686.04</v>
       </c>
       <c r="E46" t="n">
-        <v>64690.8</v>
+        <v>65340.3</v>
       </c>
       <c r="F46" t="n">
-        <v>932.59</v>
+        <v>649.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.01</v>
       </c>
       <c r="H46" t="n">
-        <v>3738.59</v>
+        <v>3224.03</v>
       </c>
       <c r="I46" t="n">
-        <v>57892.69</v>
+        <v>58030.41</v>
       </c>
       <c r="J46" t="n">
-        <v>60770.49</v>
+        <v>61478.46</v>
       </c>
       <c r="K46" t="n">
-        <v>62066.65</v>
+        <v>62821.51</v>
       </c>
       <c r="L46" t="n">
-        <v>63362.81</v>
+        <v>64164.55</v>
       </c>
       <c r="M46" t="n">
-        <v>65449.79</v>
+        <v>66560.10000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>67536.77</v>
+        <v>68955.64999999999</v>
       </c>
       <c r="O46" t="n">
-        <v>68042.11</v>
+        <v>69246.19</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4371,19 +4373,17 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="U46" s="8" t="n">
@@ -4406,50 +4406,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>64684.42</v>
+        <v>65340.59</v>
       </c>
       <c r="C47" t="n">
-        <v>66910.06</v>
+        <v>65658.34</v>
       </c>
       <c r="D47" t="n">
-        <v>63686.04</v>
+        <v>62233.01</v>
       </c>
       <c r="E47" t="n">
-        <v>65340.3</v>
+        <v>63482</v>
       </c>
       <c r="F47" t="n">
-        <v>649.5</v>
+        <v>-1858.3</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.0284</v>
       </c>
       <c r="H47" t="n">
-        <v>3224.03</v>
+        <v>3425.32</v>
       </c>
       <c r="I47" t="n">
-        <v>58030.41</v>
+        <v>60462.01</v>
       </c>
       <c r="J47" t="n">
-        <v>61478.46</v>
+        <v>62137.4</v>
       </c>
       <c r="K47" t="n">
-        <v>62821.51</v>
+        <v>63728.29</v>
       </c>
       <c r="L47" t="n">
-        <v>64164.55</v>
+        <v>65319.17</v>
       </c>
       <c r="M47" t="n">
-        <v>66560.10000000001</v>
+        <v>66952.31</v>
       </c>
       <c r="N47" t="n">
-        <v>68955.64999999999</v>
+        <v>68585.45</v>
       </c>
       <c r="O47" t="n">
-        <v>69246.19</v>
+        <v>70134.09</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4457,18 +4457,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4481,59 +4481,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>65340.59</v>
+        <v>63485.44</v>
       </c>
       <c r="C48" t="n">
-        <v>65658.34</v>
+        <v>65401.69</v>
       </c>
       <c r="D48" t="n">
-        <v>62233.01</v>
+        <v>62226.58</v>
       </c>
       <c r="E48" t="n">
-        <v>63482</v>
+        <v>64844.89</v>
       </c>
       <c r="F48" t="n">
-        <v>-1858.3</v>
+        <v>1362.89</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0284</v>
+        <v>0.0215</v>
       </c>
       <c r="H48" t="n">
-        <v>3425.32</v>
+        <v>3175.11</v>
       </c>
       <c r="I48" t="n">
-        <v>60462.01</v>
+        <v>58807.69</v>
       </c>
       <c r="J48" t="n">
-        <v>62137.4</v>
+        <v>59824.84</v>
       </c>
       <c r="K48" t="n">
-        <v>63728.29</v>
+        <v>61769.34</v>
       </c>
       <c r="L48" t="n">
-        <v>65319.17</v>
+        <v>63713.84</v>
       </c>
       <c r="M48" t="n">
-        <v>66952.31</v>
+        <v>65194.66</v>
       </c>
       <c r="N48" t="n">
-        <v>68585.45</v>
+        <v>66675.49000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>70134.09</v>
+        <v>69083.66</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4541,19 +4537,19 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
@@ -4565,55 +4561,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>63485.44</v>
+        <v>64845.38</v>
       </c>
       <c r="C49" t="n">
-        <v>65401.69</v>
+        <v>65321.84</v>
       </c>
       <c r="D49" t="n">
-        <v>62226.58</v>
+        <v>62487.7</v>
       </c>
       <c r="E49" t="n">
-        <v>64844.89</v>
+        <v>62818.65</v>
       </c>
       <c r="F49" t="n">
-        <v>1362.89</v>
+        <v>-2026.23</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0215</v>
+        <v>-0.0312</v>
       </c>
       <c r="H49" t="n">
-        <v>3175.11</v>
+        <v>2834.14</v>
       </c>
       <c r="I49" t="n">
-        <v>58807.69</v>
+        <v>59051.46</v>
       </c>
       <c r="J49" t="n">
-        <v>59824.84</v>
+        <v>62185.15</v>
       </c>
       <c r="K49" t="n">
-        <v>61769.34</v>
+        <v>63257.33</v>
       </c>
       <c r="L49" t="n">
-        <v>63713.84</v>
+        <v>64329.51</v>
       </c>
       <c r="M49" t="n">
-        <v>65194.66</v>
+        <v>66432.44</v>
       </c>
       <c r="N49" t="n">
-        <v>66675.49000000001</v>
+        <v>68535.38</v>
       </c>
       <c r="O49" t="n">
-        <v>69083.66</v>
+        <v>68576.8</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4621,18 +4621,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4654,50 +4654,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>64845.38</v>
+        <v>62819.38</v>
       </c>
       <c r="C50" t="n">
-        <v>65321.84</v>
+        <v>79463.71000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>62487.7</v>
+        <v>62687.1</v>
       </c>
       <c r="E50" t="n">
-        <v>62818.65</v>
+        <v>77755.27</v>
       </c>
       <c r="F50" t="n">
-        <v>-2026.23</v>
+        <v>14936.61</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0312</v>
+        <v>0.2378</v>
       </c>
       <c r="H50" t="n">
-        <v>2834.14</v>
+        <v>16776.61</v>
       </c>
       <c r="I50" t="n">
-        <v>59051.46</v>
+        <v>59653.56</v>
       </c>
       <c r="J50" t="n">
-        <v>62185.15</v>
+        <v>59441.45</v>
       </c>
       <c r="K50" t="n">
-        <v>63257.33</v>
+        <v>61401.58</v>
       </c>
       <c r="L50" t="n">
-        <v>64329.51</v>
+        <v>63361.71</v>
       </c>
       <c r="M50" t="n">
-        <v>66432.44</v>
+        <v>64235.72</v>
       </c>
       <c r="N50" t="n">
-        <v>68535.38</v>
+        <v>65109.73</v>
       </c>
       <c r="O50" t="n">
-        <v>68576.8</v>
+        <v>68155.98</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4705,83 +4705,83 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W50" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W50" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>62819.38</v>
+        <v>77748.88</v>
       </c>
       <c r="C51" t="n">
-        <v>79463.71000000001</v>
+        <v>81346.95</v>
       </c>
       <c r="D51" t="n">
-        <v>62687.1</v>
+        <v>76688.83</v>
       </c>
       <c r="E51" t="n">
-        <v>77755.27</v>
+        <v>77667.57000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>14936.61</v>
+        <v>-87.7</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.2378</v>
+        <v>-0.0011</v>
       </c>
       <c r="H51" t="n">
-        <v>16776.61</v>
+        <v>4658.12</v>
       </c>
       <c r="I51" t="n">
-        <v>59653.56</v>
+        <v>45910.49</v>
       </c>
       <c r="J51" t="n">
-        <v>59441.45</v>
+        <v>64318.59</v>
       </c>
       <c r="K51" t="n">
-        <v>61401.58</v>
+        <v>69366.96000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>63361.71</v>
+        <v>74415.34</v>
       </c>
       <c r="M51" t="n">
-        <v>64235.72</v>
+        <v>86143.57000000001</v>
       </c>
       <c r="N51" t="n">
-        <v>65109.73</v>
+        <v>97871.8</v>
       </c>
       <c r="O51" t="n">
-        <v>68155.98</v>
+        <v>96240.32000000001</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4794,78 +4794,76 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>77748.88</v>
+        <v>77673.7</v>
       </c>
       <c r="C52" t="n">
-        <v>81346.95</v>
+        <v>82262.21000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>76688.83</v>
+        <v>76248.3</v>
       </c>
       <c r="E52" t="n">
-        <v>77667.57000000001</v>
+        <v>80350.05</v>
       </c>
       <c r="F52" t="n">
-        <v>-87.7</v>
+        <v>2682.48</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0345</v>
       </c>
       <c r="H52" t="n">
-        <v>4658.12</v>
+        <v>6013.91</v>
       </c>
       <c r="I52" t="n">
-        <v>45910.49</v>
+        <v>72030.7</v>
       </c>
       <c r="J52" t="n">
-        <v>64318.59</v>
+        <v>72334.28999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>69366.96000000001</v>
+        <v>75338.50999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>74415.34</v>
+        <v>78342.73</v>
       </c>
       <c r="M52" t="n">
-        <v>86143.57000000001</v>
+        <v>79996.63</v>
       </c>
       <c r="N52" t="n">
-        <v>97871.8</v>
+        <v>81650.53999999999</v>
       </c>
       <c r="O52" t="n">
-        <v>96240.32000000001</v>
+        <v>86005.08</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4878,14 +4876,18 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4904,50 +4906,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>77673.7</v>
+        <v>80349.2</v>
       </c>
       <c r="C53" t="n">
-        <v>82262.21000000001</v>
+        <v>80432.31</v>
       </c>
       <c r="D53" t="n">
-        <v>76248.3</v>
+        <v>76162.91</v>
       </c>
       <c r="E53" t="n">
-        <v>80350.05</v>
+        <v>76838.16</v>
       </c>
       <c r="F53" t="n">
-        <v>2682.48</v>
+        <v>-3511.89</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0345</v>
+        <v>-0.0437</v>
       </c>
       <c r="H53" t="n">
-        <v>6013.91</v>
+        <v>4269.4</v>
       </c>
       <c r="I53" t="n">
-        <v>72030.7</v>
+        <v>70234.39999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>72334.28999999999</v>
+        <v>74883.53999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>75338.50999999999</v>
+        <v>77343.09</v>
       </c>
       <c r="L53" t="n">
-        <v>78342.73</v>
+        <v>79802.64999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>79996.63</v>
+        <v>83357</v>
       </c>
       <c r="N53" t="n">
-        <v>81650.53999999999</v>
+        <v>86911.35000000001</v>
       </c>
       <c r="O53" t="n">
-        <v>86005.08</v>
+        <v>88276.12</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4955,23 +4957,21 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4983,57 +4983,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>80349.2</v>
+        <v>76830.28</v>
       </c>
       <c r="C54" t="n">
-        <v>80432.31</v>
+        <v>81911.14</v>
       </c>
       <c r="D54" t="n">
-        <v>76162.91</v>
+        <v>74944.59</v>
       </c>
       <c r="E54" t="n">
-        <v>76838.16</v>
+        <v>81142.61</v>
       </c>
       <c r="F54" t="n">
-        <v>-3511.89</v>
+        <v>4304.45</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0437</v>
+        <v>0.056</v>
       </c>
       <c r="H54" t="n">
-        <v>4269.4</v>
+        <v>6966.55</v>
       </c>
       <c r="I54" t="n">
-        <v>70234.39999999999</v>
+        <v>71893.52</v>
       </c>
       <c r="J54" t="n">
-        <v>74883.53999999999</v>
+        <v>71839.03</v>
       </c>
       <c r="K54" t="n">
-        <v>77343.09</v>
+        <v>74703.46000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>79802.64999999999</v>
+        <v>77567.88</v>
       </c>
       <c r="M54" t="n">
-        <v>83357</v>
+        <v>78972.86</v>
       </c>
       <c r="N54" t="n">
-        <v>86911.35000000001</v>
+        <v>80377.83</v>
       </c>
       <c r="O54" t="n">
-        <v>88276.12</v>
+        <v>84701.71000000001</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5041,22 +5041,24 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
@@ -5067,57 +5069,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>76830.28</v>
+        <v>81143.62</v>
       </c>
       <c r="C55" t="n">
-        <v>81911.14</v>
+        <v>87363.75999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>74944.59</v>
+        <v>80867.09</v>
       </c>
       <c r="E55" t="n">
-        <v>81142.61</v>
+        <v>84458.09</v>
       </c>
       <c r="F55" t="n">
-        <v>4304.45</v>
+        <v>3315.48</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.056</v>
+        <v>0.0409</v>
       </c>
       <c r="H55" t="n">
-        <v>6966.55</v>
+        <v>6496.67</v>
       </c>
       <c r="I55" t="n">
-        <v>71893.52</v>
+        <v>67978.05</v>
       </c>
       <c r="J55" t="n">
-        <v>71839.03</v>
+        <v>75533.42999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>74703.46000000001</v>
+        <v>77659.34</v>
       </c>
       <c r="L55" t="n">
-        <v>77567.88</v>
+        <v>79785.24000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>78972.86</v>
+        <v>84625.88</v>
       </c>
       <c r="N55" t="n">
-        <v>80377.83</v>
+        <v>89466.53</v>
       </c>
       <c r="O55" t="n">
-        <v>84701.71000000001</v>
+        <v>88877.69</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5135,14 +5137,12 @@
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
@@ -5151,59 +5151,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>81143.62</v>
+        <v>84454.12</v>
       </c>
       <c r="C56" t="n">
-        <v>87363.75999999999</v>
+        <v>87146.35000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>80867.09</v>
+        <v>82570.72</v>
       </c>
       <c r="E56" t="n">
-        <v>84458.09</v>
+        <v>86480.3</v>
       </c>
       <c r="F56" t="n">
-        <v>3315.48</v>
+        <v>2022.22</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0409</v>
+        <v>0.0239</v>
       </c>
       <c r="H56" t="n">
-        <v>6496.67</v>
+        <v>4575.63</v>
       </c>
       <c r="I56" t="n">
-        <v>67978.05</v>
+        <v>74370.41</v>
       </c>
       <c r="J56" t="n">
-        <v>75533.42999999999</v>
+        <v>78132.75</v>
       </c>
       <c r="K56" t="n">
-        <v>77659.34</v>
+        <v>81209.75</v>
       </c>
       <c r="L56" t="n">
-        <v>79785.24000000001</v>
+        <v>84286.75</v>
       </c>
       <c r="M56" t="n">
-        <v>84625.88</v>
+        <v>87706.42</v>
       </c>
       <c r="N56" t="n">
-        <v>89466.53</v>
+        <v>91126.09</v>
       </c>
       <c r="O56" t="n">
-        <v>88877.69</v>
+        <v>93860.42999999999</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5235,75 +5231,81 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>84454.12</v>
+        <v>86480.00999999999</v>
       </c>
       <c r="C57" t="n">
-        <v>87146.35000000001</v>
+        <v>86971.78</v>
       </c>
       <c r="D57" t="n">
-        <v>82570.72</v>
+        <v>80336.91</v>
       </c>
       <c r="E57" t="n">
-        <v>86480.3</v>
+        <v>82912.23</v>
       </c>
       <c r="F57" t="n">
-        <v>2022.22</v>
+        <v>-3568.08</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0239</v>
+        <v>-0.0413</v>
       </c>
       <c r="H57" t="n">
-        <v>4575.63</v>
+        <v>6634.88</v>
       </c>
       <c r="I57" t="n">
-        <v>74370.41</v>
+        <v>77995.09</v>
       </c>
       <c r="J57" t="n">
-        <v>78132.75</v>
+        <v>82715.56</v>
       </c>
       <c r="K57" t="n">
-        <v>81209.75</v>
+        <v>84192.49000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>84286.75</v>
+        <v>85669.42</v>
       </c>
       <c r="M57" t="n">
-        <v>87706.42</v>
+        <v>88768.12</v>
       </c>
       <c r="N57" t="n">
-        <v>91126.09</v>
+        <v>91866.82000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>93860.42999999999</v>
+        <v>91721.98</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
+      <c r="Q57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5317,74 +5319,70 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>86480.00999999999</v>
+        <v>83673.00999999999</v>
       </c>
       <c r="C58" t="n">
-        <v>86971.78</v>
+        <v>83923.59</v>
       </c>
       <c r="D58" t="n">
-        <v>80336.91</v>
+        <v>83652.21000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>82827.78</v>
+        <v>83826.05</v>
       </c>
       <c r="F58" t="n">
-        <v>-3652.52</v>
+        <v>913.8200000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0422</v>
+        <v>0.011</v>
       </c>
       <c r="H58" t="n">
-        <v>6634.88</v>
+        <v>271.38</v>
       </c>
       <c r="I58" t="n">
-        <v>77995.09</v>
+        <v>73702.03</v>
       </c>
       <c r="J58" t="n">
-        <v>82715.56</v>
+        <v>75906.28999999999</v>
       </c>
       <c r="K58" t="n">
-        <v>84192.49000000001</v>
+        <v>79594.78999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>85669.42</v>
+        <v>83283.28999999999</v>
       </c>
       <c r="M58" t="n">
-        <v>88768.12</v>
+        <v>86229.66</v>
       </c>
       <c r="N58" t="n">
-        <v>91866.82000000001</v>
+        <v>89176.03999999999</v>
       </c>
       <c r="O58" t="n">
-        <v>91721.98</v>
+        <v>93606.66</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5403,7 +5401,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5333,22 +5333,22 @@
         <v>83673.00999999999</v>
       </c>
       <c r="C58" t="n">
-        <v>83923.59</v>
+        <v>83892.44</v>
       </c>
       <c r="D58" t="n">
         <v>83652.21000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>83826.05</v>
+        <v>83670.78</v>
       </c>
       <c r="F58" t="n">
-        <v>913.8200000000001</v>
+        <v>758.55</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.011</v>
+        <v>0.0091</v>
       </c>
       <c r="H58" t="n">
-        <v>271.38</v>
+        <v>240.23</v>
       </c>
       <c r="I58" t="n">
         <v>73702.03</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>3450.73</v>
       </c>
       <c r="I2" t="n">
-        <v>104491.84</v>
+        <v>104784.02</v>
       </c>
       <c r="J2" t="n">
-        <v>110122.71</v>
+        <v>110232.28</v>
       </c>
       <c r="K2" t="n">
-        <v>112338.27</v>
+        <v>112411.32</v>
       </c>
       <c r="L2" t="n">
-        <v>114553.83</v>
+        <v>114590.35</v>
       </c>
       <c r="M2" t="n">
-        <v>118477.04</v>
+        <v>118404</v>
       </c>
       <c r="N2" t="n">
-        <v>122400.26</v>
+        <v>122217.64</v>
       </c>
       <c r="O2" t="n">
-        <v>122908.16</v>
+        <v>122762.06</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5253,13 +5253,13 @@
         <v>80336.91</v>
       </c>
       <c r="E57" t="n">
-        <v>82912.23</v>
+        <v>83679.47</v>
       </c>
       <c r="F57" t="n">
-        <v>-3568.08</v>
+        <v>-2800.84</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0413</v>
+        <v>-0.0324</v>
       </c>
       <c r="H57" t="n">
         <v>6634.88</v>
@@ -5290,12 +5290,12 @@
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
@@ -5330,43 +5330,43 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>83673.00999999999</v>
+        <v>81754.48</v>
       </c>
       <c r="C58" t="n">
-        <v>83892.44</v>
+        <v>82870.52</v>
       </c>
       <c r="D58" t="n">
-        <v>83652.21000000001</v>
+        <v>81197.99000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>83670.78</v>
+        <v>82770</v>
       </c>
       <c r="F58" t="n">
-        <v>758.55</v>
+        <v>-909.47</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0091</v>
+        <v>-0.0109</v>
       </c>
       <c r="H58" t="n">
-        <v>240.23</v>
+        <v>1672.52</v>
       </c>
       <c r="I58" t="n">
         <v>73702.03</v>
       </c>
       <c r="J58" t="n">
-        <v>75906.28999999999</v>
+        <v>77057.16</v>
       </c>
       <c r="K58" t="n">
-        <v>79594.78999999999</v>
+        <v>80362.03</v>
       </c>
       <c r="L58" t="n">
-        <v>83283.28999999999</v>
+        <v>83666.91</v>
       </c>
       <c r="M58" t="n">
-        <v>86229.66</v>
+        <v>86996.91</v>
       </c>
       <c r="N58" t="n">
-        <v>89176.03999999999</v>
+        <v>90326.91</v>
       </c>
       <c r="O58" t="n">
         <v>93606.66</v>
@@ -5380,9 +5380,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>3450.73</v>
       </c>
       <c r="I2" t="n">
-        <v>104784.02</v>
+        <v>105110.77</v>
       </c>
       <c r="J2" t="n">
-        <v>110232.28</v>
+        <v>110354.81</v>
       </c>
       <c r="K2" t="n">
-        <v>112411.32</v>
+        <v>112493</v>
       </c>
       <c r="L2" t="n">
-        <v>114590.35</v>
+        <v>114631.19</v>
       </c>
       <c r="M2" t="n">
-        <v>118404</v>
+        <v>118322.31</v>
       </c>
       <c r="N2" t="n">
-        <v>122217.64</v>
+        <v>122013.42</v>
       </c>
       <c r="O2" t="n">
-        <v>122762.06</v>
+        <v>122598.69</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5330,25 +5330,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>81754.48</v>
+        <v>83679.47</v>
       </c>
       <c r="C58" t="n">
-        <v>82870.52</v>
+        <v>84249.22</v>
       </c>
       <c r="D58" t="n">
-        <v>81197.99000000001</v>
+        <v>81681.63</v>
       </c>
       <c r="E58" t="n">
-        <v>82770</v>
+        <v>83152.86</v>
       </c>
       <c r="F58" t="n">
-        <v>-909.47</v>
+        <v>-526.61</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0063</v>
       </c>
       <c r="H58" t="n">
-        <v>1672.52</v>
+        <v>2567.59</v>
       </c>
       <c r="I58" t="n">
         <v>73702.03</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>3450.73</v>
       </c>
       <c r="I2" t="n">
-        <v>105110.77</v>
+        <v>110138.29</v>
       </c>
       <c r="J2" t="n">
-        <v>110354.81</v>
+        <v>112240.13</v>
       </c>
       <c r="K2" t="n">
-        <v>112493</v>
+        <v>113749.88</v>
       </c>
       <c r="L2" t="n">
-        <v>114631.19</v>
+        <v>115259.63</v>
       </c>
       <c r="M2" t="n">
-        <v>118322.31</v>
+        <v>117065.43</v>
       </c>
       <c r="N2" t="n">
-        <v>122013.42</v>
+        <v>118871.23</v>
       </c>
       <c r="O2" t="n">
-        <v>122598.69</v>
+        <v>120084.93</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -693,8 +693,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -5336,19 +5338,19 @@
         <v>84249.22</v>
       </c>
       <c r="D58" t="n">
-        <v>81681.63</v>
+        <v>80962.52</v>
       </c>
       <c r="E58" t="n">
-        <v>83152.86</v>
+        <v>81499.97</v>
       </c>
       <c r="F58" t="n">
-        <v>-526.61</v>
+        <v>-2179.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.026</v>
       </c>
       <c r="H58" t="n">
-        <v>2567.59</v>
+        <v>3286.7</v>
       </c>
       <c r="I58" t="n">
         <v>73702.03</v>
@@ -5377,12 +5379,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5341,13 +5341,13 @@
         <v>80962.52</v>
       </c>
       <c r="E58" t="n">
-        <v>81499.97</v>
+        <v>81539.8</v>
       </c>
       <c r="F58" t="n">
-        <v>-2179.5</v>
+        <v>-2139.67</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.026</v>
+        <v>-0.0256</v>
       </c>
       <c r="H58" t="n">
         <v>3286.7</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5341,13 +5341,13 @@
         <v>80962.52</v>
       </c>
       <c r="E58" t="n">
-        <v>81539.8</v>
+        <v>81669.25</v>
       </c>
       <c r="F58" t="n">
-        <v>-2139.67</v>
+        <v>-2010.22</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0256</v>
+        <v>-0.024</v>
       </c>
       <c r="H58" t="n">
         <v>3286.7</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -659,25 +659,25 @@
         <v>3450.73</v>
       </c>
       <c r="I2" t="n">
-        <v>110138.29</v>
+        <v>112819.59</v>
       </c>
       <c r="J2" t="n">
-        <v>112240.13</v>
+        <v>113245.62</v>
       </c>
       <c r="K2" t="n">
-        <v>113749.88</v>
+        <v>114420.21</v>
       </c>
       <c r="L2" t="n">
-        <v>115259.63</v>
+        <v>115594.79</v>
       </c>
       <c r="M2" t="n">
-        <v>117065.43</v>
+        <v>116395.11</v>
       </c>
       <c r="N2" t="n">
-        <v>118871.23</v>
+        <v>117195.42</v>
       </c>
       <c r="O2" t="n">
-        <v>120084.93</v>
+        <v>118744.28</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,7 +690,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -698,8 +698,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -711,7 +713,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -778,7 +780,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -860,7 +862,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -948,7 +950,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1032,7 +1034,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1114,7 +1116,7 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1202,7 +1204,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1288,7 +1290,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1374,7 +1376,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1458,7 +1460,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1540,7 +1542,7 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1624,7 +1626,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1706,7 +1708,7 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1790,7 +1792,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1872,7 +1874,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1954,7 +1956,7 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2036,7 +2038,7 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2120,7 +2122,7 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2206,7 +2208,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2294,7 +2296,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2378,7 +2380,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2456,7 +2458,7 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2540,7 +2542,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2626,7 +2628,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2706,7 +2708,7 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2792,7 +2794,7 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2880,7 +2882,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2964,7 +2966,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3042,7 +3044,7 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3126,7 +3128,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3214,7 +3216,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3300,7 +3302,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3386,7 +3388,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3468,7 +3470,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3556,7 +3558,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3636,7 +3638,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3718,7 +3720,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3802,7 +3804,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3880,7 +3882,7 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3964,7 +3966,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4048,7 +4050,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4126,7 +4128,7 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4210,7 +4212,7 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4294,7 +4296,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="7" t="inlineStr">
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4378,7 +4380,7 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4464,7 +4466,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4542,7 +4544,7 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4628,7 +4630,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4710,7 +4712,7 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4794,7 +4796,7 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4876,7 +4878,7 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4964,7 +4966,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5046,7 +5048,7 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5132,7 +5134,7 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5212,7 +5214,7 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5300,7 +5302,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5341,13 +5343,13 @@
         <v>80962.52</v>
       </c>
       <c r="E58" t="n">
-        <v>81669.25</v>
+        <v>82262.38</v>
       </c>
       <c r="F58" t="n">
-        <v>-2010.22</v>
+        <v>-1417.09</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.024</v>
+        <v>-0.0169</v>
       </c>
       <c r="H58" t="n">
         <v>3286.7</v>
@@ -5379,14 +5381,12 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>3450.73</v>
       </c>
       <c r="I2" t="n">
-        <v>112819.59</v>
+        <v>114110.16</v>
       </c>
       <c r="J2" t="n">
-        <v>113245.62</v>
+        <v>114109.99</v>
       </c>
       <c r="K2" t="n">
-        <v>114420.21</v>
+        <v>114851.54</v>
       </c>
       <c r="L2" t="n">
-        <v>115594.79</v>
+        <v>115593.09</v>
       </c>
       <c r="M2" t="n">
-        <v>116395.11</v>
+        <v>115963.77</v>
       </c>
       <c r="N2" t="n">
-        <v>117195.42</v>
+        <v>116334.46</v>
       </c>
       <c r="O2" t="n">
-        <v>118744.28</v>
+        <v>117446.87</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -703,8 +705,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5340,19 +5344,19 @@
         <v>84249.22</v>
       </c>
       <c r="D58" t="n">
-        <v>80962.52</v>
+        <v>79735.86</v>
       </c>
       <c r="E58" t="n">
-        <v>82262.38</v>
+        <v>81424.08</v>
       </c>
       <c r="F58" t="n">
-        <v>-1417.09</v>
+        <v>-2255.39</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.027</v>
       </c>
       <c r="H58" t="n">
-        <v>3286.7</v>
+        <v>4513.36</v>
       </c>
       <c r="I58" t="n">
         <v>73702.03</v>
@@ -5381,12 +5385,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5405,7 +5411,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5347,13 +5347,13 @@
         <v>79735.86</v>
       </c>
       <c r="E58" t="n">
-        <v>81424.08</v>
+        <v>81499.99000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-2255.39</v>
+        <v>-2179.48</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.027</v>
+        <v>-0.026</v>
       </c>
       <c r="H58" t="n">
         <v>4513.36</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>3450.73</v>
       </c>
       <c r="I2" t="n">
-        <v>114110.16</v>
+        <v>114263.3</v>
       </c>
       <c r="J2" t="n">
-        <v>114109.99</v>
+        <v>114301.41</v>
       </c>
       <c r="K2" t="n">
-        <v>114851.54</v>
+        <v>114928.11</v>
       </c>
       <c r="L2" t="n">
-        <v>115593.09</v>
+        <v>115554.8</v>
       </c>
       <c r="M2" t="n">
-        <v>115963.77</v>
+        <v>115887.21</v>
       </c>
       <c r="N2" t="n">
-        <v>116334.46</v>
+        <v>116219.61</v>
       </c>
       <c r="O2" t="n">
-        <v>117446.87</v>
+        <v>117140.6</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5347,13 +5347,13 @@
         <v>79735.86</v>
       </c>
       <c r="E58" t="n">
-        <v>81499.99000000001</v>
+        <v>81609.94</v>
       </c>
       <c r="F58" t="n">
-        <v>-2179.48</v>
+        <v>-2069.53</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.026</v>
+        <v>-0.0247</v>
       </c>
       <c r="H58" t="n">
         <v>4513.36</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5347,13 +5347,13 @@
         <v>79735.86</v>
       </c>
       <c r="E58" t="n">
-        <v>81609.94</v>
+        <v>82005.28999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>-2069.53</v>
+        <v>-1674.18</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0247</v>
+        <v>-0.02</v>
       </c>
       <c r="H58" t="n">
         <v>4513.36</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -634,56 +634,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>115399.63</v>
+        <v>115309.22</v>
       </c>
       <c r="C2" t="n">
-        <v>117911.79</v>
+        <v>115431.31</v>
       </c>
       <c r="D2" t="n">
-        <v>114461.06</v>
+        <v>108713.4</v>
       </c>
       <c r="E2" t="n">
-        <v>115306.09</v>
+        <v>112122.64</v>
       </c>
       <c r="F2" t="n">
-        <v>-101.56</v>
+        <v>-3183.45</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0276</v>
       </c>
       <c r="H2" t="n">
-        <v>3450.73</v>
+        <v>6717.91</v>
       </c>
       <c r="I2" t="n">
-        <v>114263.3</v>
+        <v>111010.34</v>
       </c>
       <c r="J2" t="n">
-        <v>114301.41</v>
+        <v>111415.2</v>
       </c>
       <c r="K2" t="n">
-        <v>114928.11</v>
+        <v>113580.73</v>
       </c>
       <c r="L2" t="n">
-        <v>115554.8</v>
+        <v>115746.26</v>
       </c>
       <c r="M2" t="n">
-        <v>115887.21</v>
+        <v>117031.46</v>
       </c>
       <c r="N2" t="n">
-        <v>116219.61</v>
+        <v>118316.65</v>
       </c>
       <c r="O2" t="n">
-        <v>117140.6</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>121362.52</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -692,23 +696,17 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -717,237 +715,233 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>115309.22</v>
+        <v>112117.88</v>
       </c>
       <c r="C3" t="n">
-        <v>115431.31</v>
+        <v>125559.21</v>
       </c>
       <c r="D3" t="n">
-        <v>108713.4</v>
+        <v>111589.95</v>
       </c>
       <c r="E3" t="n">
-        <v>112122.64</v>
+        <v>123513.48</v>
       </c>
       <c r="F3" t="n">
-        <v>-3183.45</v>
+        <v>11390.84</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0276</v>
+        <v>0.1016</v>
       </c>
       <c r="H3" t="n">
-        <v>6717.91</v>
+        <v>13969.26</v>
       </c>
       <c r="I3" t="n">
-        <v>111010.34</v>
+        <v>101995.48</v>
       </c>
       <c r="J3" t="n">
-        <v>111415.2</v>
+        <v>105429.87</v>
       </c>
       <c r="K3" t="n">
-        <v>113580.73</v>
+        <v>108763.68</v>
       </c>
       <c r="L3" t="n">
-        <v>115746.26</v>
+        <v>112097.5</v>
       </c>
       <c r="M3" t="n">
-        <v>117031.46</v>
+        <v>115481.6</v>
       </c>
       <c r="N3" t="n">
-        <v>118316.65</v>
+        <v>118865.7</v>
       </c>
       <c r="O3" t="n">
-        <v>121362.52</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
+        <v>122149.23</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
-      </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112117.88</v>
+        <v>123510.45</v>
       </c>
       <c r="C4" t="n">
-        <v>125559.21</v>
+        <v>126198.07</v>
       </c>
       <c r="D4" t="n">
-        <v>111589.95</v>
+        <v>104582.41</v>
       </c>
       <c r="E4" t="n">
-        <v>123513.48</v>
+        <v>115169.77</v>
       </c>
       <c r="F4" t="n">
-        <v>11390.84</v>
+        <v>-8343.709999999999</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.1016</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>13969.26</v>
+        <v>21615.66</v>
       </c>
       <c r="I4" t="n">
-        <v>101995.48</v>
+        <v>97620.7</v>
       </c>
       <c r="J4" t="n">
-        <v>105429.87</v>
+        <v>112013.67</v>
       </c>
       <c r="K4" t="n">
-        <v>108763.68</v>
+        <v>116528.85</v>
       </c>
       <c r="L4" t="n">
-        <v>112097.5</v>
+        <v>121044.03</v>
       </c>
       <c r="M4" t="n">
-        <v>115481.6</v>
+        <v>130498.11</v>
       </c>
       <c r="N4" t="n">
-        <v>118865.7</v>
+        <v>139952.18</v>
       </c>
       <c r="O4" t="n">
-        <v>122149.23</v>
+        <v>139528.47</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
+      </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>123510.45</v>
+        <v>115161.68</v>
       </c>
       <c r="C5" t="n">
-        <v>126198.07</v>
+        <v>116020.48</v>
       </c>
       <c r="D5" t="n">
-        <v>104582.41</v>
+        <v>103598.43</v>
       </c>
       <c r="E5" t="n">
-        <v>115169.77</v>
+        <v>108666.71</v>
       </c>
       <c r="F5" t="n">
-        <v>-8343.709999999999</v>
+        <v>-6503.05</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0565</v>
       </c>
       <c r="H5" t="n">
-        <v>21615.66</v>
+        <v>12422.05</v>
       </c>
       <c r="I5" t="n">
-        <v>97620.7</v>
+        <v>82966.75999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>112013.67</v>
+        <v>93443.87</v>
       </c>
       <c r="K5" t="n">
-        <v>116528.85</v>
+        <v>104361.94</v>
       </c>
       <c r="L5" t="n">
-        <v>121044.03</v>
+        <v>115280</v>
       </c>
       <c r="M5" t="n">
-        <v>130498.11</v>
+        <v>125977.59</v>
       </c>
       <c r="N5" t="n">
-        <v>139952.18</v>
+        <v>136675.18</v>
       </c>
       <c r="O5" t="n">
-        <v>139528.47</v>
+        <v>147813.73</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q5" s="6" t="n">
+        <v/>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
@@ -975,57 +969,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>115161.68</v>
+        <v>108667.45</v>
       </c>
       <c r="C6" t="n">
-        <v>116020.48</v>
+        <v>115260.91</v>
       </c>
       <c r="D6" t="n">
-        <v>103598.43</v>
+        <v>106778</v>
       </c>
       <c r="E6" t="n">
-        <v>108666.71</v>
+        <v>114472.45</v>
       </c>
       <c r="F6" t="n">
-        <v>-6503.05</v>
+        <v>5805.73</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0565</v>
+        <v>0.0534</v>
       </c>
       <c r="H6" t="n">
-        <v>12422.05</v>
+        <v>8482.91</v>
       </c>
       <c r="I6" t="n">
-        <v>82966.75999999999</v>
+        <v>91176.38</v>
       </c>
       <c r="J6" t="n">
-        <v>93443.87</v>
+        <v>95673.28</v>
       </c>
       <c r="K6" t="n">
-        <v>104361.94</v>
+        <v>102455.68</v>
       </c>
       <c r="L6" t="n">
-        <v>115280</v>
+        <v>109238.08</v>
       </c>
       <c r="M6" t="n">
-        <v>125977.59</v>
+        <v>114877.74</v>
       </c>
       <c r="N6" t="n">
-        <v>136675.18</v>
+        <v>120517.39</v>
       </c>
       <c r="O6" t="n">
-        <v>147813.73</v>
+        <v>128442.54</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1033,19 +1027,19 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1059,77 +1053,79 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>108667.45</v>
+        <v>114479.85</v>
       </c>
       <c r="C7" t="n">
-        <v>115260.91</v>
+        <v>116273.31</v>
       </c>
       <c r="D7" t="n">
-        <v>106778</v>
+        <v>106376.69</v>
       </c>
       <c r="E7" t="n">
-        <v>114472.45</v>
+        <v>110639.62</v>
       </c>
       <c r="F7" t="n">
-        <v>5805.73</v>
+        <v>-3832.82</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0534</v>
+        <v>-0.0335</v>
       </c>
       <c r="H7" t="n">
-        <v>8482.91</v>
+        <v>9896.620000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>91176.38</v>
+        <v>98295.09</v>
       </c>
       <c r="J7" t="n">
-        <v>95673.28</v>
+        <v>107716.04</v>
       </c>
       <c r="K7" t="n">
-        <v>102455.68</v>
+        <v>110230.99</v>
       </c>
       <c r="L7" t="n">
-        <v>109238.08</v>
+        <v>112745.95</v>
       </c>
       <c r="M7" t="n">
-        <v>114877.74</v>
+        <v>118713.9</v>
       </c>
       <c r="N7" t="n">
-        <v>120517.39</v>
+        <v>124681.85</v>
       </c>
       <c r="O7" t="n">
-        <v>128442.54</v>
+        <v>123743.81</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1143,57 +1139,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>114479.85</v>
+        <v>110646.91</v>
       </c>
       <c r="C8" t="n">
-        <v>116273.31</v>
+        <v>110764.91</v>
       </c>
       <c r="D8" t="n">
-        <v>106376.69</v>
+        <v>98962.06</v>
       </c>
       <c r="E8" t="n">
-        <v>110639.62</v>
+        <v>104719.64</v>
       </c>
       <c r="F8" t="n">
-        <v>-3832.82</v>
+        <v>-5919.98</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0335</v>
+        <v>-0.0535</v>
       </c>
       <c r="H8" t="n">
-        <v>9896.620000000001</v>
+        <v>11802.85</v>
       </c>
       <c r="I8" t="n">
-        <v>98295.09</v>
+        <v>96480.06</v>
       </c>
       <c r="J8" t="n">
-        <v>107716.04</v>
+        <v>100400.31</v>
       </c>
       <c r="K8" t="n">
-        <v>110230.99</v>
+        <v>105691.31</v>
       </c>
       <c r="L8" t="n">
-        <v>112745.95</v>
+        <v>110982.31</v>
       </c>
       <c r="M8" t="n">
-        <v>118713.9</v>
+        <v>115587.94</v>
       </c>
       <c r="N8" t="n">
-        <v>124681.85</v>
+        <v>120193.56</v>
       </c>
       <c r="O8" t="n">
-        <v>123743.81</v>
+        <v>126169.94</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1229,69 +1225,69 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110646.91</v>
+        <v>104723.77</v>
       </c>
       <c r="C9" t="n">
-        <v>110764.91</v>
+        <v>107428.26</v>
       </c>
       <c r="D9" t="n">
-        <v>98962.06</v>
+        <v>92971.16</v>
       </c>
       <c r="E9" t="n">
-        <v>104719.64</v>
+        <v>94177.08</v>
       </c>
       <c r="F9" t="n">
-        <v>-5919.98</v>
+        <v>-10542.56</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0535</v>
+        <v>-0.1007</v>
       </c>
       <c r="H9" t="n">
-        <v>11802.85</v>
+        <v>14457.09</v>
       </c>
       <c r="I9" t="n">
-        <v>96480.06</v>
+        <v>87159.21000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>100400.31</v>
+        <v>92844.87</v>
       </c>
       <c r="K9" t="n">
-        <v>105691.31</v>
+        <v>98818.21000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>110982.31</v>
+        <v>104791.56</v>
       </c>
       <c r="M9" t="n">
-        <v>115587.94</v>
+        <v>110621.07</v>
       </c>
       <c r="N9" t="n">
-        <v>120193.56</v>
+        <v>116450.57</v>
       </c>
       <c r="O9" t="n">
-        <v>126169.94</v>
+        <v>122567.77</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
@@ -1322,62 +1318,60 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>104723.77</v>
+        <v>94180.88</v>
       </c>
       <c r="C10" t="n">
-        <v>107428.26</v>
+        <v>95928.37</v>
       </c>
       <c r="D10" t="n">
-        <v>92971.16</v>
+        <v>80659.81</v>
       </c>
       <c r="E10" t="n">
-        <v>94177.08</v>
+        <v>86805.00999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-10542.56</v>
+        <v>-7372.07</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.1007</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>14457.09</v>
+        <v>15268.55</v>
       </c>
       <c r="I10" t="n">
-        <v>87159.21000000001</v>
+        <v>78514.07000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>92844.87</v>
+        <v>76708.67</v>
       </c>
       <c r="K10" t="n">
-        <v>98818.21000000001</v>
+        <v>86948.53</v>
       </c>
       <c r="L10" t="n">
-        <v>104791.56</v>
+        <v>97188.39</v>
       </c>
       <c r="M10" t="n">
-        <v>110621.07</v>
+        <v>101405.62</v>
       </c>
       <c r="N10" t="n">
-        <v>116450.57</v>
+        <v>105622.86</v>
       </c>
       <c r="O10" t="n">
-        <v>122567.77</v>
+        <v>121885.35</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
@@ -1408,50 +1402,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>94180.88</v>
+        <v>86798.77</v>
       </c>
       <c r="C11" t="n">
-        <v>95928.37</v>
+        <v>92969.09</v>
       </c>
       <c r="D11" t="n">
-        <v>80659.81</v>
+        <v>85272.2</v>
       </c>
       <c r="E11" t="n">
-        <v>86805.00999999999</v>
+        <v>90394.31</v>
       </c>
       <c r="F11" t="n">
-        <v>-7372.07</v>
+        <v>3589.3</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.0413</v>
       </c>
       <c r="H11" t="n">
-        <v>15268.55</v>
+        <v>7696.89</v>
       </c>
       <c r="I11" t="n">
-        <v>78514.07000000001</v>
+        <v>65391.26</v>
       </c>
       <c r="J11" t="n">
-        <v>76708.67</v>
+        <v>70791.91</v>
       </c>
       <c r="K11" t="n">
-        <v>86948.53</v>
+        <v>79170.73</v>
       </c>
       <c r="L11" t="n">
-        <v>97188.39</v>
+        <v>87549.55</v>
       </c>
       <c r="M11" t="n">
-        <v>101405.62</v>
+        <v>94439.28999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>105622.86</v>
+        <v>101329.02</v>
       </c>
       <c r="O11" t="n">
-        <v>121885.35</v>
+        <v>111196.92</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1459,14 +1453,12 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1485,57 +1477,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>86798.77</v>
+        <v>90389.11</v>
       </c>
       <c r="C12" t="n">
-        <v>92969.09</v>
+        <v>94060.77</v>
       </c>
       <c r="D12" t="n">
-        <v>85272.2</v>
+        <v>83862.25</v>
       </c>
       <c r="E12" t="n">
-        <v>90394.31</v>
+        <v>90405.64</v>
       </c>
       <c r="F12" t="n">
-        <v>3589.3</v>
+        <v>11.33</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0413</v>
+        <v>0.0001</v>
       </c>
       <c r="H12" t="n">
-        <v>7696.89</v>
+        <v>10198.52</v>
       </c>
       <c r="I12" t="n">
-        <v>65391.26</v>
+        <v>77575.3</v>
       </c>
       <c r="J12" t="n">
-        <v>70791.91</v>
+        <v>83334.25999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>79170.73</v>
+        <v>86545.87</v>
       </c>
       <c r="L12" t="n">
-        <v>87549.55</v>
+        <v>89757.48</v>
       </c>
       <c r="M12" t="n">
-        <v>94439.28999999999</v>
+        <v>94242.75999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>101329.02</v>
+        <v>98728.03999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>111196.92</v>
+        <v>100665.98</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1543,8 +1535,10 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
@@ -1574,50 +1568,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>90389.11</v>
+        <v>90424.59</v>
       </c>
       <c r="C13" t="n">
-        <v>94060.77</v>
+        <v>94601.57000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>83862.25</v>
+        <v>87634.94</v>
       </c>
       <c r="E13" t="n">
-        <v>90405.64</v>
+        <v>88175.17999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>11.33</v>
+        <v>-2230.46</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0247</v>
       </c>
       <c r="H13" t="n">
-        <v>10198.52</v>
+        <v>6966.63</v>
       </c>
       <c r="I13" t="n">
-        <v>77575.3</v>
+        <v>73663.73</v>
       </c>
       <c r="J13" t="n">
-        <v>83334.25999999999</v>
+        <v>80929.17999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>86545.87</v>
+        <v>85306.38</v>
       </c>
       <c r="L13" t="n">
-        <v>89757.48</v>
+        <v>89683.58</v>
       </c>
       <c r="M13" t="n">
-        <v>94242.75999999999</v>
+        <v>95504.89999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>98728.03999999999</v>
+        <v>101326.23</v>
       </c>
       <c r="O13" t="n">
-        <v>100665.98</v>
+        <v>104259.3</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1625,14 +1619,12 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1658,50 +1650,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>90424.59</v>
+        <v>88171.08</v>
       </c>
       <c r="C14" t="n">
-        <v>94601.57000000001</v>
+        <v>90264.57000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>87634.94</v>
+        <v>84436.31</v>
       </c>
       <c r="E14" t="n">
-        <v>88175.17999999999</v>
+        <v>88621.75</v>
       </c>
       <c r="F14" t="n">
-        <v>-2230.46</v>
+        <v>446.57</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0051</v>
       </c>
       <c r="H14" t="n">
-        <v>6966.63</v>
+        <v>5828.26</v>
       </c>
       <c r="I14" t="n">
-        <v>73663.73</v>
+        <v>80668.3</v>
       </c>
       <c r="J14" t="n">
-        <v>80929.17999999999</v>
+        <v>79737.00999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>85306.38</v>
+        <v>84691.86</v>
       </c>
       <c r="L14" t="n">
-        <v>89683.58</v>
+        <v>89646.72</v>
       </c>
       <c r="M14" t="n">
-        <v>95504.89999999999</v>
+        <v>91658.5</v>
       </c>
       <c r="N14" t="n">
-        <v>101326.23</v>
+        <v>93670.28</v>
       </c>
       <c r="O14" t="n">
-        <v>104259.3</v>
+        <v>101568.2</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1709,8 +1701,10 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
@@ -1733,57 +1727,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>88171.08</v>
+        <v>88621.39999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>90264.57000000001</v>
+        <v>90501.92999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>84436.31</v>
+        <v>86411.8</v>
       </c>
       <c r="E15" t="n">
-        <v>88621.75</v>
+        <v>87835.84</v>
       </c>
       <c r="F15" t="n">
-        <v>446.57</v>
+        <v>-785.91</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0051</v>
+        <v>-0.0089</v>
       </c>
       <c r="H15" t="n">
-        <v>5828.26</v>
+        <v>4090.13</v>
       </c>
       <c r="I15" t="n">
-        <v>80668.3</v>
+        <v>78608.05</v>
       </c>
       <c r="J15" t="n">
-        <v>79737.00999999999</v>
+        <v>83429.14999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>84691.86</v>
+        <v>85707.62</v>
       </c>
       <c r="L15" t="n">
-        <v>89646.72</v>
+        <v>87986.10000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>91658.5</v>
+        <v>91535.88</v>
       </c>
       <c r="N15" t="n">
-        <v>93670.28</v>
+        <v>95085.66</v>
       </c>
       <c r="O15" t="n">
-        <v>101568.2</v>
+        <v>96092.83</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1791,10 +1785,8 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
@@ -1817,57 +1809,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>88621.39999999999</v>
+        <v>87835.78999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>90501.92999999999</v>
+        <v>91712.59</v>
       </c>
       <c r="D16" t="n">
-        <v>86411.8</v>
+        <v>86717.91</v>
       </c>
       <c r="E16" t="n">
-        <v>87835.84</v>
+        <v>91413.49000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-785.91</v>
+        <v>3577.66</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0089</v>
+        <v>0.0407</v>
       </c>
       <c r="H16" t="n">
-        <v>4090.13</v>
+        <v>4994.67</v>
       </c>
       <c r="I16" t="n">
-        <v>78608.05</v>
+        <v>82321.66</v>
       </c>
       <c r="J16" t="n">
-        <v>83429.14999999999</v>
+        <v>83435.19</v>
       </c>
       <c r="K16" t="n">
-        <v>85707.62</v>
+        <v>85790.77</v>
       </c>
       <c r="L16" t="n">
-        <v>87986.10000000001</v>
+        <v>88146.35000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>91535.88</v>
+        <v>89880.89999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>95085.66</v>
+        <v>91615.46000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>96092.83</v>
+        <v>94592.06</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1878,16 +1870,20 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1897,59 +1893,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>87835.78999999999</v>
+        <v>91414.62</v>
       </c>
       <c r="C17" t="n">
-        <v>91712.59</v>
+        <v>94762.07000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>86717.91</v>
+        <v>89233.88</v>
       </c>
       <c r="E17" t="n">
-        <v>91413.49000000001</v>
+        <v>90827.46000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>3577.66</v>
+        <v>-586.03</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0407</v>
+        <v>-0.0064</v>
       </c>
       <c r="H17" t="n">
-        <v>4994.67</v>
+        <v>5528.2</v>
       </c>
       <c r="I17" t="n">
-        <v>82321.66</v>
+        <v>81723.24000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>83435.19</v>
+        <v>87517.94</v>
       </c>
       <c r="K17" t="n">
-        <v>85790.77</v>
+        <v>88916.16</v>
       </c>
       <c r="L17" t="n">
-        <v>88146.35000000001</v>
+        <v>90314.37</v>
       </c>
       <c r="M17" t="n">
-        <v>89880.89999999999</v>
+        <v>93910.83</v>
       </c>
       <c r="N17" t="n">
-        <v>91615.46000000001</v>
+        <v>97507.28999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>94592.06</v>
+        <v>96707.25999999999</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1962,7 +1954,7 @@
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
@@ -1970,10 +1962,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1983,55 +1973,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>91414.62</v>
+        <v>90825.86</v>
       </c>
       <c r="C18" t="n">
-        <v>94762.07000000001</v>
+        <v>97860.60000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>89233.88</v>
+        <v>90055.02</v>
       </c>
       <c r="E18" t="n">
-        <v>90827.46000000001</v>
+        <v>93634.42999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-586.03</v>
+        <v>2806.97</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0064</v>
+        <v>0.0309</v>
       </c>
       <c r="H18" t="n">
-        <v>5528.2</v>
+        <v>7805.58</v>
       </c>
       <c r="I18" t="n">
-        <v>81723.24000000001</v>
+        <v>83705.67999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>87517.94</v>
+        <v>84714.00999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>88916.16</v>
+        <v>88063.36</v>
       </c>
       <c r="L18" t="n">
-        <v>90314.37</v>
+        <v>91412.72</v>
       </c>
       <c r="M18" t="n">
-        <v>93910.83</v>
+        <v>93591.56</v>
       </c>
       <c r="N18" t="n">
-        <v>97507.28999999999</v>
+        <v>95770.39999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>96707.25999999999</v>
+        <v>100290.27</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2044,17 +2038,19 @@
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
@@ -2063,84 +2059,80 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>90825.86</v>
+        <v>93655.67</v>
       </c>
       <c r="C19" t="n">
-        <v>97860.60000000001</v>
+        <v>93660.83</v>
       </c>
       <c r="D19" t="n">
-        <v>90055.02</v>
+        <v>86003.71000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>93634.42999999999</v>
+        <v>86572.22</v>
       </c>
       <c r="F19" t="n">
-        <v>2806.97</v>
+        <v>-7062.21</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0309</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>7805.58</v>
+        <v>7657.12</v>
       </c>
       <c r="I19" t="n">
-        <v>83705.67999999999</v>
+        <v>82249.45</v>
       </c>
       <c r="J19" t="n">
-        <v>84714.00999999999</v>
+        <v>85667.16</v>
       </c>
       <c r="K19" t="n">
-        <v>88063.36</v>
+        <v>89731.64</v>
       </c>
       <c r="L19" t="n">
-        <v>91412.72</v>
+        <v>93796.12</v>
       </c>
       <c r="M19" t="n">
-        <v>93591.56</v>
+        <v>97537.22</v>
       </c>
       <c r="N19" t="n">
-        <v>95770.39999999999</v>
+        <v>101278.32</v>
       </c>
       <c r="O19" t="n">
-        <v>100290.27</v>
+        <v>105666.18</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
+      <c r="Q19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
@@ -2149,58 +2141,64 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>93655.67</v>
+        <v>86566.52</v>
       </c>
       <c r="C20" t="n">
-        <v>93660.83</v>
+        <v>90439.28999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>86003.71000000001</v>
+        <v>75698.89999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>86572.22</v>
+        <v>76974.45</v>
       </c>
       <c r="F20" t="n">
-        <v>-7062.21</v>
+        <v>-9597.77</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.1109</v>
       </c>
       <c r="H20" t="n">
-        <v>7657.12</v>
+        <v>14740.39</v>
       </c>
       <c r="I20" t="n">
-        <v>82249.45</v>
+        <v>78346.59</v>
       </c>
       <c r="J20" t="n">
-        <v>85667.16</v>
+        <v>77285.08</v>
       </c>
       <c r="K20" t="n">
-        <v>89731.64</v>
+        <v>82743.66</v>
       </c>
       <c r="L20" t="n">
-        <v>93796.12</v>
+        <v>88202.24000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>97537.22</v>
+        <v>90400.78</v>
       </c>
       <c r="N20" t="n">
-        <v>101278.32</v>
+        <v>92599.31</v>
       </c>
       <c r="O20" t="n">
-        <v>105666.18</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
+        <v>101317.95</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
@@ -2217,8 +2215,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2226,89 +2226,81 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>86566.52</v>
+        <v>76968.88</v>
       </c>
       <c r="C21" t="n">
-        <v>90439.28999999999</v>
+        <v>79258.61</v>
       </c>
       <c r="D21" t="n">
-        <v>75698.89999999999</v>
+        <v>60074.2</v>
       </c>
       <c r="E21" t="n">
-        <v>76974.45</v>
+        <v>70264.73</v>
       </c>
       <c r="F21" t="n">
-        <v>-9597.77</v>
+        <v>-6709.72</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.1109</v>
+        <v>-0.0872</v>
       </c>
       <c r="H21" t="n">
-        <v>14740.39</v>
+        <v>19184.41</v>
       </c>
       <c r="I21" t="n">
-        <v>78346.59</v>
+        <v>60958.51</v>
       </c>
       <c r="J21" t="n">
-        <v>77285.08</v>
+        <v>59186.73</v>
       </c>
       <c r="K21" t="n">
-        <v>82743.66</v>
+        <v>69604.25</v>
       </c>
       <c r="L21" t="n">
-        <v>88202.24000000001</v>
+        <v>80021.77</v>
       </c>
       <c r="M21" t="n">
-        <v>90400.78</v>
+        <v>84344.64</v>
       </c>
       <c r="N21" t="n">
-        <v>92599.31</v>
+        <v>88667.50999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>101317.95</v>
+        <v>105179.68</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2326,67 +2318,63 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>76968.88</v>
+        <v>70243.33</v>
       </c>
       <c r="C22" t="n">
-        <v>79258.61</v>
+        <v>71369.97</v>
       </c>
       <c r="D22" t="n">
-        <v>60074.2</v>
+        <v>65092.11</v>
       </c>
       <c r="E22" t="n">
-        <v>70264.73</v>
+        <v>68788.19</v>
       </c>
       <c r="F22" t="n">
-        <v>-6709.72</v>
+        <v>-1476.54</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0872</v>
+        <v>-0.021</v>
       </c>
       <c r="H22" t="n">
-        <v>19184.41</v>
+        <v>6277.86</v>
       </c>
       <c r="I22" t="n">
-        <v>60958.51</v>
+        <v>40889.8</v>
       </c>
       <c r="J22" t="n">
-        <v>59186.73</v>
+        <v>51379.48</v>
       </c>
       <c r="K22" t="n">
-        <v>69604.25</v>
+        <v>60672.52</v>
       </c>
       <c r="L22" t="n">
-        <v>80021.77</v>
+        <v>69965.57000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>84344.64</v>
+        <v>79856.92999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>88667.50999999999</v>
+        <v>89748.28999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>105179.68</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>98443.02</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
       </c>
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2403,55 +2391,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>70243.33</v>
+        <v>68782.39999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>71369.97</v>
+        <v>70067.23</v>
       </c>
       <c r="D23" t="n">
-        <v>65092.11</v>
+        <v>65637.42999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>68788.19</v>
+        <v>67659.39</v>
       </c>
       <c r="F23" t="n">
-        <v>-1476.54</v>
+        <v>-1128.8</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.021</v>
+        <v>-0.0164</v>
       </c>
       <c r="H23" t="n">
-        <v>6277.86</v>
+        <v>4429.8</v>
       </c>
       <c r="I23" t="n">
-        <v>40889.8</v>
+        <v>58814.25</v>
       </c>
       <c r="J23" t="n">
-        <v>51379.48</v>
+        <v>62788.9</v>
       </c>
       <c r="K23" t="n">
-        <v>60672.52</v>
+        <v>65649.25999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>69965.57000000001</v>
+        <v>68509.61</v>
       </c>
       <c r="M23" t="n">
-        <v>79856.92999999999</v>
+        <v>71927.12</v>
       </c>
       <c r="N23" t="n">
-        <v>89748.28999999999</v>
+        <v>75344.62</v>
       </c>
       <c r="O23" t="n">
-        <v>98443.02</v>
+        <v>77647.83</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2459,8 +2451,10 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
@@ -2490,70 +2484,74 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>68782.39999999999</v>
+        <v>67668.42999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>70067.23</v>
+        <v>69953.53</v>
       </c>
       <c r="D24" t="n">
-        <v>65637.42999999999</v>
+        <v>62553.19</v>
       </c>
       <c r="E24" t="n">
-        <v>67659.39</v>
+        <v>65738.10000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-1128.8</v>
+        <v>-1921.29</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0164</v>
+        <v>-0.0284</v>
       </c>
       <c r="H24" t="n">
-        <v>4429.8</v>
+        <v>7400.34</v>
       </c>
       <c r="I24" t="n">
-        <v>58814.25</v>
+        <v>61207.62</v>
       </c>
       <c r="J24" t="n">
-        <v>62788.9</v>
+        <v>63133.12</v>
       </c>
       <c r="K24" t="n">
-        <v>65649.25999999999</v>
+        <v>65444.49</v>
       </c>
       <c r="L24" t="n">
-        <v>68509.61</v>
+        <v>67755.86</v>
       </c>
       <c r="M24" t="n">
-        <v>71927.12</v>
+        <v>69874.28999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>75344.62</v>
+        <v>71992.72</v>
       </c>
       <c r="O24" t="n">
-        <v>77647.83</v>
+        <v>74497.03999999999</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2565,86 +2563,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>67668.42999999999</v>
+        <v>65734.08</v>
       </c>
       <c r="C25" t="n">
-        <v>69953.53</v>
+        <v>74051.8</v>
       </c>
       <c r="D25" t="n">
-        <v>62553.19</v>
+        <v>65303.14</v>
       </c>
       <c r="E25" t="n">
-        <v>65738.10000000001</v>
+        <v>65969.78</v>
       </c>
       <c r="F25" t="n">
-        <v>-1921.29</v>
+        <v>231.68</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0284</v>
+        <v>0.0035</v>
       </c>
       <c r="H25" t="n">
-        <v>7400.34</v>
+        <v>8748.67</v>
       </c>
       <c r="I25" t="n">
-        <v>61207.62</v>
+        <v>55152.84</v>
       </c>
       <c r="J25" t="n">
-        <v>63133.12</v>
+        <v>58080.13</v>
       </c>
       <c r="K25" t="n">
-        <v>65444.49</v>
+        <v>62037.93</v>
       </c>
       <c r="L25" t="n">
-        <v>67755.86</v>
+        <v>65995.73</v>
       </c>
       <c r="M25" t="n">
-        <v>69874.28999999999</v>
+        <v>69438.27</v>
       </c>
       <c r="N25" t="n">
-        <v>71992.72</v>
+        <v>72880.82000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>74497.03999999999</v>
+        <v>77353.88</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
@@ -2653,55 +2645,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>65734.08</v>
+        <v>65969.59</v>
       </c>
       <c r="C26" t="n">
-        <v>74051.8</v>
+        <v>73927.33</v>
       </c>
       <c r="D26" t="n">
-        <v>65303.14</v>
+        <v>65858.00999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>65969.78</v>
+        <v>72789.91</v>
       </c>
       <c r="F26" t="n">
-        <v>231.68</v>
+        <v>6820.13</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.1034</v>
       </c>
       <c r="H26" t="n">
-        <v>8748.67</v>
+        <v>8069.32</v>
       </c>
       <c r="I26" t="n">
-        <v>55152.84</v>
+        <v>56554.47</v>
       </c>
       <c r="J26" t="n">
-        <v>58080.13</v>
+        <v>55367.27</v>
       </c>
       <c r="K26" t="n">
-        <v>62037.93</v>
+        <v>61595.45</v>
       </c>
       <c r="L26" t="n">
-        <v>65995.73</v>
+        <v>67823.63</v>
       </c>
       <c r="M26" t="n">
-        <v>69438.27</v>
+        <v>70344.12</v>
       </c>
       <c r="N26" t="n">
-        <v>72880.82000000001</v>
+        <v>72864.60000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>77353.88</v>
+        <v>82800.47</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2712,9 +2708,9 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -2724,7 +2720,7 @@
       </c>
       <c r="U26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V26" s="8" t="n">
@@ -2737,57 +2733,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>65969.59</v>
+        <v>72798.17</v>
       </c>
       <c r="C27" t="n">
-        <v>73927.33</v>
+        <v>75988.39999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>65858.00999999999</v>
+        <v>67372.88</v>
       </c>
       <c r="E27" t="n">
-        <v>72789.91</v>
+        <v>67845.21000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>6820.13</v>
+        <v>-4944.7</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.1034</v>
+        <v>-0.0679</v>
       </c>
       <c r="H27" t="n">
-        <v>8069.32</v>
+        <v>8615.52</v>
       </c>
       <c r="I27" t="n">
-        <v>56554.47</v>
+        <v>57788.69</v>
       </c>
       <c r="J27" t="n">
-        <v>55367.27</v>
+        <v>66169.22</v>
       </c>
       <c r="K27" t="n">
-        <v>61595.45</v>
+        <v>68755.25</v>
       </c>
       <c r="L27" t="n">
-        <v>67823.63</v>
+        <v>71341.28999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>70344.12</v>
+        <v>76824.57000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>72864.60000000001</v>
+        <v>82307.86</v>
       </c>
       <c r="O27" t="n">
-        <v>82800.47</v>
+        <v>81996.64999999999</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2795,23 +2791,21 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2830,50 +2824,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>72798.17</v>
+        <v>67843</v>
       </c>
       <c r="C28" t="n">
-        <v>75988.39999999999</v>
+        <v>71985.74000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>67372.88</v>
+        <v>64971.71</v>
       </c>
       <c r="E28" t="n">
-        <v>67845.21000000001</v>
+        <v>65954.92</v>
       </c>
       <c r="F28" t="n">
-        <v>-4944.7</v>
+        <v>-1890.29</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0679</v>
+        <v>-0.0279</v>
       </c>
       <c r="H28" t="n">
-        <v>8615.52</v>
+        <v>7014.04</v>
       </c>
       <c r="I28" t="n">
-        <v>57788.69</v>
+        <v>58757.35</v>
       </c>
       <c r="J28" t="n">
-        <v>66169.22</v>
+        <v>57311.97</v>
       </c>
       <c r="K28" t="n">
-        <v>68755.25</v>
+        <v>63537.45</v>
       </c>
       <c r="L28" t="n">
-        <v>71341.28999999999</v>
+        <v>69762.92</v>
       </c>
       <c r="M28" t="n">
-        <v>76824.57000000001</v>
+        <v>72152.97</v>
       </c>
       <c r="N28" t="n">
-        <v>82307.86</v>
+        <v>74543.02</v>
       </c>
       <c r="O28" t="n">
-        <v>81996.64999999999</v>
+        <v>84603.92</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2905,59 +2899,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>67843</v>
+        <v>65958.35000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>71985.74000000001</v>
+        <v>69230.36</v>
       </c>
       <c r="D29" t="n">
-        <v>64971.71</v>
+        <v>65725.25999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>65954.92</v>
+        <v>68981.89999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>-1890.29</v>
+        <v>3026.98</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0279</v>
+        <v>0.0459</v>
       </c>
       <c r="H29" t="n">
-        <v>7014.04</v>
+        <v>3505.1</v>
       </c>
       <c r="I29" t="n">
-        <v>58757.35</v>
+        <v>57957.67</v>
       </c>
       <c r="J29" t="n">
-        <v>57311.97</v>
+        <v>57678.99</v>
       </c>
       <c r="K29" t="n">
-        <v>63537.45</v>
+        <v>62447.9</v>
       </c>
       <c r="L29" t="n">
-        <v>69762.92</v>
+        <v>67216.82000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>72152.97</v>
+        <v>69461.94</v>
       </c>
       <c r="N29" t="n">
-        <v>74543.02</v>
+        <v>71707.06</v>
       </c>
       <c r="O29" t="n">
-        <v>84603.92</v>
+        <v>78999.78</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2965,19 +2955,19 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
@@ -2989,55 +2979,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>65958.35000000001</v>
+        <v>68982.91</v>
       </c>
       <c r="C30" t="n">
-        <v>69230.36</v>
+        <v>73784.23</v>
       </c>
       <c r="D30" t="n">
-        <v>65725.25999999999</v>
+        <v>67740.50999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>68981.89999999999</v>
+        <v>70753.41</v>
       </c>
       <c r="F30" t="n">
-        <v>3026.98</v>
+        <v>1771.51</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0459</v>
+        <v>0.0257</v>
       </c>
       <c r="H30" t="n">
-        <v>3505.1</v>
+        <v>6043.73</v>
       </c>
       <c r="I30" t="n">
-        <v>57957.67</v>
+        <v>62220.16</v>
       </c>
       <c r="J30" t="n">
-        <v>57678.99</v>
+        <v>66228.84</v>
       </c>
       <c r="K30" t="n">
-        <v>62447.9</v>
+        <v>67229.35000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>67216.82000000001</v>
+        <v>68229.85000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>69461.94</v>
+        <v>70734.45</v>
       </c>
       <c r="N30" t="n">
-        <v>71707.06</v>
+        <v>73239.03999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>78999.78</v>
+        <v>72735.46000000001</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3058,11 +3052,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W30" s="11" t="inlineStr">
         <is>
@@ -3071,57 +3069,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>68982.91</v>
+        <v>70757.62</v>
       </c>
       <c r="C31" t="n">
-        <v>73784.23</v>
+        <v>78320.67999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>67740.50999999999</v>
+        <v>70588.52</v>
       </c>
       <c r="E31" t="n">
-        <v>70753.41</v>
+        <v>73856.35000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>1771.51</v>
+        <v>3102.95</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0257</v>
+        <v>0.0439</v>
       </c>
       <c r="H31" t="n">
-        <v>6043.73</v>
+        <v>7732.16</v>
       </c>
       <c r="I31" t="n">
-        <v>62220.16</v>
+        <v>61696.78</v>
       </c>
       <c r="J31" t="n">
-        <v>66228.84</v>
+        <v>64705.2</v>
       </c>
       <c r="K31" t="n">
-        <v>67229.35000000001</v>
+        <v>67731.53999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>68229.85000000001</v>
+        <v>70757.89</v>
       </c>
       <c r="M31" t="n">
-        <v>70734.45</v>
+        <v>73775.27</v>
       </c>
       <c r="N31" t="n">
-        <v>73239.03999999999</v>
+        <v>76792.64999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>72735.46000000001</v>
+        <v>79827.96000000001</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3147,10 +3145,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V31" s="8" t="n">
+        <v/>
       </c>
       <c r="W31" s="11" t="inlineStr">
         <is>
@@ -3166,50 +3162,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>70757.62</v>
+        <v>73854.25</v>
       </c>
       <c r="C32" t="n">
-        <v>78320.67999999999</v>
+        <v>79468</v>
       </c>
       <c r="D32" t="n">
-        <v>70588.52</v>
+        <v>73775.57000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>73856.35000000001</v>
+        <v>78657.53999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>3102.95</v>
+        <v>4801.19</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0439</v>
+        <v>0.065</v>
       </c>
       <c r="H32" t="n">
-        <v>7732.16</v>
+        <v>5692.43</v>
       </c>
       <c r="I32" t="n">
-        <v>61696.78</v>
+        <v>62856.37</v>
       </c>
       <c r="J32" t="n">
-        <v>64705.2</v>
+        <v>65825.07000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>67731.53999999999</v>
+        <v>69990.27</v>
       </c>
       <c r="L32" t="n">
-        <v>70757.89</v>
+        <v>74155.48</v>
       </c>
       <c r="M32" t="n">
-        <v>73775.27</v>
+        <v>77722.42999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>76792.64999999999</v>
+        <v>81289.38</v>
       </c>
       <c r="O32" t="n">
-        <v>79827.96000000001</v>
+        <v>86052.84</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3230,10 +3226,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3252,50 +3246,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>73854.25</v>
+        <v>78661.02</v>
       </c>
       <c r="C33" t="n">
-        <v>79468</v>
+        <v>79488.17</v>
       </c>
       <c r="D33" t="n">
-        <v>73775.57000000001</v>
+        <v>74958.57000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>78657.53999999999</v>
+        <v>78538.23</v>
       </c>
       <c r="F33" t="n">
-        <v>4801.19</v>
+        <v>-119.31</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.065</v>
+        <v>-0.0015</v>
       </c>
       <c r="H33" t="n">
-        <v>5692.43</v>
+        <v>4529.6</v>
       </c>
       <c r="I33" t="n">
-        <v>62856.37</v>
+        <v>68083.14</v>
       </c>
       <c r="J33" t="n">
-        <v>65825.07000000001</v>
+        <v>73982.99000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>69990.27</v>
+        <v>75811.32000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>74155.48</v>
+        <v>77639.66</v>
       </c>
       <c r="M33" t="n">
-        <v>77722.42999999999</v>
+        <v>81503.75</v>
       </c>
       <c r="N33" t="n">
-        <v>81289.38</v>
+        <v>85367.85000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>86052.84</v>
+        <v>85160.42999999999</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3303,18 +3297,18 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3329,57 +3323,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>78661.02</v>
+        <v>78540.28999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>79488.17</v>
+        <v>82792.21000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>74958.57000000001</v>
+        <v>78217.96000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>78538.23</v>
+        <v>82138.92999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>-119.31</v>
+        <v>3600.7</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0458</v>
       </c>
       <c r="H34" t="n">
-        <v>4529.6</v>
+        <v>4574.25</v>
       </c>
       <c r="I34" t="n">
-        <v>68083.14</v>
+        <v>70428.97</v>
       </c>
       <c r="J34" t="n">
-        <v>73982.99000000001</v>
+        <v>74666.05</v>
       </c>
       <c r="K34" t="n">
-        <v>75811.32000000001</v>
+        <v>76273.42999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>77639.66</v>
+        <v>77880.8</v>
       </c>
       <c r="M34" t="n">
-        <v>81503.75</v>
+        <v>80803.03</v>
       </c>
       <c r="N34" t="n">
-        <v>85367.85000000001</v>
+        <v>83725.25999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>85160.42999999999</v>
+        <v>84017.77</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3387,18 +3381,18 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R34" s="6" t="n">
+        <v/>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3413,77 +3407,79 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>78540.28999999999</v>
+        <v>82139.05</v>
       </c>
       <c r="C35" t="n">
-        <v>82792.21000000001</v>
+        <v>82326.23</v>
       </c>
       <c r="D35" t="n">
-        <v>78217.96000000001</v>
+        <v>76783.41</v>
       </c>
       <c r="E35" t="n">
-        <v>82138.92999999999</v>
+        <v>77429.35000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>3600.7</v>
+        <v>-4709.58</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0458</v>
+        <v>-0.0573</v>
       </c>
       <c r="H35" t="n">
-        <v>4574.25</v>
+        <v>5542.82</v>
       </c>
       <c r="I35" t="n">
-        <v>70428.97</v>
+        <v>73643.71000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>74666.05</v>
+        <v>78381.60000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>76273.42999999999</v>
+        <v>79851.8</v>
       </c>
       <c r="L35" t="n">
-        <v>77880.8</v>
+        <v>81322.00999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>80803.03</v>
+        <v>84426.05</v>
       </c>
       <c r="N35" t="n">
-        <v>83725.25999999999</v>
+        <v>87530.10000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>84017.77</v>
+        <v>87366.46000000001</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
+      <c r="Q35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3495,67 +3491,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>82139.05</v>
+        <v>77426.34</v>
       </c>
       <c r="C36" t="n">
-        <v>82326.23</v>
+        <v>78100.56</v>
       </c>
       <c r="D36" t="n">
-        <v>76783.41</v>
+        <v>74255.23</v>
       </c>
       <c r="E36" t="n">
-        <v>77429.35000000001</v>
+        <v>76981.12</v>
       </c>
       <c r="F36" t="n">
-        <v>-4709.58</v>
+        <v>-448.23</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0573</v>
+        <v>-0.0058</v>
       </c>
       <c r="H36" t="n">
-        <v>5542.82</v>
+        <v>3845.33</v>
       </c>
       <c r="I36" t="n">
-        <v>73643.71000000001</v>
+        <v>71240.59</v>
       </c>
       <c r="J36" t="n">
-        <v>78381.60000000001</v>
+        <v>70823.78999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>79851.8</v>
+        <v>74657.94</v>
       </c>
       <c r="L36" t="n">
-        <v>81322.00999999999</v>
+        <v>78492.09</v>
       </c>
       <c r="M36" t="n">
-        <v>84426.05</v>
+        <v>80200.75999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>87530.10000000001</v>
+        <v>81909.44</v>
       </c>
       <c r="O36" t="n">
-        <v>87366.46000000001</v>
+        <v>87869.05</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q36" s="6" t="n">
+        <v/>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
@@ -3564,7 +3554,7 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3586,56 +3576,58 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>77426.34</v>
+        <v>76981.12</v>
       </c>
       <c r="C37" t="n">
-        <v>78100.56</v>
+        <v>77990.87</v>
       </c>
       <c r="D37" t="n">
-        <v>74255.23</v>
+        <v>72435.62</v>
       </c>
       <c r="E37" t="n">
-        <v>76981.12</v>
+        <v>73579.69</v>
       </c>
       <c r="F37" t="n">
-        <v>-448.23</v>
+        <v>-3401.44</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0442</v>
       </c>
       <c r="H37" t="n">
-        <v>3845.33</v>
+        <v>5555.24</v>
       </c>
       <c r="I37" t="n">
-        <v>71240.59</v>
+        <v>70409.91</v>
       </c>
       <c r="J37" t="n">
-        <v>70823.78999999999</v>
+        <v>73537.41</v>
       </c>
       <c r="K37" t="n">
-        <v>74657.94</v>
+        <v>75058.46000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>78492.09</v>
+        <v>76579.50999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>80200.75999999999</v>
+        <v>78903.78999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>81909.44</v>
+        <v>81228.07000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>87869.05</v>
+        <v>81945.89</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
@@ -3644,7 +3636,7 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3666,57 +3658,59 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>76981.12</v>
+        <v>73580.21000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>77990.87</v>
+        <v>73969.57000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>72435.62</v>
+        <v>59108.92</v>
       </c>
       <c r="E38" t="n">
-        <v>73579.69</v>
+        <v>63239.52</v>
       </c>
       <c r="F38" t="n">
-        <v>-3401.44</v>
+        <v>-10340.17</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0442</v>
+        <v>-0.1405</v>
       </c>
       <c r="H38" t="n">
-        <v>5555.24</v>
+        <v>14860.65</v>
       </c>
       <c r="I38" t="n">
-        <v>70409.91</v>
+        <v>66880.38</v>
       </c>
       <c r="J38" t="n">
-        <v>73537.41</v>
+        <v>67207.67</v>
       </c>
       <c r="K38" t="n">
-        <v>75058.46000000001</v>
+        <v>70802.07000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>76579.50999999999</v>
+        <v>74396.47</v>
       </c>
       <c r="M38" t="n">
-        <v>78903.78999999999</v>
+        <v>76357.31</v>
       </c>
       <c r="N38" t="n">
-        <v>81228.07000000001</v>
+        <v>78318.14999999999</v>
       </c>
       <c r="O38" t="n">
-        <v>81945.89</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
+        <v>83546.11</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
@@ -3748,69 +3742,63 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>73580.21000000001</v>
+        <v>63244.09</v>
       </c>
       <c r="C39" t="n">
-        <v>73969.57000000001</v>
+        <v>65749.78</v>
       </c>
       <c r="D39" t="n">
-        <v>59108.92</v>
+        <v>60756.69</v>
       </c>
       <c r="E39" t="n">
-        <v>63239.52</v>
+        <v>65710.39999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>-10340.17</v>
+        <v>2470.88</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.1405</v>
+        <v>0.0391</v>
       </c>
       <c r="H39" t="n">
-        <v>14860.65</v>
+        <v>4993.09</v>
       </c>
       <c r="I39" t="n">
-        <v>66880.38</v>
+        <v>44248.27</v>
       </c>
       <c r="J39" t="n">
-        <v>67207.67</v>
+        <v>46729</v>
       </c>
       <c r="K39" t="n">
-        <v>70802.07000000001</v>
+        <v>55809.19</v>
       </c>
       <c r="L39" t="n">
-        <v>74396.47</v>
+        <v>64889.38</v>
       </c>
       <c r="M39" t="n">
-        <v>76357.31</v>
+        <v>70669.85000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>78318.14999999999</v>
+        <v>76450.31</v>
       </c>
       <c r="O39" t="n">
-        <v>83546.11</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>88830.22</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3827,55 +3815,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>63244.09</v>
+        <v>65711.11</v>
       </c>
       <c r="C40" t="n">
-        <v>65749.78</v>
+        <v>67248.13</v>
       </c>
       <c r="D40" t="n">
-        <v>60756.69</v>
+        <v>62201.14</v>
       </c>
       <c r="E40" t="n">
-        <v>65710.39999999999</v>
+        <v>63237.54</v>
       </c>
       <c r="F40" t="n">
-        <v>2470.88</v>
+        <v>-2472.86</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0391</v>
+        <v>-0.0376</v>
       </c>
       <c r="H40" t="n">
-        <v>4993.09</v>
+        <v>5046.99</v>
       </c>
       <c r="I40" t="n">
-        <v>44248.27</v>
+        <v>55763.59</v>
       </c>
       <c r="J40" t="n">
-        <v>46729</v>
+        <v>61945.89</v>
       </c>
       <c r="K40" t="n">
-        <v>55809.19</v>
+        <v>63213.85</v>
       </c>
       <c r="L40" t="n">
-        <v>64889.38</v>
+        <v>64481.82</v>
       </c>
       <c r="M40" t="n">
-        <v>70669.85000000001</v>
+        <v>68206.95</v>
       </c>
       <c r="N40" t="n">
-        <v>76450.31</v>
+        <v>71932.07000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>88830.22</v>
+        <v>70742.88</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3883,12 +3875,14 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3914,50 +3908,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>65711.11</v>
+        <v>63240.79</v>
       </c>
       <c r="C41" t="n">
-        <v>67248.13</v>
+        <v>65544</v>
       </c>
       <c r="D41" t="n">
-        <v>62201.14</v>
+        <v>58075.92</v>
       </c>
       <c r="E41" t="n">
-        <v>63237.54</v>
+        <v>59532.34</v>
       </c>
       <c r="F41" t="n">
-        <v>-2472.86</v>
+        <v>-3705.2</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0376</v>
+        <v>-0.0586</v>
       </c>
       <c r="H41" t="n">
-        <v>5046.99</v>
+        <v>7468.08</v>
       </c>
       <c r="I41" t="n">
-        <v>55763.59</v>
+        <v>57154.16</v>
       </c>
       <c r="J41" t="n">
-        <v>61945.89</v>
+        <v>57447</v>
       </c>
       <c r="K41" t="n">
-        <v>63213.85</v>
+        <v>60714.04</v>
       </c>
       <c r="L41" t="n">
-        <v>64481.82</v>
+        <v>63981.09</v>
       </c>
       <c r="M41" t="n">
-        <v>68206.95</v>
+        <v>65761.03</v>
       </c>
       <c r="N41" t="n">
-        <v>71932.07000000001</v>
+        <v>67540.98</v>
       </c>
       <c r="O41" t="n">
-        <v>70742.88</v>
+        <v>72295.12</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3989,59 +3983,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>63240.79</v>
+        <v>59522.79</v>
       </c>
       <c r="C42" t="n">
-        <v>65544</v>
+        <v>63935.85</v>
       </c>
       <c r="D42" t="n">
-        <v>58075.92</v>
+        <v>57747.77</v>
       </c>
       <c r="E42" t="n">
-        <v>59532.34</v>
+        <v>63547.88</v>
       </c>
       <c r="F42" t="n">
-        <v>-3705.2</v>
+        <v>4015.54</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0586</v>
+        <v>0.0675</v>
       </c>
       <c r="H42" t="n">
-        <v>7468.08</v>
+        <v>6188.08</v>
       </c>
       <c r="I42" t="n">
-        <v>57154.16</v>
+        <v>50607.84</v>
       </c>
       <c r="J42" t="n">
-        <v>57447</v>
+        <v>50925.45</v>
       </c>
       <c r="K42" t="n">
-        <v>60714.04</v>
+        <v>55798.3</v>
       </c>
       <c r="L42" t="n">
-        <v>63981.09</v>
+        <v>60671.15</v>
       </c>
       <c r="M42" t="n">
-        <v>65761.03</v>
+        <v>63266.38</v>
       </c>
       <c r="N42" t="n">
-        <v>67540.98</v>
+        <v>65861.61</v>
       </c>
       <c r="O42" t="n">
-        <v>72295.12</v>
+        <v>73012.08</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4049,19 +4039,19 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4073,55 +4063,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>59522.79</v>
+        <v>63551.02</v>
       </c>
       <c r="C43" t="n">
-        <v>63935.85</v>
+        <v>64658.97</v>
       </c>
       <c r="D43" t="n">
-        <v>57747.77</v>
+        <v>61275.83</v>
       </c>
       <c r="E43" t="n">
-        <v>63547.88</v>
+        <v>63758.22</v>
       </c>
       <c r="F43" t="n">
-        <v>4015.54</v>
+        <v>210.34</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0675</v>
+        <v>0.0033</v>
       </c>
       <c r="H43" t="n">
-        <v>6188.08</v>
+        <v>3383.14</v>
       </c>
       <c r="I43" t="n">
-        <v>50607.84</v>
+        <v>51559.68</v>
       </c>
       <c r="J43" t="n">
-        <v>50925.45</v>
+        <v>58712.84</v>
       </c>
       <c r="K43" t="n">
-        <v>55798.3</v>
+        <v>60453.84</v>
       </c>
       <c r="L43" t="n">
-        <v>60671.15</v>
+        <v>62194.84</v>
       </c>
       <c r="M43" t="n">
-        <v>63266.38</v>
+        <v>66641.92</v>
       </c>
       <c r="N43" t="n">
-        <v>65861.61</v>
+        <v>71089</v>
       </c>
       <c r="O43" t="n">
-        <v>73012.08</v>
+        <v>70123.92999999999</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4134,13 +4128,11 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4155,57 +4147,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>63551.02</v>
+        <v>63757.17</v>
       </c>
       <c r="C44" t="n">
-        <v>64658.97</v>
+        <v>65507.59</v>
       </c>
       <c r="D44" t="n">
-        <v>61275.83</v>
+        <v>61769</v>
       </c>
       <c r="E44" t="n">
-        <v>63758.22</v>
+        <v>64690.8</v>
       </c>
       <c r="F44" t="n">
-        <v>210.34</v>
+        <v>932.59</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0146</v>
       </c>
       <c r="H44" t="n">
-        <v>3383.14</v>
+        <v>3738.59</v>
       </c>
       <c r="I44" t="n">
-        <v>51559.68</v>
+        <v>57892.69</v>
       </c>
       <c r="J44" t="n">
-        <v>58712.84</v>
+        <v>60770.49</v>
       </c>
       <c r="K44" t="n">
-        <v>60453.84</v>
+        <v>62066.65</v>
       </c>
       <c r="L44" t="n">
-        <v>62194.84</v>
+        <v>63362.81</v>
       </c>
       <c r="M44" t="n">
-        <v>66641.92</v>
+        <v>65449.79</v>
       </c>
       <c r="N44" t="n">
-        <v>71089</v>
+        <v>67536.77</v>
       </c>
       <c r="O44" t="n">
-        <v>70123.92999999999</v>
+        <v>68042.11</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4213,16 +4205,20 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4244,50 +4240,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>63757.17</v>
+        <v>64684.42</v>
       </c>
       <c r="C45" t="n">
-        <v>65507.59</v>
+        <v>66910.06</v>
       </c>
       <c r="D45" t="n">
-        <v>61769</v>
+        <v>63686.04</v>
       </c>
       <c r="E45" t="n">
-        <v>64690.8</v>
+        <v>65340.3</v>
       </c>
       <c r="F45" t="n">
-        <v>932.59</v>
+        <v>649.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.01</v>
       </c>
       <c r="H45" t="n">
-        <v>3738.59</v>
+        <v>3224.03</v>
       </c>
       <c r="I45" t="n">
-        <v>57892.69</v>
+        <v>58030.41</v>
       </c>
       <c r="J45" t="n">
-        <v>60770.49</v>
+        <v>61478.46</v>
       </c>
       <c r="K45" t="n">
-        <v>62066.65</v>
+        <v>62821.51</v>
       </c>
       <c r="L45" t="n">
-        <v>63362.81</v>
+        <v>64164.55</v>
       </c>
       <c r="M45" t="n">
-        <v>65449.79</v>
+        <v>66560.10000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>67536.77</v>
+        <v>68955.64999999999</v>
       </c>
       <c r="O45" t="n">
-        <v>68042.11</v>
+        <v>69246.19</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4295,19 +4291,17 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="U45" s="8" t="n">
@@ -4330,50 +4324,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>64684.42</v>
+        <v>65340.59</v>
       </c>
       <c r="C46" t="n">
-        <v>66910.06</v>
+        <v>65658.34</v>
       </c>
       <c r="D46" t="n">
-        <v>63686.04</v>
+        <v>62233.01</v>
       </c>
       <c r="E46" t="n">
-        <v>65340.3</v>
+        <v>63482</v>
       </c>
       <c r="F46" t="n">
-        <v>649.5</v>
+        <v>-1858.3</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.0284</v>
       </c>
       <c r="H46" t="n">
-        <v>3224.03</v>
+        <v>3425.32</v>
       </c>
       <c r="I46" t="n">
-        <v>58030.41</v>
+        <v>60462.01</v>
       </c>
       <c r="J46" t="n">
-        <v>61478.46</v>
+        <v>62137.4</v>
       </c>
       <c r="K46" t="n">
-        <v>62821.51</v>
+        <v>63728.29</v>
       </c>
       <c r="L46" t="n">
-        <v>64164.55</v>
+        <v>65319.17</v>
       </c>
       <c r="M46" t="n">
-        <v>66560.10000000001</v>
+        <v>66952.31</v>
       </c>
       <c r="N46" t="n">
-        <v>68955.64999999999</v>
+        <v>68585.45</v>
       </c>
       <c r="O46" t="n">
-        <v>69246.19</v>
+        <v>70134.09</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4381,18 +4375,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4405,59 +4399,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>65340.59</v>
+        <v>63485.44</v>
       </c>
       <c r="C47" t="n">
-        <v>65658.34</v>
+        <v>65401.69</v>
       </c>
       <c r="D47" t="n">
-        <v>62233.01</v>
+        <v>62226.58</v>
       </c>
       <c r="E47" t="n">
-        <v>63482</v>
+        <v>64844.89</v>
       </c>
       <c r="F47" t="n">
-        <v>-1858.3</v>
+        <v>1362.89</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0284</v>
+        <v>0.0215</v>
       </c>
       <c r="H47" t="n">
-        <v>3425.32</v>
+        <v>3175.11</v>
       </c>
       <c r="I47" t="n">
-        <v>60462.01</v>
+        <v>58807.69</v>
       </c>
       <c r="J47" t="n">
-        <v>62137.4</v>
+        <v>59824.84</v>
       </c>
       <c r="K47" t="n">
-        <v>63728.29</v>
+        <v>61769.34</v>
       </c>
       <c r="L47" t="n">
-        <v>65319.17</v>
+        <v>63713.84</v>
       </c>
       <c r="M47" t="n">
-        <v>66952.31</v>
+        <v>65194.66</v>
       </c>
       <c r="N47" t="n">
-        <v>68585.45</v>
+        <v>66675.49000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>70134.09</v>
+        <v>69083.66</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4465,19 +4455,19 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4489,55 +4479,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>63485.44</v>
+        <v>64845.38</v>
       </c>
       <c r="C48" t="n">
-        <v>65401.69</v>
+        <v>65321.84</v>
       </c>
       <c r="D48" t="n">
-        <v>62226.58</v>
+        <v>62487.7</v>
       </c>
       <c r="E48" t="n">
-        <v>64844.89</v>
+        <v>62818.65</v>
       </c>
       <c r="F48" t="n">
-        <v>1362.89</v>
+        <v>-2026.23</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0215</v>
+        <v>-0.0312</v>
       </c>
       <c r="H48" t="n">
-        <v>3175.11</v>
+        <v>2834.14</v>
       </c>
       <c r="I48" t="n">
-        <v>58807.69</v>
+        <v>59051.46</v>
       </c>
       <c r="J48" t="n">
-        <v>59824.84</v>
+        <v>62185.15</v>
       </c>
       <c r="K48" t="n">
-        <v>61769.34</v>
+        <v>63257.33</v>
       </c>
       <c r="L48" t="n">
-        <v>63713.84</v>
+        <v>64329.51</v>
       </c>
       <c r="M48" t="n">
-        <v>65194.66</v>
+        <v>66432.44</v>
       </c>
       <c r="N48" t="n">
-        <v>66675.49000000001</v>
+        <v>68535.38</v>
       </c>
       <c r="O48" t="n">
-        <v>69083.66</v>
+        <v>68576.8</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4545,18 +4539,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4578,50 +4572,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>64845.38</v>
+        <v>62819.38</v>
       </c>
       <c r="C49" t="n">
-        <v>65321.84</v>
+        <v>79463.71000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>62487.7</v>
+        <v>62687.1</v>
       </c>
       <c r="E49" t="n">
-        <v>62818.65</v>
+        <v>77755.27</v>
       </c>
       <c r="F49" t="n">
-        <v>-2026.23</v>
+        <v>14936.61</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0312</v>
+        <v>0.2378</v>
       </c>
       <c r="H49" t="n">
-        <v>2834.14</v>
+        <v>16776.61</v>
       </c>
       <c r="I49" t="n">
-        <v>59051.46</v>
+        <v>59653.56</v>
       </c>
       <c r="J49" t="n">
-        <v>62185.15</v>
+        <v>59441.45</v>
       </c>
       <c r="K49" t="n">
-        <v>63257.33</v>
+        <v>61401.58</v>
       </c>
       <c r="L49" t="n">
-        <v>64329.51</v>
+        <v>63361.71</v>
       </c>
       <c r="M49" t="n">
-        <v>66432.44</v>
+        <v>64235.72</v>
       </c>
       <c r="N49" t="n">
-        <v>68535.38</v>
+        <v>65109.73</v>
       </c>
       <c r="O49" t="n">
-        <v>68576.8</v>
+        <v>68155.98</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4629,83 +4623,83 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W49" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W49" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>62819.38</v>
+        <v>77748.88</v>
       </c>
       <c r="C50" t="n">
-        <v>79463.71000000001</v>
+        <v>81346.95</v>
       </c>
       <c r="D50" t="n">
-        <v>62687.1</v>
+        <v>76688.83</v>
       </c>
       <c r="E50" t="n">
-        <v>77755.27</v>
+        <v>77667.57000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>14936.61</v>
+        <v>-87.7</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.2378</v>
+        <v>-0.0011</v>
       </c>
       <c r="H50" t="n">
-        <v>16776.61</v>
+        <v>4658.12</v>
       </c>
       <c r="I50" t="n">
-        <v>59653.56</v>
+        <v>45910.49</v>
       </c>
       <c r="J50" t="n">
-        <v>59441.45</v>
+        <v>64318.59</v>
       </c>
       <c r="K50" t="n">
-        <v>61401.58</v>
+        <v>69366.96000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>63361.71</v>
+        <v>74415.34</v>
       </c>
       <c r="M50" t="n">
-        <v>64235.72</v>
+        <v>86143.57000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>65109.73</v>
+        <v>97871.8</v>
       </c>
       <c r="O50" t="n">
-        <v>68155.98</v>
+        <v>96240.32000000001</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4718,78 +4712,76 @@
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>77748.88</v>
+        <v>77673.7</v>
       </c>
       <c r="C51" t="n">
-        <v>81346.95</v>
+        <v>82262.21000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>76688.83</v>
+        <v>76248.3</v>
       </c>
       <c r="E51" t="n">
-        <v>77667.57000000001</v>
+        <v>80350.05</v>
       </c>
       <c r="F51" t="n">
-        <v>-87.7</v>
+        <v>2682.48</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0345</v>
       </c>
       <c r="H51" t="n">
-        <v>4658.12</v>
+        <v>6013.91</v>
       </c>
       <c r="I51" t="n">
-        <v>45910.49</v>
+        <v>72030.7</v>
       </c>
       <c r="J51" t="n">
-        <v>64318.59</v>
+        <v>72334.28999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>69366.96000000001</v>
+        <v>75338.50999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>74415.34</v>
+        <v>78342.73</v>
       </c>
       <c r="M51" t="n">
-        <v>86143.57000000001</v>
+        <v>79996.63</v>
       </c>
       <c r="N51" t="n">
-        <v>97871.8</v>
+        <v>81650.53999999999</v>
       </c>
       <c r="O51" t="n">
-        <v>96240.32000000001</v>
+        <v>86005.08</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4802,14 +4794,18 @@
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4828,50 +4824,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>77673.7</v>
+        <v>80349.2</v>
       </c>
       <c r="C52" t="n">
-        <v>82262.21000000001</v>
+        <v>80432.31</v>
       </c>
       <c r="D52" t="n">
-        <v>76248.3</v>
+        <v>76162.91</v>
       </c>
       <c r="E52" t="n">
-        <v>80350.05</v>
+        <v>76838.16</v>
       </c>
       <c r="F52" t="n">
-        <v>2682.48</v>
+        <v>-3511.89</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0345</v>
+        <v>-0.0437</v>
       </c>
       <c r="H52" t="n">
-        <v>6013.91</v>
+        <v>4269.4</v>
       </c>
       <c r="I52" t="n">
-        <v>72030.7</v>
+        <v>70234.39999999999</v>
       </c>
       <c r="J52" t="n">
-        <v>72334.28999999999</v>
+        <v>74883.53999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>75338.50999999999</v>
+        <v>77343.09</v>
       </c>
       <c r="L52" t="n">
-        <v>78342.73</v>
+        <v>79802.64999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>79996.63</v>
+        <v>83357</v>
       </c>
       <c r="N52" t="n">
-        <v>81650.53999999999</v>
+        <v>86911.35000000001</v>
       </c>
       <c r="O52" t="n">
-        <v>86005.08</v>
+        <v>88276.12</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4879,23 +4875,21 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4907,57 +4901,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>80349.2</v>
+        <v>76830.28</v>
       </c>
       <c r="C53" t="n">
-        <v>80432.31</v>
+        <v>81911.14</v>
       </c>
       <c r="D53" t="n">
-        <v>76162.91</v>
+        <v>74944.59</v>
       </c>
       <c r="E53" t="n">
-        <v>76838.16</v>
+        <v>81142.61</v>
       </c>
       <c r="F53" t="n">
-        <v>-3511.89</v>
+        <v>4304.45</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0437</v>
+        <v>0.056</v>
       </c>
       <c r="H53" t="n">
-        <v>4269.4</v>
+        <v>6966.55</v>
       </c>
       <c r="I53" t="n">
-        <v>70234.39999999999</v>
+        <v>71893.52</v>
       </c>
       <c r="J53" t="n">
-        <v>74883.53999999999</v>
+        <v>71839.03</v>
       </c>
       <c r="K53" t="n">
-        <v>77343.09</v>
+        <v>74703.46000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>79802.64999999999</v>
+        <v>77567.88</v>
       </c>
       <c r="M53" t="n">
-        <v>83357</v>
+        <v>78972.86</v>
       </c>
       <c r="N53" t="n">
-        <v>86911.35000000001</v>
+        <v>80377.83</v>
       </c>
       <c r="O53" t="n">
-        <v>88276.12</v>
+        <v>84701.71000000001</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4965,22 +4959,24 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
@@ -4991,57 +4987,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>76830.28</v>
+        <v>81143.62</v>
       </c>
       <c r="C54" t="n">
-        <v>81911.14</v>
+        <v>87363.75999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>74944.59</v>
+        <v>80867.09</v>
       </c>
       <c r="E54" t="n">
-        <v>81142.61</v>
+        <v>84458.09</v>
       </c>
       <c r="F54" t="n">
-        <v>4304.45</v>
+        <v>3315.48</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.056</v>
+        <v>0.0409</v>
       </c>
       <c r="H54" t="n">
-        <v>6966.55</v>
+        <v>6496.67</v>
       </c>
       <c r="I54" t="n">
-        <v>71893.52</v>
+        <v>67978.05</v>
       </c>
       <c r="J54" t="n">
-        <v>71839.03</v>
+        <v>75533.42999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>74703.46000000001</v>
+        <v>77659.34</v>
       </c>
       <c r="L54" t="n">
-        <v>77567.88</v>
+        <v>79785.24000000001</v>
       </c>
       <c r="M54" t="n">
-        <v>78972.86</v>
+        <v>84625.88</v>
       </c>
       <c r="N54" t="n">
-        <v>80377.83</v>
+        <v>89466.53</v>
       </c>
       <c r="O54" t="n">
-        <v>84701.71000000001</v>
+        <v>88877.69</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5059,14 +5055,12 @@
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
@@ -5075,59 +5069,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>81143.62</v>
+        <v>84454.12</v>
       </c>
       <c r="C55" t="n">
-        <v>87363.75999999999</v>
+        <v>87146.35000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>80867.09</v>
+        <v>82570.72</v>
       </c>
       <c r="E55" t="n">
-        <v>84458.09</v>
+        <v>86480.3</v>
       </c>
       <c r="F55" t="n">
-        <v>3315.48</v>
+        <v>2022.22</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0409</v>
+        <v>0.0239</v>
       </c>
       <c r="H55" t="n">
-        <v>6496.67</v>
+        <v>4575.63</v>
       </c>
       <c r="I55" t="n">
-        <v>67978.05</v>
+        <v>74370.41</v>
       </c>
       <c r="J55" t="n">
-        <v>75533.42999999999</v>
+        <v>78132.75</v>
       </c>
       <c r="K55" t="n">
-        <v>77659.34</v>
+        <v>81209.75</v>
       </c>
       <c r="L55" t="n">
-        <v>79785.24000000001</v>
+        <v>84286.75</v>
       </c>
       <c r="M55" t="n">
-        <v>84625.88</v>
+        <v>87706.42</v>
       </c>
       <c r="N55" t="n">
-        <v>89466.53</v>
+        <v>91126.09</v>
       </c>
       <c r="O55" t="n">
-        <v>88877.69</v>
+        <v>93860.42999999999</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5159,75 +5149,81 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>84454.12</v>
+        <v>86480.00999999999</v>
       </c>
       <c r="C56" t="n">
-        <v>87146.35000000001</v>
+        <v>86971.78</v>
       </c>
       <c r="D56" t="n">
-        <v>82570.72</v>
+        <v>80336.91</v>
       </c>
       <c r="E56" t="n">
-        <v>86480.3</v>
+        <v>83679.47</v>
       </c>
       <c r="F56" t="n">
-        <v>2022.22</v>
+        <v>-2800.84</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0239</v>
+        <v>-0.0324</v>
       </c>
       <c r="H56" t="n">
-        <v>4575.63</v>
+        <v>6634.88</v>
       </c>
       <c r="I56" t="n">
-        <v>74370.41</v>
+        <v>77995.09</v>
       </c>
       <c r="J56" t="n">
-        <v>78132.75</v>
+        <v>82715.56</v>
       </c>
       <c r="K56" t="n">
-        <v>81209.75</v>
+        <v>84192.49000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>84286.75</v>
+        <v>85669.42</v>
       </c>
       <c r="M56" t="n">
-        <v>87706.42</v>
+        <v>88768.12</v>
       </c>
       <c r="N56" t="n">
-        <v>91126.09</v>
+        <v>91866.82000000001</v>
       </c>
       <c r="O56" t="n">
-        <v>93860.42999999999</v>
+        <v>91721.98</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
@@ -5241,65 +5237,63 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>86480.00999999999</v>
+        <v>83679.47</v>
       </c>
       <c r="C57" t="n">
-        <v>86971.78</v>
+        <v>84249.22</v>
       </c>
       <c r="D57" t="n">
-        <v>80336.91</v>
+        <v>79735.86</v>
       </c>
       <c r="E57" t="n">
-        <v>83679.47</v>
+        <v>81382.14999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>-2800.84</v>
+        <v>-2297.32</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0324</v>
+        <v>-0.0275</v>
       </c>
       <c r="H57" t="n">
-        <v>6634.88</v>
+        <v>4513.36</v>
       </c>
       <c r="I57" t="n">
-        <v>77995.09</v>
+        <v>73702.03</v>
       </c>
       <c r="J57" t="n">
-        <v>82715.56</v>
+        <v>77057.16</v>
       </c>
       <c r="K57" t="n">
-        <v>84192.49000000001</v>
+        <v>80362.03</v>
       </c>
       <c r="L57" t="n">
-        <v>85669.42</v>
+        <v>83666.91</v>
       </c>
       <c r="M57" t="n">
-        <v>88768.12</v>
+        <v>86996.91</v>
       </c>
       <c r="N57" t="n">
-        <v>91866.82000000001</v>
+        <v>90326.91</v>
       </c>
       <c r="O57" t="n">
-        <v>91721.98</v>
+        <v>93606.66</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q57" s="6" t="n">
+        <v/>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
@@ -5334,50 +5328,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>83679.47</v>
+        <v>82012.34</v>
       </c>
       <c r="C58" t="n">
-        <v>84249.22</v>
+        <v>82331.34</v>
       </c>
       <c r="D58" t="n">
-        <v>79735.86</v>
+        <v>81942.16</v>
       </c>
       <c r="E58" t="n">
-        <v>82005.28999999999</v>
+        <v>82259.17</v>
       </c>
       <c r="F58" t="n">
-        <v>-1674.18</v>
+        <v>877.02</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.0108</v>
       </c>
       <c r="H58" t="n">
-        <v>4513.36</v>
+        <v>389.18</v>
       </c>
       <c r="I58" t="n">
-        <v>73702.03</v>
+        <v>75222.5</v>
       </c>
       <c r="J58" t="n">
-        <v>77057.16</v>
+        <v>76563.59</v>
       </c>
       <c r="K58" t="n">
-        <v>80362.03</v>
+        <v>79125.47</v>
       </c>
       <c r="L58" t="n">
-        <v>83666.91</v>
+        <v>81687.34</v>
       </c>
       <c r="M58" t="n">
-        <v>86996.91</v>
+        <v>83638.83</v>
       </c>
       <c r="N58" t="n">
-        <v>90326.91</v>
+        <v>85590.31</v>
       </c>
       <c r="O58" t="n">
-        <v>93606.66</v>
+        <v>88762.58</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5385,14 +5379,12 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5411,7 +5403,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -659,34 +659,34 @@
         <v>6717.91</v>
       </c>
       <c r="I2" t="n">
-        <v>111010.34</v>
+        <v>111678.16</v>
       </c>
       <c r="J2" t="n">
-        <v>111415.2</v>
+        <v>111665.64</v>
       </c>
       <c r="K2" t="n">
-        <v>113580.73</v>
+        <v>113747.69</v>
       </c>
       <c r="L2" t="n">
-        <v>115746.26</v>
+        <v>115829.74</v>
       </c>
       <c r="M2" t="n">
-        <v>117031.46</v>
+        <v>116864.5</v>
       </c>
       <c r="N2" t="n">
-        <v>118316.65</v>
+        <v>117899.26</v>
       </c>
       <c r="O2" t="n">
-        <v>121362.52</v>
+        <v>121028.6</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -5257,13 +5257,13 @@
         <v>79735.86</v>
       </c>
       <c r="E57" t="n">
-        <v>81382.14999999999</v>
+        <v>82017.60000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>-2297.32</v>
+        <v>-1661.87</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0275</v>
+        <v>-0.0199</v>
       </c>
       <c r="H57" t="n">
         <v>4513.36</v>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5332,43 +5332,43 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>82012.34</v>
+        <v>81844.42999999999</v>
       </c>
       <c r="C58" t="n">
-        <v>82331.34</v>
+        <v>81844.42999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>81942.16</v>
+        <v>81475.82000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>82259.17</v>
+        <v>81543.66</v>
       </c>
       <c r="F58" t="n">
-        <v>877.02</v>
+        <v>-473.95</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0058</v>
       </c>
       <c r="H58" t="n">
-        <v>389.18</v>
+        <v>368.61</v>
       </c>
       <c r="I58" t="n">
         <v>75222.5</v>
       </c>
       <c r="J58" t="n">
-        <v>76563.59</v>
+        <v>77516.77</v>
       </c>
       <c r="K58" t="n">
-        <v>79125.47</v>
+        <v>79760.92</v>
       </c>
       <c r="L58" t="n">
-        <v>81687.34</v>
+        <v>82005.07000000001</v>
       </c>
       <c r="M58" t="n">
-        <v>83638.83</v>
+        <v>84274.28</v>
       </c>
       <c r="N58" t="n">
-        <v>85590.31</v>
+        <v>86543.49000000001</v>
       </c>
       <c r="O58" t="n">
         <v>88762.58</v>
@@ -5382,9 +5382,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5338,19 +5338,19 @@
         <v>81844.42999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>81475.82000000001</v>
+        <v>81131.63</v>
       </c>
       <c r="E58" t="n">
-        <v>81543.66</v>
+        <v>81496.84</v>
       </c>
       <c r="F58" t="n">
-        <v>-473.95</v>
+        <v>-520.76</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0063</v>
       </c>
       <c r="H58" t="n">
-        <v>368.61</v>
+        <v>712.8</v>
       </c>
       <c r="I58" t="n">
         <v>75222.5</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5332,25 +5332,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>81844.42999999999</v>
+        <v>82017.60000000001</v>
       </c>
       <c r="C58" t="n">
-        <v>81844.42999999999</v>
+        <v>83112.45</v>
       </c>
       <c r="D58" t="n">
-        <v>81131.63</v>
+        <v>81668.22</v>
       </c>
       <c r="E58" t="n">
-        <v>81496.84</v>
+        <v>82759.13</v>
       </c>
       <c r="F58" t="n">
-        <v>-520.76</v>
+        <v>741.53</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>712.8</v>
+        <v>1444.23</v>
       </c>
       <c r="I58" t="n">
         <v>75222.5</v>
@@ -5382,9 +5382,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -659,34 +659,34 @@
         <v>6717.91</v>
       </c>
       <c r="I2" t="n">
-        <v>111678.16</v>
+        <v>112371.85</v>
       </c>
       <c r="J2" t="n">
-        <v>111665.64</v>
+        <v>111925.77</v>
       </c>
       <c r="K2" t="n">
-        <v>113747.69</v>
+        <v>113921.11</v>
       </c>
       <c r="L2" t="n">
-        <v>115829.74</v>
+        <v>115916.45</v>
       </c>
       <c r="M2" t="n">
-        <v>116864.5</v>
+        <v>116691.08</v>
       </c>
       <c r="N2" t="n">
-        <v>117899.26</v>
+        <v>117465.71</v>
       </c>
       <c r="O2" t="n">
-        <v>121028.6</v>
+        <v>120681.76</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -5335,22 +5335,22 @@
         <v>82017.60000000001</v>
       </c>
       <c r="C58" t="n">
-        <v>83112.45</v>
+        <v>84275.92999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>81668.22</v>
+        <v>81107.23</v>
       </c>
       <c r="E58" t="n">
-        <v>82759.13</v>
+        <v>84256.61</v>
       </c>
       <c r="F58" t="n">
-        <v>741.53</v>
+        <v>2239.01</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0273</v>
       </c>
       <c r="H58" t="n">
-        <v>1444.23</v>
+        <v>3168.7</v>
       </c>
       <c r="I58" t="n">
         <v>75222.5</v>
@@ -5384,11 +5384,13 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5401,11 +5403,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5335,22 +5335,22 @@
         <v>82017.60000000001</v>
       </c>
       <c r="C58" t="n">
-        <v>84275.92999999999</v>
+        <v>84280.19</v>
       </c>
       <c r="D58" t="n">
         <v>81107.23</v>
       </c>
       <c r="E58" t="n">
-        <v>84256.61</v>
+        <v>82658.17</v>
       </c>
       <c r="F58" t="n">
-        <v>2239.01</v>
+        <v>640.5700000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0273</v>
+        <v>0.0078</v>
       </c>
       <c r="H58" t="n">
-        <v>3168.7</v>
+        <v>3172.95</v>
       </c>
       <c r="I58" t="n">
         <v>75222.5</v>
@@ -5384,12 +5384,12 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U58" s="8" t="n">

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -659,25 +659,25 @@
         <v>6717.91</v>
       </c>
       <c r="I2" t="n">
-        <v>112371.85</v>
+        <v>112803.88</v>
       </c>
       <c r="J2" t="n">
-        <v>111925.77</v>
+        <v>112465.81</v>
       </c>
       <c r="K2" t="n">
-        <v>113921.11</v>
+        <v>114137.12</v>
       </c>
       <c r="L2" t="n">
-        <v>115916.45</v>
+        <v>115808.44</v>
       </c>
       <c r="M2" t="n">
-        <v>116691.08</v>
+        <v>116475.06</v>
       </c>
       <c r="N2" t="n">
-        <v>117465.71</v>
+        <v>117141.68</v>
       </c>
       <c r="O2" t="n">
-        <v>120681.76</v>
+        <v>119817.7</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -710,14 +710,10 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -796,7 +792,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W3" s="9" t="inlineStr">
+      <c r="W3" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -878,7 +874,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="W4" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -962,7 +958,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1046,7 +1042,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1132,7 +1128,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1218,7 +1214,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1304,7 +1300,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1388,7 +1384,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1470,7 +1466,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1554,7 +1550,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1636,7 +1632,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1720,7 +1716,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1802,7 +1798,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1888,7 +1884,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1968,7 +1964,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2054,7 +2050,7 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2136,7 +2132,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2226,7 +2222,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2308,7 +2304,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2386,7 +2382,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2470,7 +2466,7 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2558,7 +2554,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2640,7 +2636,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2726,7 +2722,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2810,7 +2806,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2894,7 +2890,7 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2974,7 +2970,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3062,7 +3058,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3148,7 +3144,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3232,7 +3228,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3316,7 +3312,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3400,7 +3396,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3486,7 +3482,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3566,7 +3562,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3648,7 +3644,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3732,7 +3728,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3810,7 +3806,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3894,7 +3890,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3978,7 +3974,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4058,7 +4054,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4140,7 +4136,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4226,7 +4222,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4310,7 +4306,7 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4394,7 +4390,7 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4474,7 +4470,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4558,7 +4554,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4646,7 +4642,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4724,7 +4720,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4810,7 +4806,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4894,7 +4890,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4980,7 +4976,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5064,7 +5060,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5144,7 +5140,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5230,7 +5226,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5314,7 +5310,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5335,22 +5331,22 @@
         <v>82017.60000000001</v>
       </c>
       <c r="C58" t="n">
-        <v>84280.19</v>
+        <v>84840.05</v>
       </c>
       <c r="D58" t="n">
-        <v>81107.23</v>
+        <v>81046.8</v>
       </c>
       <c r="E58" t="n">
-        <v>82658.17</v>
+        <v>81172.32000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>640.5700000000001</v>
+        <v>-845.28</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0078</v>
+        <v>-0.0103</v>
       </c>
       <c r="H58" t="n">
-        <v>3172.95</v>
+        <v>3793.24</v>
       </c>
       <c r="I58" t="n">
         <v>75222.5</v>
@@ -5382,9 +5378,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5398,12 +5394,16 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>6717.91</v>
       </c>
       <c r="I2" t="n">
-        <v>112803.88</v>
+        <v>114314.01</v>
       </c>
       <c r="J2" t="n">
-        <v>112465.81</v>
+        <v>114159.64</v>
       </c>
       <c r="K2" t="n">
-        <v>114137.12</v>
+        <v>114836.81</v>
       </c>
       <c r="L2" t="n">
-        <v>115808.44</v>
+        <v>115513.98</v>
       </c>
       <c r="M2" t="n">
-        <v>116475.06</v>
+        <v>115775.38</v>
       </c>
       <c r="N2" t="n">
-        <v>117141.68</v>
+        <v>116036.78</v>
       </c>
       <c r="O2" t="n">
-        <v>119817.7</v>
+        <v>117129.72</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -5334,19 +5334,19 @@
         <v>84840.05</v>
       </c>
       <c r="D58" t="n">
-        <v>81046.8</v>
+        <v>80530.27</v>
       </c>
       <c r="E58" t="n">
-        <v>81172.32000000001</v>
+        <v>80760.53999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>-845.28</v>
+        <v>-1257.06</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0103</v>
+        <v>-0.0153</v>
       </c>
       <c r="H58" t="n">
-        <v>3793.24</v>
+        <v>4309.78</v>
       </c>
       <c r="I58" t="n">
         <v>75222.5</v>
@@ -5375,12 +5375,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,83 +634,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>115309.22</v>
+        <v>112117.88</v>
       </c>
       <c r="C2" t="n">
-        <v>115431.31</v>
+        <v>125559.21</v>
       </c>
       <c r="D2" t="n">
-        <v>108713.4</v>
+        <v>111589.95</v>
       </c>
       <c r="E2" t="n">
-        <v>112122.64</v>
+        <v>123513.48</v>
       </c>
       <c r="F2" t="n">
-        <v>-3183.45</v>
+        <v>11390.84</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0276</v>
+        <v>0.1016</v>
       </c>
       <c r="H2" t="n">
-        <v>6717.91</v>
+        <v>13969.26</v>
       </c>
       <c r="I2" t="n">
-        <v>114314.01</v>
+        <v>101995.48</v>
       </c>
       <c r="J2" t="n">
-        <v>114159.64</v>
+        <v>105429.87</v>
       </c>
       <c r="K2" t="n">
-        <v>114836.81</v>
+        <v>108763.68</v>
       </c>
       <c r="L2" t="n">
-        <v>115513.98</v>
+        <v>112097.5</v>
       </c>
       <c r="M2" t="n">
-        <v>115775.38</v>
+        <v>115481.6</v>
       </c>
       <c r="N2" t="n">
-        <v>116036.78</v>
+        <v>118865.7</v>
       </c>
       <c r="O2" t="n">
-        <v>117129.72</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>122149.23</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
-      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -718,149 +718,149 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>112117.88</v>
+        <v>123510.45</v>
       </c>
       <c r="C3" t="n">
-        <v>125559.21</v>
+        <v>126198.07</v>
       </c>
       <c r="D3" t="n">
-        <v>111589.95</v>
+        <v>104582.41</v>
       </c>
       <c r="E3" t="n">
-        <v>123513.48</v>
+        <v>115169.77</v>
       </c>
       <c r="F3" t="n">
-        <v>11390.84</v>
+        <v>-8343.709999999999</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.1016</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>13969.26</v>
+        <v>21615.66</v>
       </c>
       <c r="I3" t="n">
-        <v>101995.48</v>
+        <v>97620.7</v>
       </c>
       <c r="J3" t="n">
-        <v>105429.87</v>
+        <v>112013.67</v>
       </c>
       <c r="K3" t="n">
-        <v>108763.68</v>
+        <v>116528.85</v>
       </c>
       <c r="L3" t="n">
-        <v>112097.5</v>
+        <v>121044.03</v>
       </c>
       <c r="M3" t="n">
-        <v>115481.6</v>
+        <v>130498.11</v>
       </c>
       <c r="N3" t="n">
-        <v>118865.7</v>
+        <v>139952.18</v>
       </c>
       <c r="O3" t="n">
-        <v>122149.23</v>
+        <v>139528.47</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W3" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>123510.45</v>
+        <v>115161.68</v>
       </c>
       <c r="C4" t="n">
-        <v>126198.07</v>
+        <v>116020.48</v>
       </c>
       <c r="D4" t="n">
-        <v>104582.41</v>
+        <v>103598.43</v>
       </c>
       <c r="E4" t="n">
-        <v>115169.77</v>
+        <v>108666.71</v>
       </c>
       <c r="F4" t="n">
-        <v>-8343.709999999999</v>
+        <v>-6503.05</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0565</v>
       </c>
       <c r="H4" t="n">
-        <v>21615.66</v>
+        <v>12422.05</v>
       </c>
       <c r="I4" t="n">
-        <v>97620.7</v>
+        <v>82966.75999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>112013.67</v>
+        <v>93443.87</v>
       </c>
       <c r="K4" t="n">
-        <v>116528.85</v>
+        <v>104361.94</v>
       </c>
       <c r="L4" t="n">
-        <v>121044.03</v>
+        <v>115280</v>
       </c>
       <c r="M4" t="n">
-        <v>130498.11</v>
+        <v>125977.59</v>
       </c>
       <c r="N4" t="n">
-        <v>139952.18</v>
+        <v>136675.18</v>
       </c>
       <c r="O4" t="n">
-        <v>139528.47</v>
+        <v>147813.73</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q4" s="6" t="n">
+        <v/>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -874,64 +874,64 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>115161.68</v>
+        <v>108667.45</v>
       </c>
       <c r="C5" t="n">
-        <v>116020.48</v>
+        <v>115260.91</v>
       </c>
       <c r="D5" t="n">
-        <v>103598.43</v>
+        <v>106778</v>
       </c>
       <c r="E5" t="n">
-        <v>108666.71</v>
+        <v>114472.45</v>
       </c>
       <c r="F5" t="n">
-        <v>-6503.05</v>
+        <v>5805.73</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0565</v>
+        <v>0.0534</v>
       </c>
       <c r="H5" t="n">
-        <v>12422.05</v>
+        <v>8482.91</v>
       </c>
       <c r="I5" t="n">
-        <v>82966.75999999999</v>
+        <v>91176.38</v>
       </c>
       <c r="J5" t="n">
-        <v>93443.87</v>
+        <v>95673.28</v>
       </c>
       <c r="K5" t="n">
-        <v>104361.94</v>
+        <v>102455.68</v>
       </c>
       <c r="L5" t="n">
-        <v>115280</v>
+        <v>109238.08</v>
       </c>
       <c r="M5" t="n">
-        <v>125977.59</v>
+        <v>114877.74</v>
       </c>
       <c r="N5" t="n">
-        <v>136675.18</v>
+        <v>120517.39</v>
       </c>
       <c r="O5" t="n">
-        <v>147813.73</v>
+        <v>128442.54</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -939,102 +939,104 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>108667.45</v>
+        <v>114479.85</v>
       </c>
       <c r="C6" t="n">
-        <v>115260.91</v>
+        <v>116273.31</v>
       </c>
       <c r="D6" t="n">
-        <v>106778</v>
+        <v>106376.69</v>
       </c>
       <c r="E6" t="n">
-        <v>114472.45</v>
+        <v>110639.62</v>
       </c>
       <c r="F6" t="n">
-        <v>5805.73</v>
+        <v>-3832.82</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0534</v>
+        <v>-0.0335</v>
       </c>
       <c r="H6" t="n">
-        <v>8482.91</v>
+        <v>9896.620000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>91176.38</v>
+        <v>98295.09</v>
       </c>
       <c r="J6" t="n">
-        <v>95673.28</v>
+        <v>107716.04</v>
       </c>
       <c r="K6" t="n">
-        <v>102455.68</v>
+        <v>110230.99</v>
       </c>
       <c r="L6" t="n">
-        <v>109238.08</v>
+        <v>112745.95</v>
       </c>
       <c r="M6" t="n">
-        <v>114877.74</v>
+        <v>118713.9</v>
       </c>
       <c r="N6" t="n">
-        <v>120517.39</v>
+        <v>124681.85</v>
       </c>
       <c r="O6" t="n">
-        <v>128442.54</v>
+        <v>123743.81</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1042,64 +1044,64 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>114479.85</v>
+        <v>110646.91</v>
       </c>
       <c r="C7" t="n">
-        <v>116273.31</v>
+        <v>110764.91</v>
       </c>
       <c r="D7" t="n">
-        <v>106376.69</v>
+        <v>98962.06</v>
       </c>
       <c r="E7" t="n">
-        <v>110639.62</v>
+        <v>104719.64</v>
       </c>
       <c r="F7" t="n">
-        <v>-3832.82</v>
+        <v>-5919.98</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0335</v>
+        <v>-0.0535</v>
       </c>
       <c r="H7" t="n">
-        <v>9896.620000000001</v>
+        <v>11802.85</v>
       </c>
       <c r="I7" t="n">
-        <v>98295.09</v>
+        <v>96480.06</v>
       </c>
       <c r="J7" t="n">
-        <v>107716.04</v>
+        <v>100400.31</v>
       </c>
       <c r="K7" t="n">
-        <v>110230.99</v>
+        <v>105691.31</v>
       </c>
       <c r="L7" t="n">
-        <v>112745.95</v>
+        <v>110982.31</v>
       </c>
       <c r="M7" t="n">
-        <v>118713.9</v>
+        <v>115587.94</v>
       </c>
       <c r="N7" t="n">
-        <v>124681.85</v>
+        <v>120193.56</v>
       </c>
       <c r="O7" t="n">
-        <v>123743.81</v>
+        <v>126169.94</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1114,7 +1116,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1128,79 +1130,79 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>110646.91</v>
+        <v>104723.77</v>
       </c>
       <c r="C8" t="n">
-        <v>110764.91</v>
+        <v>107428.26</v>
       </c>
       <c r="D8" t="n">
-        <v>98962.06</v>
+        <v>92971.16</v>
       </c>
       <c r="E8" t="n">
-        <v>104719.64</v>
+        <v>94177.08</v>
       </c>
       <c r="F8" t="n">
-        <v>-5919.98</v>
+        <v>-10542.56</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0535</v>
+        <v>-0.1007</v>
       </c>
       <c r="H8" t="n">
-        <v>11802.85</v>
+        <v>14457.09</v>
       </c>
       <c r="I8" t="n">
-        <v>96480.06</v>
+        <v>87159.21000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>100400.31</v>
+        <v>92844.87</v>
       </c>
       <c r="K8" t="n">
-        <v>105691.31</v>
+        <v>98818.21000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>110982.31</v>
+        <v>104791.56</v>
       </c>
       <c r="M8" t="n">
-        <v>115587.94</v>
+        <v>110621.07</v>
       </c>
       <c r="N8" t="n">
-        <v>120193.56</v>
+        <v>116450.57</v>
       </c>
       <c r="O8" t="n">
-        <v>126169.94</v>
+        <v>122567.77</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1214,7 +1216,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1228,65 +1230,63 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104723.77</v>
+        <v>94180.88</v>
       </c>
       <c r="C9" t="n">
-        <v>107428.26</v>
+        <v>95928.37</v>
       </c>
       <c r="D9" t="n">
-        <v>92971.16</v>
+        <v>80659.81</v>
       </c>
       <c r="E9" t="n">
-        <v>94177.08</v>
+        <v>86805.00999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-10542.56</v>
+        <v>-7372.07</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.1007</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>14457.09</v>
+        <v>15268.55</v>
       </c>
       <c r="I9" t="n">
-        <v>87159.21000000001</v>
+        <v>78514.07000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>92844.87</v>
+        <v>76708.67</v>
       </c>
       <c r="K9" t="n">
-        <v>98818.21000000001</v>
+        <v>86948.53</v>
       </c>
       <c r="L9" t="n">
-        <v>104791.56</v>
+        <v>97188.39</v>
       </c>
       <c r="M9" t="n">
-        <v>110621.07</v>
+        <v>101405.62</v>
       </c>
       <c r="N9" t="n">
-        <v>116450.57</v>
+        <v>105622.86</v>
       </c>
       <c r="O9" t="n">
-        <v>122567.77</v>
+        <v>121885.35</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1300,7 +1300,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1314,50 +1314,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94180.88</v>
+        <v>86798.77</v>
       </c>
       <c r="C10" t="n">
-        <v>95928.37</v>
+        <v>92969.09</v>
       </c>
       <c r="D10" t="n">
-        <v>80659.81</v>
+        <v>85272.2</v>
       </c>
       <c r="E10" t="n">
-        <v>86805.00999999999</v>
+        <v>90394.31</v>
       </c>
       <c r="F10" t="n">
-        <v>-7372.07</v>
+        <v>3589.3</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.0413</v>
       </c>
       <c r="H10" t="n">
-        <v>15268.55</v>
+        <v>7696.89</v>
       </c>
       <c r="I10" t="n">
-        <v>78514.07000000001</v>
+        <v>65391.26</v>
       </c>
       <c r="J10" t="n">
-        <v>76708.67</v>
+        <v>70791.91</v>
       </c>
       <c r="K10" t="n">
-        <v>86948.53</v>
+        <v>79170.73</v>
       </c>
       <c r="L10" t="n">
-        <v>97188.39</v>
+        <v>87549.55</v>
       </c>
       <c r="M10" t="n">
-        <v>101405.62</v>
+        <v>94439.28999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>105622.86</v>
+        <v>101329.02</v>
       </c>
       <c r="O10" t="n">
-        <v>121885.35</v>
+        <v>111196.92</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1365,14 +1365,12 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1384,64 +1382,64 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>86798.77</v>
+        <v>90389.11</v>
       </c>
       <c r="C11" t="n">
-        <v>92969.09</v>
+        <v>94060.77</v>
       </c>
       <c r="D11" t="n">
-        <v>85272.2</v>
+        <v>83862.25</v>
       </c>
       <c r="E11" t="n">
-        <v>90394.31</v>
+        <v>90405.64</v>
       </c>
       <c r="F11" t="n">
-        <v>3589.3</v>
+        <v>11.33</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0413</v>
+        <v>0.0001</v>
       </c>
       <c r="H11" t="n">
-        <v>7696.89</v>
+        <v>10198.52</v>
       </c>
       <c r="I11" t="n">
-        <v>65391.26</v>
+        <v>77575.3</v>
       </c>
       <c r="J11" t="n">
-        <v>70791.91</v>
+        <v>83334.25999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>79170.73</v>
+        <v>86545.87</v>
       </c>
       <c r="L11" t="n">
-        <v>87549.55</v>
+        <v>89757.48</v>
       </c>
       <c r="M11" t="n">
-        <v>94439.28999999999</v>
+        <v>94242.75999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>101329.02</v>
+        <v>98728.03999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>111196.92</v>
+        <v>100665.98</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1449,10 +1447,12 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1466,7 +1466,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1480,50 +1480,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>90389.11</v>
+        <v>90424.59</v>
       </c>
       <c r="C12" t="n">
-        <v>94060.77</v>
+        <v>94601.57000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>83862.25</v>
+        <v>87634.94</v>
       </c>
       <c r="E12" t="n">
-        <v>90405.64</v>
+        <v>88175.17999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>11.33</v>
+        <v>-2230.46</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0247</v>
       </c>
       <c r="H12" t="n">
-        <v>10198.52</v>
+        <v>6966.63</v>
       </c>
       <c r="I12" t="n">
-        <v>77575.3</v>
+        <v>73663.73</v>
       </c>
       <c r="J12" t="n">
-        <v>83334.25999999999</v>
+        <v>80929.17999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>86545.87</v>
+        <v>85306.38</v>
       </c>
       <c r="L12" t="n">
-        <v>89757.48</v>
+        <v>89683.58</v>
       </c>
       <c r="M12" t="n">
-        <v>94242.75999999999</v>
+        <v>95504.89999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>98728.03999999999</v>
+        <v>101326.23</v>
       </c>
       <c r="O12" t="n">
-        <v>100665.98</v>
+        <v>104259.3</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1531,14 +1531,12 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1550,7 +1548,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1564,50 +1562,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>90424.59</v>
+        <v>88171.08</v>
       </c>
       <c r="C13" t="n">
-        <v>94601.57000000001</v>
+        <v>90264.57000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>87634.94</v>
+        <v>84436.31</v>
       </c>
       <c r="E13" t="n">
-        <v>88175.17999999999</v>
+        <v>88621.75</v>
       </c>
       <c r="F13" t="n">
-        <v>-2230.46</v>
+        <v>446.57</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0051</v>
       </c>
       <c r="H13" t="n">
-        <v>6966.63</v>
+        <v>5828.26</v>
       </c>
       <c r="I13" t="n">
-        <v>73663.73</v>
+        <v>80668.3</v>
       </c>
       <c r="J13" t="n">
-        <v>80929.17999999999</v>
+        <v>79737.00999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>85306.38</v>
+        <v>84691.86</v>
       </c>
       <c r="L13" t="n">
-        <v>89683.58</v>
+        <v>89646.72</v>
       </c>
       <c r="M13" t="n">
-        <v>95504.89999999999</v>
+        <v>91658.5</v>
       </c>
       <c r="N13" t="n">
-        <v>101326.23</v>
+        <v>93670.28</v>
       </c>
       <c r="O13" t="n">
-        <v>104259.3</v>
+        <v>101568.2</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1615,10 +1613,12 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1632,64 +1632,64 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>88171.08</v>
+        <v>88621.39999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>90264.57000000001</v>
+        <v>90501.92999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>84436.31</v>
+        <v>86411.8</v>
       </c>
       <c r="E14" t="n">
-        <v>88621.75</v>
+        <v>87835.84</v>
       </c>
       <c r="F14" t="n">
-        <v>446.57</v>
+        <v>-785.91</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0051</v>
+        <v>-0.0089</v>
       </c>
       <c r="H14" t="n">
-        <v>5828.26</v>
+        <v>4090.13</v>
       </c>
       <c r="I14" t="n">
-        <v>80668.3</v>
+        <v>78608.05</v>
       </c>
       <c r="J14" t="n">
-        <v>79737.00999999999</v>
+        <v>83429.14999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>84691.86</v>
+        <v>85707.62</v>
       </c>
       <c r="L14" t="n">
-        <v>89646.72</v>
+        <v>87986.10000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>91658.5</v>
+        <v>91535.88</v>
       </c>
       <c r="N14" t="n">
-        <v>93670.28</v>
+        <v>95085.66</v>
       </c>
       <c r="O14" t="n">
-        <v>101568.2</v>
+        <v>96092.83</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1697,12 +1697,10 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1716,64 +1714,64 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>88621.39999999999</v>
+        <v>87835.78999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>90501.92999999999</v>
+        <v>91712.59</v>
       </c>
       <c r="D15" t="n">
-        <v>86411.8</v>
+        <v>86717.91</v>
       </c>
       <c r="E15" t="n">
-        <v>87835.84</v>
+        <v>91413.49000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-785.91</v>
+        <v>3577.66</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0089</v>
+        <v>0.0407</v>
       </c>
       <c r="H15" t="n">
-        <v>4090.13</v>
+        <v>4994.67</v>
       </c>
       <c r="I15" t="n">
-        <v>78608.05</v>
+        <v>82321.66</v>
       </c>
       <c r="J15" t="n">
-        <v>83429.14999999999</v>
+        <v>83435.19</v>
       </c>
       <c r="K15" t="n">
-        <v>85707.62</v>
+        <v>85790.77</v>
       </c>
       <c r="L15" t="n">
-        <v>87986.10000000001</v>
+        <v>88146.35000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>91535.88</v>
+        <v>89880.89999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>95085.66</v>
+        <v>91615.46000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>96092.83</v>
+        <v>94592.06</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1786,76 +1784,76 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>87835.78999999999</v>
+        <v>91414.62</v>
       </c>
       <c r="C16" t="n">
-        <v>91712.59</v>
+        <v>94762.07000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>86717.91</v>
+        <v>89233.88</v>
       </c>
       <c r="E16" t="n">
-        <v>91413.49000000001</v>
+        <v>90827.46000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>3577.66</v>
+        <v>-586.03</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0407</v>
+        <v>-0.0064</v>
       </c>
       <c r="H16" t="n">
-        <v>4994.67</v>
+        <v>5528.2</v>
       </c>
       <c r="I16" t="n">
-        <v>82321.66</v>
+        <v>81723.24000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>83435.19</v>
+        <v>87517.94</v>
       </c>
       <c r="K16" t="n">
-        <v>85790.77</v>
+        <v>88916.16</v>
       </c>
       <c r="L16" t="n">
-        <v>88146.35000000001</v>
+        <v>90314.37</v>
       </c>
       <c r="M16" t="n">
-        <v>89880.89999999999</v>
+        <v>93910.83</v>
       </c>
       <c r="N16" t="n">
-        <v>91615.46000000001</v>
+        <v>97507.28999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>94592.06</v>
+        <v>96707.25999999999</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1866,9 +1864,9 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
@@ -1876,68 +1874,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>91414.62</v>
+        <v>90825.86</v>
       </c>
       <c r="C17" t="n">
-        <v>94762.07000000001</v>
+        <v>97860.60000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>89233.88</v>
+        <v>90055.02</v>
       </c>
       <c r="E17" t="n">
-        <v>90827.46000000001</v>
+        <v>93634.42999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-586.03</v>
+        <v>2806.97</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0064</v>
+        <v>0.0309</v>
       </c>
       <c r="H17" t="n">
-        <v>5528.2</v>
+        <v>7805.58</v>
       </c>
       <c r="I17" t="n">
-        <v>81723.24000000001</v>
+        <v>83705.67999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>87517.94</v>
+        <v>84714.00999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>88916.16</v>
+        <v>88063.36</v>
       </c>
       <c r="L17" t="n">
-        <v>90314.37</v>
+        <v>91412.72</v>
       </c>
       <c r="M17" t="n">
-        <v>93910.83</v>
+        <v>93591.56</v>
       </c>
       <c r="N17" t="n">
-        <v>97507.28999999999</v>
+        <v>95770.39999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>96707.25999999999</v>
+        <v>100290.27</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1948,165 +1948,169 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>90825.86</v>
+        <v>93655.67</v>
       </c>
       <c r="C18" t="n">
-        <v>97860.60000000001</v>
+        <v>93660.83</v>
       </c>
       <c r="D18" t="n">
-        <v>90055.02</v>
+        <v>86003.71000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>93634.42999999999</v>
+        <v>86572.22</v>
       </c>
       <c r="F18" t="n">
-        <v>2806.97</v>
+        <v>-7062.21</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0309</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>7805.58</v>
+        <v>7657.12</v>
       </c>
       <c r="I18" t="n">
-        <v>83705.67999999999</v>
+        <v>82249.45</v>
       </c>
       <c r="J18" t="n">
-        <v>84714.00999999999</v>
+        <v>85667.16</v>
       </c>
       <c r="K18" t="n">
-        <v>88063.36</v>
+        <v>89731.64</v>
       </c>
       <c r="L18" t="n">
-        <v>91412.72</v>
+        <v>93796.12</v>
       </c>
       <c r="M18" t="n">
-        <v>93591.56</v>
+        <v>97537.22</v>
       </c>
       <c r="N18" t="n">
-        <v>95770.39999999999</v>
+        <v>101278.32</v>
       </c>
       <c r="O18" t="n">
-        <v>100290.27</v>
+        <v>105666.18</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>93655.67</v>
+        <v>86566.52</v>
       </c>
       <c r="C19" t="n">
-        <v>93660.83</v>
+        <v>90439.28999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>86003.71000000001</v>
+        <v>75698.89999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>86572.22</v>
+        <v>76974.45</v>
       </c>
       <c r="F19" t="n">
-        <v>-7062.21</v>
+        <v>-9597.77</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.1109</v>
       </c>
       <c r="H19" t="n">
-        <v>7657.12</v>
+        <v>14740.39</v>
       </c>
       <c r="I19" t="n">
-        <v>82249.45</v>
+        <v>78346.59</v>
       </c>
       <c r="J19" t="n">
-        <v>85667.16</v>
+        <v>77285.08</v>
       </c>
       <c r="K19" t="n">
-        <v>89731.64</v>
+        <v>82743.66</v>
       </c>
       <c r="L19" t="n">
-        <v>93796.12</v>
+        <v>88202.24000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>97537.22</v>
+        <v>90400.78</v>
       </c>
       <c r="N19" t="n">
-        <v>101278.32</v>
+        <v>92599.31</v>
       </c>
       <c r="O19" t="n">
-        <v>105666.18</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
+        <v>101317.95</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
@@ -2118,13 +2122,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2134,87 +2140,79 @@
       </c>
       <c r="W19" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>86566.52</v>
+        <v>76968.88</v>
       </c>
       <c r="C20" t="n">
-        <v>90439.28999999999</v>
+        <v>79258.61</v>
       </c>
       <c r="D20" t="n">
-        <v>75698.89999999999</v>
+        <v>60074.2</v>
       </c>
       <c r="E20" t="n">
-        <v>76974.45</v>
+        <v>70264.73</v>
       </c>
       <c r="F20" t="n">
-        <v>-9597.77</v>
+        <v>-6709.72</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.1109</v>
+        <v>-0.0872</v>
       </c>
       <c r="H20" t="n">
-        <v>14740.39</v>
+        <v>19184.41</v>
       </c>
       <c r="I20" t="n">
-        <v>78346.59</v>
+        <v>60958.51</v>
       </c>
       <c r="J20" t="n">
-        <v>77285.08</v>
+        <v>59186.73</v>
       </c>
       <c r="K20" t="n">
-        <v>82743.66</v>
+        <v>69604.25</v>
       </c>
       <c r="L20" t="n">
-        <v>88202.24000000001</v>
+        <v>80021.77</v>
       </c>
       <c r="M20" t="n">
-        <v>90400.78</v>
+        <v>84344.64</v>
       </c>
       <c r="N20" t="n">
-        <v>92599.31</v>
+        <v>88667.50999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>101317.95</v>
+        <v>105179.68</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2222,7 +2220,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2232,67 +2230,63 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>76968.88</v>
+        <v>70243.33</v>
       </c>
       <c r="C21" t="n">
-        <v>79258.61</v>
+        <v>71369.97</v>
       </c>
       <c r="D21" t="n">
-        <v>60074.2</v>
+        <v>65092.11</v>
       </c>
       <c r="E21" t="n">
-        <v>70264.73</v>
+        <v>68788.19</v>
       </c>
       <c r="F21" t="n">
-        <v>-6709.72</v>
+        <v>-1476.54</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0872</v>
+        <v>-0.021</v>
       </c>
       <c r="H21" t="n">
-        <v>19184.41</v>
+        <v>6277.86</v>
       </c>
       <c r="I21" t="n">
-        <v>60958.51</v>
+        <v>40889.8</v>
       </c>
       <c r="J21" t="n">
-        <v>59186.73</v>
+        <v>51379.48</v>
       </c>
       <c r="K21" t="n">
-        <v>69604.25</v>
+        <v>60672.52</v>
       </c>
       <c r="L21" t="n">
-        <v>80021.77</v>
+        <v>69965.57000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>84344.64</v>
+        <v>79856.92999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>88667.50999999999</v>
+        <v>89748.28999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>105179.68</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>98443.02</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
       </c>
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2304,60 +2298,64 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>70243.33</v>
+        <v>68782.39999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>71369.97</v>
+        <v>70067.23</v>
       </c>
       <c r="D22" t="n">
-        <v>65092.11</v>
+        <v>65637.42999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>68788.19</v>
+        <v>67659.39</v>
       </c>
       <c r="F22" t="n">
-        <v>-1476.54</v>
+        <v>-1128.8</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.021</v>
+        <v>-0.0164</v>
       </c>
       <c r="H22" t="n">
-        <v>6277.86</v>
+        <v>4429.8</v>
       </c>
       <c r="I22" t="n">
-        <v>40889.8</v>
+        <v>58814.25</v>
       </c>
       <c r="J22" t="n">
-        <v>51379.48</v>
+        <v>62788.9</v>
       </c>
       <c r="K22" t="n">
-        <v>60672.52</v>
+        <v>65649.25999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>69965.57000000001</v>
+        <v>68509.61</v>
       </c>
       <c r="M22" t="n">
-        <v>79856.92999999999</v>
+        <v>71927.12</v>
       </c>
       <c r="N22" t="n">
-        <v>89748.28999999999</v>
+        <v>75344.62</v>
       </c>
       <c r="O22" t="n">
-        <v>98443.02</v>
+        <v>77647.83</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2365,10 +2363,12 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2382,7 +2382,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2396,218 +2396,220 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>68782.39999999999</v>
+        <v>67668.42999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>70067.23</v>
+        <v>69953.53</v>
       </c>
       <c r="D23" t="n">
-        <v>65637.42999999999</v>
+        <v>62553.19</v>
       </c>
       <c r="E23" t="n">
-        <v>67659.39</v>
+        <v>65738.10000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-1128.8</v>
+        <v>-1921.29</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0164</v>
+        <v>-0.0284</v>
       </c>
       <c r="H23" t="n">
-        <v>4429.8</v>
+        <v>7400.34</v>
       </c>
       <c r="I23" t="n">
-        <v>58814.25</v>
+        <v>61207.62</v>
       </c>
       <c r="J23" t="n">
-        <v>62788.9</v>
+        <v>63133.12</v>
       </c>
       <c r="K23" t="n">
-        <v>65649.25999999999</v>
+        <v>65444.49</v>
       </c>
       <c r="L23" t="n">
-        <v>68509.61</v>
+        <v>67755.86</v>
       </c>
       <c r="M23" t="n">
-        <v>71927.12</v>
+        <v>69874.28999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>75344.62</v>
+        <v>71992.72</v>
       </c>
       <c r="O23" t="n">
-        <v>77647.83</v>
+        <v>74497.03999999999</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>67668.42999999999</v>
+        <v>65734.08</v>
       </c>
       <c r="C24" t="n">
-        <v>69953.53</v>
+        <v>74051.8</v>
       </c>
       <c r="D24" t="n">
-        <v>62553.19</v>
+        <v>65303.14</v>
       </c>
       <c r="E24" t="n">
-        <v>65738.10000000001</v>
+        <v>65969.78</v>
       </c>
       <c r="F24" t="n">
-        <v>-1921.29</v>
+        <v>231.68</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0284</v>
+        <v>0.0035</v>
       </c>
       <c r="H24" t="n">
-        <v>7400.34</v>
+        <v>8748.67</v>
       </c>
       <c r="I24" t="n">
-        <v>61207.62</v>
+        <v>55152.84</v>
       </c>
       <c r="J24" t="n">
-        <v>63133.12</v>
+        <v>58080.13</v>
       </c>
       <c r="K24" t="n">
-        <v>65444.49</v>
+        <v>62037.93</v>
       </c>
       <c r="L24" t="n">
-        <v>67755.86</v>
+        <v>65995.73</v>
       </c>
       <c r="M24" t="n">
-        <v>69874.28999999999</v>
+        <v>69438.27</v>
       </c>
       <c r="N24" t="n">
-        <v>71992.72</v>
+        <v>72880.82000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>74497.03999999999</v>
+        <v>77353.88</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65734.08</v>
+        <v>65969.59</v>
       </c>
       <c r="C25" t="n">
-        <v>74051.8</v>
+        <v>73927.33</v>
       </c>
       <c r="D25" t="n">
-        <v>65303.14</v>
+        <v>65858.00999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>65969.78</v>
+        <v>72789.91</v>
       </c>
       <c r="F25" t="n">
-        <v>231.68</v>
+        <v>6820.13</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.1034</v>
       </c>
       <c r="H25" t="n">
-        <v>8748.67</v>
+        <v>8069.32</v>
       </c>
       <c r="I25" t="n">
-        <v>55152.84</v>
+        <v>56554.47</v>
       </c>
       <c r="J25" t="n">
-        <v>58080.13</v>
+        <v>55367.27</v>
       </c>
       <c r="K25" t="n">
-        <v>62037.93</v>
+        <v>61595.45</v>
       </c>
       <c r="L25" t="n">
-        <v>65995.73</v>
+        <v>67823.63</v>
       </c>
       <c r="M25" t="n">
-        <v>69438.27</v>
+        <v>70344.12</v>
       </c>
       <c r="N25" t="n">
-        <v>72880.82000000001</v>
+        <v>72864.60000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>77353.88</v>
+        <v>82800.47</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2620,7 +2622,7 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -2630,70 +2632,70 @@
       </c>
       <c r="U25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>65969.59</v>
+        <v>72798.17</v>
       </c>
       <c r="C26" t="n">
-        <v>73927.33</v>
+        <v>75988.39999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>65858.00999999999</v>
+        <v>67372.88</v>
       </c>
       <c r="E26" t="n">
-        <v>72789.91</v>
+        <v>67845.21000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>6820.13</v>
+        <v>-4944.7</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.1034</v>
+        <v>-0.0679</v>
       </c>
       <c r="H26" t="n">
-        <v>8069.32</v>
+        <v>8615.52</v>
       </c>
       <c r="I26" t="n">
-        <v>56554.47</v>
+        <v>57788.69</v>
       </c>
       <c r="J26" t="n">
-        <v>55367.27</v>
+        <v>66169.22</v>
       </c>
       <c r="K26" t="n">
-        <v>61595.45</v>
+        <v>68755.25</v>
       </c>
       <c r="L26" t="n">
-        <v>67823.63</v>
+        <v>71341.28999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>70344.12</v>
+        <v>76824.57000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>72864.60000000001</v>
+        <v>82307.86</v>
       </c>
       <c r="O26" t="n">
-        <v>82800.47</v>
+        <v>81996.64999999999</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2701,28 +2703,26 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2736,50 +2736,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>72798.17</v>
+        <v>67843</v>
       </c>
       <c r="C27" t="n">
-        <v>75988.39999999999</v>
+        <v>71985.74000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>67372.88</v>
+        <v>64971.71</v>
       </c>
       <c r="E27" t="n">
-        <v>67845.21000000001</v>
+        <v>65954.92</v>
       </c>
       <c r="F27" t="n">
-        <v>-4944.7</v>
+        <v>-1890.29</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0679</v>
+        <v>-0.0279</v>
       </c>
       <c r="H27" t="n">
-        <v>8615.52</v>
+        <v>7014.04</v>
       </c>
       <c r="I27" t="n">
-        <v>57788.69</v>
+        <v>58757.35</v>
       </c>
       <c r="J27" t="n">
-        <v>66169.22</v>
+        <v>57311.97</v>
       </c>
       <c r="K27" t="n">
-        <v>68755.25</v>
+        <v>63537.45</v>
       </c>
       <c r="L27" t="n">
-        <v>71341.28999999999</v>
+        <v>69762.92</v>
       </c>
       <c r="M27" t="n">
-        <v>76824.57000000001</v>
+        <v>72152.97</v>
       </c>
       <c r="N27" t="n">
-        <v>82307.86</v>
+        <v>74543.02</v>
       </c>
       <c r="O27" t="n">
-        <v>81996.64999999999</v>
+        <v>84603.92</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2792,7 +2792,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2806,64 +2806,60 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>67843</v>
+        <v>65958.35000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>71985.74000000001</v>
+        <v>69230.36</v>
       </c>
       <c r="D28" t="n">
-        <v>64971.71</v>
+        <v>65725.25999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>65954.92</v>
+        <v>68981.89999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>-1890.29</v>
+        <v>3026.98</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0279</v>
+        <v>0.0459</v>
       </c>
       <c r="H28" t="n">
-        <v>7014.04</v>
+        <v>3505.1</v>
       </c>
       <c r="I28" t="n">
-        <v>58757.35</v>
+        <v>57957.67</v>
       </c>
       <c r="J28" t="n">
-        <v>57311.97</v>
+        <v>57678.99</v>
       </c>
       <c r="K28" t="n">
-        <v>63537.45</v>
+        <v>62447.9</v>
       </c>
       <c r="L28" t="n">
-        <v>69762.92</v>
+        <v>67216.82000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>72152.97</v>
+        <v>69461.94</v>
       </c>
       <c r="N28" t="n">
-        <v>74543.02</v>
+        <v>71707.06</v>
       </c>
       <c r="O28" t="n">
-        <v>84603.92</v>
+        <v>78999.78</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2871,79 +2867,83 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>65958.35000000001</v>
+        <v>68982.91</v>
       </c>
       <c r="C29" t="n">
-        <v>69230.36</v>
+        <v>73784.23</v>
       </c>
       <c r="D29" t="n">
-        <v>65725.25999999999</v>
+        <v>67740.50999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>68981.89999999999</v>
+        <v>70753.41</v>
       </c>
       <c r="F29" t="n">
-        <v>3026.98</v>
+        <v>1771.51</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0459</v>
+        <v>0.0257</v>
       </c>
       <c r="H29" t="n">
-        <v>3505.1</v>
+        <v>6043.73</v>
       </c>
       <c r="I29" t="n">
-        <v>57957.67</v>
+        <v>62220.16</v>
       </c>
       <c r="J29" t="n">
-        <v>57678.99</v>
+        <v>66228.84</v>
       </c>
       <c r="K29" t="n">
-        <v>62447.9</v>
+        <v>67229.35000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>67216.82000000001</v>
+        <v>68229.85000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>69461.94</v>
+        <v>70734.45</v>
       </c>
       <c r="N29" t="n">
-        <v>71707.06</v>
+        <v>73239.03999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>78999.78</v>
+        <v>72735.46000000001</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2954,7 +2954,7 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2964,70 +2964,74 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>68982.91</v>
+        <v>70757.62</v>
       </c>
       <c r="C30" t="n">
-        <v>73784.23</v>
+        <v>78320.67999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>67740.50999999999</v>
+        <v>70588.52</v>
       </c>
       <c r="E30" t="n">
-        <v>70753.41</v>
+        <v>73856.35000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>1771.51</v>
+        <v>3102.95</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0257</v>
+        <v>0.0439</v>
       </c>
       <c r="H30" t="n">
-        <v>6043.73</v>
+        <v>7732.16</v>
       </c>
       <c r="I30" t="n">
-        <v>62220.16</v>
+        <v>61696.78</v>
       </c>
       <c r="J30" t="n">
-        <v>66228.84</v>
+        <v>64705.2</v>
       </c>
       <c r="K30" t="n">
-        <v>67229.35000000001</v>
+        <v>67731.53999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>68229.85000000001</v>
+        <v>70757.89</v>
       </c>
       <c r="M30" t="n">
-        <v>70734.45</v>
+        <v>73775.27</v>
       </c>
       <c r="N30" t="n">
-        <v>73239.03999999999</v>
+        <v>76792.64999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>72735.46000000001</v>
+        <v>79827.96000000001</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3038,7 +3042,7 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3053,12 +3057,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="V30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3072,50 +3074,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>70757.62</v>
+        <v>73854.25</v>
       </c>
       <c r="C31" t="n">
-        <v>78320.67999999999</v>
+        <v>79468</v>
       </c>
       <c r="D31" t="n">
-        <v>70588.52</v>
+        <v>73775.57000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>73856.35000000001</v>
+        <v>78657.53999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>3102.95</v>
+        <v>4801.19</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0439</v>
+        <v>0.065</v>
       </c>
       <c r="H31" t="n">
-        <v>7732.16</v>
+        <v>5692.43</v>
       </c>
       <c r="I31" t="n">
-        <v>61696.78</v>
+        <v>62856.37</v>
       </c>
       <c r="J31" t="n">
-        <v>64705.2</v>
+        <v>65825.07000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>67731.53999999999</v>
+        <v>69990.27</v>
       </c>
       <c r="L31" t="n">
-        <v>70757.89</v>
+        <v>74155.48</v>
       </c>
       <c r="M31" t="n">
-        <v>73775.27</v>
+        <v>77722.42999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>76792.64999999999</v>
+        <v>81289.38</v>
       </c>
       <c r="O31" t="n">
-        <v>79827.96000000001</v>
+        <v>86052.84</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3126,7 +3128,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3136,15 +3138,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3158,50 +3158,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>73854.25</v>
+        <v>78661.02</v>
       </c>
       <c r="C32" t="n">
-        <v>79468</v>
+        <v>79488.17</v>
       </c>
       <c r="D32" t="n">
-        <v>73775.57000000001</v>
+        <v>74958.57000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>78657.53999999999</v>
+        <v>78538.23</v>
       </c>
       <c r="F32" t="n">
-        <v>4801.19</v>
+        <v>-119.31</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.065</v>
+        <v>-0.0015</v>
       </c>
       <c r="H32" t="n">
-        <v>5692.43</v>
+        <v>4529.6</v>
       </c>
       <c r="I32" t="n">
-        <v>62856.37</v>
+        <v>68083.14</v>
       </c>
       <c r="J32" t="n">
-        <v>65825.07000000001</v>
+        <v>73982.99000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>69990.27</v>
+        <v>75811.32000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>74155.48</v>
+        <v>77639.66</v>
       </c>
       <c r="M32" t="n">
-        <v>77722.42999999999</v>
+        <v>81503.75</v>
       </c>
       <c r="N32" t="n">
-        <v>81289.38</v>
+        <v>85367.85000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>86052.84</v>
+        <v>85160.42999999999</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3209,18 +3209,18 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3228,64 +3228,64 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>78661.02</v>
+        <v>78540.28999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>79488.17</v>
+        <v>82792.21000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>74958.57000000001</v>
+        <v>78217.96000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>78538.23</v>
+        <v>82138.92999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>-119.31</v>
+        <v>3600.7</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0458</v>
       </c>
       <c r="H33" t="n">
-        <v>4529.6</v>
+        <v>4574.25</v>
       </c>
       <c r="I33" t="n">
-        <v>68083.14</v>
+        <v>70428.97</v>
       </c>
       <c r="J33" t="n">
-        <v>73982.99000000001</v>
+        <v>74666.05</v>
       </c>
       <c r="K33" t="n">
-        <v>75811.32000000001</v>
+        <v>76273.42999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>77639.66</v>
+        <v>77880.8</v>
       </c>
       <c r="M33" t="n">
-        <v>81503.75</v>
+        <v>80803.03</v>
       </c>
       <c r="N33" t="n">
-        <v>85367.85000000001</v>
+        <v>83725.25999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>85160.42999999999</v>
+        <v>84017.77</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3293,18 +3293,18 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3312,83 +3312,85 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>78540.28999999999</v>
+        <v>82139.05</v>
       </c>
       <c r="C34" t="n">
-        <v>82792.21000000001</v>
+        <v>82326.23</v>
       </c>
       <c r="D34" t="n">
-        <v>78217.96000000001</v>
+        <v>76783.41</v>
       </c>
       <c r="E34" t="n">
-        <v>82138.92999999999</v>
+        <v>77429.35000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>3600.7</v>
+        <v>-4709.58</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0458</v>
+        <v>-0.0573</v>
       </c>
       <c r="H34" t="n">
-        <v>4574.25</v>
+        <v>5542.82</v>
       </c>
       <c r="I34" t="n">
-        <v>70428.97</v>
+        <v>73643.71000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>74666.05</v>
+        <v>78381.60000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>76273.42999999999</v>
+        <v>79851.8</v>
       </c>
       <c r="L34" t="n">
-        <v>77880.8</v>
+        <v>81322.00999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>80803.03</v>
+        <v>84426.05</v>
       </c>
       <c r="N34" t="n">
-        <v>83725.25999999999</v>
+        <v>87530.10000000001</v>
       </c>
       <c r="O34" t="n">
-        <v>84017.77</v>
+        <v>87366.46000000001</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3396,81 +3398,75 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>82139.05</v>
+        <v>77426.34</v>
       </c>
       <c r="C35" t="n">
-        <v>82326.23</v>
+        <v>78100.56</v>
       </c>
       <c r="D35" t="n">
-        <v>76783.41</v>
+        <v>74255.23</v>
       </c>
       <c r="E35" t="n">
-        <v>77429.35000000001</v>
+        <v>76981.12</v>
       </c>
       <c r="F35" t="n">
-        <v>-4709.58</v>
+        <v>-448.23</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0573</v>
+        <v>-0.0058</v>
       </c>
       <c r="H35" t="n">
-        <v>5542.82</v>
+        <v>3845.33</v>
       </c>
       <c r="I35" t="n">
-        <v>73643.71000000001</v>
+        <v>71240.59</v>
       </c>
       <c r="J35" t="n">
-        <v>78381.60000000001</v>
+        <v>70823.78999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>79851.8</v>
+        <v>74657.94</v>
       </c>
       <c r="L35" t="n">
-        <v>81322.00999999999</v>
+        <v>78492.09</v>
       </c>
       <c r="M35" t="n">
-        <v>84426.05</v>
+        <v>80200.75999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>87530.10000000001</v>
+        <v>81909.44</v>
       </c>
       <c r="O35" t="n">
-        <v>87366.46000000001</v>
+        <v>87869.05</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q35" s="6" t="n">
+        <v/>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3482,7 +3478,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3492,65 +3488,67 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>77426.34</v>
+        <v>76981.12</v>
       </c>
       <c r="C36" t="n">
-        <v>78100.56</v>
+        <v>77990.87</v>
       </c>
       <c r="D36" t="n">
-        <v>74255.23</v>
+        <v>72435.62</v>
       </c>
       <c r="E36" t="n">
-        <v>76981.12</v>
+        <v>73579.69</v>
       </c>
       <c r="F36" t="n">
-        <v>-448.23</v>
+        <v>-3401.44</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0442</v>
       </c>
       <c r="H36" t="n">
-        <v>3845.33</v>
+        <v>5555.24</v>
       </c>
       <c r="I36" t="n">
-        <v>71240.59</v>
+        <v>70409.91</v>
       </c>
       <c r="J36" t="n">
-        <v>70823.78999999999</v>
+        <v>73537.41</v>
       </c>
       <c r="K36" t="n">
-        <v>74657.94</v>
+        <v>75058.46000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>78492.09</v>
+        <v>76579.50999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>80200.75999999999</v>
+        <v>78903.78999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>81909.44</v>
+        <v>81228.07000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>87869.05</v>
+        <v>81945.89</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3562,7 +3560,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3572,57 +3570,59 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>76981.12</v>
+        <v>73580.21000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>77990.87</v>
+        <v>73969.57000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>72435.62</v>
+        <v>59108.92</v>
       </c>
       <c r="E37" t="n">
-        <v>73579.69</v>
+        <v>63239.52</v>
       </c>
       <c r="F37" t="n">
-        <v>-3401.44</v>
+        <v>-10340.17</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0442</v>
+        <v>-0.1405</v>
       </c>
       <c r="H37" t="n">
-        <v>5555.24</v>
+        <v>14860.65</v>
       </c>
       <c r="I37" t="n">
-        <v>70409.91</v>
+        <v>66880.38</v>
       </c>
       <c r="J37" t="n">
-        <v>73537.41</v>
+        <v>67207.67</v>
       </c>
       <c r="K37" t="n">
-        <v>75058.46000000001</v>
+        <v>70802.07000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>76579.50999999999</v>
+        <v>74396.47</v>
       </c>
       <c r="M37" t="n">
-        <v>78903.78999999999</v>
+        <v>76357.31</v>
       </c>
       <c r="N37" t="n">
-        <v>81228.07000000001</v>
+        <v>78318.14999999999</v>
       </c>
       <c r="O37" t="n">
-        <v>81945.89</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
+        <v>83546.11</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
@@ -3630,7 +3630,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3644,7 +3644,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3654,69 +3654,63 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>73580.21000000001</v>
+        <v>63244.09</v>
       </c>
       <c r="C38" t="n">
-        <v>73969.57000000001</v>
+        <v>65749.78</v>
       </c>
       <c r="D38" t="n">
-        <v>59108.92</v>
+        <v>60756.69</v>
       </c>
       <c r="E38" t="n">
-        <v>63239.52</v>
+        <v>65710.39999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>-10340.17</v>
+        <v>2470.88</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.1405</v>
+        <v>0.0391</v>
       </c>
       <c r="H38" t="n">
-        <v>14860.65</v>
+        <v>4993.09</v>
       </c>
       <c r="I38" t="n">
-        <v>66880.38</v>
+        <v>44248.27</v>
       </c>
       <c r="J38" t="n">
-        <v>67207.67</v>
+        <v>46729</v>
       </c>
       <c r="K38" t="n">
-        <v>70802.07000000001</v>
+        <v>55809.19</v>
       </c>
       <c r="L38" t="n">
-        <v>74396.47</v>
+        <v>64889.38</v>
       </c>
       <c r="M38" t="n">
-        <v>76357.31</v>
+        <v>70669.85000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>78318.14999999999</v>
+        <v>76450.31</v>
       </c>
       <c r="O38" t="n">
-        <v>83546.11</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>88830.22</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3728,60 +3722,64 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>63244.09</v>
+        <v>65711.11</v>
       </c>
       <c r="C39" t="n">
-        <v>65749.78</v>
+        <v>67248.13</v>
       </c>
       <c r="D39" t="n">
-        <v>60756.69</v>
+        <v>62201.14</v>
       </c>
       <c r="E39" t="n">
-        <v>65710.39999999999</v>
+        <v>63237.54</v>
       </c>
       <c r="F39" t="n">
-        <v>2470.88</v>
+        <v>-2472.86</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0391</v>
+        <v>-0.0376</v>
       </c>
       <c r="H39" t="n">
-        <v>4993.09</v>
+        <v>5046.99</v>
       </c>
       <c r="I39" t="n">
-        <v>44248.27</v>
+        <v>55763.59</v>
       </c>
       <c r="J39" t="n">
-        <v>46729</v>
+        <v>61945.89</v>
       </c>
       <c r="K39" t="n">
-        <v>55809.19</v>
+        <v>63213.85</v>
       </c>
       <c r="L39" t="n">
-        <v>64889.38</v>
+        <v>64481.82</v>
       </c>
       <c r="M39" t="n">
-        <v>70669.85000000001</v>
+        <v>68206.95</v>
       </c>
       <c r="N39" t="n">
-        <v>76450.31</v>
+        <v>71932.07000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>88830.22</v>
+        <v>70742.88</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3789,12 +3787,14 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3806,7 +3806,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3820,50 +3820,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>65711.11</v>
+        <v>63240.79</v>
       </c>
       <c r="C40" t="n">
-        <v>67248.13</v>
+        <v>65544</v>
       </c>
       <c r="D40" t="n">
-        <v>62201.14</v>
+        <v>58075.92</v>
       </c>
       <c r="E40" t="n">
-        <v>63237.54</v>
+        <v>59532.34</v>
       </c>
       <c r="F40" t="n">
-        <v>-2472.86</v>
+        <v>-3705.2</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0376</v>
+        <v>-0.0586</v>
       </c>
       <c r="H40" t="n">
-        <v>5046.99</v>
+        <v>7468.08</v>
       </c>
       <c r="I40" t="n">
-        <v>55763.59</v>
+        <v>57154.16</v>
       </c>
       <c r="J40" t="n">
-        <v>61945.89</v>
+        <v>57447</v>
       </c>
       <c r="K40" t="n">
-        <v>63213.85</v>
+        <v>60714.04</v>
       </c>
       <c r="L40" t="n">
-        <v>64481.82</v>
+        <v>63981.09</v>
       </c>
       <c r="M40" t="n">
-        <v>68206.95</v>
+        <v>65761.03</v>
       </c>
       <c r="N40" t="n">
-        <v>71932.07000000001</v>
+        <v>67540.98</v>
       </c>
       <c r="O40" t="n">
-        <v>70742.88</v>
+        <v>72295.12</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3876,7 +3876,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3890,64 +3890,60 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>63240.79</v>
+        <v>59522.79</v>
       </c>
       <c r="C41" t="n">
-        <v>65544</v>
+        <v>63935.85</v>
       </c>
       <c r="D41" t="n">
-        <v>58075.92</v>
+        <v>57747.77</v>
       </c>
       <c r="E41" t="n">
-        <v>59532.34</v>
+        <v>63547.88</v>
       </c>
       <c r="F41" t="n">
-        <v>-3705.2</v>
+        <v>4015.54</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0586</v>
+        <v>0.0675</v>
       </c>
       <c r="H41" t="n">
-        <v>7468.08</v>
+        <v>6188.08</v>
       </c>
       <c r="I41" t="n">
-        <v>57154.16</v>
+        <v>50607.84</v>
       </c>
       <c r="J41" t="n">
-        <v>57447</v>
+        <v>50925.45</v>
       </c>
       <c r="K41" t="n">
-        <v>60714.04</v>
+        <v>55798.3</v>
       </c>
       <c r="L41" t="n">
-        <v>63981.09</v>
+        <v>60671.15</v>
       </c>
       <c r="M41" t="n">
-        <v>65761.03</v>
+        <v>63266.38</v>
       </c>
       <c r="N41" t="n">
-        <v>67540.98</v>
+        <v>65861.61</v>
       </c>
       <c r="O41" t="n">
-        <v>72295.12</v>
+        <v>73012.08</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3955,79 +3951,83 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>59522.79</v>
+        <v>63551.02</v>
       </c>
       <c r="C42" t="n">
-        <v>63935.85</v>
+        <v>64658.97</v>
       </c>
       <c r="D42" t="n">
-        <v>57747.77</v>
+        <v>61275.83</v>
       </c>
       <c r="E42" t="n">
-        <v>63547.88</v>
+        <v>63758.22</v>
       </c>
       <c r="F42" t="n">
-        <v>4015.54</v>
+        <v>210.34</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0675</v>
+        <v>0.0033</v>
       </c>
       <c r="H42" t="n">
-        <v>6188.08</v>
+        <v>3383.14</v>
       </c>
       <c r="I42" t="n">
-        <v>50607.84</v>
+        <v>51559.68</v>
       </c>
       <c r="J42" t="n">
-        <v>50925.45</v>
+        <v>58712.84</v>
       </c>
       <c r="K42" t="n">
-        <v>55798.3</v>
+        <v>60453.84</v>
       </c>
       <c r="L42" t="n">
-        <v>60671.15</v>
+        <v>62194.84</v>
       </c>
       <c r="M42" t="n">
-        <v>63266.38</v>
+        <v>66641.92</v>
       </c>
       <c r="N42" t="n">
-        <v>65861.61</v>
+        <v>71089</v>
       </c>
       <c r="O42" t="n">
-        <v>73012.08</v>
+        <v>70123.92999999999</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4038,15 +4038,13 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4054,64 +4052,64 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>63551.02</v>
+        <v>63757.17</v>
       </c>
       <c r="C43" t="n">
-        <v>64658.97</v>
+        <v>65507.59</v>
       </c>
       <c r="D43" t="n">
-        <v>61275.83</v>
+        <v>61769</v>
       </c>
       <c r="E43" t="n">
-        <v>63758.22</v>
+        <v>64690.8</v>
       </c>
       <c r="F43" t="n">
-        <v>210.34</v>
+        <v>932.59</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0146</v>
       </c>
       <c r="H43" t="n">
-        <v>3383.14</v>
+        <v>3738.59</v>
       </c>
       <c r="I43" t="n">
-        <v>51559.68</v>
+        <v>57892.69</v>
       </c>
       <c r="J43" t="n">
-        <v>58712.84</v>
+        <v>60770.49</v>
       </c>
       <c r="K43" t="n">
-        <v>60453.84</v>
+        <v>62066.65</v>
       </c>
       <c r="L43" t="n">
-        <v>62194.84</v>
+        <v>63362.81</v>
       </c>
       <c r="M43" t="n">
-        <v>66641.92</v>
+        <v>65449.79</v>
       </c>
       <c r="N43" t="n">
-        <v>71089</v>
+        <v>67536.77</v>
       </c>
       <c r="O43" t="n">
-        <v>70123.92999999999</v>
+        <v>68042.11</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4119,16 +4117,20 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4136,7 +4138,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4150,50 +4152,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>63757.17</v>
+        <v>64684.42</v>
       </c>
       <c r="C44" t="n">
-        <v>65507.59</v>
+        <v>66910.06</v>
       </c>
       <c r="D44" t="n">
-        <v>61769</v>
+        <v>63686.04</v>
       </c>
       <c r="E44" t="n">
-        <v>64690.8</v>
+        <v>65340.3</v>
       </c>
       <c r="F44" t="n">
-        <v>932.59</v>
+        <v>649.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.01</v>
       </c>
       <c r="H44" t="n">
-        <v>3738.59</v>
+        <v>3224.03</v>
       </c>
       <c r="I44" t="n">
-        <v>57892.69</v>
+        <v>58030.41</v>
       </c>
       <c r="J44" t="n">
-        <v>60770.49</v>
+        <v>61478.46</v>
       </c>
       <c r="K44" t="n">
-        <v>62066.65</v>
+        <v>62821.51</v>
       </c>
       <c r="L44" t="n">
-        <v>63362.81</v>
+        <v>64164.55</v>
       </c>
       <c r="M44" t="n">
-        <v>65449.79</v>
+        <v>66560.10000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>67536.77</v>
+        <v>68955.64999999999</v>
       </c>
       <c r="O44" t="n">
-        <v>68042.11</v>
+        <v>69246.19</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4201,28 +4203,26 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4236,50 +4236,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>64684.42</v>
+        <v>65340.59</v>
       </c>
       <c r="C45" t="n">
-        <v>66910.06</v>
+        <v>65658.34</v>
       </c>
       <c r="D45" t="n">
-        <v>63686.04</v>
+        <v>62233.01</v>
       </c>
       <c r="E45" t="n">
-        <v>65340.3</v>
+        <v>63482</v>
       </c>
       <c r="F45" t="n">
-        <v>649.5</v>
+        <v>-1858.3</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.0284</v>
       </c>
       <c r="H45" t="n">
-        <v>3224.03</v>
+        <v>3425.32</v>
       </c>
       <c r="I45" t="n">
-        <v>58030.41</v>
+        <v>60462.01</v>
       </c>
       <c r="J45" t="n">
-        <v>61478.46</v>
+        <v>62137.4</v>
       </c>
       <c r="K45" t="n">
-        <v>62821.51</v>
+        <v>63728.29</v>
       </c>
       <c r="L45" t="n">
-        <v>64164.55</v>
+        <v>65319.17</v>
       </c>
       <c r="M45" t="n">
-        <v>66560.10000000001</v>
+        <v>66952.31</v>
       </c>
       <c r="N45" t="n">
-        <v>68955.64999999999</v>
+        <v>68585.45</v>
       </c>
       <c r="O45" t="n">
-        <v>69246.19</v>
+        <v>70134.09</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4287,18 +4287,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4306,64 +4306,60 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>65340.59</v>
+        <v>63485.44</v>
       </c>
       <c r="C46" t="n">
-        <v>65658.34</v>
+        <v>65401.69</v>
       </c>
       <c r="D46" t="n">
-        <v>62233.01</v>
+        <v>62226.58</v>
       </c>
       <c r="E46" t="n">
-        <v>63482</v>
+        <v>64844.89</v>
       </c>
       <c r="F46" t="n">
-        <v>-1858.3</v>
+        <v>1362.89</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0284</v>
+        <v>0.0215</v>
       </c>
       <c r="H46" t="n">
-        <v>3425.32</v>
+        <v>3175.11</v>
       </c>
       <c r="I46" t="n">
-        <v>60462.01</v>
+        <v>58807.69</v>
       </c>
       <c r="J46" t="n">
-        <v>62137.4</v>
+        <v>59824.84</v>
       </c>
       <c r="K46" t="n">
-        <v>63728.29</v>
+        <v>61769.34</v>
       </c>
       <c r="L46" t="n">
-        <v>65319.17</v>
+        <v>63713.84</v>
       </c>
       <c r="M46" t="n">
-        <v>66952.31</v>
+        <v>65194.66</v>
       </c>
       <c r="N46" t="n">
-        <v>68585.45</v>
+        <v>66675.49000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>70134.09</v>
+        <v>69083.66</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4371,79 +4367,83 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>63485.44</v>
+        <v>64845.38</v>
       </c>
       <c r="C47" t="n">
-        <v>65401.69</v>
+        <v>65321.84</v>
       </c>
       <c r="D47" t="n">
-        <v>62226.58</v>
+        <v>62487.7</v>
       </c>
       <c r="E47" t="n">
-        <v>64844.89</v>
+        <v>62818.65</v>
       </c>
       <c r="F47" t="n">
-        <v>1362.89</v>
+        <v>-2026.23</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0215</v>
+        <v>-0.0312</v>
       </c>
       <c r="H47" t="n">
-        <v>3175.11</v>
+        <v>2834.14</v>
       </c>
       <c r="I47" t="n">
-        <v>58807.69</v>
+        <v>59051.46</v>
       </c>
       <c r="J47" t="n">
-        <v>59824.84</v>
+        <v>62185.15</v>
       </c>
       <c r="K47" t="n">
-        <v>61769.34</v>
+        <v>63257.33</v>
       </c>
       <c r="L47" t="n">
-        <v>63713.84</v>
+        <v>64329.51</v>
       </c>
       <c r="M47" t="n">
-        <v>65194.66</v>
+        <v>66432.44</v>
       </c>
       <c r="N47" t="n">
-        <v>66675.49000000001</v>
+        <v>68535.38</v>
       </c>
       <c r="O47" t="n">
-        <v>69083.66</v>
+        <v>68576.8</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4451,18 +4451,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4470,7 +4470,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4484,50 +4484,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>64845.38</v>
+        <v>62819.38</v>
       </c>
       <c r="C48" t="n">
-        <v>65321.84</v>
+        <v>79463.71000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>62487.7</v>
+        <v>62687.1</v>
       </c>
       <c r="E48" t="n">
-        <v>62818.65</v>
+        <v>77755.27</v>
       </c>
       <c r="F48" t="n">
-        <v>-2026.23</v>
+        <v>14936.61</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0312</v>
+        <v>0.2378</v>
       </c>
       <c r="H48" t="n">
-        <v>2834.14</v>
+        <v>16776.61</v>
       </c>
       <c r="I48" t="n">
-        <v>59051.46</v>
+        <v>59653.56</v>
       </c>
       <c r="J48" t="n">
-        <v>62185.15</v>
+        <v>59441.45</v>
       </c>
       <c r="K48" t="n">
-        <v>63257.33</v>
+        <v>61401.58</v>
       </c>
       <c r="L48" t="n">
-        <v>64329.51</v>
+        <v>63361.71</v>
       </c>
       <c r="M48" t="n">
-        <v>66432.44</v>
+        <v>64235.72</v>
       </c>
       <c r="N48" t="n">
-        <v>68535.38</v>
+        <v>65109.73</v>
       </c>
       <c r="O48" t="n">
-        <v>68576.8</v>
+        <v>68155.98</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4535,83 +4535,83 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
-      </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>62819.38</v>
+        <v>77748.88</v>
       </c>
       <c r="C49" t="n">
-        <v>79463.71000000001</v>
+        <v>81346.95</v>
       </c>
       <c r="D49" t="n">
-        <v>62687.1</v>
+        <v>76688.83</v>
       </c>
       <c r="E49" t="n">
-        <v>77755.27</v>
+        <v>77667.57000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>14936.61</v>
+        <v>-87.7</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.2378</v>
+        <v>-0.0011</v>
       </c>
       <c r="H49" t="n">
-        <v>16776.61</v>
+        <v>4658.12</v>
       </c>
       <c r="I49" t="n">
-        <v>59653.56</v>
+        <v>45910.49</v>
       </c>
       <c r="J49" t="n">
-        <v>59441.45</v>
+        <v>64318.59</v>
       </c>
       <c r="K49" t="n">
-        <v>61401.58</v>
+        <v>69366.96000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>63361.71</v>
+        <v>74415.34</v>
       </c>
       <c r="M49" t="n">
-        <v>64235.72</v>
+        <v>86143.57000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>65109.73</v>
+        <v>97871.8</v>
       </c>
       <c r="O49" t="n">
-        <v>68155.98</v>
+        <v>96240.32000000001</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4622,80 +4622,78 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>77748.88</v>
+        <v>77673.7</v>
       </c>
       <c r="C50" t="n">
-        <v>81346.95</v>
+        <v>82262.21000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>76688.83</v>
+        <v>76248.3</v>
       </c>
       <c r="E50" t="n">
-        <v>77667.57000000001</v>
+        <v>80350.05</v>
       </c>
       <c r="F50" t="n">
-        <v>-87.7</v>
+        <v>2682.48</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0345</v>
       </c>
       <c r="H50" t="n">
-        <v>4658.12</v>
+        <v>6013.91</v>
       </c>
       <c r="I50" t="n">
-        <v>45910.49</v>
+        <v>72030.7</v>
       </c>
       <c r="J50" t="n">
-        <v>64318.59</v>
+        <v>72334.28999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>69366.96000000001</v>
+        <v>75338.50999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>74415.34</v>
+        <v>78342.73</v>
       </c>
       <c r="M50" t="n">
-        <v>86143.57000000001</v>
+        <v>79996.63</v>
       </c>
       <c r="N50" t="n">
-        <v>97871.8</v>
+        <v>81650.53999999999</v>
       </c>
       <c r="O50" t="n">
-        <v>96240.32000000001</v>
+        <v>86005.08</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4706,21 +4704,25 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4734,50 +4736,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>77673.7</v>
+        <v>80349.2</v>
       </c>
       <c r="C51" t="n">
-        <v>82262.21000000001</v>
+        <v>80432.31</v>
       </c>
       <c r="D51" t="n">
-        <v>76248.3</v>
+        <v>76162.91</v>
       </c>
       <c r="E51" t="n">
-        <v>80350.05</v>
+        <v>76838.16</v>
       </c>
       <c r="F51" t="n">
-        <v>2682.48</v>
+        <v>-3511.89</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0345</v>
+        <v>-0.0437</v>
       </c>
       <c r="H51" t="n">
-        <v>6013.91</v>
+        <v>4269.4</v>
       </c>
       <c r="I51" t="n">
-        <v>72030.7</v>
+        <v>70234.39999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>72334.28999999999</v>
+        <v>74883.53999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>75338.50999999999</v>
+        <v>77343.09</v>
       </c>
       <c r="L51" t="n">
-        <v>78342.73</v>
+        <v>79802.64999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>79996.63</v>
+        <v>83357</v>
       </c>
       <c r="N51" t="n">
-        <v>81650.53999999999</v>
+        <v>86911.35000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>86005.08</v>
+        <v>88276.12</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4785,85 +4787,83 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>80349.2</v>
+        <v>76830.28</v>
       </c>
       <c r="C52" t="n">
-        <v>80432.31</v>
+        <v>81911.14</v>
       </c>
       <c r="D52" t="n">
-        <v>76162.91</v>
+        <v>74944.59</v>
       </c>
       <c r="E52" t="n">
-        <v>76838.16</v>
+        <v>81142.61</v>
       </c>
       <c r="F52" t="n">
-        <v>-3511.89</v>
+        <v>4304.45</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0437</v>
+        <v>0.056</v>
       </c>
       <c r="H52" t="n">
-        <v>4269.4</v>
+        <v>6966.55</v>
       </c>
       <c r="I52" t="n">
-        <v>70234.39999999999</v>
+        <v>71893.52</v>
       </c>
       <c r="J52" t="n">
-        <v>74883.53999999999</v>
+        <v>71839.03</v>
       </c>
       <c r="K52" t="n">
-        <v>77343.09</v>
+        <v>74703.46000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>79802.64999999999</v>
+        <v>77567.88</v>
       </c>
       <c r="M52" t="n">
-        <v>83357</v>
+        <v>78972.86</v>
       </c>
       <c r="N52" t="n">
-        <v>86911.35000000001</v>
+        <v>80377.83</v>
       </c>
       <c r="O52" t="n">
-        <v>88276.12</v>
+        <v>84701.71000000001</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4871,83 +4871,85 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>76830.28</v>
+        <v>81143.62</v>
       </c>
       <c r="C53" t="n">
-        <v>81911.14</v>
+        <v>87363.75999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>74944.59</v>
+        <v>80867.09</v>
       </c>
       <c r="E53" t="n">
-        <v>81142.61</v>
+        <v>84458.09</v>
       </c>
       <c r="F53" t="n">
-        <v>4304.45</v>
+        <v>3315.48</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.056</v>
+        <v>0.0409</v>
       </c>
       <c r="H53" t="n">
-        <v>6966.55</v>
+        <v>6496.67</v>
       </c>
       <c r="I53" t="n">
-        <v>71893.52</v>
+        <v>67978.05</v>
       </c>
       <c r="J53" t="n">
-        <v>71839.03</v>
+        <v>75533.42999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>74703.46000000001</v>
+        <v>77659.34</v>
       </c>
       <c r="L53" t="n">
-        <v>77567.88</v>
+        <v>79785.24000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>78972.86</v>
+        <v>84625.88</v>
       </c>
       <c r="N53" t="n">
-        <v>80377.83</v>
+        <v>89466.53</v>
       </c>
       <c r="O53" t="n">
-        <v>84701.71000000001</v>
+        <v>88877.69</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4958,82 +4960,76 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>81143.62</v>
+        <v>84454.12</v>
       </c>
       <c r="C54" t="n">
-        <v>87363.75999999999</v>
+        <v>87146.35000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>80867.09</v>
+        <v>82570.72</v>
       </c>
       <c r="E54" t="n">
-        <v>84458.09</v>
+        <v>86480.3</v>
       </c>
       <c r="F54" t="n">
-        <v>3315.48</v>
+        <v>2022.22</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0409</v>
+        <v>0.0239</v>
       </c>
       <c r="H54" t="n">
-        <v>6496.67</v>
+        <v>4575.63</v>
       </c>
       <c r="I54" t="n">
-        <v>67978.05</v>
+        <v>74370.41</v>
       </c>
       <c r="J54" t="n">
-        <v>75533.42999999999</v>
+        <v>78132.75</v>
       </c>
       <c r="K54" t="n">
-        <v>77659.34</v>
+        <v>81209.75</v>
       </c>
       <c r="L54" t="n">
-        <v>79785.24000000001</v>
+        <v>84286.75</v>
       </c>
       <c r="M54" t="n">
-        <v>84625.88</v>
+        <v>87706.42</v>
       </c>
       <c r="N54" t="n">
-        <v>89466.53</v>
+        <v>91126.09</v>
       </c>
       <c r="O54" t="n">
-        <v>88877.69</v>
+        <v>93860.42999999999</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5044,7 +5040,7 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="10" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5060,79 +5056,85 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>84454.12</v>
+        <v>86480.00999999999</v>
       </c>
       <c r="C55" t="n">
-        <v>87146.35000000001</v>
+        <v>86971.78</v>
       </c>
       <c r="D55" t="n">
-        <v>82570.72</v>
+        <v>80336.91</v>
       </c>
       <c r="E55" t="n">
-        <v>86480.3</v>
+        <v>83679.47</v>
       </c>
       <c r="F55" t="n">
-        <v>2022.22</v>
+        <v>-2800.84</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0239</v>
+        <v>-0.0324</v>
       </c>
       <c r="H55" t="n">
-        <v>4575.63</v>
+        <v>6634.88</v>
       </c>
       <c r="I55" t="n">
-        <v>74370.41</v>
+        <v>77995.09</v>
       </c>
       <c r="J55" t="n">
-        <v>78132.75</v>
+        <v>82715.56</v>
       </c>
       <c r="K55" t="n">
-        <v>81209.75</v>
+        <v>84192.49000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>84286.75</v>
+        <v>85669.42</v>
       </c>
       <c r="M55" t="n">
-        <v>87706.42</v>
+        <v>88768.12</v>
       </c>
       <c r="N55" t="n">
-        <v>91126.09</v>
+        <v>91866.82000000001</v>
       </c>
       <c r="O55" t="n">
-        <v>93860.42999999999</v>
+        <v>91721.98</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5140,81 +5142,79 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>86480.00999999999</v>
+        <v>83679.47</v>
       </c>
       <c r="C56" t="n">
-        <v>86971.78</v>
+        <v>84249.22</v>
       </c>
       <c r="D56" t="n">
-        <v>80336.91</v>
+        <v>79735.86</v>
       </c>
       <c r="E56" t="n">
-        <v>83679.47</v>
+        <v>82017.60000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>-2800.84</v>
+        <v>-1661.87</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0324</v>
+        <v>-0.0199</v>
       </c>
       <c r="H56" t="n">
-        <v>6634.88</v>
+        <v>4513.36</v>
       </c>
       <c r="I56" t="n">
-        <v>77995.09</v>
+        <v>73702.03</v>
       </c>
       <c r="J56" t="n">
-        <v>82715.56</v>
+        <v>77057.16</v>
       </c>
       <c r="K56" t="n">
-        <v>84192.49000000001</v>
+        <v>80362.03</v>
       </c>
       <c r="L56" t="n">
-        <v>85669.42</v>
+        <v>83666.91</v>
       </c>
       <c r="M56" t="n">
-        <v>88768.12</v>
+        <v>86996.91</v>
       </c>
       <c r="N56" t="n">
-        <v>91866.82000000001</v>
+        <v>90326.91</v>
       </c>
       <c r="O56" t="n">
-        <v>91721.98</v>
+        <v>93606.66</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5226,7 +5226,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5240,50 +5240,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>83679.47</v>
+        <v>82017.60000000001</v>
       </c>
       <c r="C57" t="n">
-        <v>84249.22</v>
+        <v>84840.05</v>
       </c>
       <c r="D57" t="n">
-        <v>79735.86</v>
+        <v>79145.53999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>82017.60000000001</v>
+        <v>80790.84</v>
       </c>
       <c r="F57" t="n">
-        <v>-1661.87</v>
+        <v>-1226.77</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0199</v>
+        <v>-0.015</v>
       </c>
       <c r="H57" t="n">
-        <v>4513.36</v>
+        <v>5694.51</v>
       </c>
       <c r="I57" t="n">
-        <v>73702.03</v>
+        <v>75222.5</v>
       </c>
       <c r="J57" t="n">
-        <v>77057.16</v>
+        <v>77516.77</v>
       </c>
       <c r="K57" t="n">
-        <v>80362.03</v>
+        <v>79760.92</v>
       </c>
       <c r="L57" t="n">
-        <v>83666.91</v>
+        <v>82005.07000000001</v>
       </c>
       <c r="M57" t="n">
-        <v>86996.91</v>
+        <v>84274.28</v>
       </c>
       <c r="N57" t="n">
-        <v>90326.91</v>
+        <v>86543.49000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>93606.66</v>
+        <v>88762.58</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5293,81 +5293,83 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>82017.60000000001</v>
+        <v>80039.69</v>
       </c>
       <c r="C58" t="n">
-        <v>84840.05</v>
+        <v>80173.53</v>
       </c>
       <c r="D58" t="n">
-        <v>80530.27</v>
+        <v>79909.19</v>
       </c>
       <c r="E58" t="n">
-        <v>80760.53999999999</v>
+        <v>80082.45</v>
       </c>
       <c r="F58" t="n">
-        <v>-1257.06</v>
+        <v>-708.38</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0153</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>4309.78</v>
+        <v>264.34</v>
       </c>
       <c r="I58" t="n">
-        <v>75222.5</v>
+        <v>73451.03</v>
       </c>
       <c r="J58" t="n">
-        <v>77516.77</v>
+        <v>74495.35000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>79760.92</v>
+        <v>77943.58</v>
       </c>
       <c r="L58" t="n">
-        <v>82005.07000000001</v>
+        <v>81391.81</v>
       </c>
       <c r="M58" t="n">
-        <v>84274.28</v>
+        <v>83638.09</v>
       </c>
       <c r="N58" t="n">
-        <v>86543.49000000001</v>
+        <v>85884.37</v>
       </c>
       <c r="O58" t="n">
-        <v>88762.58</v>
+        <v>90534.55</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5375,20 +5377,16 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5396,14 +5394,14 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>13969.26</v>
       </c>
       <c r="I2" t="n">
-        <v>101995.48</v>
+        <v>103440.52</v>
       </c>
       <c r="J2" t="n">
-        <v>105429.87</v>
+        <v>107236.17</v>
       </c>
       <c r="K2" t="n">
-        <v>108763.68</v>
+        <v>109486.2</v>
       </c>
       <c r="L2" t="n">
-        <v>112097.5</v>
+        <v>111736.24</v>
       </c>
       <c r="M2" t="n">
-        <v>115481.6</v>
+        <v>114759.08</v>
       </c>
       <c r="N2" t="n">
-        <v>118865.7</v>
+        <v>117781.92</v>
       </c>
       <c r="O2" t="n">
-        <v>122149.23</v>
+        <v>119259.15</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5253,13 +5253,13 @@
         <v>79145.53999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>80790.84</v>
+        <v>80024.00999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>-1226.77</v>
+        <v>-1993.59</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.015</v>
+        <v>-0.0243</v>
       </c>
       <c r="H57" t="n">
         <v>5694.51</v>
@@ -5330,43 +5330,43 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>80039.69</v>
+        <v>80009.5</v>
       </c>
       <c r="C58" t="n">
-        <v>80173.53</v>
+        <v>80202.84</v>
       </c>
       <c r="D58" t="n">
-        <v>79909.19</v>
+        <v>79913.31</v>
       </c>
       <c r="E58" t="n">
-        <v>80082.45</v>
+        <v>79988.03</v>
       </c>
       <c r="F58" t="n">
-        <v>-708.38</v>
+        <v>-35.98</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0004</v>
       </c>
       <c r="H58" t="n">
-        <v>264.34</v>
+        <v>289.53</v>
       </c>
       <c r="I58" t="n">
         <v>73451.03</v>
       </c>
       <c r="J58" t="n">
-        <v>74495.35000000001</v>
+        <v>73345.11</v>
       </c>
       <c r="K58" t="n">
-        <v>77943.58</v>
+        <v>77176.75</v>
       </c>
       <c r="L58" t="n">
-        <v>81391.81</v>
+        <v>81008.39999999999</v>
       </c>
       <c r="M58" t="n">
-        <v>83638.09</v>
+        <v>82871.25999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>85884.37</v>
+        <v>84734.12</v>
       </c>
       <c r="O58" t="n">
         <v>90534.55</v>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -5330,25 +5330,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>80009.5</v>
+        <v>80024.00999999999</v>
       </c>
       <c r="C58" t="n">
-        <v>80202.84</v>
+        <v>80846.77</v>
       </c>
       <c r="D58" t="n">
-        <v>79913.31</v>
+        <v>79278.71000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>79988.03</v>
+        <v>80786.67</v>
       </c>
       <c r="F58" t="n">
-        <v>-35.98</v>
+        <v>762.66</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0095</v>
       </c>
       <c r="H58" t="n">
-        <v>289.53</v>
+        <v>1568.05</v>
       </c>
       <c r="I58" t="n">
         <v>73451.03</v>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>13969.26</v>
       </c>
       <c r="I2" t="n">
-        <v>103440.52</v>
+        <v>103885.71</v>
       </c>
       <c r="J2" t="n">
-        <v>107236.17</v>
+        <v>107792.65</v>
       </c>
       <c r="K2" t="n">
-        <v>109486.2</v>
+        <v>109708.8</v>
       </c>
       <c r="L2" t="n">
-        <v>111736.24</v>
+        <v>111624.94</v>
       </c>
       <c r="M2" t="n">
-        <v>114759.08</v>
+        <v>114536.48</v>
       </c>
       <c r="N2" t="n">
-        <v>117781.92</v>
+        <v>117448.03</v>
       </c>
       <c r="O2" t="n">
-        <v>119259.15</v>
+        <v>118368.77</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5333,22 +5333,22 @@
         <v>80024.00999999999</v>
       </c>
       <c r="C58" t="n">
-        <v>80846.77</v>
+        <v>81262.03999999999</v>
       </c>
       <c r="D58" t="n">
         <v>79278.71000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>80786.67</v>
+        <v>79864.84</v>
       </c>
       <c r="F58" t="n">
-        <v>762.66</v>
+        <v>-159.16</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0095</v>
+        <v>-0.002</v>
       </c>
       <c r="H58" t="n">
-        <v>1568.05</v>
+        <v>1983.33</v>
       </c>
       <c r="I58" t="n">
         <v>73451.03</v>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>13969.26</v>
       </c>
       <c r="I2" t="n">
-        <v>103885.71</v>
+        <v>105082.47</v>
       </c>
       <c r="J2" t="n">
-        <v>107792.65</v>
+        <v>109261.34</v>
       </c>
       <c r="K2" t="n">
-        <v>109708.8</v>
+        <v>110299.39</v>
       </c>
       <c r="L2" t="n">
-        <v>111624.94</v>
+        <v>111337.44</v>
       </c>
       <c r="M2" t="n">
-        <v>114536.48</v>
+        <v>113945.89</v>
       </c>
       <c r="N2" t="n">
-        <v>117448.03</v>
+        <v>116554.35</v>
       </c>
       <c r="O2" t="n">
-        <v>118368.77</v>
+        <v>116021.99</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,12 +700,12 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -5333,22 +5333,22 @@
         <v>80024.00999999999</v>
       </c>
       <c r="C58" t="n">
-        <v>81262.03999999999</v>
+        <v>81703.2</v>
       </c>
       <c r="D58" t="n">
-        <v>79278.71000000001</v>
+        <v>76418.34</v>
       </c>
       <c r="E58" t="n">
-        <v>79864.84</v>
+        <v>77059.36</v>
       </c>
       <c r="F58" t="n">
-        <v>-159.16</v>
+        <v>-2964.65</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.002</v>
+        <v>-0.037</v>
       </c>
       <c r="H58" t="n">
-        <v>1983.33</v>
+        <v>5284.87</v>
       </c>
       <c r="I58" t="n">
         <v>73451.03</v>
@@ -5377,12 +5377,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5401,7 +5403,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/BTC_weekly.xlsx
+++ b/three_gate/analysis/BTC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>13969.26</v>
       </c>
       <c r="I2" t="n">
-        <v>105082.47</v>
+        <v>105913.11</v>
       </c>
       <c r="J2" t="n">
-        <v>109261.34</v>
+        <v>109572.83</v>
       </c>
       <c r="K2" t="n">
-        <v>110299.39</v>
+        <v>110507.05</v>
       </c>
       <c r="L2" t="n">
-        <v>111337.44</v>
+        <v>111441.27</v>
       </c>
       <c r="M2" t="n">
-        <v>113945.89</v>
+        <v>113738.23</v>
       </c>
       <c r="N2" t="n">
-        <v>116554.35</v>
+        <v>116035.2</v>
       </c>
       <c r="O2" t="n">
-        <v>116021.99</v>
+        <v>115606.67</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5333,22 +5333,22 @@
         <v>80024.00999999999</v>
       </c>
       <c r="C58" t="n">
-        <v>81703.2</v>
+        <v>81889.95</v>
       </c>
       <c r="D58" t="n">
-        <v>76418.34</v>
+        <v>77161.59</v>
       </c>
       <c r="E58" t="n">
-        <v>77059.36</v>
+        <v>77225.8</v>
       </c>
       <c r="F58" t="n">
-        <v>-2964.65</v>
+        <v>-2798.21</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.037</v>
+        <v>-0.035</v>
       </c>
       <c r="H58" t="n">
-        <v>5284.87</v>
+        <v>4728.36</v>
       </c>
       <c r="I58" t="n">
         <v>73451.03</v>
